--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C69723-3318-4BB2-B571-E270BA0B8876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A1D7E3-E344-4737-B12E-4E855E517454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="824">
   <si>
     <t>池</t>
   </si>
@@ -2489,33 +2502,6 @@
   </si>
   <si>
     <t>生命低於 30% 時，造成的傷害提高 {v}%</t>
-  </si>
-  <si>
-    <t>0.55000000000000004</t>
-  </si>
-  <si>
-    <t>7.4999999999999997E-2</t>
-  </si>
-  <si>
-    <t>1.2E-2</t>
-  </si>
-  <si>
-    <t>1.4999999999999999E-2</t>
-  </si>
-  <si>
-    <t>2.2000000000000002</t>
-  </si>
-  <si>
-    <t>5.0000000000000001E-3</t>
-  </si>
-  <si>
-    <t>3.0000000000000001E-3</t>
-  </si>
-  <si>
-    <t>3.5000000000000003E-2</t>
-  </si>
-  <si>
-    <t>2.5000000000000001E-2</t>
   </si>
   <si>
     <t>出現部位
@@ -3123,11 +3109,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3508,9 +3494,11 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="35.375" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3541,8 +3529,8 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>832</v>
+      <c r="K1" s="1" t="s">
+        <v>823</v>
       </c>
       <c r="L1" t="s">
         <v>10</v>
@@ -3582,8 +3570,8 @@
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>823</v>
+      <c r="F2" s="2">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -3646,8 +3634,8 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>823</v>
+      <c r="F4" s="2">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -3815,8 +3803,8 @@
       <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>824</v>
+      <c r="I9" s="2">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K9" t="s">
         <v>32</v>
@@ -4266,8 +4254,8 @@
       <c r="E23">
         <v>3</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>825</v>
+      <c r="F23" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G23" t="s">
         <v>24</v>
@@ -4298,8 +4286,8 @@
       <c r="E24">
         <v>2</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>825</v>
+      <c r="F24" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G24" t="s">
         <v>24</v>
@@ -4362,8 +4350,8 @@
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>826</v>
+      <c r="F26" s="2">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G26" t="s">
         <v>24</v>
@@ -4371,8 +4359,8 @@
       <c r="H26">
         <v>4</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>827</v>
+      <c r="I26" s="2">
+        <v>2.2000000000000002</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -4397,8 +4385,8 @@
       <c r="E27">
         <v>3</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>826</v>
+      <c r="F27" s="2">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G27" t="s">
         <v>24</v>
@@ -4406,8 +4394,8 @@
       <c r="H27">
         <v>4</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>827</v>
+      <c r="I27" s="2">
+        <v>2.2000000000000002</v>
       </c>
       <c r="J27">
         <v>4</v>
@@ -4432,8 +4420,8 @@
       <c r="E28">
         <v>3</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>826</v>
+      <c r="F28" s="2">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G28" t="s">
         <v>24</v>
@@ -4499,8 +4487,8 @@
       <c r="E30">
         <v>3</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>825</v>
+      <c r="F30" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
@@ -4534,8 +4522,8 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>828</v>
+      <c r="F31" s="2">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G31" t="s">
         <v>24</v>
@@ -4566,8 +4554,8 @@
       <c r="E32">
         <v>0.8</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>829</v>
+      <c r="F32" s="2">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G32" t="s">
         <v>24</v>
@@ -4671,8 +4659,8 @@
       <c r="E35">
         <v>3</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>830</v>
+      <c r="F35" s="2">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G35" t="s">
         <v>24</v>
@@ -4706,8 +4694,8 @@
       <c r="E36">
         <v>3</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>831</v>
+      <c r="F36" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G36" t="s">
         <v>24</v>
@@ -4741,8 +4729,8 @@
       <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>831</v>
+      <c r="F37" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
@@ -4776,8 +4764,8 @@
       <c r="E38">
         <v>3</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>831</v>
+      <c r="F38" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G38" t="s">
         <v>24</v>
@@ -4811,8 +4799,8 @@
       <c r="E39">
         <v>3</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>831</v>
+      <c r="F39" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G39" t="s">
         <v>24</v>
@@ -4846,8 +4834,8 @@
       <c r="E40">
         <v>3</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>831</v>
+      <c r="F40" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -4881,8 +4869,8 @@
       <c r="E41">
         <v>3</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>831</v>
+      <c r="F41" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
@@ -4916,8 +4904,8 @@
       <c r="E42">
         <v>3</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>831</v>
+      <c r="F42" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G42" t="s">
         <v>24</v>
@@ -4951,8 +4939,8 @@
       <c r="E43">
         <v>3</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>831</v>
+      <c r="F43" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G43" t="s">
         <v>24</v>
@@ -5266,8 +5254,8 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>828</v>
+      <c r="F52" s="2">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
@@ -5301,8 +5289,8 @@
       <c r="E53">
         <v>2.5</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>825</v>
+      <c r="F53" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -5333,7 +5321,7 @@
       <c r="E54">
         <v>4</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="2">
         <v>0.02</v>
       </c>
       <c r="G54" t="s">
@@ -5368,7 +5356,7 @@
       <c r="E55">
         <v>2</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>0.01</v>
       </c>
       <c r="G55" t="s">
@@ -5377,8 +5365,8 @@
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>827</v>
+      <c r="I55" s="2">
+        <v>2.2000000000000002</v>
       </c>
       <c r="K55" t="s">
         <v>146</v>
@@ -5400,7 +5388,7 @@
       <c r="E56">
         <v>4</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>0.02</v>
       </c>
       <c r="G56" t="s">
@@ -5435,8 +5423,8 @@
       <c r="E57">
         <v>2</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>826</v>
+      <c r="F57" s="2">
+        <v>1.4999999999999901E-2</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -5470,7 +5458,7 @@
       <c r="E58">
         <v>10</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <v>0.04</v>
       </c>
       <c r="G58" t="s">
@@ -5505,7 +5493,7 @@
       <c r="E59">
         <v>10</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>0.04</v>
       </c>
       <c r="G59" t="s">
@@ -5540,7 +5528,7 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>0.06</v>
       </c>
       <c r="G60" t="s">
@@ -5575,7 +5563,7 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <v>0.06</v>
       </c>
       <c r="G61" t="s">
@@ -5610,7 +5598,7 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>0.06</v>
       </c>
       <c r="G62" t="s">
@@ -5645,7 +5633,7 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <v>0.06</v>
       </c>
       <c r="G63" t="s">
@@ -5680,7 +5668,7 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="2">
         <v>0.06</v>
       </c>
       <c r="G64" t="s">
@@ -5715,7 +5703,7 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="2">
         <v>0.06</v>
       </c>
       <c r="G65" t="s">
@@ -5750,7 +5738,7 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <v>0.06</v>
       </c>
       <c r="G66" t="s">
@@ -5785,7 +5773,7 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="2">
         <v>0.06</v>
       </c>
       <c r="G67" t="s">
@@ -5820,7 +5808,7 @@
       <c r="E68">
         <v>3</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="2">
         <v>0.06</v>
       </c>
       <c r="G68" t="s">
@@ -5855,7 +5843,7 @@
       <c r="E69">
         <v>4</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="2">
         <v>0.02</v>
       </c>
       <c r="G69" t="s">
@@ -5890,8 +5878,8 @@
       <c r="E70">
         <v>3</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>825</v>
+      <c r="F70" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G70" t="s">
         <v>24</v>
@@ -5922,7 +5910,7 @@
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="2">
         <v>0.01</v>
       </c>
       <c r="G71" t="s">
@@ -5957,8 +5945,8 @@
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>828</v>
+      <c r="F72" s="2">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G72" t="s">
         <v>24</v>
@@ -5992,8 +5980,8 @@
       <c r="E73">
         <v>3</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>826</v>
+      <c r="F73" s="2">
+        <v>1.4999999999999901E-2</v>
       </c>
       <c r="G73" t="s">
         <v>24</v>
@@ -6027,7 +6015,7 @@
       <c r="E74">
         <v>3</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <v>0.2</v>
       </c>
       <c r="G74" t="s">
@@ -6062,7 +6050,7 @@
       <c r="E75">
         <v>2</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <v>0.3</v>
       </c>
       <c r="G75" t="s">
@@ -6097,7 +6085,7 @@
       <c r="E76">
         <v>2</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <v>0.01</v>
       </c>
       <c r="G76" t="s">
@@ -6132,8 +6120,8 @@
       <c r="E77">
         <v>3</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>826</v>
+      <c r="F77" s="2">
+        <v>1.4999999999999901E-2</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
@@ -6167,8 +6155,8 @@
       <c r="E78">
         <v>2.5</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>825</v>
+      <c r="F78" s="2">
+        <v>1.2E-2</v>
       </c>
       <c r="G78" t="s">
         <v>24</v>
@@ -6202,7 +6190,7 @@
       <c r="E79">
         <v>2</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <v>0.08</v>
       </c>
       <c r="G79" t="s">
@@ -6237,8 +6225,8 @@
       <c r="E80">
         <v>3</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>831</v>
+      <c r="F80" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G80" t="s">
         <v>24</v>
@@ -6272,7 +6260,7 @@
       <c r="E81">
         <v>4</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <v>0.02</v>
       </c>
       <c r="G81" t="s">

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A1D7E3-E344-4737-B12E-4E855E517454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8C767D-0E8C-4F66-A7EC-485BF3CF2F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="825">
   <si>
     <t>池</t>
   </si>
@@ -305,18 +305,12 @@
     <t>lifesteal</t>
   </si>
   <si>
-    <t>吸血%</t>
-  </si>
-  <si>
     <t>chest;wrist;ring;amulet</t>
   </si>
   <si>
     <t>manaSteal</t>
   </si>
   <si>
-    <t>吸魔%</t>
-  </si>
-  <si>
     <t>eliteDmg</t>
   </si>
   <si>
@@ -2490,9 +2484,6 @@
   </si>
   <si>
     <t>萬象汲取</t>
-  </si>
-  <si>
-    <t>攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
   </si>
   <si>
     <t>godWrath</t>
@@ -2512,6 +2503,22 @@
 boots＝靴子；ring＝戒指 I／II；amulet＝項鍊
 all_lock＝全鎖定（不會出現在任何裝備部位上，也不會出現在屬性面板）
 多部位用 ; 分隔，例如 ring;amulet＝戒指與項鍊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FALSE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸魔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次對敵人造成傷害時，額外回復 {v} 點生命與法力</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3112,7 +3119,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3530,7 +3537,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="L1" t="s">
         <v>10</v>
@@ -3570,7 +3577,7 @@
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2">
         <v>0.55000000000000004</v>
       </c>
       <c r="G2" t="s">
@@ -3634,7 +3641,7 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>0.55000000000000004</v>
       </c>
       <c r="G4" t="s">
@@ -3803,7 +3810,7 @@
       <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K9" t="s">
@@ -4254,7 +4261,7 @@
       <c r="E23">
         <v>3</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23">
         <v>1.2E-2</v>
       </c>
       <c r="G23" t="s">
@@ -4286,7 +4293,7 @@
       <c r="E24">
         <v>2</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24">
         <v>1.2E-2</v>
       </c>
       <c r="G24" t="s">
@@ -4350,7 +4357,7 @@
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G26" t="s">
@@ -4359,7 +4366,7 @@
       <c r="H26">
         <v>4</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26">
         <v>2.2000000000000002</v>
       </c>
       <c r="J26">
@@ -4385,7 +4392,7 @@
       <c r="E27">
         <v>3</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G27" t="s">
@@ -4394,7 +4401,7 @@
       <c r="H27">
         <v>4</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27">
         <v>2.2000000000000002</v>
       </c>
       <c r="J27">
@@ -4420,7 +4427,7 @@
       <c r="E28">
         <v>3</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G28" t="s">
@@ -4487,7 +4494,7 @@
       <c r="E30">
         <v>3</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30">
         <v>1.2E-2</v>
       </c>
       <c r="G30" t="s">
@@ -4513,8 +4520,8 @@
       <c r="B31" t="s">
         <v>89</v>
       </c>
-      <c r="C31" t="s">
-        <v>90</v>
+      <c r="C31" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4522,11 +4529,11 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G31" t="s">
-        <v>24</v>
+      <c r="G31" s="2" t="s">
+        <v>822</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -4535,7 +4542,7 @@
         <v>1.4</v>
       </c>
       <c r="K31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -4543,10 +4550,10 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="D32">
         <v>0.8</v>
@@ -4554,11 +4561,11 @@
       <c r="E32">
         <v>0.8</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G32" t="s">
-        <v>24</v>
+      <c r="G32" s="2" t="s">
+        <v>822</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -4570,7 +4577,7 @@
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -4578,10 +4585,10 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -4605,7 +4612,7 @@
         <v>3</v>
       </c>
       <c r="K33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -4613,10 +4620,10 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -4640,7 +4647,7 @@
         <v>3</v>
       </c>
       <c r="K34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -4648,10 +4655,10 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -4659,7 +4666,7 @@
       <c r="E35">
         <v>3</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G35" t="s">
@@ -4675,7 +4682,7 @@
         <v>3</v>
       </c>
       <c r="K35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -4683,10 +4690,10 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -4694,7 +4701,7 @@
       <c r="E36">
         <v>3</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G36" t="s">
@@ -4710,7 +4717,7 @@
         <v>3</v>
       </c>
       <c r="K36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -4718,10 +4725,10 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -4729,7 +4736,7 @@
       <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G37" t="s">
@@ -4745,7 +4752,7 @@
         <v>3</v>
       </c>
       <c r="K37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -4753,10 +4760,10 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -4764,7 +4771,7 @@
       <c r="E38">
         <v>3</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G38" t="s">
@@ -4780,7 +4787,7 @@
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -4788,10 +4795,10 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -4799,7 +4806,7 @@
       <c r="E39">
         <v>3</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G39" t="s">
@@ -4815,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -4823,10 +4830,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -4834,7 +4841,7 @@
       <c r="E40">
         <v>3</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G40" t="s">
@@ -4850,7 +4857,7 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -4858,10 +4865,10 @@
         <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -4869,7 +4876,7 @@
       <c r="E41">
         <v>3</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G41" t="s">
@@ -4885,7 +4892,7 @@
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -4893,10 +4900,10 @@
         <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -4904,7 +4911,7 @@
       <c r="E42">
         <v>3</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G42" t="s">
@@ -4920,7 +4927,7 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -4928,10 +4935,10 @@
         <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -4939,7 +4946,7 @@
       <c r="E43">
         <v>3</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G43" t="s">
@@ -4955,7 +4962,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -4963,10 +4970,10 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -4990,7 +4997,7 @@
         <v>3</v>
       </c>
       <c r="K44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -4998,10 +5005,10 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -5025,7 +5032,7 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -5033,10 +5040,10 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D46">
         <v>5</v>
@@ -5060,7 +5067,7 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -5068,10 +5075,10 @@
         <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -5095,7 +5102,7 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -5103,10 +5110,10 @@
         <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -5130,7 +5137,7 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -5138,10 +5145,10 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -5165,7 +5172,7 @@
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -5173,10 +5180,10 @@
         <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -5200,7 +5207,7 @@
         <v>3</v>
       </c>
       <c r="K50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -5208,10 +5215,10 @@
         <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -5235,7 +5242,7 @@
         <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -5243,10 +5250,10 @@
         <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -5254,7 +5261,7 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G52" t="s">
@@ -5270,7 +5277,7 @@
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -5278,10 +5285,10 @@
         <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -5289,7 +5296,7 @@
       <c r="E53">
         <v>2.5</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53">
         <v>1.2E-2</v>
       </c>
       <c r="G53" t="s">
@@ -5302,7 +5309,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -5310,10 +5317,10 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -5321,7 +5328,7 @@
       <c r="E54">
         <v>4</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54">
         <v>0.02</v>
       </c>
       <c r="G54" t="s">
@@ -5337,7 +5344,7 @@
         <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -5345,10 +5352,10 @@
         <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -5356,7 +5363,7 @@
       <c r="E55">
         <v>2</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55">
         <v>0.01</v>
       </c>
       <c r="G55" t="s">
@@ -5365,11 +5372,11 @@
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55">
         <v>2.2000000000000002</v>
       </c>
       <c r="K55" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -5377,10 +5384,10 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -5388,7 +5395,7 @@
       <c r="E56">
         <v>4</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56">
         <v>0.02</v>
       </c>
       <c r="G56" t="s">
@@ -5404,7 +5411,7 @@
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -5412,10 +5419,10 @@
         <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D57">
         <v>5</v>
@@ -5423,7 +5430,7 @@
       <c r="E57">
         <v>2</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57">
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G57" t="s">
@@ -5439,7 +5446,7 @@
         <v>3</v>
       </c>
       <c r="K57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -5447,10 +5454,10 @@
         <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58">
         <v>30</v>
@@ -5458,7 +5465,7 @@
       <c r="E58">
         <v>10</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58">
         <v>0.04</v>
       </c>
       <c r="G58" t="s">
@@ -5474,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="K58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -5482,10 +5489,10 @@
         <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D59">
         <v>30</v>
@@ -5493,7 +5500,7 @@
       <c r="E59">
         <v>10</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59">
         <v>0.04</v>
       </c>
       <c r="G59" t="s">
@@ -5509,7 +5516,7 @@
         <v>3</v>
       </c>
       <c r="K59" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -5517,10 +5524,10 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D60">
         <v>30</v>
@@ -5528,7 +5535,7 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60">
         <v>0.06</v>
       </c>
       <c r="G60" t="s">
@@ -5544,7 +5551,7 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -5552,10 +5559,10 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D61">
         <v>30</v>
@@ -5563,7 +5570,7 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61">
         <v>0.06</v>
       </c>
       <c r="G61" t="s">
@@ -5579,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -5587,10 +5594,10 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D62">
         <v>30</v>
@@ -5598,7 +5605,7 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62">
         <v>0.06</v>
       </c>
       <c r="G62" t="s">
@@ -5614,7 +5621,7 @@
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -5622,10 +5629,10 @@
         <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C63" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D63">
         <v>30</v>
@@ -5633,7 +5640,7 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63">
         <v>0.06</v>
       </c>
       <c r="G63" t="s">
@@ -5649,7 +5656,7 @@
         <v>3</v>
       </c>
       <c r="K63" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -5657,10 +5664,10 @@
         <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D64">
         <v>30</v>
@@ -5668,7 +5675,7 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64">
         <v>0.06</v>
       </c>
       <c r="G64" t="s">
@@ -5684,7 +5691,7 @@
         <v>3</v>
       </c>
       <c r="K64" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -5692,10 +5699,10 @@
         <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D65">
         <v>30</v>
@@ -5703,7 +5710,7 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65">
         <v>0.06</v>
       </c>
       <c r="G65" t="s">
@@ -5719,7 +5726,7 @@
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -5727,10 +5734,10 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D66">
         <v>30</v>
@@ -5738,7 +5745,7 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66">
         <v>0.06</v>
       </c>
       <c r="G66" t="s">
@@ -5754,7 +5761,7 @@
         <v>3</v>
       </c>
       <c r="K66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -5762,10 +5769,10 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D67">
         <v>30</v>
@@ -5773,7 +5780,7 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67">
         <v>0.06</v>
       </c>
       <c r="G67" t="s">
@@ -5789,7 +5796,7 @@
         <v>3</v>
       </c>
       <c r="K67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -5797,10 +5804,10 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -5808,7 +5815,7 @@
       <c r="E68">
         <v>3</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68">
         <v>0.06</v>
       </c>
       <c r="G68" t="s">
@@ -5824,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="K68" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -5832,10 +5839,10 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -5843,7 +5850,7 @@
       <c r="E69">
         <v>4</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69">
         <v>0.02</v>
       </c>
       <c r="G69" t="s">
@@ -5859,7 +5866,7 @@
         <v>4</v>
       </c>
       <c r="K69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -5867,10 +5874,10 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C70" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -5878,7 +5885,7 @@
       <c r="E70">
         <v>3</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70">
         <v>1.2E-2</v>
       </c>
       <c r="G70" t="s">
@@ -5899,10 +5906,10 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -5910,7 +5917,7 @@
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71">
         <v>0.01</v>
       </c>
       <c r="G71" t="s">
@@ -5926,7 +5933,7 @@
         <v>4</v>
       </c>
       <c r="K71" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -5934,10 +5941,10 @@
         <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -5945,7 +5952,7 @@
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G72" t="s">
@@ -5961,7 +5968,7 @@
         <v>4</v>
       </c>
       <c r="K72" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -5969,10 +5976,10 @@
         <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -5980,7 +5987,7 @@
       <c r="E73">
         <v>3</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73">
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G73" t="s">
@@ -5996,7 +6003,7 @@
         <v>4</v>
       </c>
       <c r="K73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,10 +6011,10 @@
         <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -6015,7 +6022,7 @@
       <c r="E74">
         <v>3</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74">
         <v>0.2</v>
       </c>
       <c r="G74" t="s">
@@ -6031,7 +6038,7 @@
         <v>4</v>
       </c>
       <c r="K74" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,10 +6046,10 @@
         <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -6050,7 +6057,7 @@
       <c r="E75">
         <v>2</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75">
         <v>0.3</v>
       </c>
       <c r="G75" t="s">
@@ -6066,7 +6073,7 @@
         <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,10 +6081,10 @@
         <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C76" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -6085,7 +6092,7 @@
       <c r="E76">
         <v>2</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76">
         <v>0.01</v>
       </c>
       <c r="G76" t="s">
@@ -6101,7 +6108,7 @@
         <v>4</v>
       </c>
       <c r="K76" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,10 +6116,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -6120,7 +6127,7 @@
       <c r="E77">
         <v>3</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77">
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G77" t="s">
@@ -6144,10 +6151,10 @@
         <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D78">
         <v>2.5</v>
@@ -6155,7 +6162,7 @@
       <c r="E78">
         <v>2.5</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78">
         <v>1.2E-2</v>
       </c>
       <c r="G78" t="s">
@@ -6179,10 +6186,10 @@
         <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -6190,7 +6197,7 @@
       <c r="E79">
         <v>2</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79">
         <v>0.08</v>
       </c>
       <c r="G79" t="s">
@@ -6214,10 +6221,10 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C80" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -6225,7 +6232,7 @@
       <c r="E80">
         <v>3</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G80" t="s">
@@ -6241,7 +6248,7 @@
         <v>4</v>
       </c>
       <c r="K80" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -6249,10 +6256,10 @@
         <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C81" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -6260,7 +6267,7 @@
       <c r="E81">
         <v>4</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81">
         <v>0.02</v>
       </c>
       <c r="G81" t="s">
@@ -6276,18 +6283,18 @@
         <v>4</v>
       </c>
       <c r="K81" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>201</v>
+      </c>
+      <c r="B82" t="s">
+        <v>202</v>
+      </c>
+      <c r="C82" t="s">
         <v>203</v>
-      </c>
-      <c r="B82" t="s">
-        <v>204</v>
-      </c>
-      <c r="C82" t="s">
-        <v>205</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -6296,18 +6303,18 @@
         <v>2</v>
       </c>
       <c r="N82" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B83" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C83" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -6316,18 +6323,18 @@
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B84" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D84">
         <v>10</v>
@@ -6336,18 +6343,18 @@
         <v>2</v>
       </c>
       <c r="N84" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -6356,18 +6363,18 @@
         <v>1.5</v>
       </c>
       <c r="N85" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D86">
         <v>12</v>
@@ -6376,18 +6383,18 @@
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C87" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D87">
         <v>6</v>
@@ -6396,18 +6403,18 @@
         <v>1.5</v>
       </c>
       <c r="N87" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C88" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D88">
         <v>5</v>
@@ -6416,4060 +6423,4060 @@
         <v>1.5</v>
       </c>
       <c r="N88" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B89" t="s">
+        <v>225</v>
+      </c>
+      <c r="C89" t="s">
+        <v>226</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="N89" t="s">
         <v>227</v>
       </c>
-      <c r="C89" t="s">
+      <c r="Q89" t="s">
         <v>228</v>
       </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="N89" t="s">
+      <c r="R89" t="s">
         <v>229</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>230</v>
-      </c>
-      <c r="R89" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s">
+        <v>230</v>
+      </c>
+      <c r="C90" t="s">
+        <v>231</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="N90" t="s">
         <v>232</v>
       </c>
-      <c r="C90" t="s">
+      <c r="O90" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q90" t="s">
         <v>233</v>
       </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="N90" t="s">
+      <c r="R90" t="s">
         <v>234</v>
-      </c>
-      <c r="O90" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>235</v>
-      </c>
-      <c r="R90" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B91" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="N91" t="s">
         <v>237</v>
       </c>
-      <c r="C91" t="s">
+      <c r="O91" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>233</v>
+      </c>
+      <c r="R91" t="s">
         <v>238</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="N91" t="s">
-        <v>239</v>
-      </c>
-      <c r="O91" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>235</v>
-      </c>
-      <c r="R91" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B92" t="s">
+        <v>239</v>
+      </c>
+      <c r="C92" t="s">
+        <v>240</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="N92" t="s">
         <v>241</v>
       </c>
-      <c r="C92" t="s">
+      <c r="Q92" t="s">
+        <v>233</v>
+      </c>
+      <c r="R92" t="s">
         <v>242</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="N92" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>235</v>
-      </c>
-      <c r="R92" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B93" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="N93" t="s">
         <v>245</v>
       </c>
-      <c r="C93" t="s">
+      <c r="Q93" t="s">
+        <v>228</v>
+      </c>
+      <c r="R93" t="s">
         <v>246</v>
-      </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="N93" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>230</v>
-      </c>
-      <c r="R93" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B94" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" t="s">
+        <v>249</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="N94" t="s">
         <v>250</v>
       </c>
-      <c r="C94" t="s">
+      <c r="Q94" t="s">
         <v>251</v>
       </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="N94" t="s">
+      <c r="R94" t="s">
         <v>252</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>253</v>
-      </c>
-      <c r="R94" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B95" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" t="s">
+        <v>261</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="N95" t="s">
         <v>262</v>
       </c>
-      <c r="C95" t="s">
+      <c r="O95" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>255</v>
+      </c>
+      <c r="R95" t="s">
         <v>263</v>
-      </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="N95" t="s">
-        <v>264</v>
-      </c>
-      <c r="O95" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>257</v>
-      </c>
-      <c r="R95" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
+        <v>264</v>
+      </c>
+      <c r="C96" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="N96" t="s">
         <v>266</v>
       </c>
-      <c r="C96" t="s">
+      <c r="O96" t="s">
         <v>267</v>
       </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="N96" t="s">
+      <c r="Q96" t="s">
+        <v>256</v>
+      </c>
+      <c r="R96" t="s">
         <v>268</v>
-      </c>
-      <c r="O96" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>258</v>
-      </c>
-      <c r="R96" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s">
+        <v>269</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="N97" t="s">
         <v>271</v>
       </c>
-      <c r="C97" t="s">
+      <c r="O97" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q97" t="s">
         <v>272</v>
       </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="R97" t="s">
         <v>273</v>
-      </c>
-      <c r="O97" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>274</v>
-      </c>
-      <c r="R97" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B98" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98" t="s">
+        <v>275</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="N98" t="s">
         <v>276</v>
       </c>
-      <c r="C98" t="s">
+      <c r="O98" t="s">
         <v>277</v>
       </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="N98" t="s">
+      <c r="Q98" t="s">
+        <v>257</v>
+      </c>
+      <c r="R98" t="s">
         <v>278</v>
-      </c>
-      <c r="O98" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>259</v>
-      </c>
-      <c r="R98" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B99" t="s">
+        <v>279</v>
+      </c>
+      <c r="C99" t="s">
+        <v>280</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="N99" t="s">
         <v>281</v>
       </c>
-      <c r="C99" t="s">
+      <c r="O99" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>259</v>
+      </c>
+      <c r="R99" t="s">
         <v>282</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="N99" t="s">
-        <v>283</v>
-      </c>
-      <c r="O99" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>261</v>
-      </c>
-      <c r="R99" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B100" t="s">
+        <v>284</v>
+      </c>
+      <c r="C100" t="s">
+        <v>285</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="N100" t="s">
         <v>286</v>
       </c>
-      <c r="C100" t="s">
+      <c r="O100" t="s">
         <v>287</v>
       </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="N100" t="s">
+      <c r="Q100" t="s">
+        <v>255</v>
+      </c>
+      <c r="R100" t="s">
         <v>288</v>
-      </c>
-      <c r="O100" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>257</v>
-      </c>
-      <c r="R100" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
+        <v>289</v>
+      </c>
+      <c r="C101" t="s">
+        <v>290</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="N101" t="s">
         <v>291</v>
       </c>
-      <c r="C101" t="s">
+      <c r="Q101" t="s">
+        <v>272</v>
+      </c>
+      <c r="R101" t="s">
         <v>292</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="N101" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>274</v>
-      </c>
-      <c r="R101" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B102" t="s">
+        <v>293</v>
+      </c>
+      <c r="C102" t="s">
+        <v>294</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="N102" t="s">
         <v>295</v>
       </c>
-      <c r="C102" t="s">
+      <c r="O102" t="s">
+        <v>223</v>
+      </c>
+      <c r="P102" t="s">
         <v>296</v>
       </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="N102" t="s">
+      <c r="Q102" t="s">
+        <v>233</v>
+      </c>
+      <c r="R102" t="s">
         <v>297</v>
-      </c>
-      <c r="O102" t="s">
-        <v>225</v>
-      </c>
-      <c r="P102" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>235</v>
-      </c>
-      <c r="R102" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B103" t="s">
+        <v>298</v>
+      </c>
+      <c r="C103" t="s">
+        <v>299</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="N103" t="s">
         <v>300</v>
       </c>
-      <c r="C103" t="s">
+      <c r="O103" t="s">
+        <v>223</v>
+      </c>
+      <c r="P103" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>233</v>
+      </c>
+      <c r="R103" t="s">
         <v>301</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="N103" t="s">
-        <v>302</v>
-      </c>
-      <c r="O103" t="s">
-        <v>225</v>
-      </c>
-      <c r="P103" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>235</v>
-      </c>
-      <c r="R103" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B104" t="s">
+        <v>302</v>
+      </c>
+      <c r="C104" t="s">
+        <v>303</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="N104" t="s">
         <v>304</v>
       </c>
-      <c r="C104" t="s">
+      <c r="O104" t="s">
+        <v>223</v>
+      </c>
+      <c r="P104" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>233</v>
+      </c>
+      <c r="R104" t="s">
         <v>305</v>
-      </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="N104" t="s">
-        <v>306</v>
-      </c>
-      <c r="O104" t="s">
-        <v>225</v>
-      </c>
-      <c r="P104" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>235</v>
-      </c>
-      <c r="R104" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B105" t="s">
+        <v>306</v>
+      </c>
+      <c r="C105" t="s">
+        <v>307</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="N105" t="s">
         <v>308</v>
       </c>
-      <c r="C105" t="s">
+      <c r="O105" t="s">
+        <v>258</v>
+      </c>
+      <c r="P105" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>233</v>
+      </c>
+      <c r="R105" t="s">
         <v>309</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="N105" t="s">
-        <v>310</v>
-      </c>
-      <c r="O105" t="s">
-        <v>260</v>
-      </c>
-      <c r="P105" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>235</v>
-      </c>
-      <c r="R105" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B106" t="s">
+        <v>310</v>
+      </c>
+      <c r="C106" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="N106" t="s">
         <v>312</v>
       </c>
-      <c r="C106" t="s">
+      <c r="O106" t="s">
+        <v>223</v>
+      </c>
+      <c r="P106" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>233</v>
+      </c>
+      <c r="R106" t="s">
         <v>313</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="N106" t="s">
-        <v>314</v>
-      </c>
-      <c r="O106" t="s">
-        <v>225</v>
-      </c>
-      <c r="P106" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>235</v>
-      </c>
-      <c r="R106" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B107" t="s">
+        <v>314</v>
+      </c>
+      <c r="C107" t="s">
+        <v>315</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="N107" t="s">
         <v>316</v>
       </c>
-      <c r="C107" t="s">
+      <c r="O107" t="s">
+        <v>223</v>
+      </c>
+      <c r="P107" t="s">
         <v>317</v>
       </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="N107" t="s">
+      <c r="Q107" t="s">
+        <v>224</v>
+      </c>
+      <c r="R107" t="s">
         <v>318</v>
-      </c>
-      <c r="O107" t="s">
-        <v>225</v>
-      </c>
-      <c r="P107" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>226</v>
-      </c>
-      <c r="R107" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B108" t="s">
+        <v>319</v>
+      </c>
+      <c r="C108" t="s">
+        <v>320</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="N108" t="s">
         <v>321</v>
       </c>
-      <c r="C108" t="s">
+      <c r="O108" t="s">
+        <v>223</v>
+      </c>
+      <c r="P108" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>224</v>
+      </c>
+      <c r="R108" t="s">
         <v>322</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="N108" t="s">
-        <v>323</v>
-      </c>
-      <c r="O108" t="s">
-        <v>225</v>
-      </c>
-      <c r="P108" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>226</v>
-      </c>
-      <c r="R108" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B109" t="s">
+        <v>323</v>
+      </c>
+      <c r="C109" t="s">
+        <v>324</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="N109" t="s">
         <v>325</v>
       </c>
-      <c r="C109" t="s">
+      <c r="O109" t="s">
+        <v>223</v>
+      </c>
+      <c r="P109" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>224</v>
+      </c>
+      <c r="R109" t="s">
         <v>326</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="N109" t="s">
-        <v>327</v>
-      </c>
-      <c r="O109" t="s">
-        <v>225</v>
-      </c>
-      <c r="P109" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>226</v>
-      </c>
-      <c r="R109" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B110" t="s">
+        <v>327</v>
+      </c>
+      <c r="C110" t="s">
+        <v>328</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="N110" t="s">
         <v>329</v>
       </c>
-      <c r="C110" t="s">
+      <c r="O110" t="s">
+        <v>223</v>
+      </c>
+      <c r="P110" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>224</v>
+      </c>
+      <c r="R110" t="s">
         <v>330</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="N110" t="s">
-        <v>331</v>
-      </c>
-      <c r="O110" t="s">
-        <v>225</v>
-      </c>
-      <c r="P110" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>226</v>
-      </c>
-      <c r="R110" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B111" t="s">
+        <v>331</v>
+      </c>
+      <c r="C111" t="s">
+        <v>332</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="N111" t="s">
         <v>333</v>
       </c>
-      <c r="C111" t="s">
+      <c r="O111" t="s">
+        <v>223</v>
+      </c>
+      <c r="P111" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>224</v>
+      </c>
+      <c r="R111" t="s">
         <v>334</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="N111" t="s">
-        <v>335</v>
-      </c>
-      <c r="O111" t="s">
-        <v>225</v>
-      </c>
-      <c r="P111" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>226</v>
-      </c>
-      <c r="R111" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B112" t="s">
+        <v>335</v>
+      </c>
+      <c r="C112" t="s">
+        <v>336</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="N112" t="s">
         <v>337</v>
       </c>
-      <c r="C112" t="s">
+      <c r="O112" t="s">
+        <v>223</v>
+      </c>
+      <c r="P112" t="s">
         <v>338</v>
       </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="N112" t="s">
+      <c r="Q112" t="s">
+        <v>233</v>
+      </c>
+      <c r="R112" t="s">
         <v>339</v>
-      </c>
-      <c r="O112" t="s">
-        <v>225</v>
-      </c>
-      <c r="P112" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>235</v>
-      </c>
-      <c r="R112" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B113" t="s">
+        <v>340</v>
+      </c>
+      <c r="C113" t="s">
+        <v>341</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="N113" t="s">
         <v>342</v>
       </c>
-      <c r="C113" t="s">
+      <c r="O113" t="s">
+        <v>223</v>
+      </c>
+      <c r="P113" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>233</v>
+      </c>
+      <c r="R113" t="s">
         <v>343</v>
-      </c>
-      <c r="D113">
-        <v>0</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="N113" t="s">
-        <v>344</v>
-      </c>
-      <c r="O113" t="s">
-        <v>225</v>
-      </c>
-      <c r="P113" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>235</v>
-      </c>
-      <c r="R113" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B114" t="s">
+        <v>344</v>
+      </c>
+      <c r="C114" t="s">
+        <v>345</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="N114" t="s">
         <v>346</v>
       </c>
-      <c r="C114" t="s">
+      <c r="O114" t="s">
+        <v>223</v>
+      </c>
+      <c r="P114" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>233</v>
+      </c>
+      <c r="R114" t="s">
         <v>347</v>
-      </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="N114" t="s">
-        <v>348</v>
-      </c>
-      <c r="O114" t="s">
-        <v>225</v>
-      </c>
-      <c r="P114" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>235</v>
-      </c>
-      <c r="R114" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
+        <v>348</v>
+      </c>
+      <c r="C115" t="s">
+        <v>349</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="N115" t="s">
         <v>350</v>
       </c>
-      <c r="C115" t="s">
+      <c r="O115" t="s">
+        <v>223</v>
+      </c>
+      <c r="P115" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>233</v>
+      </c>
+      <c r="R115" t="s">
         <v>351</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="N115" t="s">
-        <v>352</v>
-      </c>
-      <c r="O115" t="s">
-        <v>225</v>
-      </c>
-      <c r="P115" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>235</v>
-      </c>
-      <c r="R115" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" t="s">
+        <v>353</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="N116" t="s">
         <v>354</v>
       </c>
-      <c r="C116" t="s">
+      <c r="O116" t="s">
+        <v>223</v>
+      </c>
+      <c r="P116" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>233</v>
+      </c>
+      <c r="R116" t="s">
         <v>355</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="N116" t="s">
-        <v>356</v>
-      </c>
-      <c r="O116" t="s">
-        <v>225</v>
-      </c>
-      <c r="P116" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>235</v>
-      </c>
-      <c r="R116" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B117" t="s">
+        <v>356</v>
+      </c>
+      <c r="C117" t="s">
+        <v>357</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="N117" t="s">
         <v>358</v>
       </c>
-      <c r="C117" t="s">
+      <c r="O117" t="s">
         <v>359</v>
       </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="N117" t="s">
+      <c r="P117" t="s">
         <v>360</v>
       </c>
-      <c r="O117" t="s">
+      <c r="Q117" t="s">
+        <v>247</v>
+      </c>
+      <c r="R117" t="s">
         <v>361</v>
-      </c>
-      <c r="P117" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>249</v>
-      </c>
-      <c r="R117" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B118" t="s">
+        <v>362</v>
+      </c>
+      <c r="C118" t="s">
+        <v>363</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="N118" t="s">
         <v>364</v>
       </c>
-      <c r="C118" t="s">
+      <c r="O118" t="s">
+        <v>223</v>
+      </c>
+      <c r="P118" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>247</v>
+      </c>
+      <c r="R118" t="s">
         <v>365</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="N118" t="s">
-        <v>366</v>
-      </c>
-      <c r="O118" t="s">
-        <v>225</v>
-      </c>
-      <c r="P118" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>249</v>
-      </c>
-      <c r="R118" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B119" t="s">
+        <v>366</v>
+      </c>
+      <c r="C119" t="s">
+        <v>367</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
         <v>368</v>
       </c>
-      <c r="C119" t="s">
+      <c r="O119" t="s">
+        <v>223</v>
+      </c>
+      <c r="P119" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>247</v>
+      </c>
+      <c r="R119" t="s">
         <v>369</v>
-      </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="N119" t="s">
-        <v>370</v>
-      </c>
-      <c r="O119" t="s">
-        <v>225</v>
-      </c>
-      <c r="P119" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>249</v>
-      </c>
-      <c r="R119" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B120" t="s">
+        <v>370</v>
+      </c>
+      <c r="C120" t="s">
+        <v>371</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="N120" t="s">
         <v>372</v>
       </c>
-      <c r="C120" t="s">
+      <c r="O120" t="s">
+        <v>359</v>
+      </c>
+      <c r="P120" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>247</v>
+      </c>
+      <c r="R120" t="s">
         <v>373</v>
-      </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="N120" t="s">
-        <v>374</v>
-      </c>
-      <c r="O120" t="s">
-        <v>361</v>
-      </c>
-      <c r="P120" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>249</v>
-      </c>
-      <c r="R120" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B121" t="s">
+        <v>374</v>
+      </c>
+      <c r="C121" t="s">
+        <v>375</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="N121" t="s">
         <v>376</v>
       </c>
-      <c r="C121" t="s">
+      <c r="O121" t="s">
+        <v>223</v>
+      </c>
+      <c r="P121" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R121" t="s">
         <v>377</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="N121" t="s">
-        <v>378</v>
-      </c>
-      <c r="O121" t="s">
-        <v>225</v>
-      </c>
-      <c r="P121" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>249</v>
-      </c>
-      <c r="R121" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B122" t="s">
+        <v>378</v>
+      </c>
+      <c r="C122" t="s">
+        <v>379</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="N122" t="s">
         <v>380</v>
       </c>
-      <c r="C122" t="s">
+      <c r="O122" t="s">
+        <v>283</v>
+      </c>
+      <c r="P122" t="s">
         <v>381</v>
       </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="N122" t="s">
+      <c r="Q122" t="s">
         <v>382</v>
       </c>
-      <c r="O122" t="s">
-        <v>285</v>
-      </c>
-      <c r="P122" t="s">
+      <c r="R122" t="s">
         <v>383</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>384</v>
-      </c>
-      <c r="R122" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B123" t="s">
+        <v>384</v>
+      </c>
+      <c r="C123" t="s">
+        <v>385</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="N123" t="s">
         <v>386</v>
       </c>
-      <c r="C123" t="s">
+      <c r="O123" t="s">
+        <v>283</v>
+      </c>
+      <c r="P123" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>382</v>
+      </c>
+      <c r="R123" t="s">
         <v>387</v>
-      </c>
-      <c r="D123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="N123" t="s">
-        <v>388</v>
-      </c>
-      <c r="O123" t="s">
-        <v>285</v>
-      </c>
-      <c r="P123" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>384</v>
-      </c>
-      <c r="R123" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B124" t="s">
+        <v>388</v>
+      </c>
+      <c r="C124" t="s">
+        <v>389</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="N124" t="s">
         <v>390</v>
       </c>
-      <c r="C124" t="s">
+      <c r="O124" t="s">
+        <v>223</v>
+      </c>
+      <c r="P124" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>382</v>
+      </c>
+      <c r="R124" t="s">
         <v>391</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="N124" t="s">
-        <v>392</v>
-      </c>
-      <c r="O124" t="s">
-        <v>225</v>
-      </c>
-      <c r="P124" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>384</v>
-      </c>
-      <c r="R124" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
+        <v>392</v>
+      </c>
+      <c r="C125" t="s">
+        <v>393</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="N125" t="s">
         <v>394</v>
       </c>
-      <c r="C125" t="s">
+      <c r="O125" t="s">
+        <v>223</v>
+      </c>
+      <c r="P125" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>382</v>
+      </c>
+      <c r="R125" t="s">
         <v>395</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="N125" t="s">
-        <v>396</v>
-      </c>
-      <c r="O125" t="s">
-        <v>225</v>
-      </c>
-      <c r="P125" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>384</v>
-      </c>
-      <c r="R125" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B126" t="s">
+        <v>396</v>
+      </c>
+      <c r="C126" t="s">
+        <v>397</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="N126" t="s">
         <v>398</v>
       </c>
-      <c r="C126" t="s">
+      <c r="O126" t="s">
+        <v>223</v>
+      </c>
+      <c r="P126" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>382</v>
+      </c>
+      <c r="R126" t="s">
         <v>399</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="N126" t="s">
-        <v>400</v>
-      </c>
-      <c r="O126" t="s">
-        <v>225</v>
-      </c>
-      <c r="P126" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>384</v>
-      </c>
-      <c r="R126" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B127" t="s">
+        <v>400</v>
+      </c>
+      <c r="C127" t="s">
+        <v>401</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="N127" t="s">
         <v>402</v>
       </c>
-      <c r="C127" t="s">
+      <c r="O127" t="s">
+        <v>223</v>
+      </c>
+      <c r="P127" t="s">
         <v>403</v>
       </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="N127" t="s">
+      <c r="Q127" t="s">
+        <v>253</v>
+      </c>
+      <c r="R127" t="s">
         <v>404</v>
-      </c>
-      <c r="O127" t="s">
-        <v>225</v>
-      </c>
-      <c r="P127" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>255</v>
-      </c>
-      <c r="R127" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B128" t="s">
+        <v>405</v>
+      </c>
+      <c r="C128" t="s">
+        <v>406</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="N128" t="s">
         <v>407</v>
       </c>
-      <c r="C128" t="s">
+      <c r="O128" t="s">
+        <v>223</v>
+      </c>
+      <c r="P128" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>253</v>
+      </c>
+      <c r="R128" t="s">
         <v>408</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="N128" t="s">
-        <v>409</v>
-      </c>
-      <c r="O128" t="s">
-        <v>225</v>
-      </c>
-      <c r="P128" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>255</v>
-      </c>
-      <c r="R128" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B129" t="s">
+        <v>409</v>
+      </c>
+      <c r="C129" t="s">
+        <v>410</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="N129" t="s">
         <v>411</v>
       </c>
-      <c r="C129" t="s">
+      <c r="O129" t="s">
+        <v>223</v>
+      </c>
+      <c r="P129" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>253</v>
+      </c>
+      <c r="R129" t="s">
         <v>412</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="N129" t="s">
-        <v>413</v>
-      </c>
-      <c r="O129" t="s">
-        <v>225</v>
-      </c>
-      <c r="P129" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>255</v>
-      </c>
-      <c r="R129" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B130" t="s">
+        <v>413</v>
+      </c>
+      <c r="C130" t="s">
+        <v>414</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="N130" t="s">
         <v>415</v>
       </c>
-      <c r="C130" t="s">
+      <c r="O130" t="s">
+        <v>223</v>
+      </c>
+      <c r="P130" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>253</v>
+      </c>
+      <c r="R130" t="s">
         <v>416</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="N130" t="s">
-        <v>417</v>
-      </c>
-      <c r="O130" t="s">
-        <v>225</v>
-      </c>
-      <c r="P130" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>255</v>
-      </c>
-      <c r="R130" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B131" t="s">
+        <v>417</v>
+      </c>
+      <c r="C131" t="s">
+        <v>418</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="N131" t="s">
         <v>419</v>
       </c>
-      <c r="C131" t="s">
+      <c r="O131" t="s">
+        <v>223</v>
+      </c>
+      <c r="P131" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>253</v>
+      </c>
+      <c r="R131" t="s">
         <v>420</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="N131" t="s">
-        <v>421</v>
-      </c>
-      <c r="O131" t="s">
-        <v>225</v>
-      </c>
-      <c r="P131" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>255</v>
-      </c>
-      <c r="R131" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B132" t="s">
+        <v>421</v>
+      </c>
+      <c r="C132" t="s">
+        <v>422</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="N132" t="s">
         <v>423</v>
       </c>
-      <c r="C132" t="s">
+      <c r="O132" t="s">
+        <v>223</v>
+      </c>
+      <c r="P132" t="s">
         <v>424</v>
       </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="N132" t="s">
+      <c r="Q132" t="s">
+        <v>251</v>
+      </c>
+      <c r="R132" t="s">
         <v>425</v>
-      </c>
-      <c r="O132" t="s">
-        <v>225</v>
-      </c>
-      <c r="P132" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>253</v>
-      </c>
-      <c r="R132" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B133" t="s">
+        <v>426</v>
+      </c>
+      <c r="C133" t="s">
+        <v>427</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="N133" t="s">
         <v>428</v>
       </c>
-      <c r="C133" t="s">
+      <c r="O133" t="s">
+        <v>223</v>
+      </c>
+      <c r="P133" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>251</v>
+      </c>
+      <c r="R133" t="s">
         <v>429</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="N133" t="s">
-        <v>430</v>
-      </c>
-      <c r="O133" t="s">
-        <v>225</v>
-      </c>
-      <c r="P133" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>253</v>
-      </c>
-      <c r="R133" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B134" t="s">
+        <v>430</v>
+      </c>
+      <c r="C134" t="s">
+        <v>431</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="N134" t="s">
         <v>432</v>
       </c>
-      <c r="C134" t="s">
+      <c r="O134" t="s">
+        <v>223</v>
+      </c>
+      <c r="P134" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>251</v>
+      </c>
+      <c r="R134" t="s">
         <v>433</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="N134" t="s">
-        <v>434</v>
-      </c>
-      <c r="O134" t="s">
-        <v>225</v>
-      </c>
-      <c r="P134" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>253</v>
-      </c>
-      <c r="R134" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B135" t="s">
+        <v>434</v>
+      </c>
+      <c r="C135" t="s">
+        <v>435</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="N135" t="s">
         <v>436</v>
       </c>
-      <c r="C135" t="s">
+      <c r="O135" t="s">
+        <v>223</v>
+      </c>
+      <c r="P135" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>251</v>
+      </c>
+      <c r="R135" t="s">
         <v>437</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="N135" t="s">
-        <v>438</v>
-      </c>
-      <c r="O135" t="s">
-        <v>225</v>
-      </c>
-      <c r="P135" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q135" t="s">
-        <v>253</v>
-      </c>
-      <c r="R135" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B136" t="s">
+        <v>438</v>
+      </c>
+      <c r="C136" t="s">
+        <v>439</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="N136" t="s">
         <v>440</v>
       </c>
-      <c r="C136" t="s">
+      <c r="O136" t="s">
+        <v>359</v>
+      </c>
+      <c r="P136" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>251</v>
+      </c>
+      <c r="R136" t="s">
         <v>441</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="N136" t="s">
-        <v>442</v>
-      </c>
-      <c r="O136" t="s">
-        <v>361</v>
-      </c>
-      <c r="P136" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>253</v>
-      </c>
-      <c r="R136" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B137" t="s">
+        <v>442</v>
+      </c>
+      <c r="C137" t="s">
+        <v>443</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="N137" t="s">
         <v>444</v>
       </c>
-      <c r="C137" t="s">
+      <c r="O137" t="s">
+        <v>223</v>
+      </c>
+      <c r="P137" t="s">
         <v>445</v>
       </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="N137" t="s">
+      <c r="Q137" t="s">
+        <v>253</v>
+      </c>
+      <c r="R137" t="s">
         <v>446</v>
-      </c>
-      <c r="O137" t="s">
-        <v>225</v>
-      </c>
-      <c r="P137" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>255</v>
-      </c>
-      <c r="R137" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B138" t="s">
+        <v>447</v>
+      </c>
+      <c r="C138" t="s">
+        <v>448</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="N138" t="s">
         <v>449</v>
       </c>
-      <c r="C138" t="s">
+      <c r="O138" t="s">
+        <v>223</v>
+      </c>
+      <c r="P138" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>253</v>
+      </c>
+      <c r="R138" t="s">
         <v>450</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="N138" t="s">
-        <v>451</v>
-      </c>
-      <c r="O138" t="s">
-        <v>225</v>
-      </c>
-      <c r="P138" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>255</v>
-      </c>
-      <c r="R138" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B139" t="s">
+        <v>451</v>
+      </c>
+      <c r="C139" t="s">
+        <v>452</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="N139" t="s">
         <v>453</v>
       </c>
-      <c r="C139" t="s">
+      <c r="O139" t="s">
+        <v>223</v>
+      </c>
+      <c r="P139" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>253</v>
+      </c>
+      <c r="R139" t="s">
         <v>454</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="N139" t="s">
-        <v>455</v>
-      </c>
-      <c r="O139" t="s">
-        <v>225</v>
-      </c>
-      <c r="P139" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>255</v>
-      </c>
-      <c r="R139" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B140" t="s">
+        <v>455</v>
+      </c>
+      <c r="C140" t="s">
+        <v>456</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="N140" t="s">
         <v>457</v>
       </c>
-      <c r="C140" t="s">
+      <c r="O140" t="s">
+        <v>223</v>
+      </c>
+      <c r="P140" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>253</v>
+      </c>
+      <c r="R140" t="s">
         <v>458</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="N140" t="s">
-        <v>459</v>
-      </c>
-      <c r="O140" t="s">
-        <v>225</v>
-      </c>
-      <c r="P140" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q140" t="s">
-        <v>255</v>
-      </c>
-      <c r="R140" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B141" t="s">
+        <v>459</v>
+      </c>
+      <c r="C141" t="s">
+        <v>460</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="N141" t="s">
         <v>461</v>
       </c>
-      <c r="C141" t="s">
+      <c r="O141" t="s">
+        <v>223</v>
+      </c>
+      <c r="P141" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>253</v>
+      </c>
+      <c r="R141" t="s">
         <v>462</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="N141" t="s">
-        <v>463</v>
-      </c>
-      <c r="O141" t="s">
-        <v>225</v>
-      </c>
-      <c r="P141" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q141" t="s">
-        <v>255</v>
-      </c>
-      <c r="R141" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B142" t="s">
+        <v>463</v>
+      </c>
+      <c r="C142" t="s">
+        <v>464</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="N142" t="s">
         <v>465</v>
       </c>
-      <c r="C142" t="s">
+      <c r="O142" t="s">
+        <v>267</v>
+      </c>
+      <c r="P142" t="s">
         <v>466</v>
       </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="N142" t="s">
+      <c r="Q142" t="s">
+        <v>259</v>
+      </c>
+      <c r="R142" t="s">
         <v>467</v>
-      </c>
-      <c r="O142" t="s">
-        <v>269</v>
-      </c>
-      <c r="P142" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q142" t="s">
-        <v>261</v>
-      </c>
-      <c r="R142" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B143" t="s">
+        <v>468</v>
+      </c>
+      <c r="C143" t="s">
+        <v>469</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="N143" t="s">
         <v>470</v>
       </c>
-      <c r="C143" t="s">
+      <c r="O143" t="s">
+        <v>267</v>
+      </c>
+      <c r="P143" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>259</v>
+      </c>
+      <c r="R143" t="s">
         <v>471</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="N143" t="s">
-        <v>472</v>
-      </c>
-      <c r="O143" t="s">
-        <v>269</v>
-      </c>
-      <c r="P143" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>261</v>
-      </c>
-      <c r="R143" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B144" t="s">
+        <v>472</v>
+      </c>
+      <c r="C144" t="s">
+        <v>473</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="N144" t="s">
         <v>474</v>
       </c>
-      <c r="C144" t="s">
+      <c r="O144" t="s">
+        <v>267</v>
+      </c>
+      <c r="P144" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>259</v>
+      </c>
+      <c r="R144" t="s">
         <v>475</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="N144" t="s">
-        <v>476</v>
-      </c>
-      <c r="O144" t="s">
-        <v>269</v>
-      </c>
-      <c r="P144" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q144" t="s">
-        <v>261</v>
-      </c>
-      <c r="R144" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B145" t="s">
+        <v>476</v>
+      </c>
+      <c r="C145" t="s">
+        <v>477</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="N145" t="s">
         <v>478</v>
       </c>
-      <c r="C145" t="s">
+      <c r="O145" t="s">
+        <v>267</v>
+      </c>
+      <c r="P145" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>259</v>
+      </c>
+      <c r="R145" t="s">
         <v>479</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="N145" t="s">
-        <v>480</v>
-      </c>
-      <c r="O145" t="s">
-        <v>269</v>
-      </c>
-      <c r="P145" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q145" t="s">
-        <v>261</v>
-      </c>
-      <c r="R145" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B146" t="s">
+        <v>480</v>
+      </c>
+      <c r="C146" t="s">
+        <v>481</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="N146" t="s">
         <v>482</v>
       </c>
-      <c r="C146" t="s">
+      <c r="O146" t="s">
+        <v>267</v>
+      </c>
+      <c r="P146" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>259</v>
+      </c>
+      <c r="R146" t="s">
         <v>483</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="N146" t="s">
-        <v>484</v>
-      </c>
-      <c r="O146" t="s">
-        <v>269</v>
-      </c>
-      <c r="P146" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>261</v>
-      </c>
-      <c r="R146" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
+        <v>484</v>
+      </c>
+      <c r="C147" t="s">
+        <v>485</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="N147" t="s">
         <v>486</v>
       </c>
-      <c r="C147" t="s">
+      <c r="O147" t="s">
+        <v>267</v>
+      </c>
+      <c r="P147" t="s">
         <v>487</v>
       </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="N147" t="s">
+      <c r="Q147" t="s">
+        <v>256</v>
+      </c>
+      <c r="R147" t="s">
         <v>488</v>
-      </c>
-      <c r="O147" t="s">
-        <v>269</v>
-      </c>
-      <c r="P147" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q147" t="s">
-        <v>258</v>
-      </c>
-      <c r="R147" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
+        <v>489</v>
+      </c>
+      <c r="C148" t="s">
+        <v>490</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="N148" t="s">
         <v>491</v>
       </c>
-      <c r="C148" t="s">
+      <c r="O148" t="s">
+        <v>267</v>
+      </c>
+      <c r="P148" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>256</v>
+      </c>
+      <c r="R148" t="s">
         <v>492</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="N148" t="s">
-        <v>493</v>
-      </c>
-      <c r="O148" t="s">
-        <v>269</v>
-      </c>
-      <c r="P148" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>258</v>
-      </c>
-      <c r="R148" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B149" t="s">
+        <v>493</v>
+      </c>
+      <c r="C149" t="s">
+        <v>494</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="N149" t="s">
         <v>495</v>
       </c>
-      <c r="C149" t="s">
+      <c r="O149" t="s">
+        <v>267</v>
+      </c>
+      <c r="P149" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>256</v>
+      </c>
+      <c r="R149" t="s">
         <v>496</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="N149" t="s">
-        <v>497</v>
-      </c>
-      <c r="O149" t="s">
-        <v>269</v>
-      </c>
-      <c r="P149" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>258</v>
-      </c>
-      <c r="R149" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B150" t="s">
+        <v>497</v>
+      </c>
+      <c r="C150" t="s">
+        <v>498</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="N150" t="s">
         <v>499</v>
       </c>
-      <c r="C150" t="s">
+      <c r="O150" t="s">
+        <v>267</v>
+      </c>
+      <c r="P150" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>256</v>
+      </c>
+      <c r="R150" t="s">
         <v>500</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="N150" t="s">
-        <v>501</v>
-      </c>
-      <c r="O150" t="s">
-        <v>269</v>
-      </c>
-      <c r="P150" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q150" t="s">
-        <v>258</v>
-      </c>
-      <c r="R150" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B151" t="s">
+        <v>501</v>
+      </c>
+      <c r="C151" t="s">
+        <v>502</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="N151" t="s">
         <v>503</v>
       </c>
-      <c r="C151" t="s">
+      <c r="O151" t="s">
+        <v>267</v>
+      </c>
+      <c r="P151" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>256</v>
+      </c>
+      <c r="R151" t="s">
         <v>504</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="N151" t="s">
-        <v>505</v>
-      </c>
-      <c r="O151" t="s">
-        <v>269</v>
-      </c>
-      <c r="P151" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q151" t="s">
-        <v>258</v>
-      </c>
-      <c r="R151" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B152" t="s">
+        <v>505</v>
+      </c>
+      <c r="C152" t="s">
+        <v>506</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="N152" t="s">
         <v>507</v>
       </c>
-      <c r="C152" t="s">
+      <c r="O152" t="s">
+        <v>267</v>
+      </c>
+      <c r="P152" t="s">
         <v>508</v>
       </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="N152" t="s">
+      <c r="Q152" t="s">
+        <v>257</v>
+      </c>
+      <c r="R152" t="s">
         <v>509</v>
-      </c>
-      <c r="O152" t="s">
-        <v>269</v>
-      </c>
-      <c r="P152" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q152" t="s">
-        <v>259</v>
-      </c>
-      <c r="R152" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B153" t="s">
+        <v>510</v>
+      </c>
+      <c r="C153" t="s">
+        <v>511</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="N153" t="s">
         <v>512</v>
       </c>
-      <c r="C153" t="s">
+      <c r="O153" t="s">
+        <v>267</v>
+      </c>
+      <c r="P153" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>257</v>
+      </c>
+      <c r="R153" t="s">
         <v>513</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="N153" t="s">
-        <v>514</v>
-      </c>
-      <c r="O153" t="s">
-        <v>269</v>
-      </c>
-      <c r="P153" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q153" t="s">
-        <v>259</v>
-      </c>
-      <c r="R153" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B154" t="s">
+        <v>514</v>
+      </c>
+      <c r="C154" t="s">
+        <v>515</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="N154" t="s">
         <v>516</v>
       </c>
-      <c r="C154" t="s">
+      <c r="O154" t="s">
+        <v>267</v>
+      </c>
+      <c r="P154" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>257</v>
+      </c>
+      <c r="R154" t="s">
         <v>517</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="N154" t="s">
-        <v>518</v>
-      </c>
-      <c r="O154" t="s">
-        <v>269</v>
-      </c>
-      <c r="P154" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q154" t="s">
-        <v>259</v>
-      </c>
-      <c r="R154" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B155" t="s">
+        <v>518</v>
+      </c>
+      <c r="C155" t="s">
+        <v>519</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="N155" t="s">
         <v>520</v>
       </c>
-      <c r="C155" t="s">
+      <c r="O155" t="s">
+        <v>267</v>
+      </c>
+      <c r="P155" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>257</v>
+      </c>
+      <c r="R155" t="s">
         <v>521</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="N155" t="s">
-        <v>522</v>
-      </c>
-      <c r="O155" t="s">
-        <v>269</v>
-      </c>
-      <c r="P155" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q155" t="s">
-        <v>259</v>
-      </c>
-      <c r="R155" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B156" t="s">
+        <v>522</v>
+      </c>
+      <c r="C156" t="s">
+        <v>523</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="N156" t="s">
         <v>524</v>
       </c>
-      <c r="C156" t="s">
+      <c r="O156" t="s">
+        <v>267</v>
+      </c>
+      <c r="P156" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>257</v>
+      </c>
+      <c r="R156" t="s">
         <v>525</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="N156" t="s">
-        <v>526</v>
-      </c>
-      <c r="O156" t="s">
-        <v>269</v>
-      </c>
-      <c r="P156" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>259</v>
-      </c>
-      <c r="R156" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B157" t="s">
+        <v>526</v>
+      </c>
+      <c r="C157" t="s">
+        <v>527</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="N157" t="s">
         <v>528</v>
       </c>
-      <c r="C157" t="s">
+      <c r="O157" t="s">
         <v>529</v>
       </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="N157" t="s">
+      <c r="P157" t="s">
         <v>530</v>
       </c>
-      <c r="O157" t="s">
+      <c r="Q157" t="s">
+        <v>255</v>
+      </c>
+      <c r="R157" t="s">
         <v>531</v>
-      </c>
-      <c r="P157" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>257</v>
-      </c>
-      <c r="R157" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B158" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" t="s">
+        <v>533</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="N158" t="s">
         <v>534</v>
       </c>
-      <c r="C158" t="s">
+      <c r="O158" t="s">
+        <v>529</v>
+      </c>
+      <c r="P158" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>255</v>
+      </c>
+      <c r="R158" t="s">
         <v>535</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="N158" t="s">
-        <v>536</v>
-      </c>
-      <c r="O158" t="s">
-        <v>531</v>
-      </c>
-      <c r="P158" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>257</v>
-      </c>
-      <c r="R158" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B159" t="s">
+        <v>536</v>
+      </c>
+      <c r="C159" t="s">
+        <v>537</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="N159" t="s">
         <v>538</v>
       </c>
-      <c r="C159" t="s">
+      <c r="O159" t="s">
+        <v>529</v>
+      </c>
+      <c r="P159" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>255</v>
+      </c>
+      <c r="R159" t="s">
         <v>539</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="N159" t="s">
-        <v>540</v>
-      </c>
-      <c r="O159" t="s">
-        <v>531</v>
-      </c>
-      <c r="P159" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>257</v>
-      </c>
-      <c r="R159" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B160" t="s">
+        <v>540</v>
+      </c>
+      <c r="C160" t="s">
+        <v>541</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="N160" t="s">
         <v>542</v>
       </c>
-      <c r="C160" t="s">
+      <c r="O160" t="s">
+        <v>529</v>
+      </c>
+      <c r="P160" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>255</v>
+      </c>
+      <c r="R160" t="s">
         <v>543</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="N160" t="s">
-        <v>544</v>
-      </c>
-      <c r="O160" t="s">
-        <v>531</v>
-      </c>
-      <c r="P160" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q160" t="s">
-        <v>257</v>
-      </c>
-      <c r="R160" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B161" t="s">
+        <v>544</v>
+      </c>
+      <c r="C161" t="s">
+        <v>545</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="N161" t="s">
         <v>546</v>
       </c>
-      <c r="C161" t="s">
+      <c r="O161" t="s">
+        <v>529</v>
+      </c>
+      <c r="P161" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>255</v>
+      </c>
+      <c r="R161" t="s">
         <v>547</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="N161" t="s">
-        <v>548</v>
-      </c>
-      <c r="O161" t="s">
-        <v>531</v>
-      </c>
-      <c r="P161" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q161" t="s">
-        <v>257</v>
-      </c>
-      <c r="R161" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B162" t="s">
+        <v>548</v>
+      </c>
+      <c r="C162" t="s">
+        <v>549</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="N162" t="s">
         <v>550</v>
       </c>
-      <c r="C162" t="s">
+      <c r="O162" t="s">
+        <v>529</v>
+      </c>
+      <c r="P162" t="s">
         <v>551</v>
       </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="N162" t="s">
+      <c r="Q162" t="s">
+        <v>247</v>
+      </c>
+      <c r="R162" t="s">
         <v>552</v>
-      </c>
-      <c r="O162" t="s">
-        <v>531</v>
-      </c>
-      <c r="P162" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>249</v>
-      </c>
-      <c r="R162" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B163" t="s">
+        <v>553</v>
+      </c>
+      <c r="C163" t="s">
+        <v>554</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="N163" t="s">
         <v>555</v>
       </c>
-      <c r="C163" t="s">
+      <c r="O163" t="s">
+        <v>529</v>
+      </c>
+      <c r="P163" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>247</v>
+      </c>
+      <c r="R163" t="s">
         <v>556</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="N163" t="s">
-        <v>557</v>
-      </c>
-      <c r="O163" t="s">
-        <v>531</v>
-      </c>
-      <c r="P163" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q163" t="s">
-        <v>249</v>
-      </c>
-      <c r="R163" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B164" t="s">
+        <v>557</v>
+      </c>
+      <c r="C164" t="s">
+        <v>558</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="N164" t="s">
         <v>559</v>
       </c>
-      <c r="C164" t="s">
+      <c r="O164" t="s">
+        <v>529</v>
+      </c>
+      <c r="P164" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>247</v>
+      </c>
+      <c r="R164" t="s">
         <v>560</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="N164" t="s">
-        <v>561</v>
-      </c>
-      <c r="O164" t="s">
-        <v>531</v>
-      </c>
-      <c r="P164" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q164" t="s">
-        <v>249</v>
-      </c>
-      <c r="R164" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B165" t="s">
+        <v>561</v>
+      </c>
+      <c r="C165" t="s">
+        <v>562</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="N165" t="s">
         <v>563</v>
       </c>
-      <c r="C165" t="s">
+      <c r="O165" t="s">
+        <v>529</v>
+      </c>
+      <c r="P165" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>247</v>
+      </c>
+      <c r="R165" t="s">
         <v>564</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="N165" t="s">
-        <v>565</v>
-      </c>
-      <c r="O165" t="s">
-        <v>531</v>
-      </c>
-      <c r="P165" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>249</v>
-      </c>
-      <c r="R165" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
+        <v>565</v>
+      </c>
+      <c r="C166" t="s">
+        <v>566</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="N166" t="s">
         <v>567</v>
       </c>
-      <c r="C166" t="s">
+      <c r="O166" t="s">
+        <v>529</v>
+      </c>
+      <c r="P166" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>247</v>
+      </c>
+      <c r="R166" t="s">
         <v>568</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="N166" t="s">
-        <v>569</v>
-      </c>
-      <c r="O166" t="s">
-        <v>531</v>
-      </c>
-      <c r="P166" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q166" t="s">
-        <v>249</v>
-      </c>
-      <c r="R166" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B167" t="s">
+        <v>569</v>
+      </c>
+      <c r="C167" t="s">
+        <v>570</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="N167" t="s">
         <v>571</v>
       </c>
-      <c r="C167" t="s">
+      <c r="O167" t="s">
+        <v>529</v>
+      </c>
+      <c r="P167" t="s">
         <v>572</v>
       </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="Q167" t="s">
+        <v>251</v>
+      </c>
+      <c r="R167" t="s">
         <v>573</v>
-      </c>
-      <c r="O167" t="s">
-        <v>531</v>
-      </c>
-      <c r="P167" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>253</v>
-      </c>
-      <c r="R167" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B168" t="s">
+        <v>574</v>
+      </c>
+      <c r="C168" t="s">
+        <v>575</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="N168" t="s">
         <v>576</v>
       </c>
-      <c r="C168" t="s">
+      <c r="O168" t="s">
+        <v>529</v>
+      </c>
+      <c r="P168" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>251</v>
+      </c>
+      <c r="R168" t="s">
         <v>577</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="N168" t="s">
-        <v>578</v>
-      </c>
-      <c r="O168" t="s">
-        <v>531</v>
-      </c>
-      <c r="P168" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>253</v>
-      </c>
-      <c r="R168" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B169" t="s">
+        <v>578</v>
+      </c>
+      <c r="C169" t="s">
+        <v>579</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="N169" t="s">
         <v>580</v>
       </c>
-      <c r="C169" t="s">
+      <c r="O169" t="s">
+        <v>529</v>
+      </c>
+      <c r="P169" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>251</v>
+      </c>
+      <c r="R169" t="s">
         <v>581</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="N169" t="s">
-        <v>582</v>
-      </c>
-      <c r="O169" t="s">
-        <v>531</v>
-      </c>
-      <c r="P169" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>253</v>
-      </c>
-      <c r="R169" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B170" t="s">
+        <v>582</v>
+      </c>
+      <c r="C170" t="s">
+        <v>583</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="N170" t="s">
         <v>584</v>
       </c>
-      <c r="C170" t="s">
+      <c r="O170" t="s">
+        <v>529</v>
+      </c>
+      <c r="P170" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>251</v>
+      </c>
+      <c r="R170" t="s">
         <v>585</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="N170" t="s">
-        <v>586</v>
-      </c>
-      <c r="O170" t="s">
-        <v>531</v>
-      </c>
-      <c r="P170" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>253</v>
-      </c>
-      <c r="R170" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B171" t="s">
+        <v>586</v>
+      </c>
+      <c r="C171" t="s">
+        <v>587</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="N171" t="s">
         <v>588</v>
       </c>
-      <c r="C171" t="s">
+      <c r="O171" t="s">
+        <v>529</v>
+      </c>
+      <c r="P171" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>251</v>
+      </c>
+      <c r="R171" t="s">
         <v>589</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="L171">
-        <v>0</v>
-      </c>
-      <c r="N171" t="s">
-        <v>590</v>
-      </c>
-      <c r="O171" t="s">
-        <v>531</v>
-      </c>
-      <c r="P171" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>253</v>
-      </c>
-      <c r="R171" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B172" t="s">
+        <v>590</v>
+      </c>
+      <c r="C172" t="s">
+        <v>591</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="N172" t="s">
         <v>592</v>
       </c>
-      <c r="C172" t="s">
+      <c r="O172" t="s">
+        <v>258</v>
+      </c>
+      <c r="P172" t="s">
         <v>593</v>
       </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-      <c r="N172" t="s">
+      <c r="Q172" t="s">
+        <v>224</v>
+      </c>
+      <c r="R172" t="s">
         <v>594</v>
-      </c>
-      <c r="O172" t="s">
-        <v>260</v>
-      </c>
-      <c r="P172" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>226</v>
-      </c>
-      <c r="R172" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>595</v>
+      </c>
+      <c r="C173" t="s">
+        <v>596</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="N173" t="s">
         <v>597</v>
       </c>
-      <c r="C173" t="s">
+      <c r="O173" t="s">
+        <v>258</v>
+      </c>
+      <c r="P173" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>224</v>
+      </c>
+      <c r="R173" t="s">
         <v>598</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="L173">
-        <v>0</v>
-      </c>
-      <c r="N173" t="s">
-        <v>599</v>
-      </c>
-      <c r="O173" t="s">
-        <v>260</v>
-      </c>
-      <c r="P173" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>226</v>
-      </c>
-      <c r="R173" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B174" t="s">
+        <v>599</v>
+      </c>
+      <c r="C174" t="s">
+        <v>600</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="N174" t="s">
         <v>601</v>
       </c>
-      <c r="C174" t="s">
+      <c r="O174" t="s">
+        <v>258</v>
+      </c>
+      <c r="P174" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>224</v>
+      </c>
+      <c r="R174" t="s">
         <v>602</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-      <c r="N174" t="s">
-        <v>603</v>
-      </c>
-      <c r="O174" t="s">
-        <v>260</v>
-      </c>
-      <c r="P174" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>226</v>
-      </c>
-      <c r="R174" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B175" t="s">
+        <v>603</v>
+      </c>
+      <c r="C175" t="s">
+        <v>604</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="N175" t="s">
         <v>605</v>
       </c>
-      <c r="C175" t="s">
+      <c r="O175" t="s">
+        <v>258</v>
+      </c>
+      <c r="P175" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>224</v>
+      </c>
+      <c r="R175" t="s">
         <v>606</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="L175">
-        <v>0</v>
-      </c>
-      <c r="N175" t="s">
-        <v>607</v>
-      </c>
-      <c r="O175" t="s">
-        <v>260</v>
-      </c>
-      <c r="P175" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>226</v>
-      </c>
-      <c r="R175" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B176" t="s">
+        <v>607</v>
+      </c>
+      <c r="C176" t="s">
+        <v>608</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="N176" t="s">
         <v>609</v>
       </c>
-      <c r="C176" t="s">
+      <c r="O176" t="s">
+        <v>258</v>
+      </c>
+      <c r="P176" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>224</v>
+      </c>
+      <c r="R176" t="s">
         <v>610</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="L176">
-        <v>0</v>
-      </c>
-      <c r="N176" t="s">
-        <v>611</v>
-      </c>
-      <c r="O176" t="s">
-        <v>260</v>
-      </c>
-      <c r="P176" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>226</v>
-      </c>
-      <c r="R176" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B177" t="s">
+        <v>611</v>
+      </c>
+      <c r="C177" t="s">
+        <v>612</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="N177" t="s">
         <v>613</v>
       </c>
-      <c r="C177" t="s">
+      <c r="O177" t="s">
+        <v>258</v>
+      </c>
+      <c r="P177" t="s">
         <v>614</v>
       </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-      <c r="N177" t="s">
+      <c r="Q177" t="s">
+        <v>259</v>
+      </c>
+      <c r="R177" t="s">
         <v>615</v>
-      </c>
-      <c r="O177" t="s">
-        <v>260</v>
-      </c>
-      <c r="P177" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>261</v>
-      </c>
-      <c r="R177" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B178" t="s">
+        <v>616</v>
+      </c>
+      <c r="C178" t="s">
+        <v>617</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="N178" t="s">
         <v>618</v>
       </c>
-      <c r="C178" t="s">
+      <c r="O178" t="s">
+        <v>258</v>
+      </c>
+      <c r="P178" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>259</v>
+      </c>
+      <c r="R178" t="s">
         <v>619</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="L178">
-        <v>0</v>
-      </c>
-      <c r="N178" t="s">
-        <v>620</v>
-      </c>
-      <c r="O178" t="s">
-        <v>260</v>
-      </c>
-      <c r="P178" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>261</v>
-      </c>
-      <c r="R178" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B179" t="s">
+        <v>620</v>
+      </c>
+      <c r="C179" t="s">
+        <v>621</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="N179" t="s">
         <v>622</v>
       </c>
-      <c r="C179" t="s">
+      <c r="O179" t="s">
+        <v>258</v>
+      </c>
+      <c r="P179" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>259</v>
+      </c>
+      <c r="R179" t="s">
         <v>623</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-      <c r="N179" t="s">
-        <v>624</v>
-      </c>
-      <c r="O179" t="s">
-        <v>260</v>
-      </c>
-      <c r="P179" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>261</v>
-      </c>
-      <c r="R179" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B180" t="s">
+        <v>624</v>
+      </c>
+      <c r="C180" t="s">
+        <v>625</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="N180" t="s">
         <v>626</v>
       </c>
-      <c r="C180" t="s">
+      <c r="O180" t="s">
+        <v>258</v>
+      </c>
+      <c r="P180" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>259</v>
+      </c>
+      <c r="R180" t="s">
         <v>627</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="N180" t="s">
-        <v>628</v>
-      </c>
-      <c r="O180" t="s">
-        <v>260</v>
-      </c>
-      <c r="P180" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q180" t="s">
-        <v>261</v>
-      </c>
-      <c r="R180" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B181" t="s">
+        <v>628</v>
+      </c>
+      <c r="C181" t="s">
+        <v>629</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="N181" t="s">
         <v>630</v>
       </c>
-      <c r="C181" t="s">
+      <c r="O181" t="s">
+        <v>258</v>
+      </c>
+      <c r="P181" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>259</v>
+      </c>
+      <c r="R181" t="s">
         <v>631</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="L181">
-        <v>0</v>
-      </c>
-      <c r="N181" t="s">
-        <v>632</v>
-      </c>
-      <c r="O181" t="s">
-        <v>260</v>
-      </c>
-      <c r="P181" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q181" t="s">
-        <v>261</v>
-      </c>
-      <c r="R181" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B182" t="s">
+        <v>632</v>
+      </c>
+      <c r="C182" t="s">
+        <v>633</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="N182" t="s">
         <v>634</v>
       </c>
-      <c r="C182" t="s">
+      <c r="O182" t="s">
+        <v>258</v>
+      </c>
+      <c r="P182" t="s">
         <v>635</v>
       </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="N182" t="s">
+      <c r="Q182" t="s">
+        <v>257</v>
+      </c>
+      <c r="R182" t="s">
         <v>636</v>
-      </c>
-      <c r="O182" t="s">
-        <v>260</v>
-      </c>
-      <c r="P182" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>259</v>
-      </c>
-      <c r="R182" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B183" t="s">
+        <v>637</v>
+      </c>
+      <c r="C183" t="s">
+        <v>638</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="N183" t="s">
         <v>639</v>
       </c>
-      <c r="C183" t="s">
+      <c r="O183" t="s">
+        <v>258</v>
+      </c>
+      <c r="P183" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>257</v>
+      </c>
+      <c r="R183" t="s">
         <v>640</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="L183">
-        <v>0</v>
-      </c>
-      <c r="N183" t="s">
-        <v>641</v>
-      </c>
-      <c r="O183" t="s">
-        <v>260</v>
-      </c>
-      <c r="P183" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>259</v>
-      </c>
-      <c r="R183" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B184" t="s">
+        <v>641</v>
+      </c>
+      <c r="C184" t="s">
+        <v>642</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="N184" t="s">
         <v>643</v>
       </c>
-      <c r="C184" t="s">
+      <c r="O184" t="s">
+        <v>258</v>
+      </c>
+      <c r="P184" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>257</v>
+      </c>
+      <c r="R184" t="s">
         <v>644</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="N184" t="s">
-        <v>645</v>
-      </c>
-      <c r="O184" t="s">
-        <v>260</v>
-      </c>
-      <c r="P184" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q184" t="s">
-        <v>259</v>
-      </c>
-      <c r="R184" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B185" t="s">
+        <v>645</v>
+      </c>
+      <c r="C185" t="s">
+        <v>646</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="N185" t="s">
         <v>647</v>
       </c>
-      <c r="C185" t="s">
+      <c r="O185" t="s">
+        <v>258</v>
+      </c>
+      <c r="P185" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>257</v>
+      </c>
+      <c r="R185" t="s">
         <v>648</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="N185" t="s">
-        <v>649</v>
-      </c>
-      <c r="O185" t="s">
-        <v>260</v>
-      </c>
-      <c r="P185" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>259</v>
-      </c>
-      <c r="R185" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B186" t="s">
+        <v>649</v>
+      </c>
+      <c r="C186" t="s">
+        <v>650</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="N186" t="s">
         <v>651</v>
       </c>
-      <c r="C186" t="s">
+      <c r="O186" t="s">
+        <v>258</v>
+      </c>
+      <c r="P186" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>257</v>
+      </c>
+      <c r="R186" t="s">
         <v>652</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="L186">
-        <v>0</v>
-      </c>
-      <c r="N186" t="s">
-        <v>653</v>
-      </c>
-      <c r="O186" t="s">
-        <v>260</v>
-      </c>
-      <c r="P186" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q186" t="s">
-        <v>259</v>
-      </c>
-      <c r="R186" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B187" t="s">
+        <v>653</v>
+      </c>
+      <c r="C187" t="s">
+        <v>654</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="N187" t="s">
         <v>655</v>
       </c>
-      <c r="C187" t="s">
+      <c r="O187" t="s">
+        <v>254</v>
+      </c>
+      <c r="P187" t="s">
         <v>656</v>
       </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="L187">
-        <v>0</v>
-      </c>
-      <c r="N187" t="s">
+      <c r="Q187" t="s">
+        <v>272</v>
+      </c>
+      <c r="R187" t="s">
         <v>657</v>
-      </c>
-      <c r="O187" t="s">
-        <v>256</v>
-      </c>
-      <c r="P187" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q187" t="s">
-        <v>274</v>
-      </c>
-      <c r="R187" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B188" t="s">
+        <v>658</v>
+      </c>
+      <c r="C188" t="s">
+        <v>659</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="N188" t="s">
         <v>660</v>
       </c>
-      <c r="C188" t="s">
+      <c r="O188" t="s">
+        <v>254</v>
+      </c>
+      <c r="P188" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>272</v>
+      </c>
+      <c r="R188" t="s">
         <v>661</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="L188">
-        <v>0</v>
-      </c>
-      <c r="N188" t="s">
-        <v>662</v>
-      </c>
-      <c r="O188" t="s">
-        <v>256</v>
-      </c>
-      <c r="P188" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>274</v>
-      </c>
-      <c r="R188" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B189" t="s">
+        <v>662</v>
+      </c>
+      <c r="C189" t="s">
+        <v>663</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="N189" t="s">
         <v>664</v>
       </c>
-      <c r="C189" t="s">
+      <c r="O189" t="s">
+        <v>254</v>
+      </c>
+      <c r="P189" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>272</v>
+      </c>
+      <c r="R189" t="s">
         <v>665</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="L189">
-        <v>0</v>
-      </c>
-      <c r="N189" t="s">
-        <v>666</v>
-      </c>
-      <c r="O189" t="s">
-        <v>256</v>
-      </c>
-      <c r="P189" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q189" t="s">
-        <v>274</v>
-      </c>
-      <c r="R189" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B190" t="s">
+        <v>666</v>
+      </c>
+      <c r="C190" t="s">
+        <v>667</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="N190" t="s">
         <v>668</v>
       </c>
-      <c r="C190" t="s">
+      <c r="O190" t="s">
+        <v>254</v>
+      </c>
+      <c r="P190" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>272</v>
+      </c>
+      <c r="R190" t="s">
         <v>669</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="L190">
-        <v>0</v>
-      </c>
-      <c r="N190" t="s">
-        <v>670</v>
-      </c>
-      <c r="O190" t="s">
-        <v>256</v>
-      </c>
-      <c r="P190" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q190" t="s">
-        <v>274</v>
-      </c>
-      <c r="R190" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B191" t="s">
+        <v>670</v>
+      </c>
+      <c r="C191" t="s">
+        <v>671</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="N191" t="s">
         <v>672</v>
       </c>
-      <c r="C191" t="s">
+      <c r="O191" t="s">
+        <v>254</v>
+      </c>
+      <c r="P191" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>272</v>
+      </c>
+      <c r="R191" t="s">
         <v>673</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="L191">
-        <v>0</v>
-      </c>
-      <c r="N191" t="s">
-        <v>674</v>
-      </c>
-      <c r="O191" t="s">
-        <v>256</v>
-      </c>
-      <c r="P191" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q191" t="s">
-        <v>274</v>
-      </c>
-      <c r="R191" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B192" t="s">
+        <v>674</v>
+      </c>
+      <c r="C192" t="s">
+        <v>675</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="N192" t="s">
         <v>676</v>
       </c>
-      <c r="C192" t="s">
+      <c r="O192" t="s">
+        <v>254</v>
+      </c>
+      <c r="P192" t="s">
         <v>677</v>
       </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="L192">
-        <v>0</v>
-      </c>
-      <c r="N192" t="s">
+      <c r="Q192" t="s">
+        <v>255</v>
+      </c>
+      <c r="R192" t="s">
         <v>678</v>
-      </c>
-      <c r="O192" t="s">
-        <v>256</v>
-      </c>
-      <c r="P192" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q192" t="s">
-        <v>257</v>
-      </c>
-      <c r="R192" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>679</v>
+      </c>
+      <c r="C193" t="s">
+        <v>680</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="N193" t="s">
         <v>681</v>
       </c>
-      <c r="C193" t="s">
+      <c r="O193" t="s">
+        <v>254</v>
+      </c>
+      <c r="P193" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>255</v>
+      </c>
+      <c r="R193" t="s">
         <v>682</v>
-      </c>
-      <c r="D193">
-        <v>0</v>
-      </c>
-      <c r="L193">
-        <v>0</v>
-      </c>
-      <c r="N193" t="s">
-        <v>683</v>
-      </c>
-      <c r="O193" t="s">
-        <v>256</v>
-      </c>
-      <c r="P193" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>257</v>
-      </c>
-      <c r="R193" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B194" t="s">
+        <v>683</v>
+      </c>
+      <c r="C194" t="s">
+        <v>684</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="N194" t="s">
         <v>685</v>
       </c>
-      <c r="C194" t="s">
+      <c r="O194" t="s">
+        <v>254</v>
+      </c>
+      <c r="P194" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>255</v>
+      </c>
+      <c r="R194" t="s">
         <v>686</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="L194">
-        <v>0</v>
-      </c>
-      <c r="N194" t="s">
-        <v>687</v>
-      </c>
-      <c r="O194" t="s">
-        <v>256</v>
-      </c>
-      <c r="P194" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q194" t="s">
-        <v>257</v>
-      </c>
-      <c r="R194" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B195" t="s">
+        <v>687</v>
+      </c>
+      <c r="C195" t="s">
+        <v>688</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="N195" t="s">
         <v>689</v>
       </c>
-      <c r="C195" t="s">
+      <c r="O195" t="s">
+        <v>254</v>
+      </c>
+      <c r="P195" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>255</v>
+      </c>
+      <c r="R195" t="s">
         <v>690</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="L195">
-        <v>0</v>
-      </c>
-      <c r="N195" t="s">
-        <v>691</v>
-      </c>
-      <c r="O195" t="s">
-        <v>256</v>
-      </c>
-      <c r="P195" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q195" t="s">
-        <v>257</v>
-      </c>
-      <c r="R195" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B196" t="s">
+        <v>691</v>
+      </c>
+      <c r="C196" t="s">
+        <v>692</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="N196" t="s">
         <v>693</v>
       </c>
-      <c r="C196" t="s">
+      <c r="O196" t="s">
+        <v>254</v>
+      </c>
+      <c r="P196" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>255</v>
+      </c>
+      <c r="R196" t="s">
         <v>694</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="L196">
-        <v>0</v>
-      </c>
-      <c r="N196" t="s">
-        <v>695</v>
-      </c>
-      <c r="O196" t="s">
-        <v>256</v>
-      </c>
-      <c r="P196" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>257</v>
-      </c>
-      <c r="R196" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B197" t="s">
+        <v>695</v>
+      </c>
+      <c r="C197" t="s">
+        <v>696</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="N197" t="s">
         <v>697</v>
       </c>
-      <c r="C197" t="s">
+      <c r="O197" t="s">
+        <v>254</v>
+      </c>
+      <c r="P197" t="s">
         <v>698</v>
       </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="L197">
-        <v>0</v>
-      </c>
-      <c r="N197" t="s">
+      <c r="Q197" t="s">
+        <v>256</v>
+      </c>
+      <c r="R197" t="s">
         <v>699</v>
-      </c>
-      <c r="O197" t="s">
-        <v>256</v>
-      </c>
-      <c r="P197" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q197" t="s">
-        <v>258</v>
-      </c>
-      <c r="R197" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B198" t="s">
+        <v>700</v>
+      </c>
+      <c r="C198" t="s">
+        <v>701</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="N198" t="s">
         <v>702</v>
       </c>
-      <c r="C198" t="s">
+      <c r="O198" t="s">
+        <v>254</v>
+      </c>
+      <c r="P198" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>256</v>
+      </c>
+      <c r="R198" t="s">
         <v>703</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="L198">
-        <v>0</v>
-      </c>
-      <c r="N198" t="s">
-        <v>704</v>
-      </c>
-      <c r="O198" t="s">
-        <v>256</v>
-      </c>
-      <c r="P198" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q198" t="s">
-        <v>258</v>
-      </c>
-      <c r="R198" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B199" t="s">
+        <v>704</v>
+      </c>
+      <c r="C199" t="s">
+        <v>705</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="N199" t="s">
         <v>706</v>
       </c>
-      <c r="C199" t="s">
+      <c r="O199" t="s">
+        <v>254</v>
+      </c>
+      <c r="P199" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>256</v>
+      </c>
+      <c r="R199" t="s">
         <v>707</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-      <c r="N199" t="s">
-        <v>708</v>
-      </c>
-      <c r="O199" t="s">
-        <v>256</v>
-      </c>
-      <c r="P199" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q199" t="s">
-        <v>258</v>
-      </c>
-      <c r="R199" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B200" t="s">
+        <v>708</v>
+      </c>
+      <c r="C200" t="s">
+        <v>709</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="N200" t="s">
         <v>710</v>
       </c>
-      <c r="C200" t="s">
+      <c r="O200" t="s">
+        <v>254</v>
+      </c>
+      <c r="P200" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>256</v>
+      </c>
+      <c r="R200" t="s">
         <v>711</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-      <c r="N200" t="s">
-        <v>712</v>
-      </c>
-      <c r="O200" t="s">
-        <v>256</v>
-      </c>
-      <c r="P200" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q200" t="s">
-        <v>258</v>
-      </c>
-      <c r="R200" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B201" t="s">
+        <v>712</v>
+      </c>
+      <c r="C201" t="s">
+        <v>713</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="N201" t="s">
         <v>714</v>
       </c>
-      <c r="C201" t="s">
+      <c r="O201" t="s">
+        <v>254</v>
+      </c>
+      <c r="P201" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>256</v>
+      </c>
+      <c r="R201" t="s">
         <v>715</v>
-      </c>
-      <c r="D201">
-        <v>0</v>
-      </c>
-      <c r="L201">
-        <v>0</v>
-      </c>
-      <c r="N201" t="s">
-        <v>716</v>
-      </c>
-      <c r="O201" t="s">
-        <v>256</v>
-      </c>
-      <c r="P201" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q201" t="s">
-        <v>258</v>
-      </c>
-      <c r="R201" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>716</v>
+      </c>
+      <c r="C202" t="s">
+        <v>717</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="N202" t="s">
         <v>718</v>
       </c>
-      <c r="C202" t="s">
+      <c r="O202" t="s">
+        <v>359</v>
+      </c>
+      <c r="P202" t="s">
         <v>719</v>
       </c>
-      <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="L202">
-        <v>0</v>
-      </c>
-      <c r="N202" t="s">
+      <c r="Q202" t="s">
+        <v>259</v>
+      </c>
+      <c r="R202" t="s">
         <v>720</v>
-      </c>
-      <c r="O202" t="s">
-        <v>361</v>
-      </c>
-      <c r="P202" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q202" t="s">
-        <v>261</v>
-      </c>
-      <c r="R202" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B203" t="s">
+        <v>721</v>
+      </c>
+      <c r="C203" t="s">
+        <v>722</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="N203" t="s">
         <v>723</v>
       </c>
-      <c r="C203" t="s">
+      <c r="O203" t="s">
+        <v>359</v>
+      </c>
+      <c r="P203" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>259</v>
+      </c>
+      <c r="R203" t="s">
         <v>724</v>
-      </c>
-      <c r="D203">
-        <v>0</v>
-      </c>
-      <c r="L203">
-        <v>0</v>
-      </c>
-      <c r="N203" t="s">
-        <v>725</v>
-      </c>
-      <c r="O203" t="s">
-        <v>361</v>
-      </c>
-      <c r="P203" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q203" t="s">
-        <v>261</v>
-      </c>
-      <c r="R203" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B204" t="s">
+        <v>725</v>
+      </c>
+      <c r="C204" t="s">
+        <v>726</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="N204" t="s">
         <v>727</v>
       </c>
-      <c r="C204" t="s">
+      <c r="O204" t="s">
+        <v>359</v>
+      </c>
+      <c r="P204" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>259</v>
+      </c>
+      <c r="R204" t="s">
         <v>728</v>
-      </c>
-      <c r="D204">
-        <v>0</v>
-      </c>
-      <c r="L204">
-        <v>0</v>
-      </c>
-      <c r="N204" t="s">
-        <v>729</v>
-      </c>
-      <c r="O204" t="s">
-        <v>361</v>
-      </c>
-      <c r="P204" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>261</v>
-      </c>
-      <c r="R204" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B205" t="s">
+        <v>729</v>
+      </c>
+      <c r="C205" t="s">
+        <v>730</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="N205" t="s">
         <v>731</v>
       </c>
-      <c r="C205" t="s">
+      <c r="O205" t="s">
+        <v>359</v>
+      </c>
+      <c r="P205" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>259</v>
+      </c>
+      <c r="R205" t="s">
         <v>732</v>
-      </c>
-      <c r="D205">
-        <v>0</v>
-      </c>
-      <c r="L205">
-        <v>0</v>
-      </c>
-      <c r="N205" t="s">
-        <v>733</v>
-      </c>
-      <c r="O205" t="s">
-        <v>361</v>
-      </c>
-      <c r="P205" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q205" t="s">
-        <v>261</v>
-      </c>
-      <c r="R205" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B206" t="s">
+        <v>733</v>
+      </c>
+      <c r="C206" t="s">
+        <v>734</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="N206" t="s">
         <v>735</v>
       </c>
-      <c r="C206" t="s">
+      <c r="O206" t="s">
+        <v>359</v>
+      </c>
+      <c r="P206" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>259</v>
+      </c>
+      <c r="R206" t="s">
         <v>736</v>
-      </c>
-      <c r="D206">
-        <v>0</v>
-      </c>
-      <c r="L206">
-        <v>0</v>
-      </c>
-      <c r="N206" t="s">
-        <v>737</v>
-      </c>
-      <c r="O206" t="s">
-        <v>361</v>
-      </c>
-      <c r="P206" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q206" t="s">
-        <v>261</v>
-      </c>
-      <c r="R206" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B207" t="s">
+        <v>737</v>
+      </c>
+      <c r="C207" t="s">
+        <v>738</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="N207" t="s">
         <v>739</v>
       </c>
-      <c r="C207" t="s">
+      <c r="O207" t="s">
+        <v>359</v>
+      </c>
+      <c r="P207" t="s">
         <v>740</v>
       </c>
-      <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="L207">
-        <v>0</v>
-      </c>
-      <c r="N207" t="s">
+      <c r="Q207" t="s">
+        <v>228</v>
+      </c>
+      <c r="R207" t="s">
         <v>741</v>
-      </c>
-      <c r="O207" t="s">
-        <v>361</v>
-      </c>
-      <c r="P207" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>230</v>
-      </c>
-      <c r="R207" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B208" t="s">
+        <v>742</v>
+      </c>
+      <c r="C208" t="s">
+        <v>743</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="N208" t="s">
         <v>744</v>
       </c>
-      <c r="C208" t="s">
+      <c r="O208" t="s">
+        <v>359</v>
+      </c>
+      <c r="P208" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>228</v>
+      </c>
+      <c r="R208" t="s">
         <v>745</v>
-      </c>
-      <c r="D208">
-        <v>0</v>
-      </c>
-      <c r="L208">
-        <v>0</v>
-      </c>
-      <c r="N208" t="s">
-        <v>746</v>
-      </c>
-      <c r="O208" t="s">
-        <v>361</v>
-      </c>
-      <c r="P208" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>230</v>
-      </c>
-      <c r="R208" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B209" t="s">
+        <v>746</v>
+      </c>
+      <c r="C209" t="s">
+        <v>747</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="N209" t="s">
         <v>748</v>
       </c>
-      <c r="C209" t="s">
+      <c r="O209" t="s">
+        <v>359</v>
+      </c>
+      <c r="P209" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>228</v>
+      </c>
+      <c r="R209" t="s">
         <v>749</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="L209">
-        <v>0</v>
-      </c>
-      <c r="N209" t="s">
-        <v>750</v>
-      </c>
-      <c r="O209" t="s">
-        <v>361</v>
-      </c>
-      <c r="P209" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q209" t="s">
-        <v>230</v>
-      </c>
-      <c r="R209" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B210" t="s">
+        <v>750</v>
+      </c>
+      <c r="C210" t="s">
+        <v>751</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="N210" t="s">
         <v>752</v>
       </c>
-      <c r="C210" t="s">
+      <c r="O210" t="s">
+        <v>359</v>
+      </c>
+      <c r="P210" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>228</v>
+      </c>
+      <c r="R210" t="s">
         <v>753</v>
-      </c>
-      <c r="D210">
-        <v>0</v>
-      </c>
-      <c r="L210">
-        <v>0</v>
-      </c>
-      <c r="N210" t="s">
-        <v>754</v>
-      </c>
-      <c r="O210" t="s">
-        <v>361</v>
-      </c>
-      <c r="P210" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>230</v>
-      </c>
-      <c r="R210" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B211" t="s">
+        <v>754</v>
+      </c>
+      <c r="C211" t="s">
+        <v>755</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="N211" t="s">
         <v>756</v>
       </c>
-      <c r="C211" t="s">
+      <c r="O211" t="s">
+        <v>359</v>
+      </c>
+      <c r="P211" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>228</v>
+      </c>
+      <c r="R211" t="s">
         <v>757</v>
-      </c>
-      <c r="D211">
-        <v>0</v>
-      </c>
-      <c r="L211">
-        <v>0</v>
-      </c>
-      <c r="N211" t="s">
-        <v>758</v>
-      </c>
-      <c r="O211" t="s">
-        <v>361</v>
-      </c>
-      <c r="P211" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>230</v>
-      </c>
-      <c r="R211" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B212" t="s">
+        <v>758</v>
+      </c>
+      <c r="C212" t="s">
+        <v>759</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="N212" t="s">
         <v>760</v>
       </c>
-      <c r="C212" t="s">
+      <c r="O212" t="s">
+        <v>359</v>
+      </c>
+      <c r="P212" t="s">
         <v>761</v>
       </c>
-      <c r="D212">
-        <v>0</v>
-      </c>
-      <c r="L212">
-        <v>0</v>
-      </c>
-      <c r="N212" t="s">
+      <c r="Q212" t="s">
+        <v>251</v>
+      </c>
+      <c r="R212" t="s">
         <v>762</v>
-      </c>
-      <c r="O212" t="s">
-        <v>361</v>
-      </c>
-      <c r="P212" t="s">
-        <v>763</v>
-      </c>
-      <c r="Q212" t="s">
-        <v>253</v>
-      </c>
-      <c r="R212" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B213" t="s">
+        <v>763</v>
+      </c>
+      <c r="C213" t="s">
+        <v>764</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="N213" t="s">
         <v>765</v>
       </c>
-      <c r="C213" t="s">
+      <c r="O213" t="s">
+        <v>359</v>
+      </c>
+      <c r="P213" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>251</v>
+      </c>
+      <c r="R213" t="s">
         <v>766</v>
-      </c>
-      <c r="D213">
-        <v>0</v>
-      </c>
-      <c r="L213">
-        <v>0</v>
-      </c>
-      <c r="N213" t="s">
-        <v>767</v>
-      </c>
-      <c r="O213" t="s">
-        <v>361</v>
-      </c>
-      <c r="P213" t="s">
-        <v>763</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>253</v>
-      </c>
-      <c r="R213" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B214" t="s">
+        <v>767</v>
+      </c>
+      <c r="C214" t="s">
+        <v>768</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="N214" t="s">
         <v>769</v>
       </c>
-      <c r="C214" t="s">
+      <c r="O214" t="s">
+        <v>359</v>
+      </c>
+      <c r="P214" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>251</v>
+      </c>
+      <c r="R214" t="s">
         <v>770</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="L214">
-        <v>0</v>
-      </c>
-      <c r="N214" t="s">
-        <v>771</v>
-      </c>
-      <c r="O214" t="s">
-        <v>361</v>
-      </c>
-      <c r="P214" t="s">
-        <v>763</v>
-      </c>
-      <c r="Q214" t="s">
-        <v>253</v>
-      </c>
-      <c r="R214" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B215" t="s">
+        <v>771</v>
+      </c>
+      <c r="C215" t="s">
+        <v>772</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="N215" t="s">
         <v>773</v>
       </c>
-      <c r="C215" t="s">
+      <c r="O215" t="s">
+        <v>359</v>
+      </c>
+      <c r="P215" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>251</v>
+      </c>
+      <c r="R215" t="s">
         <v>774</v>
-      </c>
-      <c r="D215">
-        <v>0</v>
-      </c>
-      <c r="L215">
-        <v>0</v>
-      </c>
-      <c r="N215" t="s">
-        <v>775</v>
-      </c>
-      <c r="O215" t="s">
-        <v>361</v>
-      </c>
-      <c r="P215" t="s">
-        <v>763</v>
-      </c>
-      <c r="Q215" t="s">
-        <v>253</v>
-      </c>
-      <c r="R215" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B216" t="s">
+        <v>775</v>
+      </c>
+      <c r="C216" t="s">
+        <v>776</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="N216" t="s">
         <v>777</v>
       </c>
-      <c r="C216" t="s">
+      <c r="O216" t="s">
+        <v>359</v>
+      </c>
+      <c r="P216" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>251</v>
+      </c>
+      <c r="R216" t="s">
         <v>778</v>
-      </c>
-      <c r="D216">
-        <v>0</v>
-      </c>
-      <c r="L216">
-        <v>0</v>
-      </c>
-      <c r="N216" t="s">
-        <v>779</v>
-      </c>
-      <c r="O216" t="s">
-        <v>361</v>
-      </c>
-      <c r="P216" t="s">
-        <v>763</v>
-      </c>
-      <c r="Q216" t="s">
-        <v>253</v>
-      </c>
-      <c r="R216" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>779</v>
+      </c>
+      <c r="B217" t="s">
+        <v>780</v>
+      </c>
+      <c r="C217" t="s">
         <v>781</v>
-      </c>
-      <c r="B217" t="s">
-        <v>782</v>
-      </c>
-      <c r="C217" t="s">
-        <v>783</v>
       </c>
       <c r="D217">
         <v>25</v>
@@ -10478,209 +10485,209 @@
         <v>33</v>
       </c>
       <c r="N217" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B218" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C218" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D218">
         <v>18</v>
       </c>
       <c r="M218" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="N218" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B219" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C219" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D219">
         <v>15</v>
       </c>
       <c r="M219" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="N219" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B220" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C220" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D220">
         <v>30</v>
       </c>
       <c r="M220" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="N220" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B221" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C221" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="M221" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N221" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B222" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C222" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D222">
         <v>25</v>
       </c>
       <c r="M222" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="N222" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B223" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C223" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D223">
         <v>12</v>
       </c>
       <c r="N223" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B224" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C224" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D224">
         <v>15</v>
       </c>
       <c r="N224" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B225" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C225" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D225">
         <v>8</v>
       </c>
       <c r="N225" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B226" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C226" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D226">
         <v>30</v>
       </c>
       <c r="N226" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B227" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C227" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D227">
         <v>5</v>
       </c>
-      <c r="N227" t="s">
-        <v>819</v>
+      <c r="N227" s="2" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B228" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C228" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D228">
         <v>35</v>
       </c>
       <c r="N228" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8C767D-0E8C-4F66-A7EC-485BF3CF2F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FADD3D-D21B-482E-B953-34D2C78BE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -947,9 +947,6 @@
     <t>貫日之刺</t>
   </si>
   <si>
-    <t>八方連刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
-  </si>
-  <si>
     <t>{"octaToSingle":true,"thrustRangePct":100,"skillDamagePct":100}</t>
   </si>
   <si>
@@ -2519,6 +2516,10 @@
   </si>
   <si>
     <t>每次對敵人造成傷害時，額外回復 {v} 點生命與法力</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3537,7 +3538,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L1" t="s">
         <v>10</v>
@@ -4521,7 +4522,7 @@
         <v>89</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4533,7 +4534,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -4553,7 +4554,7 @@
         <v>91</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D32">
         <v>0.8</v>
@@ -4565,7 +4566,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -6869,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="s">
-        <v>304</v>
+        <v>824</v>
       </c>
       <c r="O104" t="s">
         <v>223</v>
@@ -6881,7 +6882,7 @@
         <v>233</v>
       </c>
       <c r="R104" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
@@ -6889,19 +6890,19 @@
         <v>201</v>
       </c>
       <c r="B105" t="s">
+        <v>305</v>
+      </c>
+      <c r="C105" t="s">
         <v>306</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="N105" t="s">
         <v>307</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="N105" t="s">
-        <v>308</v>
       </c>
       <c r="O105" t="s">
         <v>258</v>
@@ -6913,7 +6914,7 @@
         <v>233</v>
       </c>
       <c r="R105" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -6921,19 +6922,19 @@
         <v>201</v>
       </c>
       <c r="B106" t="s">
+        <v>309</v>
+      </c>
+      <c r="C106" t="s">
         <v>310</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="N106" t="s">
         <v>311</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="N106" t="s">
-        <v>312</v>
       </c>
       <c r="O106" t="s">
         <v>223</v>
@@ -6945,7 +6946,7 @@
         <v>233</v>
       </c>
       <c r="R106" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
@@ -6953,31 +6954,31 @@
         <v>201</v>
       </c>
       <c r="B107" t="s">
+        <v>313</v>
+      </c>
+      <c r="C107" t="s">
         <v>314</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="N107" t="s">
         <v>315</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="N107" t="s">
-        <v>316</v>
       </c>
       <c r="O107" t="s">
         <v>223</v>
       </c>
       <c r="P107" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q107" t="s">
         <v>224</v>
       </c>
       <c r="R107" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
@@ -6985,31 +6986,31 @@
         <v>201</v>
       </c>
       <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
         <v>319</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="N108" t="s">
         <v>320</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="N108" t="s">
-        <v>321</v>
       </c>
       <c r="O108" t="s">
         <v>223</v>
       </c>
       <c r="P108" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q108" t="s">
         <v>224</v>
       </c>
       <c r="R108" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
@@ -7017,31 +7018,31 @@
         <v>201</v>
       </c>
       <c r="B109" t="s">
+        <v>322</v>
+      </c>
+      <c r="C109" t="s">
         <v>323</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="N109" t="s">
         <v>324</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="N109" t="s">
-        <v>325</v>
       </c>
       <c r="O109" t="s">
         <v>223</v>
       </c>
       <c r="P109" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q109" t="s">
         <v>224</v>
       </c>
       <c r="R109" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
@@ -7049,31 +7050,31 @@
         <v>201</v>
       </c>
       <c r="B110" t="s">
+        <v>326</v>
+      </c>
+      <c r="C110" t="s">
         <v>327</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="N110" t="s">
         <v>328</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="N110" t="s">
-        <v>329</v>
       </c>
       <c r="O110" t="s">
         <v>223</v>
       </c>
       <c r="P110" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q110" t="s">
         <v>224</v>
       </c>
       <c r="R110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
@@ -7081,31 +7082,31 @@
         <v>201</v>
       </c>
       <c r="B111" t="s">
+        <v>330</v>
+      </c>
+      <c r="C111" t="s">
         <v>331</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="N111" t="s">
         <v>332</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="N111" t="s">
-        <v>333</v>
       </c>
       <c r="O111" t="s">
         <v>223</v>
       </c>
       <c r="P111" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q111" t="s">
         <v>224</v>
       </c>
       <c r="R111" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
@@ -7113,31 +7114,31 @@
         <v>201</v>
       </c>
       <c r="B112" t="s">
+        <v>334</v>
+      </c>
+      <c r="C112" t="s">
         <v>335</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="N112" t="s">
         <v>336</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="N112" t="s">
-        <v>337</v>
       </c>
       <c r="O112" t="s">
         <v>223</v>
       </c>
       <c r="P112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q112" t="s">
         <v>233</v>
       </c>
       <c r="R112" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
@@ -7145,31 +7146,31 @@
         <v>201</v>
       </c>
       <c r="B113" t="s">
+        <v>339</v>
+      </c>
+      <c r="C113" t="s">
         <v>340</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="N113" t="s">
         <v>341</v>
-      </c>
-      <c r="D113">
-        <v>0</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="N113" t="s">
-        <v>342</v>
       </c>
       <c r="O113" t="s">
         <v>223</v>
       </c>
       <c r="P113" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q113" t="s">
         <v>233</v>
       </c>
       <c r="R113" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -7177,31 +7178,31 @@
         <v>201</v>
       </c>
       <c r="B114" t="s">
+        <v>343</v>
+      </c>
+      <c r="C114" t="s">
         <v>344</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="N114" t="s">
         <v>345</v>
-      </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="N114" t="s">
-        <v>346</v>
       </c>
       <c r="O114" t="s">
         <v>223</v>
       </c>
       <c r="P114" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q114" t="s">
         <v>233</v>
       </c>
       <c r="R114" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
@@ -7209,31 +7210,31 @@
         <v>201</v>
       </c>
       <c r="B115" t="s">
+        <v>347</v>
+      </c>
+      <c r="C115" t="s">
         <v>348</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="N115" t="s">
         <v>349</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="N115" t="s">
-        <v>350</v>
       </c>
       <c r="O115" t="s">
         <v>223</v>
       </c>
       <c r="P115" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q115" t="s">
         <v>233</v>
       </c>
       <c r="R115" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
@@ -7241,31 +7242,31 @@
         <v>201</v>
       </c>
       <c r="B116" t="s">
+        <v>351</v>
+      </c>
+      <c r="C116" t="s">
         <v>352</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="N116" t="s">
         <v>353</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="N116" t="s">
-        <v>354</v>
       </c>
       <c r="O116" t="s">
         <v>223</v>
       </c>
       <c r="P116" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q116" t="s">
         <v>233</v>
       </c>
       <c r="R116" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
@@ -7273,31 +7274,31 @@
         <v>201</v>
       </c>
       <c r="B117" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117" t="s">
         <v>356</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="N117" t="s">
         <v>357</v>
       </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="N117" t="s">
+      <c r="O117" t="s">
         <v>358</v>
       </c>
-      <c r="O117" t="s">
+      <c r="P117" t="s">
         <v>359</v>
-      </c>
-      <c r="P117" t="s">
-        <v>360</v>
       </c>
       <c r="Q117" t="s">
         <v>247</v>
       </c>
       <c r="R117" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
@@ -7305,31 +7306,31 @@
         <v>201</v>
       </c>
       <c r="B118" t="s">
+        <v>361</v>
+      </c>
+      <c r="C118" t="s">
         <v>362</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="N118" t="s">
         <v>363</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="N118" t="s">
-        <v>364</v>
       </c>
       <c r="O118" t="s">
         <v>223</v>
       </c>
       <c r="P118" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q118" t="s">
         <v>247</v>
       </c>
       <c r="R118" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -7337,31 +7338,31 @@
         <v>201</v>
       </c>
       <c r="B119" t="s">
+        <v>365</v>
+      </c>
+      <c r="C119" t="s">
         <v>366</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
         <v>367</v>
-      </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="N119" t="s">
-        <v>368</v>
       </c>
       <c r="O119" t="s">
         <v>223</v>
       </c>
       <c r="P119" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q119" t="s">
         <v>247</v>
       </c>
       <c r="R119" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
@@ -7369,31 +7370,31 @@
         <v>201</v>
       </c>
       <c r="B120" t="s">
+        <v>369</v>
+      </c>
+      <c r="C120" t="s">
         <v>370</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="N120" t="s">
         <v>371</v>
       </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="N120" t="s">
-        <v>372</v>
-      </c>
       <c r="O120" t="s">
+        <v>358</v>
+      </c>
+      <c r="P120" t="s">
         <v>359</v>
-      </c>
-      <c r="P120" t="s">
-        <v>360</v>
       </c>
       <c r="Q120" t="s">
         <v>247</v>
       </c>
       <c r="R120" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
@@ -7401,31 +7402,31 @@
         <v>201</v>
       </c>
       <c r="B121" t="s">
+        <v>373</v>
+      </c>
+      <c r="C121" t="s">
         <v>374</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="N121" t="s">
         <v>375</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="N121" t="s">
-        <v>376</v>
       </c>
       <c r="O121" t="s">
         <v>223</v>
       </c>
       <c r="P121" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q121" t="s">
         <v>247</v>
       </c>
       <c r="R121" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -7433,31 +7434,31 @@
         <v>201</v>
       </c>
       <c r="B122" t="s">
+        <v>377</v>
+      </c>
+      <c r="C122" t="s">
         <v>378</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="N122" t="s">
         <v>379</v>
-      </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="N122" t="s">
-        <v>380</v>
       </c>
       <c r="O122" t="s">
         <v>283</v>
       </c>
       <c r="P122" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q122" t="s">
         <v>381</v>
       </c>
-      <c r="Q122" t="s">
+      <c r="R122" t="s">
         <v>382</v>
-      </c>
-      <c r="R122" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -7465,31 +7466,31 @@
         <v>201</v>
       </c>
       <c r="B123" t="s">
+        <v>383</v>
+      </c>
+      <c r="C123" t="s">
         <v>384</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="N123" t="s">
         <v>385</v>
-      </c>
-      <c r="D123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="N123" t="s">
-        <v>386</v>
       </c>
       <c r="O123" t="s">
         <v>283</v>
       </c>
       <c r="P123" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q123" t="s">
         <v>381</v>
       </c>
-      <c r="Q123" t="s">
-        <v>382</v>
-      </c>
       <c r="R123" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
@@ -7497,31 +7498,31 @@
         <v>201</v>
       </c>
       <c r="B124" t="s">
+        <v>387</v>
+      </c>
+      <c r="C124" t="s">
         <v>388</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="N124" t="s">
         <v>389</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="N124" t="s">
-        <v>390</v>
       </c>
       <c r="O124" t="s">
         <v>223</v>
       </c>
       <c r="P124" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q124" t="s">
         <v>381</v>
       </c>
-      <c r="Q124" t="s">
-        <v>382</v>
-      </c>
       <c r="R124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
@@ -7529,31 +7530,31 @@
         <v>201</v>
       </c>
       <c r="B125" t="s">
+        <v>391</v>
+      </c>
+      <c r="C125" t="s">
         <v>392</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="N125" t="s">
         <v>393</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="N125" t="s">
-        <v>394</v>
       </c>
       <c r="O125" t="s">
         <v>223</v>
       </c>
       <c r="P125" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q125" t="s">
         <v>381</v>
       </c>
-      <c r="Q125" t="s">
-        <v>382</v>
-      </c>
       <c r="R125" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
@@ -7561,31 +7562,31 @@
         <v>201</v>
       </c>
       <c r="B126" t="s">
+        <v>395</v>
+      </c>
+      <c r="C126" t="s">
         <v>396</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="N126" t="s">
         <v>397</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="N126" t="s">
-        <v>398</v>
       </c>
       <c r="O126" t="s">
         <v>223</v>
       </c>
       <c r="P126" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q126" t="s">
         <v>381</v>
       </c>
-      <c r="Q126" t="s">
-        <v>382</v>
-      </c>
       <c r="R126" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
@@ -7593,31 +7594,31 @@
         <v>201</v>
       </c>
       <c r="B127" t="s">
+        <v>399</v>
+      </c>
+      <c r="C127" t="s">
         <v>400</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="N127" t="s">
         <v>401</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="N127" t="s">
-        <v>402</v>
       </c>
       <c r="O127" t="s">
         <v>223</v>
       </c>
       <c r="P127" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q127" t="s">
         <v>253</v>
       </c>
       <c r="R127" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
@@ -7625,31 +7626,31 @@
         <v>201</v>
       </c>
       <c r="B128" t="s">
+        <v>404</v>
+      </c>
+      <c r="C128" t="s">
         <v>405</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="N128" t="s">
         <v>406</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="N128" t="s">
-        <v>407</v>
       </c>
       <c r="O128" t="s">
         <v>223</v>
       </c>
       <c r="P128" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q128" t="s">
         <v>253</v>
       </c>
       <c r="R128" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
@@ -7657,31 +7658,31 @@
         <v>201</v>
       </c>
       <c r="B129" t="s">
+        <v>408</v>
+      </c>
+      <c r="C129" t="s">
         <v>409</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="N129" t="s">
         <v>410</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="N129" t="s">
-        <v>411</v>
       </c>
       <c r="O129" t="s">
         <v>223</v>
       </c>
       <c r="P129" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q129" t="s">
         <v>253</v>
       </c>
       <c r="R129" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
@@ -7689,31 +7690,31 @@
         <v>201</v>
       </c>
       <c r="B130" t="s">
+        <v>412</v>
+      </c>
+      <c r="C130" t="s">
         <v>413</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="N130" t="s">
         <v>414</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="N130" t="s">
-        <v>415</v>
       </c>
       <c r="O130" t="s">
         <v>223</v>
       </c>
       <c r="P130" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q130" t="s">
         <v>253</v>
       </c>
       <c r="R130" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
@@ -7721,31 +7722,31 @@
         <v>201</v>
       </c>
       <c r="B131" t="s">
+        <v>416</v>
+      </c>
+      <c r="C131" t="s">
         <v>417</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="N131" t="s">
         <v>418</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="N131" t="s">
-        <v>419</v>
       </c>
       <c r="O131" t="s">
         <v>223</v>
       </c>
       <c r="P131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q131" t="s">
         <v>253</v>
       </c>
       <c r="R131" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
@@ -7753,31 +7754,31 @@
         <v>201</v>
       </c>
       <c r="B132" t="s">
+        <v>420</v>
+      </c>
+      <c r="C132" t="s">
         <v>421</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="N132" t="s">
         <v>422</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="N132" t="s">
-        <v>423</v>
       </c>
       <c r="O132" t="s">
         <v>223</v>
       </c>
       <c r="P132" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q132" t="s">
         <v>251</v>
       </c>
       <c r="R132" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
@@ -7785,31 +7786,31 @@
         <v>201</v>
       </c>
       <c r="B133" t="s">
+        <v>425</v>
+      </c>
+      <c r="C133" t="s">
         <v>426</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="N133" t="s">
         <v>427</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="N133" t="s">
-        <v>428</v>
       </c>
       <c r="O133" t="s">
         <v>223</v>
       </c>
       <c r="P133" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q133" t="s">
         <v>251</v>
       </c>
       <c r="R133" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
@@ -7817,31 +7818,31 @@
         <v>201</v>
       </c>
       <c r="B134" t="s">
+        <v>429</v>
+      </c>
+      <c r="C134" t="s">
         <v>430</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="N134" t="s">
         <v>431</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="N134" t="s">
-        <v>432</v>
       </c>
       <c r="O134" t="s">
         <v>223</v>
       </c>
       <c r="P134" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q134" t="s">
         <v>251</v>
       </c>
       <c r="R134" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
@@ -7849,31 +7850,31 @@
         <v>201</v>
       </c>
       <c r="B135" t="s">
+        <v>433</v>
+      </c>
+      <c r="C135" t="s">
         <v>434</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="N135" t="s">
         <v>435</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="N135" t="s">
-        <v>436</v>
       </c>
       <c r="O135" t="s">
         <v>223</v>
       </c>
       <c r="P135" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q135" t="s">
         <v>251</v>
       </c>
       <c r="R135" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
@@ -7881,31 +7882,31 @@
         <v>201</v>
       </c>
       <c r="B136" t="s">
+        <v>437</v>
+      </c>
+      <c r="C136" t="s">
         <v>438</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="N136" t="s">
         <v>439</v>
       </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="N136" t="s">
-        <v>440</v>
-      </c>
       <c r="O136" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P136" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q136" t="s">
         <v>251</v>
       </c>
       <c r="R136" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
@@ -7913,31 +7914,31 @@
         <v>201</v>
       </c>
       <c r="B137" t="s">
+        <v>441</v>
+      </c>
+      <c r="C137" t="s">
         <v>442</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="N137" t="s">
         <v>443</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="N137" t="s">
-        <v>444</v>
       </c>
       <c r="O137" t="s">
         <v>223</v>
       </c>
       <c r="P137" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q137" t="s">
         <v>253</v>
       </c>
       <c r="R137" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
@@ -7945,31 +7946,31 @@
         <v>201</v>
       </c>
       <c r="B138" t="s">
+        <v>446</v>
+      </c>
+      <c r="C138" t="s">
         <v>447</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="N138" t="s">
         <v>448</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="N138" t="s">
-        <v>449</v>
       </c>
       <c r="O138" t="s">
         <v>223</v>
       </c>
       <c r="P138" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q138" t="s">
         <v>253</v>
       </c>
       <c r="R138" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
@@ -7977,31 +7978,31 @@
         <v>201</v>
       </c>
       <c r="B139" t="s">
+        <v>450</v>
+      </c>
+      <c r="C139" t="s">
         <v>451</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="N139" t="s">
         <v>452</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="N139" t="s">
-        <v>453</v>
       </c>
       <c r="O139" t="s">
         <v>223</v>
       </c>
       <c r="P139" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q139" t="s">
         <v>253</v>
       </c>
       <c r="R139" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
@@ -8009,31 +8010,31 @@
         <v>201</v>
       </c>
       <c r="B140" t="s">
+        <v>454</v>
+      </c>
+      <c r="C140" t="s">
         <v>455</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="N140" t="s">
         <v>456</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="N140" t="s">
-        <v>457</v>
       </c>
       <c r="O140" t="s">
         <v>223</v>
       </c>
       <c r="P140" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q140" t="s">
         <v>253</v>
       </c>
       <c r="R140" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
@@ -8041,31 +8042,31 @@
         <v>201</v>
       </c>
       <c r="B141" t="s">
+        <v>458</v>
+      </c>
+      <c r="C141" t="s">
         <v>459</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="N141" t="s">
         <v>460</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="N141" t="s">
-        <v>461</v>
       </c>
       <c r="O141" t="s">
         <v>223</v>
       </c>
       <c r="P141" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q141" t="s">
         <v>253</v>
       </c>
       <c r="R141" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -8073,31 +8074,31 @@
         <v>201</v>
       </c>
       <c r="B142" t="s">
+        <v>462</v>
+      </c>
+      <c r="C142" t="s">
         <v>463</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="N142" t="s">
         <v>464</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="N142" t="s">
-        <v>465</v>
       </c>
       <c r="O142" t="s">
         <v>267</v>
       </c>
       <c r="P142" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q142" t="s">
         <v>259</v>
       </c>
       <c r="R142" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
@@ -8105,31 +8106,31 @@
         <v>201</v>
       </c>
       <c r="B143" t="s">
+        <v>467</v>
+      </c>
+      <c r="C143" t="s">
         <v>468</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="N143" t="s">
         <v>469</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="N143" t="s">
-        <v>470</v>
       </c>
       <c r="O143" t="s">
         <v>267</v>
       </c>
       <c r="P143" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q143" t="s">
         <v>259</v>
       </c>
       <c r="R143" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
@@ -8137,31 +8138,31 @@
         <v>201</v>
       </c>
       <c r="B144" t="s">
+        <v>471</v>
+      </c>
+      <c r="C144" t="s">
         <v>472</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="N144" t="s">
         <v>473</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="N144" t="s">
-        <v>474</v>
       </c>
       <c r="O144" t="s">
         <v>267</v>
       </c>
       <c r="P144" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q144" t="s">
         <v>259</v>
       </c>
       <c r="R144" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
@@ -8169,31 +8170,31 @@
         <v>201</v>
       </c>
       <c r="B145" t="s">
+        <v>475</v>
+      </c>
+      <c r="C145" t="s">
         <v>476</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="N145" t="s">
         <v>477</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="N145" t="s">
-        <v>478</v>
       </c>
       <c r="O145" t="s">
         <v>267</v>
       </c>
       <c r="P145" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q145" t="s">
         <v>259</v>
       </c>
       <c r="R145" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
@@ -8201,31 +8202,31 @@
         <v>201</v>
       </c>
       <c r="B146" t="s">
+        <v>479</v>
+      </c>
+      <c r="C146" t="s">
         <v>480</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="N146" t="s">
         <v>481</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="N146" t="s">
-        <v>482</v>
       </c>
       <c r="O146" t="s">
         <v>267</v>
       </c>
       <c r="P146" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q146" t="s">
         <v>259</v>
       </c>
       <c r="R146" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
@@ -8233,31 +8234,31 @@
         <v>201</v>
       </c>
       <c r="B147" t="s">
+        <v>483</v>
+      </c>
+      <c r="C147" t="s">
         <v>484</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="N147" t="s">
         <v>485</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="N147" t="s">
-        <v>486</v>
       </c>
       <c r="O147" t="s">
         <v>267</v>
       </c>
       <c r="P147" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q147" t="s">
         <v>256</v>
       </c>
       <c r="R147" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
@@ -8265,31 +8266,31 @@
         <v>201</v>
       </c>
       <c r="B148" t="s">
+        <v>488</v>
+      </c>
+      <c r="C148" t="s">
         <v>489</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="N148" t="s">
         <v>490</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="N148" t="s">
-        <v>491</v>
       </c>
       <c r="O148" t="s">
         <v>267</v>
       </c>
       <c r="P148" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q148" t="s">
         <v>256</v>
       </c>
       <c r="R148" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
@@ -8297,31 +8298,31 @@
         <v>201</v>
       </c>
       <c r="B149" t="s">
+        <v>492</v>
+      </c>
+      <c r="C149" t="s">
         <v>493</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="N149" t="s">
         <v>494</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="N149" t="s">
-        <v>495</v>
       </c>
       <c r="O149" t="s">
         <v>267</v>
       </c>
       <c r="P149" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q149" t="s">
         <v>256</v>
       </c>
       <c r="R149" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
@@ -8329,31 +8330,31 @@
         <v>201</v>
       </c>
       <c r="B150" t="s">
+        <v>496</v>
+      </c>
+      <c r="C150" t="s">
         <v>497</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="N150" t="s">
         <v>498</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="N150" t="s">
-        <v>499</v>
       </c>
       <c r="O150" t="s">
         <v>267</v>
       </c>
       <c r="P150" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q150" t="s">
         <v>256</v>
       </c>
       <c r="R150" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
@@ -8361,31 +8362,31 @@
         <v>201</v>
       </c>
       <c r="B151" t="s">
+        <v>500</v>
+      </c>
+      <c r="C151" t="s">
         <v>501</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="N151" t="s">
         <v>502</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="N151" t="s">
-        <v>503</v>
       </c>
       <c r="O151" t="s">
         <v>267</v>
       </c>
       <c r="P151" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q151" t="s">
         <v>256</v>
       </c>
       <c r="R151" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
@@ -8393,31 +8394,31 @@
         <v>201</v>
       </c>
       <c r="B152" t="s">
+        <v>504</v>
+      </c>
+      <c r="C152" t="s">
         <v>505</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="N152" t="s">
         <v>506</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="N152" t="s">
-        <v>507</v>
       </c>
       <c r="O152" t="s">
         <v>267</v>
       </c>
       <c r="P152" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q152" t="s">
         <v>257</v>
       </c>
       <c r="R152" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
@@ -8425,31 +8426,31 @@
         <v>201</v>
       </c>
       <c r="B153" t="s">
+        <v>509</v>
+      </c>
+      <c r="C153" t="s">
         <v>510</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="N153" t="s">
         <v>511</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="N153" t="s">
-        <v>512</v>
       </c>
       <c r="O153" t="s">
         <v>267</v>
       </c>
       <c r="P153" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q153" t="s">
         <v>257</v>
       </c>
       <c r="R153" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
@@ -8457,31 +8458,31 @@
         <v>201</v>
       </c>
       <c r="B154" t="s">
+        <v>513</v>
+      </c>
+      <c r="C154" t="s">
         <v>514</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="N154" t="s">
         <v>515</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="N154" t="s">
-        <v>516</v>
       </c>
       <c r="O154" t="s">
         <v>267</v>
       </c>
       <c r="P154" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q154" t="s">
         <v>257</v>
       </c>
       <c r="R154" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
@@ -8489,31 +8490,31 @@
         <v>201</v>
       </c>
       <c r="B155" t="s">
+        <v>517</v>
+      </c>
+      <c r="C155" t="s">
         <v>518</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="N155" t="s">
         <v>519</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="N155" t="s">
-        <v>520</v>
       </c>
       <c r="O155" t="s">
         <v>267</v>
       </c>
       <c r="P155" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q155" t="s">
         <v>257</v>
       </c>
       <c r="R155" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
@@ -8521,31 +8522,31 @@
         <v>201</v>
       </c>
       <c r="B156" t="s">
+        <v>521</v>
+      </c>
+      <c r="C156" t="s">
         <v>522</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="N156" t="s">
         <v>523</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="N156" t="s">
-        <v>524</v>
       </c>
       <c r="O156" t="s">
         <v>267</v>
       </c>
       <c r="P156" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q156" t="s">
         <v>257</v>
       </c>
       <c r="R156" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
@@ -8553,31 +8554,31 @@
         <v>201</v>
       </c>
       <c r="B157" t="s">
+        <v>525</v>
+      </c>
+      <c r="C157" t="s">
         <v>526</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="N157" t="s">
         <v>527</v>
       </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="N157" t="s">
+      <c r="O157" t="s">
         <v>528</v>
       </c>
-      <c r="O157" t="s">
+      <c r="P157" t="s">
         <v>529</v>
-      </c>
-      <c r="P157" t="s">
-        <v>530</v>
       </c>
       <c r="Q157" t="s">
         <v>255</v>
       </c>
       <c r="R157" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
@@ -8585,31 +8586,31 @@
         <v>201</v>
       </c>
       <c r="B158" t="s">
+        <v>531</v>
+      </c>
+      <c r="C158" t="s">
         <v>532</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="N158" t="s">
         <v>533</v>
       </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="N158" t="s">
-        <v>534</v>
-      </c>
       <c r="O158" t="s">
+        <v>528</v>
+      </c>
+      <c r="P158" t="s">
         <v>529</v>
-      </c>
-      <c r="P158" t="s">
-        <v>530</v>
       </c>
       <c r="Q158" t="s">
         <v>255</v>
       </c>
       <c r="R158" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
@@ -8617,31 +8618,31 @@
         <v>201</v>
       </c>
       <c r="B159" t="s">
+        <v>535</v>
+      </c>
+      <c r="C159" t="s">
         <v>536</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="N159" t="s">
         <v>537</v>
       </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="N159" t="s">
-        <v>538</v>
-      </c>
       <c r="O159" t="s">
+        <v>528</v>
+      </c>
+      <c r="P159" t="s">
         <v>529</v>
-      </c>
-      <c r="P159" t="s">
-        <v>530</v>
       </c>
       <c r="Q159" t="s">
         <v>255</v>
       </c>
       <c r="R159" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
@@ -8649,31 +8650,31 @@
         <v>201</v>
       </c>
       <c r="B160" t="s">
+        <v>539</v>
+      </c>
+      <c r="C160" t="s">
         <v>540</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="N160" t="s">
         <v>541</v>
       </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="N160" t="s">
-        <v>542</v>
-      </c>
       <c r="O160" t="s">
+        <v>528</v>
+      </c>
+      <c r="P160" t="s">
         <v>529</v>
-      </c>
-      <c r="P160" t="s">
-        <v>530</v>
       </c>
       <c r="Q160" t="s">
         <v>255</v>
       </c>
       <c r="R160" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
@@ -8681,31 +8682,31 @@
         <v>201</v>
       </c>
       <c r="B161" t="s">
+        <v>543</v>
+      </c>
+      <c r="C161" t="s">
         <v>544</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="N161" t="s">
         <v>545</v>
       </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="N161" t="s">
-        <v>546</v>
-      </c>
       <c r="O161" t="s">
+        <v>528</v>
+      </c>
+      <c r="P161" t="s">
         <v>529</v>
-      </c>
-      <c r="P161" t="s">
-        <v>530</v>
       </c>
       <c r="Q161" t="s">
         <v>255</v>
       </c>
       <c r="R161" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
@@ -8713,31 +8714,31 @@
         <v>201</v>
       </c>
       <c r="B162" t="s">
+        <v>547</v>
+      </c>
+      <c r="C162" t="s">
         <v>548</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="N162" t="s">
         <v>549</v>
       </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="N162" t="s">
+      <c r="O162" t="s">
+        <v>528</v>
+      </c>
+      <c r="P162" t="s">
         <v>550</v>
-      </c>
-      <c r="O162" t="s">
-        <v>529</v>
-      </c>
-      <c r="P162" t="s">
-        <v>551</v>
       </c>
       <c r="Q162" t="s">
         <v>247</v>
       </c>
       <c r="R162" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
@@ -8745,31 +8746,31 @@
         <v>201</v>
       </c>
       <c r="B163" t="s">
+        <v>552</v>
+      </c>
+      <c r="C163" t="s">
         <v>553</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="N163" t="s">
         <v>554</v>
       </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="N163" t="s">
-        <v>555</v>
-      </c>
       <c r="O163" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P163" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q163" t="s">
         <v>247</v>
       </c>
       <c r="R163" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
@@ -8777,31 +8778,31 @@
         <v>201</v>
       </c>
       <c r="B164" t="s">
+        <v>556</v>
+      </c>
+      <c r="C164" t="s">
         <v>557</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="N164" t="s">
         <v>558</v>
       </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="N164" t="s">
-        <v>559</v>
-      </c>
       <c r="O164" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P164" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q164" t="s">
         <v>247</v>
       </c>
       <c r="R164" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
@@ -8809,31 +8810,31 @@
         <v>201</v>
       </c>
       <c r="B165" t="s">
+        <v>560</v>
+      </c>
+      <c r="C165" t="s">
         <v>561</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="N165" t="s">
         <v>562</v>
       </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="N165" t="s">
-        <v>563</v>
-      </c>
       <c r="O165" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P165" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q165" t="s">
         <v>247</v>
       </c>
       <c r="R165" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
@@ -8841,31 +8842,31 @@
         <v>201</v>
       </c>
       <c r="B166" t="s">
+        <v>564</v>
+      </c>
+      <c r="C166" t="s">
         <v>565</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="N166" t="s">
         <v>566</v>
       </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="N166" t="s">
-        <v>567</v>
-      </c>
       <c r="O166" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q166" t="s">
         <v>247</v>
       </c>
       <c r="R166" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
@@ -8873,31 +8874,31 @@
         <v>201</v>
       </c>
       <c r="B167" t="s">
+        <v>568</v>
+      </c>
+      <c r="C167" t="s">
         <v>569</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="N167" t="s">
         <v>570</v>
       </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="O167" t="s">
+        <v>528</v>
+      </c>
+      <c r="P167" t="s">
         <v>571</v>
-      </c>
-      <c r="O167" t="s">
-        <v>529</v>
-      </c>
-      <c r="P167" t="s">
-        <v>572</v>
       </c>
       <c r="Q167" t="s">
         <v>251</v>
       </c>
       <c r="R167" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
@@ -8905,31 +8906,31 @@
         <v>201</v>
       </c>
       <c r="B168" t="s">
+        <v>573</v>
+      </c>
+      <c r="C168" t="s">
         <v>574</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="N168" t="s">
         <v>575</v>
       </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="N168" t="s">
-        <v>576</v>
-      </c>
       <c r="O168" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P168" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q168" t="s">
         <v>251</v>
       </c>
       <c r="R168" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
@@ -8937,31 +8938,31 @@
         <v>201</v>
       </c>
       <c r="B169" t="s">
+        <v>577</v>
+      </c>
+      <c r="C169" t="s">
         <v>578</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="N169" t="s">
         <v>579</v>
       </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="N169" t="s">
-        <v>580</v>
-      </c>
       <c r="O169" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P169" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q169" t="s">
         <v>251</v>
       </c>
       <c r="R169" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
@@ -8969,31 +8970,31 @@
         <v>201</v>
       </c>
       <c r="B170" t="s">
+        <v>581</v>
+      </c>
+      <c r="C170" t="s">
         <v>582</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="N170" t="s">
         <v>583</v>
       </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="N170" t="s">
-        <v>584</v>
-      </c>
       <c r="O170" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P170" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q170" t="s">
         <v>251</v>
       </c>
       <c r="R170" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
@@ -9001,31 +9002,31 @@
         <v>201</v>
       </c>
       <c r="B171" t="s">
+        <v>585</v>
+      </c>
+      <c r="C171" t="s">
         <v>586</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="N171" t="s">
         <v>587</v>
       </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="L171">
-        <v>0</v>
-      </c>
-      <c r="N171" t="s">
-        <v>588</v>
-      </c>
       <c r="O171" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P171" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q171" t="s">
         <v>251</v>
       </c>
       <c r="R171" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
@@ -9033,31 +9034,31 @@
         <v>201</v>
       </c>
       <c r="B172" t="s">
+        <v>589</v>
+      </c>
+      <c r="C172" t="s">
         <v>590</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="N172" t="s">
         <v>591</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-      <c r="N172" t="s">
-        <v>592</v>
       </c>
       <c r="O172" t="s">
         <v>258</v>
       </c>
       <c r="P172" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q172" t="s">
         <v>224</v>
       </c>
       <c r="R172" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
@@ -9065,31 +9066,31 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>594</v>
+      </c>
+      <c r="C173" t="s">
         <v>595</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="N173" t="s">
         <v>596</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="L173">
-        <v>0</v>
-      </c>
-      <c r="N173" t="s">
-        <v>597</v>
       </c>
       <c r="O173" t="s">
         <v>258</v>
       </c>
       <c r="P173" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q173" t="s">
         <v>224</v>
       </c>
       <c r="R173" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
@@ -9097,31 +9098,31 @@
         <v>201</v>
       </c>
       <c r="B174" t="s">
+        <v>598</v>
+      </c>
+      <c r="C174" t="s">
         <v>599</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="N174" t="s">
         <v>600</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-      <c r="N174" t="s">
-        <v>601</v>
       </c>
       <c r="O174" t="s">
         <v>258</v>
       </c>
       <c r="P174" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q174" t="s">
         <v>224</v>
       </c>
       <c r="R174" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
@@ -9129,31 +9130,31 @@
         <v>201</v>
       </c>
       <c r="B175" t="s">
+        <v>602</v>
+      </c>
+      <c r="C175" t="s">
         <v>603</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="N175" t="s">
         <v>604</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="L175">
-        <v>0</v>
-      </c>
-      <c r="N175" t="s">
-        <v>605</v>
       </c>
       <c r="O175" t="s">
         <v>258</v>
       </c>
       <c r="P175" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q175" t="s">
         <v>224</v>
       </c>
       <c r="R175" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
@@ -9161,31 +9162,31 @@
         <v>201</v>
       </c>
       <c r="B176" t="s">
+        <v>606</v>
+      </c>
+      <c r="C176" t="s">
         <v>607</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="N176" t="s">
         <v>608</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="L176">
-        <v>0</v>
-      </c>
-      <c r="N176" t="s">
-        <v>609</v>
       </c>
       <c r="O176" t="s">
         <v>258</v>
       </c>
       <c r="P176" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q176" t="s">
         <v>224</v>
       </c>
       <c r="R176" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
@@ -9193,31 +9194,31 @@
         <v>201</v>
       </c>
       <c r="B177" t="s">
+        <v>610</v>
+      </c>
+      <c r="C177" t="s">
         <v>611</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="N177" t="s">
         <v>612</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-      <c r="N177" t="s">
-        <v>613</v>
       </c>
       <c r="O177" t="s">
         <v>258</v>
       </c>
       <c r="P177" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q177" t="s">
         <v>259</v>
       </c>
       <c r="R177" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
@@ -9225,31 +9226,31 @@
         <v>201</v>
       </c>
       <c r="B178" t="s">
+        <v>615</v>
+      </c>
+      <c r="C178" t="s">
         <v>616</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="N178" t="s">
         <v>617</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="L178">
-        <v>0</v>
-      </c>
-      <c r="N178" t="s">
-        <v>618</v>
       </c>
       <c r="O178" t="s">
         <v>258</v>
       </c>
       <c r="P178" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q178" t="s">
         <v>259</v>
       </c>
       <c r="R178" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
@@ -9257,31 +9258,31 @@
         <v>201</v>
       </c>
       <c r="B179" t="s">
+        <v>619</v>
+      </c>
+      <c r="C179" t="s">
         <v>620</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="N179" t="s">
         <v>621</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-      <c r="N179" t="s">
-        <v>622</v>
       </c>
       <c r="O179" t="s">
         <v>258</v>
       </c>
       <c r="P179" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q179" t="s">
         <v>259</v>
       </c>
       <c r="R179" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
@@ -9289,31 +9290,31 @@
         <v>201</v>
       </c>
       <c r="B180" t="s">
+        <v>623</v>
+      </c>
+      <c r="C180" t="s">
         <v>624</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="N180" t="s">
         <v>625</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="N180" t="s">
-        <v>626</v>
       </c>
       <c r="O180" t="s">
         <v>258</v>
       </c>
       <c r="P180" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q180" t="s">
         <v>259</v>
       </c>
       <c r="R180" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
@@ -9321,31 +9322,31 @@
         <v>201</v>
       </c>
       <c r="B181" t="s">
+        <v>627</v>
+      </c>
+      <c r="C181" t="s">
         <v>628</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="N181" t="s">
         <v>629</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="L181">
-        <v>0</v>
-      </c>
-      <c r="N181" t="s">
-        <v>630</v>
       </c>
       <c r="O181" t="s">
         <v>258</v>
       </c>
       <c r="P181" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q181" t="s">
         <v>259</v>
       </c>
       <c r="R181" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
@@ -9353,31 +9354,31 @@
         <v>201</v>
       </c>
       <c r="B182" t="s">
+        <v>631</v>
+      </c>
+      <c r="C182" t="s">
         <v>632</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="N182" t="s">
         <v>633</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="N182" t="s">
-        <v>634</v>
       </c>
       <c r="O182" t="s">
         <v>258</v>
       </c>
       <c r="P182" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q182" t="s">
         <v>257</v>
       </c>
       <c r="R182" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
@@ -9385,31 +9386,31 @@
         <v>201</v>
       </c>
       <c r="B183" t="s">
+        <v>636</v>
+      </c>
+      <c r="C183" t="s">
         <v>637</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="N183" t="s">
         <v>638</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="L183">
-        <v>0</v>
-      </c>
-      <c r="N183" t="s">
-        <v>639</v>
       </c>
       <c r="O183" t="s">
         <v>258</v>
       </c>
       <c r="P183" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q183" t="s">
         <v>257</v>
       </c>
       <c r="R183" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
@@ -9417,31 +9418,31 @@
         <v>201</v>
       </c>
       <c r="B184" t="s">
+        <v>640</v>
+      </c>
+      <c r="C184" t="s">
         <v>641</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="N184" t="s">
         <v>642</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="N184" t="s">
-        <v>643</v>
       </c>
       <c r="O184" t="s">
         <v>258</v>
       </c>
       <c r="P184" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q184" t="s">
         <v>257</v>
       </c>
       <c r="R184" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
@@ -9449,31 +9450,31 @@
         <v>201</v>
       </c>
       <c r="B185" t="s">
+        <v>644</v>
+      </c>
+      <c r="C185" t="s">
         <v>645</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="N185" t="s">
         <v>646</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="N185" t="s">
-        <v>647</v>
       </c>
       <c r="O185" t="s">
         <v>258</v>
       </c>
       <c r="P185" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q185" t="s">
         <v>257</v>
       </c>
       <c r="R185" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
@@ -9481,31 +9482,31 @@
         <v>201</v>
       </c>
       <c r="B186" t="s">
+        <v>648</v>
+      </c>
+      <c r="C186" t="s">
         <v>649</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="N186" t="s">
         <v>650</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="L186">
-        <v>0</v>
-      </c>
-      <c r="N186" t="s">
-        <v>651</v>
       </c>
       <c r="O186" t="s">
         <v>258</v>
       </c>
       <c r="P186" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q186" t="s">
         <v>257</v>
       </c>
       <c r="R186" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
@@ -9513,31 +9514,31 @@
         <v>201</v>
       </c>
       <c r="B187" t="s">
+        <v>652</v>
+      </c>
+      <c r="C187" t="s">
         <v>653</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="N187" t="s">
         <v>654</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="L187">
-        <v>0</v>
-      </c>
-      <c r="N187" t="s">
-        <v>655</v>
       </c>
       <c r="O187" t="s">
         <v>254</v>
       </c>
       <c r="P187" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q187" t="s">
         <v>272</v>
       </c>
       <c r="R187" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
@@ -9545,31 +9546,31 @@
         <v>201</v>
       </c>
       <c r="B188" t="s">
+        <v>657</v>
+      </c>
+      <c r="C188" t="s">
         <v>658</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="N188" t="s">
         <v>659</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="L188">
-        <v>0</v>
-      </c>
-      <c r="N188" t="s">
-        <v>660</v>
       </c>
       <c r="O188" t="s">
         <v>254</v>
       </c>
       <c r="P188" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q188" t="s">
         <v>272</v>
       </c>
       <c r="R188" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
@@ -9577,31 +9578,31 @@
         <v>201</v>
       </c>
       <c r="B189" t="s">
+        <v>661</v>
+      </c>
+      <c r="C189" t="s">
         <v>662</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="N189" t="s">
         <v>663</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="L189">
-        <v>0</v>
-      </c>
-      <c r="N189" t="s">
-        <v>664</v>
       </c>
       <c r="O189" t="s">
         <v>254</v>
       </c>
       <c r="P189" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q189" t="s">
         <v>272</v>
       </c>
       <c r="R189" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
@@ -9609,31 +9610,31 @@
         <v>201</v>
       </c>
       <c r="B190" t="s">
+        <v>665</v>
+      </c>
+      <c r="C190" t="s">
         <v>666</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="N190" t="s">
         <v>667</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="L190">
-        <v>0</v>
-      </c>
-      <c r="N190" t="s">
-        <v>668</v>
       </c>
       <c r="O190" t="s">
         <v>254</v>
       </c>
       <c r="P190" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q190" t="s">
         <v>272</v>
       </c>
       <c r="R190" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
@@ -9641,31 +9642,31 @@
         <v>201</v>
       </c>
       <c r="B191" t="s">
+        <v>669</v>
+      </c>
+      <c r="C191" t="s">
         <v>670</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="N191" t="s">
         <v>671</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="L191">
-        <v>0</v>
-      </c>
-      <c r="N191" t="s">
-        <v>672</v>
       </c>
       <c r="O191" t="s">
         <v>254</v>
       </c>
       <c r="P191" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q191" t="s">
         <v>272</v>
       </c>
       <c r="R191" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
@@ -9673,31 +9674,31 @@
         <v>201</v>
       </c>
       <c r="B192" t="s">
+        <v>673</v>
+      </c>
+      <c r="C192" t="s">
         <v>674</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="N192" t="s">
         <v>675</v>
-      </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="L192">
-        <v>0</v>
-      </c>
-      <c r="N192" t="s">
-        <v>676</v>
       </c>
       <c r="O192" t="s">
         <v>254</v>
       </c>
       <c r="P192" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q192" t="s">
         <v>255</v>
       </c>
       <c r="R192" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
@@ -9705,31 +9706,31 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>678</v>
+      </c>
+      <c r="C193" t="s">
         <v>679</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="N193" t="s">
         <v>680</v>
-      </c>
-      <c r="D193">
-        <v>0</v>
-      </c>
-      <c r="L193">
-        <v>0</v>
-      </c>
-      <c r="N193" t="s">
-        <v>681</v>
       </c>
       <c r="O193" t="s">
         <v>254</v>
       </c>
       <c r="P193" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q193" t="s">
         <v>255</v>
       </c>
       <c r="R193" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
@@ -9737,31 +9738,31 @@
         <v>201</v>
       </c>
       <c r="B194" t="s">
+        <v>682</v>
+      </c>
+      <c r="C194" t="s">
         <v>683</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="N194" t="s">
         <v>684</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="L194">
-        <v>0</v>
-      </c>
-      <c r="N194" t="s">
-        <v>685</v>
       </c>
       <c r="O194" t="s">
         <v>254</v>
       </c>
       <c r="P194" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q194" t="s">
         <v>255</v>
       </c>
       <c r="R194" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
@@ -9769,31 +9770,31 @@
         <v>201</v>
       </c>
       <c r="B195" t="s">
+        <v>686</v>
+      </c>
+      <c r="C195" t="s">
         <v>687</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="N195" t="s">
         <v>688</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="L195">
-        <v>0</v>
-      </c>
-      <c r="N195" t="s">
-        <v>689</v>
       </c>
       <c r="O195" t="s">
         <v>254</v>
       </c>
       <c r="P195" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q195" t="s">
         <v>255</v>
       </c>
       <c r="R195" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
@@ -9801,31 +9802,31 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
+        <v>690</v>
+      </c>
+      <c r="C196" t="s">
         <v>691</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="N196" t="s">
         <v>692</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="L196">
-        <v>0</v>
-      </c>
-      <c r="N196" t="s">
-        <v>693</v>
       </c>
       <c r="O196" t="s">
         <v>254</v>
       </c>
       <c r="P196" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q196" t="s">
         <v>255</v>
       </c>
       <c r="R196" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
@@ -9833,31 +9834,31 @@
         <v>201</v>
       </c>
       <c r="B197" t="s">
+        <v>694</v>
+      </c>
+      <c r="C197" t="s">
         <v>695</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="N197" t="s">
         <v>696</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="L197">
-        <v>0</v>
-      </c>
-      <c r="N197" t="s">
-        <v>697</v>
       </c>
       <c r="O197" t="s">
         <v>254</v>
       </c>
       <c r="P197" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q197" t="s">
         <v>256</v>
       </c>
       <c r="R197" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
@@ -9865,31 +9866,31 @@
         <v>201</v>
       </c>
       <c r="B198" t="s">
+        <v>699</v>
+      </c>
+      <c r="C198" t="s">
         <v>700</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="N198" t="s">
         <v>701</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="L198">
-        <v>0</v>
-      </c>
-      <c r="N198" t="s">
-        <v>702</v>
       </c>
       <c r="O198" t="s">
         <v>254</v>
       </c>
       <c r="P198" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q198" t="s">
         <v>256</v>
       </c>
       <c r="R198" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
@@ -9897,31 +9898,31 @@
         <v>201</v>
       </c>
       <c r="B199" t="s">
+        <v>703</v>
+      </c>
+      <c r="C199" t="s">
         <v>704</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="N199" t="s">
         <v>705</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-      <c r="N199" t="s">
-        <v>706</v>
       </c>
       <c r="O199" t="s">
         <v>254</v>
       </c>
       <c r="P199" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q199" t="s">
         <v>256</v>
       </c>
       <c r="R199" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
@@ -9929,31 +9930,31 @@
         <v>201</v>
       </c>
       <c r="B200" t="s">
+        <v>707</v>
+      </c>
+      <c r="C200" t="s">
         <v>708</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="N200" t="s">
         <v>709</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-      <c r="N200" t="s">
-        <v>710</v>
       </c>
       <c r="O200" t="s">
         <v>254</v>
       </c>
       <c r="P200" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q200" t="s">
         <v>256</v>
       </c>
       <c r="R200" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
@@ -9961,31 +9962,31 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
+        <v>711</v>
+      </c>
+      <c r="C201" t="s">
         <v>712</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="N201" t="s">
         <v>713</v>
-      </c>
-      <c r="D201">
-        <v>0</v>
-      </c>
-      <c r="L201">
-        <v>0</v>
-      </c>
-      <c r="N201" t="s">
-        <v>714</v>
       </c>
       <c r="O201" t="s">
         <v>254</v>
       </c>
       <c r="P201" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q201" t="s">
         <v>256</v>
       </c>
       <c r="R201" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
@@ -9993,31 +9994,31 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>715</v>
+      </c>
+      <c r="C202" t="s">
         <v>716</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="N202" t="s">
         <v>717</v>
       </c>
-      <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="L202">
-        <v>0</v>
-      </c>
-      <c r="N202" t="s">
+      <c r="O202" t="s">
+        <v>358</v>
+      </c>
+      <c r="P202" t="s">
         <v>718</v>
-      </c>
-      <c r="O202" t="s">
-        <v>359</v>
-      </c>
-      <c r="P202" t="s">
-        <v>719</v>
       </c>
       <c r="Q202" t="s">
         <v>259</v>
       </c>
       <c r="R202" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
@@ -10025,31 +10026,31 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
+        <v>720</v>
+      </c>
+      <c r="C203" t="s">
         <v>721</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="N203" t="s">
         <v>722</v>
       </c>
-      <c r="D203">
-        <v>0</v>
-      </c>
-      <c r="L203">
-        <v>0</v>
-      </c>
-      <c r="N203" t="s">
-        <v>723</v>
-      </c>
       <c r="O203" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P203" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q203" t="s">
         <v>259</v>
       </c>
       <c r="R203" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
@@ -10057,31 +10058,31 @@
         <v>201</v>
       </c>
       <c r="B204" t="s">
+        <v>724</v>
+      </c>
+      <c r="C204" t="s">
         <v>725</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="N204" t="s">
         <v>726</v>
       </c>
-      <c r="D204">
-        <v>0</v>
-      </c>
-      <c r="L204">
-        <v>0</v>
-      </c>
-      <c r="N204" t="s">
-        <v>727</v>
-      </c>
       <c r="O204" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P204" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q204" t="s">
         <v>259</v>
       </c>
       <c r="R204" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
@@ -10089,31 +10090,31 @@
         <v>201</v>
       </c>
       <c r="B205" t="s">
+        <v>728</v>
+      </c>
+      <c r="C205" t="s">
         <v>729</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="N205" t="s">
         <v>730</v>
       </c>
-      <c r="D205">
-        <v>0</v>
-      </c>
-      <c r="L205">
-        <v>0</v>
-      </c>
-      <c r="N205" t="s">
-        <v>731</v>
-      </c>
       <c r="O205" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P205" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q205" t="s">
         <v>259</v>
       </c>
       <c r="R205" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
@@ -10121,31 +10122,31 @@
         <v>201</v>
       </c>
       <c r="B206" t="s">
+        <v>732</v>
+      </c>
+      <c r="C206" t="s">
         <v>733</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="N206" t="s">
         <v>734</v>
       </c>
-      <c r="D206">
-        <v>0</v>
-      </c>
-      <c r="L206">
-        <v>0</v>
-      </c>
-      <c r="N206" t="s">
-        <v>735</v>
-      </c>
       <c r="O206" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P206" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q206" t="s">
         <v>259</v>
       </c>
       <c r="R206" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
@@ -10153,31 +10154,31 @@
         <v>201</v>
       </c>
       <c r="B207" t="s">
+        <v>736</v>
+      </c>
+      <c r="C207" t="s">
         <v>737</v>
       </c>
-      <c r="C207" t="s">
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="N207" t="s">
         <v>738</v>
       </c>
-      <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="L207">
-        <v>0</v>
-      </c>
-      <c r="N207" t="s">
+      <c r="O207" t="s">
+        <v>358</v>
+      </c>
+      <c r="P207" t="s">
         <v>739</v>
-      </c>
-      <c r="O207" t="s">
-        <v>359</v>
-      </c>
-      <c r="P207" t="s">
-        <v>740</v>
       </c>
       <c r="Q207" t="s">
         <v>228</v>
       </c>
       <c r="R207" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
@@ -10185,31 +10186,31 @@
         <v>201</v>
       </c>
       <c r="B208" t="s">
+        <v>741</v>
+      </c>
+      <c r="C208" t="s">
         <v>742</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="N208" t="s">
         <v>743</v>
       </c>
-      <c r="D208">
-        <v>0</v>
-      </c>
-      <c r="L208">
-        <v>0</v>
-      </c>
-      <c r="N208" t="s">
-        <v>744</v>
-      </c>
       <c r="O208" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P208" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q208" t="s">
         <v>228</v>
       </c>
       <c r="R208" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
@@ -10217,31 +10218,31 @@
         <v>201</v>
       </c>
       <c r="B209" t="s">
+        <v>745</v>
+      </c>
+      <c r="C209" t="s">
         <v>746</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="N209" t="s">
         <v>747</v>
       </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="L209">
-        <v>0</v>
-      </c>
-      <c r="N209" t="s">
-        <v>748</v>
-      </c>
       <c r="O209" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P209" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q209" t="s">
         <v>228</v>
       </c>
       <c r="R209" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
@@ -10249,31 +10250,31 @@
         <v>201</v>
       </c>
       <c r="B210" t="s">
+        <v>749</v>
+      </c>
+      <c r="C210" t="s">
         <v>750</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="N210" t="s">
         <v>751</v>
       </c>
-      <c r="D210">
-        <v>0</v>
-      </c>
-      <c r="L210">
-        <v>0</v>
-      </c>
-      <c r="N210" t="s">
-        <v>752</v>
-      </c>
       <c r="O210" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P210" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q210" t="s">
         <v>228</v>
       </c>
       <c r="R210" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
@@ -10281,31 +10282,31 @@
         <v>201</v>
       </c>
       <c r="B211" t="s">
+        <v>753</v>
+      </c>
+      <c r="C211" t="s">
         <v>754</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="N211" t="s">
         <v>755</v>
       </c>
-      <c r="D211">
-        <v>0</v>
-      </c>
-      <c r="L211">
-        <v>0</v>
-      </c>
-      <c r="N211" t="s">
-        <v>756</v>
-      </c>
       <c r="O211" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P211" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q211" t="s">
         <v>228</v>
       </c>
       <c r="R211" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
@@ -10313,31 +10314,31 @@
         <v>201</v>
       </c>
       <c r="B212" t="s">
+        <v>757</v>
+      </c>
+      <c r="C212" t="s">
         <v>758</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="N212" t="s">
         <v>759</v>
       </c>
-      <c r="D212">
-        <v>0</v>
-      </c>
-      <c r="L212">
-        <v>0</v>
-      </c>
-      <c r="N212" t="s">
+      <c r="O212" t="s">
+        <v>358</v>
+      </c>
+      <c r="P212" t="s">
         <v>760</v>
-      </c>
-      <c r="O212" t="s">
-        <v>359</v>
-      </c>
-      <c r="P212" t="s">
-        <v>761</v>
       </c>
       <c r="Q212" t="s">
         <v>251</v>
       </c>
       <c r="R212" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
@@ -10345,31 +10346,31 @@
         <v>201</v>
       </c>
       <c r="B213" t="s">
+        <v>762</v>
+      </c>
+      <c r="C213" t="s">
         <v>763</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="N213" t="s">
         <v>764</v>
       </c>
-      <c r="D213">
-        <v>0</v>
-      </c>
-      <c r="L213">
-        <v>0</v>
-      </c>
-      <c r="N213" t="s">
-        <v>765</v>
-      </c>
       <c r="O213" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P213" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q213" t="s">
         <v>251</v>
       </c>
       <c r="R213" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
@@ -10377,31 +10378,31 @@
         <v>201</v>
       </c>
       <c r="B214" t="s">
+        <v>766</v>
+      </c>
+      <c r="C214" t="s">
         <v>767</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="N214" t="s">
         <v>768</v>
       </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="L214">
-        <v>0</v>
-      </c>
-      <c r="N214" t="s">
-        <v>769</v>
-      </c>
       <c r="O214" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P214" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q214" t="s">
         <v>251</v>
       </c>
       <c r="R214" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
@@ -10409,31 +10410,31 @@
         <v>201</v>
       </c>
       <c r="B215" t="s">
+        <v>770</v>
+      </c>
+      <c r="C215" t="s">
         <v>771</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="N215" t="s">
         <v>772</v>
       </c>
-      <c r="D215">
-        <v>0</v>
-      </c>
-      <c r="L215">
-        <v>0</v>
-      </c>
-      <c r="N215" t="s">
-        <v>773</v>
-      </c>
       <c r="O215" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P215" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q215" t="s">
         <v>251</v>
       </c>
       <c r="R215" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
@@ -10441,42 +10442,42 @@
         <v>201</v>
       </c>
       <c r="B216" t="s">
+        <v>774</v>
+      </c>
+      <c r="C216" t="s">
         <v>775</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="N216" t="s">
         <v>776</v>
       </c>
-      <c r="D216">
-        <v>0</v>
-      </c>
-      <c r="L216">
-        <v>0</v>
-      </c>
-      <c r="N216" t="s">
-        <v>777</v>
-      </c>
       <c r="O216" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P216" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q216" t="s">
         <v>251</v>
       </c>
       <c r="R216" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>778</v>
+      </c>
+      <c r="B217" t="s">
         <v>779</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>780</v>
-      </c>
-      <c r="C217" t="s">
-        <v>781</v>
       </c>
       <c r="D217">
         <v>25</v>
@@ -10485,209 +10486,209 @@
         <v>33</v>
       </c>
       <c r="N217" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B218" t="s">
+        <v>782</v>
+      </c>
+      <c r="C218" t="s">
         <v>783</v>
-      </c>
-      <c r="C218" t="s">
-        <v>784</v>
       </c>
       <c r="D218">
         <v>18</v>
       </c>
       <c r="M218" t="s">
+        <v>784</v>
+      </c>
+      <c r="N218" t="s">
         <v>785</v>
-      </c>
-      <c r="N218" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B219" t="s">
+        <v>786</v>
+      </c>
+      <c r="C219" t="s">
         <v>787</v>
-      </c>
-      <c r="C219" t="s">
-        <v>788</v>
       </c>
       <c r="D219">
         <v>15</v>
       </c>
       <c r="M219" t="s">
+        <v>788</v>
+      </c>
+      <c r="N219" t="s">
         <v>789</v>
-      </c>
-      <c r="N219" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B220" t="s">
+        <v>790</v>
+      </c>
+      <c r="C220" t="s">
         <v>791</v>
-      </c>
-      <c r="C220" t="s">
-        <v>792</v>
       </c>
       <c r="D220">
         <v>30</v>
       </c>
       <c r="M220" t="s">
+        <v>792</v>
+      </c>
+      <c r="N220" t="s">
         <v>793</v>
-      </c>
-      <c r="N220" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B221" t="s">
+        <v>794</v>
+      </c>
+      <c r="C221" t="s">
         <v>795</v>
-      </c>
-      <c r="C221" t="s">
-        <v>796</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="M221" t="s">
+        <v>796</v>
+      </c>
+      <c r="N221" t="s">
         <v>797</v>
-      </c>
-      <c r="N221" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B222" t="s">
+        <v>798</v>
+      </c>
+      <c r="C222" t="s">
         <v>799</v>
-      </c>
-      <c r="C222" t="s">
-        <v>800</v>
       </c>
       <c r="D222">
         <v>25</v>
       </c>
       <c r="M222" t="s">
+        <v>800</v>
+      </c>
+      <c r="N222" t="s">
         <v>801</v>
-      </c>
-      <c r="N222" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B223" t="s">
+        <v>802</v>
+      </c>
+      <c r="C223" t="s">
         <v>803</v>
-      </c>
-      <c r="C223" t="s">
-        <v>804</v>
       </c>
       <c r="D223">
         <v>12</v>
       </c>
       <c r="N223" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B224" t="s">
+        <v>805</v>
+      </c>
+      <c r="C224" t="s">
         <v>806</v>
-      </c>
-      <c r="C224" t="s">
-        <v>807</v>
       </c>
       <c r="D224">
         <v>15</v>
       </c>
       <c r="N224" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B225" t="s">
+        <v>808</v>
+      </c>
+      <c r="C225" t="s">
         <v>809</v>
-      </c>
-      <c r="C225" t="s">
-        <v>810</v>
       </c>
       <c r="D225">
         <v>8</v>
       </c>
       <c r="N225" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B226" t="s">
+        <v>811</v>
+      </c>
+      <c r="C226" t="s">
         <v>812</v>
-      </c>
-      <c r="C226" t="s">
-        <v>813</v>
       </c>
       <c r="D226">
         <v>30</v>
       </c>
       <c r="N226" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B227" t="s">
+        <v>814</v>
+      </c>
+      <c r="C227" t="s">
         <v>815</v>
-      </c>
-      <c r="C227" t="s">
-        <v>816</v>
       </c>
       <c r="D227">
         <v>5</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B228" t="s">
+        <v>816</v>
+      </c>
+      <c r="C228" t="s">
         <v>817</v>
-      </c>
-      <c r="C228" t="s">
-        <v>818</v>
       </c>
       <c r="D228">
         <v>35</v>
       </c>
       <c r="N228" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FADD3D-D21B-482E-B953-34D2C78BE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5D27ED-4768-49B4-841A-8B8AEE1DDAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="823">
   <si>
     <t>池</t>
   </si>
@@ -62,9 +62,6 @@
     <t>戰力權重</t>
   </si>
   <si>
-    <t>最低稀有度</t>
-  </si>
-  <si>
     <t>每階perR</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>冷卻縮減%</t>
   </si>
   <si>
-    <t>helmet;belt;gloves;ring;amulet</t>
-  </si>
-  <si>
     <t>castSpeed</t>
   </si>
   <si>
@@ -305,9 +299,6 @@
     <t>lifesteal</t>
   </si>
   <si>
-    <t>chest;wrist;ring;amulet</t>
-  </si>
-  <si>
     <t>manaSteal</t>
   </si>
   <si>
@@ -440,9 +431,6 @@
     <t>範圍傷害%</t>
   </si>
   <si>
-    <t>weapon;amulet</t>
-  </si>
-  <si>
     <t>blockRate</t>
   </si>
   <si>
@@ -597,9 +585,6 @@
   </si>
   <si>
     <t>負重上限</t>
-  </si>
-  <si>
-    <t>shoulder;chest;legs;boots;ring;amulet</t>
   </si>
   <si>
     <t>enhanceSuccess</t>
@@ -2520,6 +2505,16 @@
   </si>
   <si>
     <t>四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>helmet;belt;ring;amulet</t>
+  </si>
+  <si>
+    <t>chest;wrist;legs;ring;amulet</t>
+  </si>
+  <si>
+    <t>最低稀有度</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3535,42 +3530,42 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>822</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -3582,27 +3577,27 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -3614,27 +3609,27 @@
         <v>0.02</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>2.6</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -3646,27 +3641,27 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -3678,27 +3673,27 @@
         <v>0.02</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>2.6</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -3710,27 +3705,27 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0.05</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -3742,27 +3737,27 @@
         <v>0.02</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3774,7 +3769,7 @@
         <v>0.15</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -3783,18 +3778,18 @@
         <v>0.6</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -3806,7 +3801,7 @@
         <v>1.2</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -3815,18 +3810,18 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3838,7 +3833,7 @@
         <v>0.04</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -3847,18 +3842,18 @@
         <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -3870,7 +3865,7 @@
         <v>0.4</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11">
         <v>8</v>
@@ -3879,18 +3874,18 @@
         <v>1.8</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
         <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -3902,7 +3897,7 @@
         <v>0.4</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12">
         <v>8</v>
@@ -3911,18 +3906,18 @@
         <v>1.8</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
         <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -3934,7 +3929,7 @@
         <v>0.4</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -3943,18 +3938,18 @@
         <v>1.8</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -3966,7 +3961,7 @@
         <v>0.4</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14">
         <v>8</v>
@@ -3975,18 +3970,18 @@
         <v>1.8</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
         <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -3998,7 +3993,7 @@
         <v>0.35</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H15">
         <v>9</v>
@@ -4007,18 +4002,18 @@
         <v>0.9</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -4030,7 +4025,7 @@
         <v>0.02</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -4039,18 +4034,18 @@
         <v>1.8</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
         <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -4062,7 +4057,7 @@
         <v>0.35</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17">
         <v>9</v>
@@ -4071,18 +4066,18 @@
         <v>0.9</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
         <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -4094,7 +4089,7 @@
         <v>0.02</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -4103,18 +4098,18 @@
         <v>1.8</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
         <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -4126,7 +4121,7 @@
         <v>0.35</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19">
         <v>9</v>
@@ -4138,18 +4133,18 @@
         <v>4</v>
       </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
       </c>
       <c r="D20">
         <v>30</v>
@@ -4161,7 +4156,7 @@
         <v>0.35</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H20">
         <v>9</v>
@@ -4173,18 +4168,18 @@
         <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
         <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
       </c>
       <c r="D21">
         <v>30</v>
@@ -4196,7 +4191,7 @@
         <v>0.35</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21">
         <v>9</v>
@@ -4208,18 +4203,18 @@
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
         <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -4231,7 +4226,7 @@
         <v>0.35</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H22">
         <v>9</v>
@@ -4243,18 +4238,18 @@
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
         <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -4266,7 +4261,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -4275,18 +4270,18 @@
         <v>2.8</v>
       </c>
       <c r="K23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
         <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -4298,7 +4293,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -4307,18 +4302,18 @@
         <v>2.4</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
         <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -4330,7 +4325,7 @@
         <v>0.05</v>
       </c>
       <c r="G25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -4339,18 +4334,18 @@
         <v>0.9</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>76</v>
       </c>
       <c r="D26">
         <v>20</v>
@@ -4362,7 +4357,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26">
         <v>4</v>
@@ -4374,18 +4369,18 @@
         <v>4</v>
       </c>
       <c r="K26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
       </c>
       <c r="D27">
         <v>20</v>
@@ -4397,7 +4392,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27">
         <v>4</v>
@@ -4409,18 +4404,18 @@
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
         <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -4432,7 +4427,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -4440,34 +4435,37 @@
       <c r="I28">
         <v>1.2</v>
       </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
       <c r="K28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
         <v>83</v>
       </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
       <c r="D29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E29">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -4476,18 +4474,18 @@
         <v>4</v>
       </c>
       <c r="K29" t="s">
-        <v>85</v>
+        <v>820</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -4499,7 +4497,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30">
         <v>4</v>
@@ -4507,34 +4505,31 @@
       <c r="I30">
         <v>1.4</v>
       </c>
-      <c r="J30">
-        <v>4</v>
-      </c>
       <c r="K30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -4542,31 +4537,34 @@
       <c r="I31">
         <v>1.4</v>
       </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
       <c r="K31" t="s">
-        <v>90</v>
+        <v>821</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="D32">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>3.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -4578,18 +4576,18 @@
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>90</v>
+        <v>821</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -4601,7 +4599,7 @@
         <v>0.02</v>
       </c>
       <c r="G33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33">
         <v>4</v>
@@ -4613,18 +4611,18 @@
         <v>3</v>
       </c>
       <c r="K33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -4636,7 +4634,7 @@
         <v>0.02</v>
       </c>
       <c r="G34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34">
         <v>4</v>
@@ -4648,18 +4646,18 @@
         <v>3</v>
       </c>
       <c r="K34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -4671,10 +4669,10 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>1.2</v>
@@ -4683,18 +4681,18 @@
         <v>3</v>
       </c>
       <c r="K35" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -4706,7 +4704,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36">
         <v>3</v>
@@ -4718,18 +4716,18 @@
         <v>3</v>
       </c>
       <c r="K36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -4741,7 +4739,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -4753,18 +4751,18 @@
         <v>3</v>
       </c>
       <c r="K37" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -4776,7 +4774,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38">
         <v>3</v>
@@ -4788,18 +4786,18 @@
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -4811,7 +4809,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H39">
         <v>3</v>
@@ -4823,18 +4821,18 @@
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -4846,7 +4844,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -4858,18 +4856,18 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -4881,7 +4879,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H41">
         <v>3</v>
@@ -4893,18 +4891,18 @@
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -4916,7 +4914,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H42">
         <v>3</v>
@@ -4928,18 +4926,18 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -4951,7 +4949,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H43">
         <v>3</v>
@@ -4963,18 +4961,18 @@
         <v>3</v>
       </c>
       <c r="K43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -4986,7 +4984,7 @@
         <v>0.02</v>
       </c>
       <c r="G44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -4998,18 +4996,18 @@
         <v>3</v>
       </c>
       <c r="K44" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -5021,7 +5019,7 @@
         <v>0.02</v>
       </c>
       <c r="G45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -5033,18 +5031,18 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D46">
         <v>5</v>
@@ -5056,7 +5054,7 @@
         <v>0.02</v>
       </c>
       <c r="G46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H46">
         <v>3</v>
@@ -5068,18 +5066,18 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -5091,7 +5089,7 @@
         <v>0.02</v>
       </c>
       <c r="G47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H47">
         <v>3</v>
@@ -5103,18 +5101,18 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -5126,7 +5124,7 @@
         <v>0.02</v>
       </c>
       <c r="G48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H48">
         <v>3</v>
@@ -5138,18 +5136,18 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -5161,7 +5159,7 @@
         <v>0.02</v>
       </c>
       <c r="G49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H49">
         <v>3</v>
@@ -5173,18 +5171,18 @@
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -5196,7 +5194,7 @@
         <v>0.02</v>
       </c>
       <c r="G50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -5208,18 +5206,18 @@
         <v>3</v>
       </c>
       <c r="K50" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -5231,7 +5229,7 @@
         <v>0.02</v>
       </c>
       <c r="G51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -5243,18 +5241,18 @@
         <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -5266,7 +5264,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H52">
         <v>4</v>
@@ -5278,18 +5276,18 @@
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -5301,7 +5299,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H53">
         <v>4</v>
@@ -5309,19 +5307,22 @@
       <c r="I53">
         <v>2</v>
       </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
       <c r="K53" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -5333,7 +5334,7 @@
         <v>0.02</v>
       </c>
       <c r="G54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -5345,18 +5346,18 @@
         <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -5368,7 +5369,7 @@
         <v>0.01</v>
       </c>
       <c r="G55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H55">
         <v>4</v>
@@ -5376,19 +5377,22 @@
       <c r="I55">
         <v>2.2000000000000002</v>
       </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -5400,7 +5404,7 @@
         <v>0.02</v>
       </c>
       <c r="G56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -5412,18 +5416,18 @@
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D57">
         <v>5</v>
@@ -5435,7 +5439,7 @@
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H57">
         <v>3</v>
@@ -5443,22 +5447,19 @@
       <c r="I57">
         <v>1</v>
       </c>
-      <c r="J57">
-        <v>3</v>
-      </c>
       <c r="K57" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D58">
         <v>30</v>
@@ -5470,7 +5471,7 @@
         <v>0.04</v>
       </c>
       <c r="G58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H58">
         <v>3</v>
@@ -5478,22 +5479,19 @@
       <c r="I58">
         <v>2</v>
       </c>
-      <c r="J58">
-        <v>3</v>
-      </c>
       <c r="K58" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D59">
         <v>30</v>
@@ -5505,7 +5503,7 @@
         <v>0.04</v>
       </c>
       <c r="G59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H59">
         <v>3</v>
@@ -5513,22 +5511,19 @@
       <c r="I59">
         <v>2</v>
       </c>
-      <c r="J59">
-        <v>3</v>
-      </c>
       <c r="K59" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D60">
         <v>30</v>
@@ -5540,7 +5535,7 @@
         <v>0.06</v>
       </c>
       <c r="G60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H60">
         <v>3</v>
@@ -5548,22 +5543,19 @@
       <c r="I60">
         <v>0.8</v>
       </c>
-      <c r="J60">
-        <v>3</v>
-      </c>
       <c r="K60" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D61">
         <v>30</v>
@@ -5575,7 +5567,7 @@
         <v>0.06</v>
       </c>
       <c r="G61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H61">
         <v>3</v>
@@ -5583,22 +5575,19 @@
       <c r="I61">
         <v>0.8</v>
       </c>
-      <c r="J61">
-        <v>3</v>
-      </c>
       <c r="K61" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D62">
         <v>30</v>
@@ -5610,7 +5599,7 @@
         <v>0.06</v>
       </c>
       <c r="G62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H62">
         <v>3</v>
@@ -5618,22 +5607,19 @@
       <c r="I62">
         <v>0.8</v>
       </c>
-      <c r="J62">
-        <v>3</v>
-      </c>
       <c r="K62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D63">
         <v>30</v>
@@ -5645,7 +5631,7 @@
         <v>0.06</v>
       </c>
       <c r="G63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -5653,22 +5639,19 @@
       <c r="I63">
         <v>0.8</v>
       </c>
-      <c r="J63">
-        <v>3</v>
-      </c>
       <c r="K63" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C64" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D64">
         <v>30</v>
@@ -5680,7 +5663,7 @@
         <v>0.06</v>
       </c>
       <c r="G64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H64">
         <v>3</v>
@@ -5688,22 +5671,19 @@
       <c r="I64">
         <v>0.8</v>
       </c>
-      <c r="J64">
-        <v>3</v>
-      </c>
       <c r="K64" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D65">
         <v>30</v>
@@ -5715,7 +5695,7 @@
         <v>0.06</v>
       </c>
       <c r="G65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H65">
         <v>3</v>
@@ -5723,22 +5703,19 @@
       <c r="I65">
         <v>0.8</v>
       </c>
-      <c r="J65">
-        <v>3</v>
-      </c>
       <c r="K65" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D66">
         <v>30</v>
@@ -5750,7 +5727,7 @@
         <v>0.06</v>
       </c>
       <c r="G66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -5758,22 +5735,19 @@
       <c r="I66">
         <v>0.8</v>
       </c>
-      <c r="J66">
-        <v>3</v>
-      </c>
       <c r="K66" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D67">
         <v>30</v>
@@ -5785,7 +5759,7 @@
         <v>0.06</v>
       </c>
       <c r="G67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H67">
         <v>3</v>
@@ -5793,22 +5767,19 @@
       <c r="I67">
         <v>0.8</v>
       </c>
-      <c r="J67">
-        <v>3</v>
-      </c>
       <c r="K67" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -5820,7 +5791,7 @@
         <v>0.06</v>
       </c>
       <c r="G68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -5832,18 +5803,18 @@
         <v>4</v>
       </c>
       <c r="K68" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -5855,7 +5826,7 @@
         <v>0.02</v>
       </c>
       <c r="G69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -5867,18 +5838,18 @@
         <v>4</v>
       </c>
       <c r="K69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -5890,7 +5861,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H70">
         <v>4</v>
@@ -5899,18 +5870,18 @@
         <v>1.5</v>
       </c>
       <c r="K70" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C71" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -5922,7 +5893,7 @@
         <v>0.01</v>
       </c>
       <c r="G71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H71">
         <v>4</v>
@@ -5931,21 +5902,21 @@
         <v>0.8</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -5957,7 +5928,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H72">
         <v>4</v>
@@ -5966,21 +5937,21 @@
         <v>0.8</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K72" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -5992,7 +5963,7 @@
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H73">
         <v>4</v>
@@ -6004,18 +5975,18 @@
         <v>4</v>
       </c>
       <c r="K73" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C74" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -6027,7 +5998,7 @@
         <v>0.2</v>
       </c>
       <c r="G74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -6036,21 +6007,21 @@
         <v>1.5</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K74" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C75" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -6062,7 +6033,7 @@
         <v>0.3</v>
       </c>
       <c r="G75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -6070,22 +6041,19 @@
       <c r="I75">
         <v>0.8</v>
       </c>
-      <c r="J75">
-        <v>4</v>
-      </c>
       <c r="K75" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -6097,7 +6065,7 @@
         <v>0.01</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -6106,21 +6074,21 @@
         <v>0.8</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C77" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -6132,7 +6100,7 @@
         <v>1.4999999999999901E-2</v>
       </c>
       <c r="G77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H77">
         <v>3</v>
@@ -6140,22 +6108,19 @@
       <c r="I77">
         <v>0.8</v>
       </c>
-      <c r="J77">
-        <v>4</v>
-      </c>
       <c r="K77" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D78">
         <v>2.5</v>
@@ -6167,7 +6132,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H78">
         <v>2</v>
@@ -6175,22 +6140,19 @@
       <c r="I78">
         <v>1.2</v>
       </c>
-      <c r="J78">
-        <v>4</v>
-      </c>
       <c r="K78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -6202,7 +6164,7 @@
         <v>0.08</v>
       </c>
       <c r="G79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H79">
         <v>2</v>
@@ -6210,22 +6172,19 @@
       <c r="I79">
         <v>1</v>
       </c>
-      <c r="J79">
-        <v>4</v>
-      </c>
       <c r="K79" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -6237,7 +6196,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -6246,21 +6205,21 @@
         <v>1.2</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C81" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -6272,7 +6231,7 @@
         <v>0.02</v>
       </c>
       <c r="G81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H81">
         <v>2</v>
@@ -6281,21 +6240,21 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K81" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B82" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -6304,18 +6263,18 @@
         <v>2</v>
       </c>
       <c r="N82" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>196</v>
+      </c>
+      <c r="B83" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" t="s">
         <v>201</v>
-      </c>
-      <c r="B83" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" t="s">
-        <v>206</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -6324,18 +6283,18 @@
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D84">
         <v>10</v>
@@ -6344,18 +6303,18 @@
         <v>2</v>
       </c>
       <c r="N84" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -6364,18 +6323,18 @@
         <v>1.5</v>
       </c>
       <c r="N85" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B86" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D86">
         <v>12</v>
@@ -6384,18 +6343,18 @@
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C87" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D87">
         <v>6</v>
@@ -6404,18 +6363,18 @@
         <v>1.5</v>
       </c>
       <c r="N87" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D88">
         <v>5</v>
@@ -6424,18 +6383,18 @@
         <v>1.5</v>
       </c>
       <c r="N88" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B89" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C89" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -6444,24 +6403,24 @@
         <v>0</v>
       </c>
       <c r="N89" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Q89" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R89" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C90" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -6470,27 +6429,27 @@
         <v>0</v>
       </c>
       <c r="N90" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="O90" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Q90" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R90" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B91" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C91" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -6499,27 +6458,27 @@
         <v>0</v>
       </c>
       <c r="N91" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O91" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Q91" t="s">
+        <v>228</v>
+      </c>
+      <c r="R91" t="s">
         <v>233</v>
-      </c>
-      <c r="R91" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -6528,24 +6487,24 @@
         <v>0</v>
       </c>
       <c r="N92" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="Q92" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R92" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C93" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -6554,24 +6513,24 @@
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="Q93" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R93" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C94" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -6580,24 +6539,24 @@
         <v>0</v>
       </c>
       <c r="N94" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Q94" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R94" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B95" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C95" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -6606,27 +6565,27 @@
         <v>0</v>
       </c>
       <c r="N95" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O95" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>250</v>
+      </c>
+      <c r="R95" t="s">
         <v>258</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>255</v>
-      </c>
-      <c r="R95" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B96" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -6635,27 +6594,27 @@
         <v>0</v>
       </c>
       <c r="N96" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="O96" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Q96" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R96" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C97" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -6664,27 +6623,27 @@
         <v>0</v>
       </c>
       <c r="N97" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O97" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q97" t="s">
         <v>267</v>
       </c>
-      <c r="Q97" t="s">
-        <v>272</v>
-      </c>
       <c r="R97" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B98" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C98" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -6693,27 +6652,27 @@
         <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="O98" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Q98" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R98" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B99" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C99" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -6722,27 +6681,27 @@
         <v>0</v>
       </c>
       <c r="N99" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O99" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>254</v>
+      </c>
+      <c r="R99" t="s">
         <v>277</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>259</v>
-      </c>
-      <c r="R99" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B100" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C100" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6751,27 +6710,27 @@
         <v>0</v>
       </c>
       <c r="N100" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O100" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="Q100" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R100" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B101" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C101" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6780,24 +6739,24 @@
         <v>0</v>
       </c>
       <c r="N101" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Q101" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R101" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C102" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6806,30 +6765,30 @@
         <v>0</v>
       </c>
       <c r="N102" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="O102" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P102" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q102" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R102" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C103" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6838,30 +6797,30 @@
         <v>0</v>
       </c>
       <c r="N103" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O103" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P103" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>228</v>
+      </c>
+      <c r="R103" t="s">
         <v>296</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>233</v>
-      </c>
-      <c r="R103" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B104" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C104" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6870,30 +6829,30 @@
         <v>0</v>
       </c>
       <c r="N104" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="O104" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q104" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R104" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B105" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C105" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6902,30 +6861,30 @@
         <v>0</v>
       </c>
       <c r="N105" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="O105" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P105" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q105" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R105" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B106" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C106" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6934,30 +6893,30 @@
         <v>0</v>
       </c>
       <c r="N106" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O106" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P106" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q106" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R106" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B107" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C107" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6966,30 +6925,30 @@
         <v>0</v>
       </c>
       <c r="N107" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="O107" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P107" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="Q107" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R107" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6998,30 +6957,30 @@
         <v>0</v>
       </c>
       <c r="N108" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="O108" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P108" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>219</v>
+      </c>
+      <c r="R108" t="s">
         <v>316</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>224</v>
-      </c>
-      <c r="R108" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B109" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C109" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -7030,30 +6989,30 @@
         <v>0</v>
       </c>
       <c r="N109" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="O109" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P109" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="Q109" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R109" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C110" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -7062,30 +7021,30 @@
         <v>0</v>
       </c>
       <c r="N110" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O110" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="Q110" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R110" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C111" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -7094,30 +7053,30 @@
         <v>0</v>
       </c>
       <c r="N111" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="O111" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P111" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="Q111" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R111" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C112" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -7126,30 +7085,30 @@
         <v>0</v>
       </c>
       <c r="N112" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="O112" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P112" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Q112" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R112" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B113" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C113" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -7158,30 +7117,30 @@
         <v>0</v>
       </c>
       <c r="N113" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="O113" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P113" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>228</v>
+      </c>
+      <c r="R113" t="s">
         <v>337</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>233</v>
-      </c>
-      <c r="R113" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B114" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C114" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -7190,30 +7149,30 @@
         <v>0</v>
       </c>
       <c r="N114" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O114" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P114" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Q114" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R114" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C115" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -7222,30 +7181,30 @@
         <v>0</v>
       </c>
       <c r="N115" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O115" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P115" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Q115" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R115" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B116" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C116" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -7254,62 +7213,62 @@
         <v>0</v>
       </c>
       <c r="N116" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="O116" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P116" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Q116" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R116" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B117" t="s">
+        <v>350</v>
+      </c>
+      <c r="C117" t="s">
+        <v>351</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="N117" t="s">
+        <v>352</v>
+      </c>
+      <c r="O117" t="s">
+        <v>353</v>
+      </c>
+      <c r="P117" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>242</v>
+      </c>
+      <c r="R117" t="s">
         <v>355</v>
-      </c>
-      <c r="C117" t="s">
-        <v>356</v>
-      </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="N117" t="s">
-        <v>357</v>
-      </c>
-      <c r="O117" t="s">
-        <v>358</v>
-      </c>
-      <c r="P117" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>247</v>
-      </c>
-      <c r="R117" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B118" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C118" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -7318,30 +7277,30 @@
         <v>0</v>
       </c>
       <c r="N118" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="O118" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P118" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>242</v>
+      </c>
+      <c r="R118" t="s">
         <v>359</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>247</v>
-      </c>
-      <c r="R118" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B119" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C119" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -7350,30 +7309,30 @@
         <v>0</v>
       </c>
       <c r="N119" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="O119" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P119" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="Q119" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R119" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B120" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C120" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -7382,30 +7341,30 @@
         <v>0</v>
       </c>
       <c r="N120" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="O120" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P120" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="Q120" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R120" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C121" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -7414,62 +7373,62 @@
         <v>0</v>
       </c>
       <c r="N121" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="O121" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P121" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="Q121" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R121" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
+        <v>372</v>
+      </c>
+      <c r="C122" t="s">
+        <v>373</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="N122" t="s">
+        <v>374</v>
+      </c>
+      <c r="O122" t="s">
+        <v>278</v>
+      </c>
+      <c r="P122" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>376</v>
+      </c>
+      <c r="R122" t="s">
         <v>377</v>
-      </c>
-      <c r="C122" t="s">
-        <v>378</v>
-      </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="N122" t="s">
-        <v>379</v>
-      </c>
-      <c r="O122" t="s">
-        <v>283</v>
-      </c>
-      <c r="P122" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>381</v>
-      </c>
-      <c r="R122" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B123" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C123" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -7478,30 +7437,30 @@
         <v>0</v>
       </c>
       <c r="N123" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="O123" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="P123" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="Q123" t="s">
+        <v>376</v>
+      </c>
+      <c r="R123" t="s">
         <v>381</v>
-      </c>
-      <c r="R123" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C124" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -7510,30 +7469,30 @@
         <v>0</v>
       </c>
       <c r="N124" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="O124" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P124" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="Q124" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="R124" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -7542,30 +7501,30 @@
         <v>0</v>
       </c>
       <c r="N125" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="O125" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P125" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="Q125" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="R125" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B126" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C126" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -7574,30 +7533,30 @@
         <v>0</v>
       </c>
       <c r="N126" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="O126" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P126" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="Q126" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="R126" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B127" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C127" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -7606,30 +7565,30 @@
         <v>0</v>
       </c>
       <c r="N127" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="O127" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P127" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Q127" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R127" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B128" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C128" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -7638,30 +7597,30 @@
         <v>0</v>
       </c>
       <c r="N128" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="O128" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P128" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>248</v>
+      </c>
+      <c r="R128" t="s">
         <v>402</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>253</v>
-      </c>
-      <c r="R128" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B129" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C129" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -7670,30 +7629,30 @@
         <v>0</v>
       </c>
       <c r="N129" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="O129" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P129" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Q129" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R129" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B130" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C130" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -7702,30 +7661,30 @@
         <v>0</v>
       </c>
       <c r="N130" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="O130" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P130" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Q130" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R130" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B131" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C131" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -7734,30 +7693,30 @@
         <v>0</v>
       </c>
       <c r="N131" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="O131" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P131" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Q131" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R131" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B132" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C132" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -7766,30 +7725,30 @@
         <v>0</v>
       </c>
       <c r="N132" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="O132" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P132" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Q132" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R132" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B133" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C133" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -7798,30 +7757,30 @@
         <v>0</v>
       </c>
       <c r="N133" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="O133" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P133" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>246</v>
+      </c>
+      <c r="R133" t="s">
         <v>423</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>251</v>
-      </c>
-      <c r="R133" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B134" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C134" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -7830,30 +7789,30 @@
         <v>0</v>
       </c>
       <c r="N134" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="O134" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P134" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Q134" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R134" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B135" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C135" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -7862,30 +7821,30 @@
         <v>0</v>
       </c>
       <c r="N135" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="O135" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P135" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Q135" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R135" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B136" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C136" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -7894,30 +7853,30 @@
         <v>0</v>
       </c>
       <c r="N136" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="O136" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P136" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Q136" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R136" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B137" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C137" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -7926,30 +7885,30 @@
         <v>0</v>
       </c>
       <c r="N137" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="O137" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P137" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q137" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R137" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B138" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C138" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -7958,30 +7917,30 @@
         <v>0</v>
       </c>
       <c r="N138" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="O138" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P138" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>248</v>
+      </c>
+      <c r="R138" t="s">
         <v>444</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>253</v>
-      </c>
-      <c r="R138" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B139" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C139" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -7990,30 +7949,30 @@
         <v>0</v>
       </c>
       <c r="N139" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="O139" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P139" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q139" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R139" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B140" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C140" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -8022,30 +7981,30 @@
         <v>0</v>
       </c>
       <c r="N140" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="O140" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P140" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q140" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R140" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B141" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C141" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -8054,30 +8013,30 @@
         <v>0</v>
       </c>
       <c r="N141" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="O141" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P141" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q141" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R141" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B142" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C142" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -8086,30 +8045,30 @@
         <v>0</v>
       </c>
       <c r="N142" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="O142" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P142" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q142" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R142" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B143" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C143" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -8118,30 +8077,30 @@
         <v>0</v>
       </c>
       <c r="N143" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O143" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P143" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>254</v>
+      </c>
+      <c r="R143" t="s">
         <v>465</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>259</v>
-      </c>
-      <c r="R143" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B144" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C144" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -8150,30 +8109,30 @@
         <v>0</v>
       </c>
       <c r="N144" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O144" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P144" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q144" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R144" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B145" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C145" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -8182,30 +8141,30 @@
         <v>0</v>
       </c>
       <c r="N145" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O145" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P145" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q145" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R145" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B146" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C146" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -8214,30 +8173,30 @@
         <v>0</v>
       </c>
       <c r="N146" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="O146" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P146" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q146" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R146" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B147" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C147" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -8246,30 +8205,30 @@
         <v>0</v>
       </c>
       <c r="N147" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="O147" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P147" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Q147" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R147" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B148" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C148" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -8278,30 +8237,30 @@
         <v>0</v>
       </c>
       <c r="N148" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O148" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P148" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>251</v>
+      </c>
+      <c r="R148" t="s">
         <v>486</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>256</v>
-      </c>
-      <c r="R148" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C149" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -8310,30 +8269,30 @@
         <v>0</v>
       </c>
       <c r="N149" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="O149" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P149" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Q149" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R149" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B150" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C150" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -8342,30 +8301,30 @@
         <v>0</v>
       </c>
       <c r="N150" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="O150" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P150" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Q150" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R150" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B151" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C151" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -8374,30 +8333,30 @@
         <v>0</v>
       </c>
       <c r="N151" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="O151" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P151" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Q151" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R151" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B152" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C152" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -8406,30 +8365,30 @@
         <v>0</v>
       </c>
       <c r="N152" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O152" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P152" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q152" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R152" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B153" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C153" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -8438,30 +8397,30 @@
         <v>0</v>
       </c>
       <c r="N153" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="O153" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P153" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>252</v>
+      </c>
+      <c r="R153" t="s">
         <v>507</v>
-      </c>
-      <c r="Q153" t="s">
-        <v>257</v>
-      </c>
-      <c r="R153" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C154" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -8470,30 +8429,30 @@
         <v>0</v>
       </c>
       <c r="N154" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="O154" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P154" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q154" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R154" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B155" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C155" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -8502,30 +8461,30 @@
         <v>0</v>
       </c>
       <c r="N155" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="O155" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P155" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q155" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R155" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B156" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C156" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -8534,62 +8493,62 @@
         <v>0</v>
       </c>
       <c r="N156" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="O156" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P156" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q156" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R156" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B157" t="s">
+        <v>520</v>
+      </c>
+      <c r="C157" t="s">
+        <v>521</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="N157" t="s">
+        <v>522</v>
+      </c>
+      <c r="O157" t="s">
+        <v>523</v>
+      </c>
+      <c r="P157" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>250</v>
+      </c>
+      <c r="R157" t="s">
         <v>525</v>
-      </c>
-      <c r="C157" t="s">
-        <v>526</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="N157" t="s">
-        <v>527</v>
-      </c>
-      <c r="O157" t="s">
-        <v>528</v>
-      </c>
-      <c r="P157" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>255</v>
-      </c>
-      <c r="R157" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B158" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C158" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -8598,30 +8557,30 @@
         <v>0</v>
       </c>
       <c r="N158" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="O158" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P158" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>250</v>
+      </c>
+      <c r="R158" t="s">
         <v>529</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>255</v>
-      </c>
-      <c r="R158" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B159" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C159" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -8630,30 +8589,30 @@
         <v>0</v>
       </c>
       <c r="N159" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O159" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P159" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="Q159" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R159" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B160" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C160" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -8662,30 +8621,30 @@
         <v>0</v>
       </c>
       <c r="N160" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O160" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P160" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="Q160" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R160" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B161" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C161" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -8694,30 +8653,30 @@
         <v>0</v>
       </c>
       <c r="N161" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O161" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P161" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="Q161" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R161" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B162" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C162" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -8726,30 +8685,30 @@
         <v>0</v>
       </c>
       <c r="N162" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="O162" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P162" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="Q162" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R162" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B163" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C163" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -8758,30 +8717,30 @@
         <v>0</v>
       </c>
       <c r="N163" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="O163" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P163" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>242</v>
+      </c>
+      <c r="R163" t="s">
         <v>550</v>
-      </c>
-      <c r="Q163" t="s">
-        <v>247</v>
-      </c>
-      <c r="R163" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B164" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C164" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -8790,30 +8749,30 @@
         <v>0</v>
       </c>
       <c r="N164" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="O164" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P164" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="Q164" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R164" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B165" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C165" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -8822,30 +8781,30 @@
         <v>0</v>
       </c>
       <c r="N165" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O165" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P165" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="Q165" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R165" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B166" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C166" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -8854,30 +8813,30 @@
         <v>0</v>
       </c>
       <c r="N166" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="O166" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P166" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="Q166" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R166" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B167" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C167" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -8886,30 +8845,30 @@
         <v>0</v>
       </c>
       <c r="N167" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="O167" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P167" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="Q167" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R167" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C168" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -8918,30 +8877,30 @@
         <v>0</v>
       </c>
       <c r="N168" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="O168" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P168" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>246</v>
+      </c>
+      <c r="R168" t="s">
         <v>571</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>251</v>
-      </c>
-      <c r="R168" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B169" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C169" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -8950,30 +8909,30 @@
         <v>0</v>
       </c>
       <c r="N169" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="O169" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P169" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="Q169" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R169" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B170" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C170" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -8982,30 +8941,30 @@
         <v>0</v>
       </c>
       <c r="N170" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="O170" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P170" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="Q170" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R170" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B171" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C171" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -9014,30 +8973,30 @@
         <v>0</v>
       </c>
       <c r="N171" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="O171" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="P171" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="Q171" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R171" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B172" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C172" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -9046,30 +9005,30 @@
         <v>0</v>
       </c>
       <c r="N172" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="O172" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P172" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="Q172" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R172" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B173" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C173" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -9078,30 +9037,30 @@
         <v>0</v>
       </c>
       <c r="N173" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="O173" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P173" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>219</v>
+      </c>
+      <c r="R173" t="s">
         <v>592</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>224</v>
-      </c>
-      <c r="R173" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B174" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C174" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -9110,30 +9069,30 @@
         <v>0</v>
       </c>
       <c r="N174" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="O174" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P174" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="Q174" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R174" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B175" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C175" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -9142,30 +9101,30 @@
         <v>0</v>
       </c>
       <c r="N175" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="O175" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P175" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="Q175" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R175" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B176" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C176" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -9174,30 +9133,30 @@
         <v>0</v>
       </c>
       <c r="N176" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="O176" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P176" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="Q176" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R176" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B177" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C177" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -9206,30 +9165,30 @@
         <v>0</v>
       </c>
       <c r="N177" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="O177" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P177" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="Q177" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R177" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B178" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C178" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -9238,30 +9197,30 @@
         <v>0</v>
       </c>
       <c r="N178" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="O178" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P178" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>254</v>
+      </c>
+      <c r="R178" t="s">
         <v>613</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>259</v>
-      </c>
-      <c r="R178" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B179" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C179" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -9270,30 +9229,30 @@
         <v>0</v>
       </c>
       <c r="N179" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O179" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P179" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="Q179" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R179" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B180" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C180" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -9302,30 +9261,30 @@
         <v>0</v>
       </c>
       <c r="N180" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="O180" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P180" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="Q180" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R180" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B181" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C181" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -9334,30 +9293,30 @@
         <v>0</v>
       </c>
       <c r="N181" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="O181" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P181" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="Q181" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R181" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B182" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C182" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -9366,30 +9325,30 @@
         <v>0</v>
       </c>
       <c r="N182" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="O182" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P182" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="Q182" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R182" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B183" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C183" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -9398,30 +9357,30 @@
         <v>0</v>
       </c>
       <c r="N183" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="O183" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P183" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>252</v>
+      </c>
+      <c r="R183" t="s">
         <v>634</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>257</v>
-      </c>
-      <c r="R183" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B184" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C184" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -9430,30 +9389,30 @@
         <v>0</v>
       </c>
       <c r="N184" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O184" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P184" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="Q184" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R184" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B185" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C185" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -9462,30 +9421,30 @@
         <v>0</v>
       </c>
       <c r="N185" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="O185" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P185" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="Q185" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R185" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B186" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C186" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -9494,30 +9453,30 @@
         <v>0</v>
       </c>
       <c r="N186" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="O186" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P186" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="Q186" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R186" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B187" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C187" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -9526,30 +9485,30 @@
         <v>0</v>
       </c>
       <c r="N187" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="O187" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P187" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="Q187" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R187" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B188" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C188" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -9558,30 +9517,30 @@
         <v>0</v>
       </c>
       <c r="N188" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="O188" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P188" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>267</v>
+      </c>
+      <c r="R188" t="s">
         <v>655</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>272</v>
-      </c>
-      <c r="R188" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B189" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C189" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -9590,30 +9549,30 @@
         <v>0</v>
       </c>
       <c r="N189" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="O189" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P189" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="Q189" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R189" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B190" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C190" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -9622,30 +9581,30 @@
         <v>0</v>
       </c>
       <c r="N190" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="O190" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P190" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="Q190" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R190" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C191" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -9654,30 +9613,30 @@
         <v>0</v>
       </c>
       <c r="N191" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="O191" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P191" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="Q191" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R191" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B192" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C192" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -9686,30 +9645,30 @@
         <v>0</v>
       </c>
       <c r="N192" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="O192" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P192" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="Q192" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R192" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C193" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -9718,30 +9677,30 @@
         <v>0</v>
       </c>
       <c r="N193" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="O193" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P193" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>250</v>
+      </c>
+      <c r="R193" t="s">
         <v>676</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>255</v>
-      </c>
-      <c r="R193" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B194" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C194" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -9750,30 +9709,30 @@
         <v>0</v>
       </c>
       <c r="N194" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="O194" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P194" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="Q194" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R194" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B195" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C195" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -9782,30 +9741,30 @@
         <v>0</v>
       </c>
       <c r="N195" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="O195" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P195" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="Q195" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R195" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C196" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -9814,30 +9773,30 @@
         <v>0</v>
       </c>
       <c r="N196" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="O196" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P196" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="Q196" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R196" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C197" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -9846,30 +9805,30 @@
         <v>0</v>
       </c>
       <c r="N197" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="O197" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P197" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="Q197" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R197" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C198" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -9878,30 +9837,30 @@
         <v>0</v>
       </c>
       <c r="N198" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="O198" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P198" t="s">
+        <v>692</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>251</v>
+      </c>
+      <c r="R198" t="s">
         <v>697</v>
-      </c>
-      <c r="Q198" t="s">
-        <v>256</v>
-      </c>
-      <c r="R198" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B199" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C199" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -9910,30 +9869,30 @@
         <v>0</v>
       </c>
       <c r="N199" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="O199" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P199" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="Q199" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R199" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B200" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C200" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -9942,30 +9901,30 @@
         <v>0</v>
       </c>
       <c r="N200" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="O200" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P200" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="Q200" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R200" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B201" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C201" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -9974,30 +9933,30 @@
         <v>0</v>
       </c>
       <c r="N201" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="O201" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P201" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="Q201" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R201" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B202" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C202" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -10006,30 +9965,30 @@
         <v>0</v>
       </c>
       <c r="N202" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="O202" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P202" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="Q202" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R202" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B203" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C203" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -10038,30 +9997,30 @@
         <v>0</v>
       </c>
       <c r="N203" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="O203" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P203" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>254</v>
+      </c>
+      <c r="R203" t="s">
         <v>718</v>
-      </c>
-      <c r="Q203" t="s">
-        <v>259</v>
-      </c>
-      <c r="R203" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B204" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C204" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -10070,30 +10029,30 @@
         <v>0</v>
       </c>
       <c r="N204" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="O204" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P204" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="Q204" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R204" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B205" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C205" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -10102,30 +10061,30 @@
         <v>0</v>
       </c>
       <c r="N205" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="O205" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P205" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="Q205" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R205" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B206" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C206" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -10134,30 +10093,30 @@
         <v>0</v>
       </c>
       <c r="N206" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="O206" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P206" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="Q206" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R206" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B207" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C207" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -10166,30 +10125,30 @@
         <v>0</v>
       </c>
       <c r="N207" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="O207" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P207" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="Q207" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R207" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B208" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C208" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -10198,30 +10157,30 @@
         <v>0</v>
       </c>
       <c r="N208" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="O208" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P208" t="s">
+        <v>734</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>223</v>
+      </c>
+      <c r="R208" t="s">
         <v>739</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>228</v>
-      </c>
-      <c r="R208" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B209" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C209" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -10230,30 +10189,30 @@
         <v>0</v>
       </c>
       <c r="N209" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="O209" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P209" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="Q209" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R209" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B210" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C210" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -10262,30 +10221,30 @@
         <v>0</v>
       </c>
       <c r="N210" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="O210" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P210" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="Q210" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R210" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B211" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C211" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -10294,30 +10253,30 @@
         <v>0</v>
       </c>
       <c r="N211" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="O211" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P211" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="Q211" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R211" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B212" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C212" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -10326,30 +10285,30 @@
         <v>0</v>
       </c>
       <c r="N212" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="O212" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P212" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Q212" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R212" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B213" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C213" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -10358,30 +10317,30 @@
         <v>0</v>
       </c>
       <c r="N213" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="O213" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P213" t="s">
+        <v>755</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>246</v>
+      </c>
+      <c r="R213" t="s">
         <v>760</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>251</v>
-      </c>
-      <c r="R213" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B214" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C214" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -10390,30 +10349,30 @@
         <v>0</v>
       </c>
       <c r="N214" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="O214" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P214" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Q214" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R214" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B215" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C215" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -10422,30 +10381,30 @@
         <v>0</v>
       </c>
       <c r="N215" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="O215" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P215" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Q215" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R215" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B216" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C216" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -10454,245 +10413,246 @@
         <v>0</v>
       </c>
       <c r="N216" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="O216" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P216" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Q216" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R216" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B217" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C217" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D217">
         <v>25</v>
       </c>
       <c r="M217" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N217" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>773</v>
+      </c>
+      <c r="B218" t="s">
+        <v>777</v>
+      </c>
+      <c r="C218" t="s">
         <v>778</v>
-      </c>
-      <c r="B218" t="s">
-        <v>782</v>
-      </c>
-      <c r="C218" t="s">
-        <v>783</v>
       </c>
       <c r="D218">
         <v>18</v>
       </c>
       <c r="M218" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="N218" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B219" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C219" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="D219">
         <v>15</v>
       </c>
       <c r="M219" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="N219" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B220" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C220" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="D220">
         <v>30</v>
       </c>
       <c r="M220" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="N220" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B221" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="C221" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="M221" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="N221" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B222" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C222" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="D222">
         <v>25</v>
       </c>
       <c r="M222" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="N222" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B223" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C223" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D223">
         <v>12</v>
       </c>
       <c r="N223" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B224" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C224" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D224">
         <v>15</v>
       </c>
       <c r="N224" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B225" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C225" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D225">
         <v>8</v>
       </c>
       <c r="N225" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B226" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C226" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D226">
         <v>30</v>
       </c>
       <c r="N226" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B227" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C227" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D227">
         <v>5</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B228" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="C228" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="D228">
         <v>35</v>
       </c>
       <c r="N228" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878DC1E3-16CE-4193-AD03-7D14E936201C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244DB9D7-22E0-406A-A512-ED6A03DFF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="820">
   <si>
     <t>池</t>
   </si>
@@ -2506,83 +2506,8 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>0.225</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>7.4999999999999997E-2</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
     <t>體質</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>2.2000000000000002</t>
-  </si>
-  <si>
-    <t>0.0025</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>0.16</t>
   </si>
 </sst>
 </file>
@@ -3175,7 +3100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3183,6 +3108,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3564,7 +3492,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="35.375" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3634,8 +3562,8 @@
       <c r="D2">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>819</v>
+      <c r="E2" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -3663,8 +3591,8 @@
       <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>820</v>
+      <c r="E3" s="3">
+        <v>0.08</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -3692,8 +3620,8 @@
       <c r="D4">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>819</v>
+      <c r="E4" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -3721,8 +3649,8 @@
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>820</v>
+      <c r="E5" s="3">
+        <v>0.08</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -3750,8 +3678,8 @@
       <c r="D6">
         <v>50</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>821</v>
+      <c r="E6" s="3">
+        <v>66</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -3779,8 +3707,8 @@
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>822</v>
+      <c r="E7" s="3">
+        <v>0.1</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -3808,8 +3736,8 @@
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>823</v>
+      <c r="E8" s="3">
+        <v>0.22500000000000001</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3818,7 +3746,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
@@ -3837,8 +3765,8 @@
       <c r="D9">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>824</v>
+      <c r="E9" s="3">
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -3846,8 +3774,8 @@
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>825</v>
+      <c r="H9" s="3">
+        <v>0.5</v>
       </c>
       <c r="J9" t="s">
         <v>30</v>
@@ -3866,8 +3794,8 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>826</v>
+      <c r="E10" s="3">
+        <v>0.02</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -3895,8 +3823,8 @@
       <c r="D11">
         <v>3</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>827</v>
+      <c r="E11" s="3">
+        <v>1.2</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3924,8 +3852,8 @@
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>827</v>
+      <c r="E12" s="3">
+        <v>1.2</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -3953,8 +3881,8 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>827</v>
+      <c r="E13" s="3">
+        <v>1.2</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -3977,13 +3905,13 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>827</v>
+      <c r="E14" s="3">
+        <v>1.2</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -4011,8 +3939,8 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>829</v>
+      <c r="E15" s="3">
+        <v>1.05</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -4040,8 +3968,8 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>820</v>
+      <c r="E16" s="3">
+        <v>0.08</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -4069,8 +3997,8 @@
       <c r="D17">
         <v>3</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>829</v>
+      <c r="E17" s="3">
+        <v>1.05</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -4098,8 +4026,8 @@
       <c r="D18">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>820</v>
+      <c r="E18" s="3">
+        <v>0.08</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
@@ -4127,8 +4055,8 @@
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>829</v>
+      <c r="E19" s="3">
+        <v>1.05</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -4159,8 +4087,8 @@
       <c r="D20">
         <v>30</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>830</v>
+      <c r="E20" s="3">
+        <v>2.1</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -4191,8 +4119,8 @@
       <c r="D21">
         <v>30</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>830</v>
+      <c r="E21" s="3">
+        <v>2.1</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -4223,8 +4151,8 @@
       <c r="D22">
         <v>30</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>830</v>
+      <c r="E22" s="3">
+        <v>2.1</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -4255,8 +4183,8 @@
       <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>831</v>
+      <c r="E23" s="3">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
@@ -4284,8 +4212,8 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>832</v>
+      <c r="E24" s="3">
+        <v>2.4E-2</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
@@ -4313,8 +4241,8 @@
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>833</v>
+      <c r="E25" s="3">
+        <v>0.4</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -4342,8 +4270,8 @@
       <c r="D26">
         <v>20</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>834</v>
+      <c r="E26" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
@@ -4351,8 +4279,8 @@
       <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>835</v>
+      <c r="H26" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="I26">
         <v>4</v>
@@ -4374,8 +4302,8 @@
       <c r="D27">
         <v>20</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>834</v>
+      <c r="E27" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
@@ -4383,8 +4311,8 @@
       <c r="G27">
         <v>4</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>835</v>
+      <c r="H27" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="I27">
         <v>4</v>
@@ -4406,8 +4334,8 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>834</v>
+      <c r="E28" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F28" t="s">
         <v>22</v>
@@ -4438,8 +4366,8 @@
       <c r="D29">
         <v>0.5</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>836</v>
+      <c r="E29" s="3">
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
@@ -4470,8 +4398,8 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>831</v>
+      <c r="E30" s="3">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F30" t="s">
         <v>22</v>
@@ -4499,8 +4427,8 @@
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>834</v>
+      <c r="E31" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>812</v>
@@ -4563,8 +4491,8 @@
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>820</v>
+      <c r="E33" s="3">
+        <v>0.08</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -4595,8 +4523,8 @@
       <c r="D34">
         <v>2</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>820</v>
+      <c r="E34" s="3">
+        <v>0.08</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
@@ -4627,8 +4555,8 @@
       <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>837</v>
+      <c r="E35" s="3">
+        <v>0.105</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
@@ -4659,8 +4587,8 @@
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>838</v>
+      <c r="E36" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F36" t="s">
         <v>22</v>
@@ -4691,8 +4619,8 @@
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>838</v>
+      <c r="E37" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F37" t="s">
         <v>22</v>
@@ -4723,8 +4651,8 @@
       <c r="D38">
         <v>5</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>838</v>
+      <c r="E38" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F38" t="s">
         <v>22</v>
@@ -4755,8 +4683,8 @@
       <c r="D39">
         <v>5</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>838</v>
+      <c r="E39" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -4787,8 +4715,8 @@
       <c r="D40">
         <v>5</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>838</v>
+      <c r="E40" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F40" t="s">
         <v>22</v>
@@ -4819,8 +4747,8 @@
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>838</v>
+      <c r="E41" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F41" t="s">
         <v>22</v>
@@ -4851,8 +4779,8 @@
       <c r="D42">
         <v>5</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>838</v>
+      <c r="E42" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
@@ -4883,8 +4811,8 @@
       <c r="D43">
         <v>5</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>838</v>
+      <c r="E43" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
@@ -4915,8 +4843,8 @@
       <c r="D44">
         <v>5</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>839</v>
+      <c r="E44" s="3">
+        <v>0.04</v>
       </c>
       <c r="F44" t="s">
         <v>22</v>
@@ -4947,8 +4875,8 @@
       <c r="D45">
         <v>5</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>839</v>
+      <c r="E45" s="3">
+        <v>0.04</v>
       </c>
       <c r="F45" t="s">
         <v>22</v>
@@ -4979,8 +4907,8 @@
       <c r="D46">
         <v>5</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>839</v>
+      <c r="E46" s="3">
+        <v>0.04</v>
       </c>
       <c r="F46" t="s">
         <v>22</v>
@@ -5011,8 +4939,8 @@
       <c r="D47">
         <v>5</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>839</v>
+      <c r="E47" s="3">
+        <v>0.04</v>
       </c>
       <c r="F47" t="s">
         <v>22</v>
@@ -5043,8 +4971,8 @@
       <c r="D48">
         <v>5</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>839</v>
+      <c r="E48" s="3">
+        <v>0.04</v>
       </c>
       <c r="F48" t="s">
         <v>22</v>
@@ -5075,8 +5003,8 @@
       <c r="D49">
         <v>5</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>839</v>
+      <c r="E49" s="3">
+        <v>0.04</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -5107,8 +5035,8 @@
       <c r="D50">
         <v>5</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>839</v>
+      <c r="E50" s="3">
+        <v>0.04</v>
       </c>
       <c r="F50" t="s">
         <v>22</v>
@@ -5139,8 +5067,8 @@
       <c r="D51">
         <v>5</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>839</v>
+      <c r="E51" s="3">
+        <v>0.04</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
@@ -5203,8 +5131,8 @@
       <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>840</v>
+      <c r="E53" s="3">
+        <v>0.03</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
@@ -5235,8 +5163,8 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>820</v>
+      <c r="E54" s="3">
+        <v>0.08</v>
       </c>
       <c r="F54" t="s">
         <v>22</v>
@@ -5267,8 +5195,8 @@
       <c r="D55">
         <v>2</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>826</v>
+      <c r="E55" s="3">
+        <v>0.02</v>
       </c>
       <c r="F55" t="s">
         <v>22</v>
@@ -5276,8 +5204,8 @@
       <c r="G55">
         <v>4</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>835</v>
+      <c r="H55" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="I55">
         <v>4</v>
@@ -5299,8 +5227,8 @@
       <c r="D56">
         <v>4</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>820</v>
+      <c r="E56" s="3">
+        <v>0.08</v>
       </c>
       <c r="F56" t="s">
         <v>22</v>
@@ -5331,8 +5259,8 @@
       <c r="D57">
         <v>5</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>840</v>
+      <c r="E57" s="3">
+        <v>0.03</v>
       </c>
       <c r="F57" t="s">
         <v>22</v>
@@ -5360,8 +5288,8 @@
       <c r="D58">
         <v>30</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>833</v>
+      <c r="E58" s="3">
+        <v>0.4</v>
       </c>
       <c r="F58" t="s">
         <v>22</v>
@@ -5389,8 +5317,8 @@
       <c r="D59">
         <v>30</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>833</v>
+      <c r="E59" s="3">
+        <v>0.4</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
@@ -5418,8 +5346,8 @@
       <c r="D60">
         <v>30</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>841</v>
+      <c r="E60" s="3">
+        <v>0.72</v>
       </c>
       <c r="F60" t="s">
         <v>22</v>
@@ -5447,8 +5375,8 @@
       <c r="D61">
         <v>30</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>841</v>
+      <c r="E61" s="3">
+        <v>0.72</v>
       </c>
       <c r="F61" t="s">
         <v>22</v>
@@ -5476,8 +5404,8 @@
       <c r="D62">
         <v>30</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>841</v>
+      <c r="E62" s="3">
+        <v>0.72</v>
       </c>
       <c r="F62" t="s">
         <v>22</v>
@@ -5505,8 +5433,8 @@
       <c r="D63">
         <v>30</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>841</v>
+      <c r="E63" s="3">
+        <v>0.72</v>
       </c>
       <c r="F63" t="s">
         <v>22</v>
@@ -5534,8 +5462,8 @@
       <c r="D64">
         <v>30</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>841</v>
+      <c r="E64" s="3">
+        <v>0.72</v>
       </c>
       <c r="F64" t="s">
         <v>22</v>
@@ -5563,8 +5491,8 @@
       <c r="D65">
         <v>30</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>841</v>
+      <c r="E65" s="3">
+        <v>0.72</v>
       </c>
       <c r="F65" t="s">
         <v>22</v>
@@ -5592,8 +5520,8 @@
       <c r="D66">
         <v>30</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>841</v>
+      <c r="E66" s="3">
+        <v>0.72</v>
       </c>
       <c r="F66" t="s">
         <v>22</v>
@@ -5621,8 +5549,8 @@
       <c r="D67">
         <v>30</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>841</v>
+      <c r="E67" s="3">
+        <v>0.72</v>
       </c>
       <c r="F67" t="s">
         <v>22</v>
@@ -5650,8 +5578,8 @@
       <c r="D68">
         <v>15</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>842</v>
+      <c r="E68" s="3">
+        <v>0.18</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
@@ -5682,8 +5610,8 @@
       <c r="D69">
         <v>10</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>820</v>
+      <c r="E69" s="3">
+        <v>0.08</v>
       </c>
       <c r="F69" t="s">
         <v>22</v>
@@ -5714,8 +5642,8 @@
       <c r="D70">
         <v>3</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>831</v>
+      <c r="E70" s="3">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -5743,8 +5671,8 @@
       <c r="D71">
         <v>2</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>826</v>
+      <c r="E71" s="3">
+        <v>0.02</v>
       </c>
       <c r="F71" t="s">
         <v>22</v>
@@ -5807,8 +5735,8 @@
       <c r="D73">
         <v>2</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>834</v>
+      <c r="E73" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F73" t="s">
         <v>22</v>
@@ -5839,8 +5767,8 @@
       <c r="D74">
         <v>3</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>843</v>
+      <c r="E74" s="3">
+        <v>0.6</v>
       </c>
       <c r="F74" t="s">
         <v>18</v>
@@ -5871,8 +5799,8 @@
       <c r="D75">
         <v>3</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>826</v>
+      <c r="E75" s="3">
+        <v>0.02</v>
       </c>
       <c r="F75" t="s">
         <v>22</v>
@@ -5903,8 +5831,8 @@
       <c r="D76">
         <v>3</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>834</v>
+      <c r="E76" s="3">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F76" t="s">
         <v>22</v>
@@ -5932,8 +5860,8 @@
       <c r="D77">
         <v>2.5</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>840</v>
+      <c r="E77" s="3">
+        <v>0.03</v>
       </c>
       <c r="F77" t="s">
         <v>22</v>
@@ -5961,8 +5889,8 @@
       <c r="D78">
         <v>2</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>844</v>
+      <c r="E78" s="3">
+        <v>0.16</v>
       </c>
       <c r="F78" t="s">
         <v>18</v>
@@ -5990,8 +5918,8 @@
       <c r="D79">
         <v>3</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>838</v>
+      <c r="E79" s="3">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F79" t="s">
         <v>22</v>
@@ -6022,8 +5950,8 @@
       <c r="D80">
         <v>4</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>820</v>
+      <c r="E80" s="3">
+        <v>0.08</v>
       </c>
       <c r="F80" t="s">
         <v>22</v>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-fireamp-cap-20261019\stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244DB9D7-22E0-406A-A512-ED6A03DFF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18283E1-C8F9-4FE4-8EE9-8E40F97C7D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -1553,12 +1553,6 @@
     <t>烈火狩</t>
   </si>
   <si>
-    <t>在火狩的持續時間內，每 0.5 秒你的火焰傷害提高 2%（火狩全部消失後結束）。</t>
-  </si>
-  <si>
-    <t>{"firehuntFireAmp":{"gap":0.5,"pct":2}}</t>
-  </si>
-  <si>
     <t>firehuntDetonate</t>
   </si>
   <si>
@@ -2507,6 +2501,14 @@
   </si>
   <si>
     <t>體質</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firehuntFireAmp":{"gap":0.5,"pct":2,"maxStacks":50}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在火狩的持續時間內，每 0.5 秒你的火焰傷害提高 2%，最多 50 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3100,7 +3102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3108,9 +3110,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3522,10 +3521,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -3562,7 +3561,7 @@
       <c r="D2">
         <v>4</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2">
         <v>2.2000000000000002</v>
       </c>
       <c r="F2" t="s">
@@ -3591,7 +3590,7 @@
       <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>0.08</v>
       </c>
       <c r="F3" t="s">
@@ -3620,7 +3619,7 @@
       <c r="D4">
         <v>4</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F4" t="s">
@@ -3649,7 +3648,7 @@
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>0.08</v>
       </c>
       <c r="F5" t="s">
@@ -3678,7 +3677,7 @@
       <c r="D6">
         <v>50</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>66</v>
       </c>
       <c r="F6" t="s">
@@ -3707,7 +3706,7 @@
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>0.1</v>
       </c>
       <c r="F7" t="s">
@@ -3736,7 +3735,7 @@
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>0.22500000000000001</v>
       </c>
       <c r="F8" t="s">
@@ -3765,7 +3764,7 @@
       <c r="D9">
         <v>10</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9">
         <v>12</v>
       </c>
       <c r="F9" t="s">
@@ -3774,7 +3773,7 @@
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>0.5</v>
       </c>
       <c r="J9" t="s">
@@ -3794,7 +3793,7 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
         <v>0.02</v>
       </c>
       <c r="F10" t="s">
@@ -3823,7 +3822,7 @@
       <c r="D11">
         <v>3</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11">
         <v>1.2</v>
       </c>
       <c r="F11" t="s">
@@ -3852,7 +3851,7 @@
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12">
         <v>1.2</v>
       </c>
       <c r="F12" t="s">
@@ -3881,7 +3880,7 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13">
         <v>1.2</v>
       </c>
       <c r="F13" t="s">
@@ -3905,12 +3904,12 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>1.2</v>
       </c>
       <c r="F14" t="s">
@@ -3939,7 +3938,7 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15">
         <v>1.05</v>
       </c>
       <c r="F15" t="s">
@@ -3968,7 +3967,7 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16">
         <v>0.08</v>
       </c>
       <c r="F16" t="s">
@@ -3997,7 +3996,7 @@
       <c r="D17">
         <v>3</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17">
         <v>1.05</v>
       </c>
       <c r="F17" t="s">
@@ -4026,7 +4025,7 @@
       <c r="D18">
         <v>4</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18">
         <v>0.08</v>
       </c>
       <c r="F18" t="s">
@@ -4055,7 +4054,7 @@
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19">
         <v>1.05</v>
       </c>
       <c r="F19" t="s">
@@ -4087,7 +4086,7 @@
       <c r="D20">
         <v>30</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20">
         <v>2.1</v>
       </c>
       <c r="F20" t="s">
@@ -4119,7 +4118,7 @@
       <c r="D21">
         <v>30</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21">
         <v>2.1</v>
       </c>
       <c r="F21" t="s">
@@ -4151,7 +4150,7 @@
       <c r="D22">
         <v>30</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22">
         <v>2.1</v>
       </c>
       <c r="F22" t="s">
@@ -4183,7 +4182,7 @@
       <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="F23" t="s">
@@ -4212,7 +4211,7 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24">
         <v>2.4E-2</v>
       </c>
       <c r="F24" t="s">
@@ -4241,7 +4240,7 @@
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25">
         <v>0.4</v>
       </c>
       <c r="F25" t="s">
@@ -4270,7 +4269,7 @@
       <c r="D26">
         <v>20</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F26" t="s">
@@ -4279,7 +4278,7 @@
       <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>2.2000000000000002</v>
       </c>
       <c r="I26">
@@ -4302,7 +4301,7 @@
       <c r="D27">
         <v>20</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F27" t="s">
@@ -4311,7 +4310,7 @@
       <c r="G27">
         <v>4</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <v>2.2000000000000002</v>
       </c>
       <c r="I27">
@@ -4334,7 +4333,7 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F28" t="s">
@@ -4366,7 +4365,7 @@
       <c r="D29">
         <v>0.5</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F29" t="s">
@@ -4382,7 +4381,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4398,7 +4397,7 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="F30" t="s">
@@ -4422,16 +4421,16 @@
         <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4443,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4454,7 +4453,7 @@
         <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4463,7 +4462,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4475,7 +4474,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4491,7 +4490,7 @@
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33">
         <v>0.08</v>
       </c>
       <c r="F33" t="s">
@@ -4523,7 +4522,7 @@
       <c r="D34">
         <v>2</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34">
         <v>0.08</v>
       </c>
       <c r="F34" t="s">
@@ -4555,7 +4554,7 @@
       <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35">
         <v>0.105</v>
       </c>
       <c r="F35" t="s">
@@ -4587,7 +4586,7 @@
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F36" t="s">
@@ -4619,7 +4618,7 @@
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F37" t="s">
@@ -4651,7 +4650,7 @@
       <c r="D38">
         <v>5</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F38" t="s">
@@ -4683,7 +4682,7 @@
       <c r="D39">
         <v>5</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F39" t="s">
@@ -4715,7 +4714,7 @@
       <c r="D40">
         <v>5</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F40" t="s">
@@ -4747,7 +4746,7 @@
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F41" t="s">
@@ -4779,7 +4778,7 @@
       <c r="D42">
         <v>5</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F42" t="s">
@@ -4811,7 +4810,7 @@
       <c r="D43">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F43" t="s">
@@ -4843,7 +4842,7 @@
       <c r="D44">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44">
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
@@ -4875,7 +4874,7 @@
       <c r="D45">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45">
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
@@ -4907,7 +4906,7 @@
       <c r="D46">
         <v>5</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46">
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
@@ -4939,7 +4938,7 @@
       <c r="D47">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47">
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
@@ -4971,7 +4970,7 @@
       <c r="D48">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48">
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
@@ -5003,7 +5002,7 @@
       <c r="D49">
         <v>5</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49">
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
@@ -5035,7 +5034,7 @@
       <c r="D50">
         <v>5</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50">
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
@@ -5067,7 +5066,7 @@
       <c r="D51">
         <v>5</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51">
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
@@ -5131,7 +5130,7 @@
       <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53">
         <v>0.03</v>
       </c>
       <c r="F53" t="s">
@@ -5163,7 +5162,7 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54">
         <v>0.08</v>
       </c>
       <c r="F54" t="s">
@@ -5195,7 +5194,7 @@
       <c r="D55">
         <v>2</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55">
         <v>0.02</v>
       </c>
       <c r="F55" t="s">
@@ -5204,7 +5203,7 @@
       <c r="G55">
         <v>4</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55">
         <v>2.2000000000000002</v>
       </c>
       <c r="I55">
@@ -5227,7 +5226,7 @@
       <c r="D56">
         <v>4</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56">
         <v>0.08</v>
       </c>
       <c r="F56" t="s">
@@ -5259,7 +5258,7 @@
       <c r="D57">
         <v>5</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57">
         <v>0.03</v>
       </c>
       <c r="F57" t="s">
@@ -5288,7 +5287,7 @@
       <c r="D58">
         <v>30</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58">
         <v>0.4</v>
       </c>
       <c r="F58" t="s">
@@ -5317,7 +5316,7 @@
       <c r="D59">
         <v>30</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59">
         <v>0.4</v>
       </c>
       <c r="F59" t="s">
@@ -5346,7 +5345,7 @@
       <c r="D60">
         <v>30</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60">
         <v>0.72</v>
       </c>
       <c r="F60" t="s">
@@ -5375,7 +5374,7 @@
       <c r="D61">
         <v>30</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61">
         <v>0.72</v>
       </c>
       <c r="F61" t="s">
@@ -5404,7 +5403,7 @@
       <c r="D62">
         <v>30</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62">
         <v>0.72</v>
       </c>
       <c r="F62" t="s">
@@ -5433,7 +5432,7 @@
       <c r="D63">
         <v>30</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63">
         <v>0.72</v>
       </c>
       <c r="F63" t="s">
@@ -5462,7 +5461,7 @@
       <c r="D64">
         <v>30</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64">
         <v>0.72</v>
       </c>
       <c r="F64" t="s">
@@ -5491,7 +5490,7 @@
       <c r="D65">
         <v>30</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65">
         <v>0.72</v>
       </c>
       <c r="F65" t="s">
@@ -5520,7 +5519,7 @@
       <c r="D66">
         <v>30</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66">
         <v>0.72</v>
       </c>
       <c r="F66" t="s">
@@ -5549,7 +5548,7 @@
       <c r="D67">
         <v>30</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67">
         <v>0.72</v>
       </c>
       <c r="F67" t="s">
@@ -5578,7 +5577,7 @@
       <c r="D68">
         <v>15</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68">
         <v>0.18</v>
       </c>
       <c r="F68" t="s">
@@ -5610,7 +5609,7 @@
       <c r="D69">
         <v>10</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69">
         <v>0.08</v>
       </c>
       <c r="F69" t="s">
@@ -5642,7 +5641,7 @@
       <c r="D70">
         <v>3</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="F70" t="s">
@@ -5671,7 +5670,7 @@
       <c r="D71">
         <v>2</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71">
         <v>0.02</v>
       </c>
       <c r="F71" t="s">
@@ -5735,7 +5734,7 @@
       <c r="D73">
         <v>2</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F73" t="s">
@@ -5767,7 +5766,7 @@
       <c r="D74">
         <v>3</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74">
         <v>0.6</v>
       </c>
       <c r="F74" t="s">
@@ -5799,7 +5798,7 @@
       <c r="D75">
         <v>3</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75">
         <v>0.02</v>
       </c>
       <c r="F75" t="s">
@@ -5831,7 +5830,7 @@
       <c r="D76">
         <v>3</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F76" t="s">
@@ -5860,7 +5859,7 @@
       <c r="D77">
         <v>2.5</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77">
         <v>0.03</v>
       </c>
       <c r="F77" t="s">
@@ -5889,7 +5888,7 @@
       <c r="D78">
         <v>2</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78">
         <v>0.16</v>
       </c>
       <c r="F78" t="s">
@@ -5918,7 +5917,7 @@
       <c r="D79">
         <v>3</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F79" t="s">
@@ -5950,7 +5949,7 @@
       <c r="D80">
         <v>4</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80">
         <v>0.08</v>
       </c>
       <c r="F80" t="s">
@@ -6552,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N103" t="s">
         <v>214</v>
@@ -8152,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>506</v>
+        <v>819</v>
       </c>
       <c r="N153" t="s">
         <v>258</v>
@@ -8164,7 +8163,7 @@
         <v>248</v>
       </c>
       <c r="Q153" t="s">
-        <v>507</v>
+        <v>818</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -8172,19 +8171,19 @@
         <v>192</v>
       </c>
       <c r="B154" t="s">
+        <v>506</v>
+      </c>
+      <c r="C154" t="s">
+        <v>507</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="M154" t="s">
         <v>508</v>
-      </c>
-      <c r="C154" t="s">
-        <v>509</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="s">
-        <v>510</v>
       </c>
       <c r="N154" t="s">
         <v>258</v>
@@ -8196,7 +8195,7 @@
         <v>248</v>
       </c>
       <c r="Q154" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -8204,19 +8203,19 @@
         <v>192</v>
       </c>
       <c r="B155" t="s">
+        <v>510</v>
+      </c>
+      <c r="C155" t="s">
+        <v>511</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="M155" t="s">
         <v>512</v>
-      </c>
-      <c r="C155" t="s">
-        <v>513</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-      <c r="M155" t="s">
-        <v>514</v>
       </c>
       <c r="N155" t="s">
         <v>258</v>
@@ -8228,7 +8227,7 @@
         <v>248</v>
       </c>
       <c r="Q155" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -8236,31 +8235,31 @@
         <v>192</v>
       </c>
       <c r="B156" t="s">
+        <v>514</v>
+      </c>
+      <c r="C156" t="s">
+        <v>515</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="s">
         <v>516</v>
       </c>
-      <c r="C156" t="s">
+      <c r="N156" t="s">
         <v>517</v>
       </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="M156" t="s">
+      <c r="O156" t="s">
         <v>518</v>
-      </c>
-      <c r="N156" t="s">
-        <v>519</v>
-      </c>
-      <c r="O156" t="s">
-        <v>520</v>
       </c>
       <c r="P156" t="s">
         <v>246</v>
       </c>
       <c r="Q156" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -8268,31 +8267,31 @@
         <v>192</v>
       </c>
       <c r="B157" t="s">
+        <v>520</v>
+      </c>
+      <c r="C157" t="s">
+        <v>521</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="M157" t="s">
         <v>522</v>
       </c>
-      <c r="C157" t="s">
-        <v>523</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <v>0</v>
-      </c>
-      <c r="M157" t="s">
-        <v>524</v>
-      </c>
       <c r="N157" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O157" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P157" t="s">
         <v>246</v>
       </c>
       <c r="Q157" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -8300,31 +8299,31 @@
         <v>192</v>
       </c>
       <c r="B158" t="s">
+        <v>524</v>
+      </c>
+      <c r="C158" t="s">
+        <v>525</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="M158" t="s">
         <v>526</v>
       </c>
-      <c r="C158" t="s">
-        <v>527</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <v>0</v>
-      </c>
-      <c r="M158" t="s">
-        <v>528</v>
-      </c>
       <c r="N158" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O158" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P158" t="s">
         <v>246</v>
       </c>
       <c r="Q158" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -8332,31 +8331,31 @@
         <v>192</v>
       </c>
       <c r="B159" t="s">
+        <v>528</v>
+      </c>
+      <c r="C159" t="s">
+        <v>529</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="M159" t="s">
         <v>530</v>
       </c>
-      <c r="C159" t="s">
-        <v>531</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="K159">
-        <v>0</v>
-      </c>
-      <c r="M159" t="s">
-        <v>532</v>
-      </c>
       <c r="N159" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O159" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P159" t="s">
         <v>246</v>
       </c>
       <c r="Q159" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -8364,31 +8363,31 @@
         <v>192</v>
       </c>
       <c r="B160" t="s">
+        <v>532</v>
+      </c>
+      <c r="C160" t="s">
+        <v>533</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="M160" t="s">
         <v>534</v>
       </c>
-      <c r="C160" t="s">
-        <v>535</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="K160">
-        <v>0</v>
-      </c>
-      <c r="M160" t="s">
-        <v>536</v>
-      </c>
       <c r="N160" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O160" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="P160" t="s">
         <v>246</v>
       </c>
       <c r="Q160" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -8396,31 +8395,31 @@
         <v>192</v>
       </c>
       <c r="B161" t="s">
+        <v>536</v>
+      </c>
+      <c r="C161" t="s">
+        <v>537</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="M161" t="s">
         <v>538</v>
       </c>
-      <c r="C161" t="s">
+      <c r="N161" t="s">
+        <v>517</v>
+      </c>
+      <c r="O161" t="s">
         <v>539</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <v>0</v>
-      </c>
-      <c r="M161" t="s">
-        <v>540</v>
-      </c>
-      <c r="N161" t="s">
-        <v>519</v>
-      </c>
-      <c r="O161" t="s">
-        <v>541</v>
       </c>
       <c r="P161" t="s">
         <v>238</v>
       </c>
       <c r="Q161" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -8428,31 +8427,31 @@
         <v>192</v>
       </c>
       <c r="B162" t="s">
+        <v>541</v>
+      </c>
+      <c r="C162" t="s">
+        <v>542</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="M162" t="s">
         <v>543</v>
       </c>
-      <c r="C162" t="s">
-        <v>544</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <v>0</v>
-      </c>
-      <c r="M162" t="s">
-        <v>545</v>
-      </c>
       <c r="N162" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O162" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P162" t="s">
         <v>238</v>
       </c>
       <c r="Q162" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -8460,31 +8459,31 @@
         <v>192</v>
       </c>
       <c r="B163" t="s">
+        <v>545</v>
+      </c>
+      <c r="C163" t="s">
+        <v>546</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="M163" t="s">
         <v>547</v>
       </c>
-      <c r="C163" t="s">
-        <v>548</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="K163">
-        <v>0</v>
-      </c>
-      <c r="M163" t="s">
-        <v>549</v>
-      </c>
       <c r="N163" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O163" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P163" t="s">
         <v>238</v>
       </c>
       <c r="Q163" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -8492,31 +8491,31 @@
         <v>192</v>
       </c>
       <c r="B164" t="s">
+        <v>549</v>
+      </c>
+      <c r="C164" t="s">
+        <v>550</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="M164" t="s">
         <v>551</v>
       </c>
-      <c r="C164" t="s">
-        <v>552</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="K164">
-        <v>0</v>
-      </c>
-      <c r="M164" t="s">
-        <v>553</v>
-      </c>
       <c r="N164" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O164" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P164" t="s">
         <v>238</v>
       </c>
       <c r="Q164" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -8524,31 +8523,31 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
+        <v>553</v>
+      </c>
+      <c r="C165" t="s">
+        <v>554</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="M165" t="s">
         <v>555</v>
       </c>
-      <c r="C165" t="s">
-        <v>556</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="K165">
-        <v>0</v>
-      </c>
-      <c r="M165" t="s">
-        <v>557</v>
-      </c>
       <c r="N165" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O165" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P165" t="s">
         <v>238</v>
       </c>
       <c r="Q165" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -8556,31 +8555,31 @@
         <v>192</v>
       </c>
       <c r="B166" t="s">
+        <v>557</v>
+      </c>
+      <c r="C166" t="s">
+        <v>558</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="M166" t="s">
         <v>559</v>
       </c>
-      <c r="C166" t="s">
+      <c r="N166" t="s">
+        <v>517</v>
+      </c>
+      <c r="O166" t="s">
         <v>560</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="K166">
-        <v>0</v>
-      </c>
-      <c r="M166" t="s">
-        <v>561</v>
-      </c>
-      <c r="N166" t="s">
-        <v>519</v>
-      </c>
-      <c r="O166" t="s">
-        <v>562</v>
       </c>
       <c r="P166" t="s">
         <v>242</v>
       </c>
       <c r="Q166" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -8588,31 +8587,31 @@
         <v>192</v>
       </c>
       <c r="B167" t="s">
+        <v>562</v>
+      </c>
+      <c r="C167" t="s">
+        <v>563</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="s">
         <v>564</v>
       </c>
-      <c r="C167" t="s">
-        <v>565</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="K167">
-        <v>0</v>
-      </c>
-      <c r="M167" t="s">
-        <v>566</v>
-      </c>
       <c r="N167" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O167" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P167" t="s">
         <v>242</v>
       </c>
       <c r="Q167" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -8620,31 +8619,31 @@
         <v>192</v>
       </c>
       <c r="B168" t="s">
+        <v>566</v>
+      </c>
+      <c r="C168" t="s">
+        <v>567</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="M168" t="s">
         <v>568</v>
       </c>
-      <c r="C168" t="s">
-        <v>569</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="K168">
-        <v>0</v>
-      </c>
-      <c r="M168" t="s">
-        <v>570</v>
-      </c>
       <c r="N168" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O168" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P168" t="s">
         <v>242</v>
       </c>
       <c r="Q168" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -8652,31 +8651,31 @@
         <v>192</v>
       </c>
       <c r="B169" t="s">
+        <v>570</v>
+      </c>
+      <c r="C169" t="s">
+        <v>571</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="M169" t="s">
         <v>572</v>
       </c>
-      <c r="C169" t="s">
-        <v>573</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="K169">
-        <v>0</v>
-      </c>
-      <c r="M169" t="s">
-        <v>574</v>
-      </c>
       <c r="N169" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O169" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P169" t="s">
         <v>242</v>
       </c>
       <c r="Q169" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -8684,31 +8683,31 @@
         <v>192</v>
       </c>
       <c r="B170" t="s">
+        <v>574</v>
+      </c>
+      <c r="C170" t="s">
+        <v>575</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="M170" t="s">
         <v>576</v>
       </c>
-      <c r="C170" t="s">
-        <v>577</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="K170">
-        <v>0</v>
-      </c>
-      <c r="M170" t="s">
-        <v>578</v>
-      </c>
       <c r="N170" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O170" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P170" t="s">
         <v>242</v>
       </c>
       <c r="Q170" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -8716,31 +8715,31 @@
         <v>192</v>
       </c>
       <c r="B171" t="s">
+        <v>578</v>
+      </c>
+      <c r="C171" t="s">
+        <v>579</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="M171" t="s">
         <v>580</v>
-      </c>
-      <c r="C171" t="s">
-        <v>581</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="K171">
-        <v>0</v>
-      </c>
-      <c r="M171" t="s">
-        <v>582</v>
       </c>
       <c r="N171" t="s">
         <v>249</v>
       </c>
       <c r="O171" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P171" t="s">
         <v>215</v>
       </c>
       <c r="Q171" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -8748,31 +8747,31 @@
         <v>192</v>
       </c>
       <c r="B172" t="s">
+        <v>583</v>
+      </c>
+      <c r="C172" t="s">
+        <v>584</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="M172" t="s">
         <v>585</v>
-      </c>
-      <c r="C172" t="s">
-        <v>586</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="K172">
-        <v>0</v>
-      </c>
-      <c r="M172" t="s">
-        <v>587</v>
       </c>
       <c r="N172" t="s">
         <v>249</v>
       </c>
       <c r="O172" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P172" t="s">
         <v>215</v>
       </c>
       <c r="Q172" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -8780,31 +8779,31 @@
         <v>192</v>
       </c>
       <c r="B173" t="s">
+        <v>587</v>
+      </c>
+      <c r="C173" t="s">
+        <v>588</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="M173" t="s">
         <v>589</v>
-      </c>
-      <c r="C173" t="s">
-        <v>590</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="K173">
-        <v>0</v>
-      </c>
-      <c r="M173" t="s">
-        <v>591</v>
       </c>
       <c r="N173" t="s">
         <v>249</v>
       </c>
       <c r="O173" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P173" t="s">
         <v>215</v>
       </c>
       <c r="Q173" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -8812,31 +8811,31 @@
         <v>192</v>
       </c>
       <c r="B174" t="s">
+        <v>591</v>
+      </c>
+      <c r="C174" t="s">
+        <v>592</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="M174" t="s">
         <v>593</v>
-      </c>
-      <c r="C174" t="s">
-        <v>594</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="M174" t="s">
-        <v>595</v>
       </c>
       <c r="N174" t="s">
         <v>249</v>
       </c>
       <c r="O174" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P174" t="s">
         <v>215</v>
       </c>
       <c r="Q174" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -8844,31 +8843,31 @@
         <v>192</v>
       </c>
       <c r="B175" t="s">
+        <v>595</v>
+      </c>
+      <c r="C175" t="s">
+        <v>596</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="M175" t="s">
         <v>597</v>
-      </c>
-      <c r="C175" t="s">
-        <v>598</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="K175">
-        <v>0</v>
-      </c>
-      <c r="M175" t="s">
-        <v>599</v>
       </c>
       <c r="N175" t="s">
         <v>249</v>
       </c>
       <c r="O175" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P175" t="s">
         <v>215</v>
       </c>
       <c r="Q175" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -8876,31 +8875,31 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
+        <v>599</v>
+      </c>
+      <c r="C176" t="s">
+        <v>600</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="M176" t="s">
         <v>601</v>
-      </c>
-      <c r="C176" t="s">
-        <v>602</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="K176">
-        <v>0</v>
-      </c>
-      <c r="M176" t="s">
-        <v>603</v>
       </c>
       <c r="N176" t="s">
         <v>249</v>
       </c>
       <c r="O176" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P176" t="s">
         <v>250</v>
       </c>
       <c r="Q176" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -8908,31 +8907,31 @@
         <v>192</v>
       </c>
       <c r="B177" t="s">
+        <v>604</v>
+      </c>
+      <c r="C177" t="s">
+        <v>605</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="M177" t="s">
         <v>606</v>
-      </c>
-      <c r="C177" t="s">
-        <v>607</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="K177">
-        <v>0</v>
-      </c>
-      <c r="M177" t="s">
-        <v>608</v>
       </c>
       <c r="N177" t="s">
         <v>249</v>
       </c>
       <c r="O177" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P177" t="s">
         <v>250</v>
       </c>
       <c r="Q177" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -8940,31 +8939,31 @@
         <v>192</v>
       </c>
       <c r="B178" t="s">
+        <v>608</v>
+      </c>
+      <c r="C178" t="s">
+        <v>609</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="M178" t="s">
         <v>610</v>
-      </c>
-      <c r="C178" t="s">
-        <v>611</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="K178">
-        <v>0</v>
-      </c>
-      <c r="M178" t="s">
-        <v>612</v>
       </c>
       <c r="N178" t="s">
         <v>249</v>
       </c>
       <c r="O178" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P178" t="s">
         <v>250</v>
       </c>
       <c r="Q178" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -8972,31 +8971,31 @@
         <v>192</v>
       </c>
       <c r="B179" t="s">
+        <v>612</v>
+      </c>
+      <c r="C179" t="s">
+        <v>613</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="M179" t="s">
         <v>614</v>
-      </c>
-      <c r="C179" t="s">
-        <v>615</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="K179">
-        <v>0</v>
-      </c>
-      <c r="M179" t="s">
-        <v>616</v>
       </c>
       <c r="N179" t="s">
         <v>249</v>
       </c>
       <c r="O179" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P179" t="s">
         <v>250</v>
       </c>
       <c r="Q179" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -9004,31 +9003,31 @@
         <v>192</v>
       </c>
       <c r="B180" t="s">
+        <v>616</v>
+      </c>
+      <c r="C180" t="s">
+        <v>617</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="M180" t="s">
         <v>618</v>
-      </c>
-      <c r="C180" t="s">
-        <v>619</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="M180" t="s">
-        <v>620</v>
       </c>
       <c r="N180" t="s">
         <v>249</v>
       </c>
       <c r="O180" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P180" t="s">
         <v>250</v>
       </c>
       <c r="Q180" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -9036,31 +9035,31 @@
         <v>192</v>
       </c>
       <c r="B181" t="s">
+        <v>620</v>
+      </c>
+      <c r="C181" t="s">
+        <v>621</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="M181" t="s">
         <v>622</v>
-      </c>
-      <c r="C181" t="s">
-        <v>623</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="K181">
-        <v>0</v>
-      </c>
-      <c r="M181" t="s">
-        <v>624</v>
       </c>
       <c r="N181" t="s">
         <v>249</v>
       </c>
       <c r="O181" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P181" t="s">
         <v>248</v>
       </c>
       <c r="Q181" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -9068,31 +9067,31 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
+        <v>625</v>
+      </c>
+      <c r="C182" t="s">
+        <v>626</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="M182" t="s">
         <v>627</v>
-      </c>
-      <c r="C182" t="s">
-        <v>628</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="K182">
-        <v>0</v>
-      </c>
-      <c r="M182" t="s">
-        <v>629</v>
       </c>
       <c r="N182" t="s">
         <v>249</v>
       </c>
       <c r="O182" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P182" t="s">
         <v>248</v>
       </c>
       <c r="Q182" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -9100,31 +9099,31 @@
         <v>192</v>
       </c>
       <c r="B183" t="s">
+        <v>629</v>
+      </c>
+      <c r="C183" t="s">
+        <v>630</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="M183" t="s">
         <v>631</v>
-      </c>
-      <c r="C183" t="s">
-        <v>632</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="K183">
-        <v>0</v>
-      </c>
-      <c r="M183" t="s">
-        <v>633</v>
       </c>
       <c r="N183" t="s">
         <v>249</v>
       </c>
       <c r="O183" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P183" t="s">
         <v>248</v>
       </c>
       <c r="Q183" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -9132,31 +9131,31 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>633</v>
+      </c>
+      <c r="C184" t="s">
+        <v>634</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="M184" t="s">
         <v>635</v>
-      </c>
-      <c r="C184" t="s">
-        <v>636</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="K184">
-        <v>0</v>
-      </c>
-      <c r="M184" t="s">
-        <v>637</v>
       </c>
       <c r="N184" t="s">
         <v>249</v>
       </c>
       <c r="O184" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P184" t="s">
         <v>248</v>
       </c>
       <c r="Q184" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -9164,31 +9163,31 @@
         <v>192</v>
       </c>
       <c r="B185" t="s">
+        <v>637</v>
+      </c>
+      <c r="C185" t="s">
+        <v>638</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="s">
         <v>639</v>
-      </c>
-      <c r="C185" t="s">
-        <v>640</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="M185" t="s">
-        <v>641</v>
       </c>
       <c r="N185" t="s">
         <v>249</v>
       </c>
       <c r="O185" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P185" t="s">
         <v>248</v>
       </c>
       <c r="Q185" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -9196,31 +9195,31 @@
         <v>192</v>
       </c>
       <c r="B186" t="s">
+        <v>641</v>
+      </c>
+      <c r="C186" t="s">
+        <v>642</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="M186" t="s">
         <v>643</v>
-      </c>
-      <c r="C186" t="s">
-        <v>644</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="K186">
-        <v>0</v>
-      </c>
-      <c r="M186" t="s">
-        <v>645</v>
       </c>
       <c r="N186" t="s">
         <v>245</v>
       </c>
       <c r="O186" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P186" t="s">
         <v>263</v>
       </c>
       <c r="Q186" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -9228,31 +9227,31 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
+        <v>646</v>
+      </c>
+      <c r="C187" t="s">
+        <v>647</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="M187" t="s">
         <v>648</v>
-      </c>
-      <c r="C187" t="s">
-        <v>649</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="K187">
-        <v>0</v>
-      </c>
-      <c r="M187" t="s">
-        <v>650</v>
       </c>
       <c r="N187" t="s">
         <v>245</v>
       </c>
       <c r="O187" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P187" t="s">
         <v>263</v>
       </c>
       <c r="Q187" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -9260,31 +9259,31 @@
         <v>192</v>
       </c>
       <c r="B188" t="s">
+        <v>650</v>
+      </c>
+      <c r="C188" t="s">
+        <v>651</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="M188" t="s">
         <v>652</v>
-      </c>
-      <c r="C188" t="s">
-        <v>653</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="K188">
-        <v>0</v>
-      </c>
-      <c r="M188" t="s">
-        <v>654</v>
       </c>
       <c r="N188" t="s">
         <v>245</v>
       </c>
       <c r="O188" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P188" t="s">
         <v>263</v>
       </c>
       <c r="Q188" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -9292,31 +9291,31 @@
         <v>192</v>
       </c>
       <c r="B189" t="s">
+        <v>654</v>
+      </c>
+      <c r="C189" t="s">
+        <v>655</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="M189" t="s">
         <v>656</v>
-      </c>
-      <c r="C189" t="s">
-        <v>657</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="K189">
-        <v>0</v>
-      </c>
-      <c r="M189" t="s">
-        <v>658</v>
       </c>
       <c r="N189" t="s">
         <v>245</v>
       </c>
       <c r="O189" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P189" t="s">
         <v>263</v>
       </c>
       <c r="Q189" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -9324,31 +9323,31 @@
         <v>192</v>
       </c>
       <c r="B190" t="s">
+        <v>658</v>
+      </c>
+      <c r="C190" t="s">
+        <v>659</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="M190" t="s">
         <v>660</v>
-      </c>
-      <c r="C190" t="s">
-        <v>661</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="K190">
-        <v>0</v>
-      </c>
-      <c r="M190" t="s">
-        <v>662</v>
       </c>
       <c r="N190" t="s">
         <v>245</v>
       </c>
       <c r="O190" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P190" t="s">
         <v>263</v>
       </c>
       <c r="Q190" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -9356,31 +9355,31 @@
         <v>192</v>
       </c>
       <c r="B191" t="s">
+        <v>662</v>
+      </c>
+      <c r="C191" t="s">
+        <v>663</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="M191" t="s">
         <v>664</v>
-      </c>
-      <c r="C191" t="s">
-        <v>665</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="K191">
-        <v>0</v>
-      </c>
-      <c r="M191" t="s">
-        <v>666</v>
       </c>
       <c r="N191" t="s">
         <v>245</v>
       </c>
       <c r="O191" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P191" t="s">
         <v>246</v>
       </c>
       <c r="Q191" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -9388,31 +9387,31 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
+        <v>667</v>
+      </c>
+      <c r="C192" t="s">
+        <v>668</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="M192" t="s">
         <v>669</v>
-      </c>
-      <c r="C192" t="s">
-        <v>670</v>
-      </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="K192">
-        <v>0</v>
-      </c>
-      <c r="M192" t="s">
-        <v>671</v>
       </c>
       <c r="N192" t="s">
         <v>245</v>
       </c>
       <c r="O192" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P192" t="s">
         <v>246</v>
       </c>
       <c r="Q192" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -9420,31 +9419,31 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>671</v>
+      </c>
+      <c r="C193" t="s">
+        <v>672</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="M193" t="s">
         <v>673</v>
-      </c>
-      <c r="C193" t="s">
-        <v>674</v>
-      </c>
-      <c r="D193">
-        <v>0</v>
-      </c>
-      <c r="K193">
-        <v>0</v>
-      </c>
-      <c r="M193" t="s">
-        <v>675</v>
       </c>
       <c r="N193" t="s">
         <v>245</v>
       </c>
       <c r="O193" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P193" t="s">
         <v>246</v>
       </c>
       <c r="Q193" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -9452,31 +9451,31 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
+        <v>675</v>
+      </c>
+      <c r="C194" t="s">
+        <v>676</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="M194" t="s">
         <v>677</v>
-      </c>
-      <c r="C194" t="s">
-        <v>678</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="K194">
-        <v>0</v>
-      </c>
-      <c r="M194" t="s">
-        <v>679</v>
       </c>
       <c r="N194" t="s">
         <v>245</v>
       </c>
       <c r="O194" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P194" t="s">
         <v>246</v>
       </c>
       <c r="Q194" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -9484,31 +9483,31 @@
         <v>192</v>
       </c>
       <c r="B195" t="s">
+        <v>679</v>
+      </c>
+      <c r="C195" t="s">
+        <v>680</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="M195" t="s">
         <v>681</v>
-      </c>
-      <c r="C195" t="s">
-        <v>682</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="K195">
-        <v>0</v>
-      </c>
-      <c r="M195" t="s">
-        <v>683</v>
       </c>
       <c r="N195" t="s">
         <v>245</v>
       </c>
       <c r="O195" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P195" t="s">
         <v>246</v>
       </c>
       <c r="Q195" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -9516,31 +9515,31 @@
         <v>192</v>
       </c>
       <c r="B196" t="s">
+        <v>683</v>
+      </c>
+      <c r="C196" t="s">
+        <v>684</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="M196" t="s">
         <v>685</v>
-      </c>
-      <c r="C196" t="s">
-        <v>686</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-      <c r="M196" t="s">
-        <v>687</v>
       </c>
       <c r="N196" t="s">
         <v>245</v>
       </c>
       <c r="O196" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P196" t="s">
         <v>247</v>
       </c>
       <c r="Q196" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -9548,31 +9547,31 @@
         <v>192</v>
       </c>
       <c r="B197" t="s">
+        <v>688</v>
+      </c>
+      <c r="C197" t="s">
+        <v>689</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="M197" t="s">
         <v>690</v>
-      </c>
-      <c r="C197" t="s">
-        <v>691</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="K197">
-        <v>0</v>
-      </c>
-      <c r="M197" t="s">
-        <v>692</v>
       </c>
       <c r="N197" t="s">
         <v>245</v>
       </c>
       <c r="O197" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P197" t="s">
         <v>247</v>
       </c>
       <c r="Q197" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -9580,31 +9579,31 @@
         <v>192</v>
       </c>
       <c r="B198" t="s">
+        <v>692</v>
+      </c>
+      <c r="C198" t="s">
+        <v>693</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="M198" t="s">
         <v>694</v>
-      </c>
-      <c r="C198" t="s">
-        <v>695</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="K198">
-        <v>0</v>
-      </c>
-      <c r="M198" t="s">
-        <v>696</v>
       </c>
       <c r="N198" t="s">
         <v>245</v>
       </c>
       <c r="O198" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P198" t="s">
         <v>247</v>
       </c>
       <c r="Q198" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -9612,31 +9611,31 @@
         <v>192</v>
       </c>
       <c r="B199" t="s">
+        <v>696</v>
+      </c>
+      <c r="C199" t="s">
+        <v>697</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="M199" t="s">
         <v>698</v>
-      </c>
-      <c r="C199" t="s">
-        <v>699</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="M199" t="s">
-        <v>700</v>
       </c>
       <c r="N199" t="s">
         <v>245</v>
       </c>
       <c r="O199" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P199" t="s">
         <v>247</v>
       </c>
       <c r="Q199" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -9644,31 +9643,31 @@
         <v>192</v>
       </c>
       <c r="B200" t="s">
+        <v>700</v>
+      </c>
+      <c r="C200" t="s">
+        <v>701</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="M200" t="s">
         <v>702</v>
-      </c>
-      <c r="C200" t="s">
-        <v>703</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="M200" t="s">
-        <v>704</v>
       </c>
       <c r="N200" t="s">
         <v>245</v>
       </c>
       <c r="O200" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P200" t="s">
         <v>247</v>
       </c>
       <c r="Q200" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -9676,31 +9675,31 @@
         <v>192</v>
       </c>
       <c r="B201" t="s">
+        <v>704</v>
+      </c>
+      <c r="C201" t="s">
+        <v>705</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="M201" t="s">
         <v>706</v>
-      </c>
-      <c r="C201" t="s">
-        <v>707</v>
-      </c>
-      <c r="D201">
-        <v>0</v>
-      </c>
-      <c r="K201">
-        <v>0</v>
-      </c>
-      <c r="M201" t="s">
-        <v>708</v>
       </c>
       <c r="N201" t="s">
         <v>349</v>
       </c>
       <c r="O201" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P201" t="s">
         <v>250</v>
       </c>
       <c r="Q201" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -9708,31 +9707,31 @@
         <v>192</v>
       </c>
       <c r="B202" t="s">
+        <v>709</v>
+      </c>
+      <c r="C202" t="s">
+        <v>710</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="M202" t="s">
         <v>711</v>
-      </c>
-      <c r="C202" t="s">
-        <v>712</v>
-      </c>
-      <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="K202">
-        <v>0</v>
-      </c>
-      <c r="M202" t="s">
-        <v>713</v>
       </c>
       <c r="N202" t="s">
         <v>349</v>
       </c>
       <c r="O202" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P202" t="s">
         <v>250</v>
       </c>
       <c r="Q202" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -9740,31 +9739,31 @@
         <v>192</v>
       </c>
       <c r="B203" t="s">
+        <v>713</v>
+      </c>
+      <c r="C203" t="s">
+        <v>714</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="M203" t="s">
         <v>715</v>
-      </c>
-      <c r="C203" t="s">
-        <v>716</v>
-      </c>
-      <c r="D203">
-        <v>0</v>
-      </c>
-      <c r="K203">
-        <v>0</v>
-      </c>
-      <c r="M203" t="s">
-        <v>717</v>
       </c>
       <c r="N203" t="s">
         <v>349</v>
       </c>
       <c r="O203" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P203" t="s">
         <v>250</v>
       </c>
       <c r="Q203" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -9772,31 +9771,31 @@
         <v>192</v>
       </c>
       <c r="B204" t="s">
+        <v>717</v>
+      </c>
+      <c r="C204" t="s">
+        <v>718</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="s">
         <v>719</v>
-      </c>
-      <c r="C204" t="s">
-        <v>720</v>
-      </c>
-      <c r="D204">
-        <v>0</v>
-      </c>
-      <c r="K204">
-        <v>0</v>
-      </c>
-      <c r="M204" t="s">
-        <v>721</v>
       </c>
       <c r="N204" t="s">
         <v>349</v>
       </c>
       <c r="O204" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P204" t="s">
         <v>250</v>
       </c>
       <c r="Q204" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -9804,31 +9803,31 @@
         <v>192</v>
       </c>
       <c r="B205" t="s">
+        <v>721</v>
+      </c>
+      <c r="C205" t="s">
+        <v>722</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="s">
         <v>723</v>
-      </c>
-      <c r="C205" t="s">
-        <v>724</v>
-      </c>
-      <c r="D205">
-        <v>0</v>
-      </c>
-      <c r="K205">
-        <v>0</v>
-      </c>
-      <c r="M205" t="s">
-        <v>725</v>
       </c>
       <c r="N205" t="s">
         <v>349</v>
       </c>
       <c r="O205" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P205" t="s">
         <v>250</v>
       </c>
       <c r="Q205" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -9836,31 +9835,31 @@
         <v>192</v>
       </c>
       <c r="B206" t="s">
+        <v>725</v>
+      </c>
+      <c r="C206" t="s">
+        <v>726</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="s">
         <v>727</v>
-      </c>
-      <c r="C206" t="s">
-        <v>728</v>
-      </c>
-      <c r="D206">
-        <v>0</v>
-      </c>
-      <c r="K206">
-        <v>0</v>
-      </c>
-      <c r="M206" t="s">
-        <v>729</v>
       </c>
       <c r="N206" t="s">
         <v>349</v>
       </c>
       <c r="O206" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P206" t="s">
         <v>219</v>
       </c>
       <c r="Q206" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -9868,31 +9867,31 @@
         <v>192</v>
       </c>
       <c r="B207" t="s">
+        <v>730</v>
+      </c>
+      <c r="C207" t="s">
+        <v>731</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="M207" t="s">
         <v>732</v>
-      </c>
-      <c r="C207" t="s">
-        <v>733</v>
-      </c>
-      <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="K207">
-        <v>0</v>
-      </c>
-      <c r="M207" t="s">
-        <v>734</v>
       </c>
       <c r="N207" t="s">
         <v>349</v>
       </c>
       <c r="O207" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P207" t="s">
         <v>219</v>
       </c>
       <c r="Q207" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -9900,31 +9899,31 @@
         <v>192</v>
       </c>
       <c r="B208" t="s">
+        <v>734</v>
+      </c>
+      <c r="C208" t="s">
+        <v>735</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="M208" t="s">
         <v>736</v>
-      </c>
-      <c r="C208" t="s">
-        <v>737</v>
-      </c>
-      <c r="D208">
-        <v>0</v>
-      </c>
-      <c r="K208">
-        <v>0</v>
-      </c>
-      <c r="M208" t="s">
-        <v>738</v>
       </c>
       <c r="N208" t="s">
         <v>349</v>
       </c>
       <c r="O208" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P208" t="s">
         <v>219</v>
       </c>
       <c r="Q208" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -9932,31 +9931,31 @@
         <v>192</v>
       </c>
       <c r="B209" t="s">
+        <v>738</v>
+      </c>
+      <c r="C209" t="s">
+        <v>739</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="M209" t="s">
         <v>740</v>
-      </c>
-      <c r="C209" t="s">
-        <v>741</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="K209">
-        <v>0</v>
-      </c>
-      <c r="M209" t="s">
-        <v>742</v>
       </c>
       <c r="N209" t="s">
         <v>349</v>
       </c>
       <c r="O209" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P209" t="s">
         <v>219</v>
       </c>
       <c r="Q209" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -9964,31 +9963,31 @@
         <v>192</v>
       </c>
       <c r="B210" t="s">
+        <v>742</v>
+      </c>
+      <c r="C210" t="s">
+        <v>743</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="M210" t="s">
         <v>744</v>
-      </c>
-      <c r="C210" t="s">
-        <v>745</v>
-      </c>
-      <c r="D210">
-        <v>0</v>
-      </c>
-      <c r="K210">
-        <v>0</v>
-      </c>
-      <c r="M210" t="s">
-        <v>746</v>
       </c>
       <c r="N210" t="s">
         <v>349</v>
       </c>
       <c r="O210" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P210" t="s">
         <v>219</v>
       </c>
       <c r="Q210" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -9996,31 +9995,31 @@
         <v>192</v>
       </c>
       <c r="B211" t="s">
+        <v>746</v>
+      </c>
+      <c r="C211" t="s">
+        <v>747</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="M211" t="s">
         <v>748</v>
-      </c>
-      <c r="C211" t="s">
-        <v>749</v>
-      </c>
-      <c r="D211">
-        <v>0</v>
-      </c>
-      <c r="K211">
-        <v>0</v>
-      </c>
-      <c r="M211" t="s">
-        <v>750</v>
       </c>
       <c r="N211" t="s">
         <v>349</v>
       </c>
       <c r="O211" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P211" t="s">
         <v>242</v>
       </c>
       <c r="Q211" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -10028,31 +10027,31 @@
         <v>192</v>
       </c>
       <c r="B212" t="s">
+        <v>751</v>
+      </c>
+      <c r="C212" t="s">
+        <v>752</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="M212" t="s">
         <v>753</v>
-      </c>
-      <c r="C212" t="s">
-        <v>754</v>
-      </c>
-      <c r="D212">
-        <v>0</v>
-      </c>
-      <c r="K212">
-        <v>0</v>
-      </c>
-      <c r="M212" t="s">
-        <v>755</v>
       </c>
       <c r="N212" t="s">
         <v>349</v>
       </c>
       <c r="O212" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P212" t="s">
         <v>242</v>
       </c>
       <c r="Q212" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -10060,31 +10059,31 @@
         <v>192</v>
       </c>
       <c r="B213" t="s">
+        <v>755</v>
+      </c>
+      <c r="C213" t="s">
+        <v>756</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="s">
         <v>757</v>
-      </c>
-      <c r="C213" t="s">
-        <v>758</v>
-      </c>
-      <c r="D213">
-        <v>0</v>
-      </c>
-      <c r="K213">
-        <v>0</v>
-      </c>
-      <c r="M213" t="s">
-        <v>759</v>
       </c>
       <c r="N213" t="s">
         <v>349</v>
       </c>
       <c r="O213" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P213" t="s">
         <v>242</v>
       </c>
       <c r="Q213" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -10092,31 +10091,31 @@
         <v>192</v>
       </c>
       <c r="B214" t="s">
+        <v>759</v>
+      </c>
+      <c r="C214" t="s">
+        <v>760</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
         <v>761</v>
-      </c>
-      <c r="C214" t="s">
-        <v>762</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="K214">
-        <v>0</v>
-      </c>
-      <c r="M214" t="s">
-        <v>763</v>
       </c>
       <c r="N214" t="s">
         <v>349</v>
       </c>
       <c r="O214" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P214" t="s">
         <v>242</v>
       </c>
       <c r="Q214" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -10124,42 +10123,42 @@
         <v>192</v>
       </c>
       <c r="B215" t="s">
+        <v>763</v>
+      </c>
+      <c r="C215" t="s">
+        <v>764</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="M215" t="s">
         <v>765</v>
-      </c>
-      <c r="C215" t="s">
-        <v>766</v>
-      </c>
-      <c r="D215">
-        <v>0</v>
-      </c>
-      <c r="K215">
-        <v>0</v>
-      </c>
-      <c r="M215" t="s">
-        <v>767</v>
       </c>
       <c r="N215" t="s">
         <v>349</v>
       </c>
       <c r="O215" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P215" t="s">
         <v>242</v>
       </c>
       <c r="Q215" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>767</v>
+      </c>
+      <c r="B216" t="s">
+        <v>768</v>
+      </c>
+      <c r="C216" t="s">
         <v>769</v>
-      </c>
-      <c r="B216" t="s">
-        <v>770</v>
-      </c>
-      <c r="C216" t="s">
-        <v>771</v>
       </c>
       <c r="D216">
         <v>25</v>
@@ -10168,209 +10167,209 @@
         <v>31</v>
       </c>
       <c r="M216" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B217" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C217" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D217">
         <v>18</v>
       </c>
       <c r="L217" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="M217" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B218" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C218" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D218">
         <v>15</v>
       </c>
       <c r="L218" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="M218" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B219" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C219" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D219">
         <v>30</v>
       </c>
       <c r="L219" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M219" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B220" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C220" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D220">
         <v>25</v>
       </c>
       <c r="L220" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="M220" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B221" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C221" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="M221" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B222" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C222" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D222">
         <v>12</v>
       </c>
       <c r="M222" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B223" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C223" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D223">
         <v>15</v>
       </c>
       <c r="M223" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B224" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C224" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D224">
         <v>8</v>
       </c>
       <c r="M224" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B225" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C225" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D225">
         <v>30</v>
       </c>
       <c r="M225" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B226" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C226" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D226">
         <v>5</v>
       </c>
       <c r="M226" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B227" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C227" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D227">
         <v>35</v>
       </c>
       <c r="M227" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-fireamp-cap-20261019\stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18283E1-C8F9-4FE4-8EE9-8E40F97C7D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD99C3C-28F3-442F-A22B-5F4C34AF7B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -1763,9 +1763,6 @@
     <t>不滅意志</t>
   </si>
   <si>
-    <t>【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
-  </si>
-  <si>
     <t>{"egKillInvuln":{"sec":0.5}}</t>
   </si>
   <si>
@@ -2509,6 +2506,10 @@
   </si>
   <si>
     <t>在火狩的持續時間內，每 0.5 秒你的火焰傷害提高 2%，最多 50 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3488,14 +3489,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q227"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3521,10 +3522,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -3548,7 +3549,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3606,7 +3607,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3809,7 +3810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3904,7 +3905,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -3925,7 +3926,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -3954,7 +3955,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3983,7 +3984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -4012,7 +4013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4041,7 +4042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -4105,7 +4106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -4169,7 +4170,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -4227,7 +4228,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -4256,7 +4257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -4288,7 +4289,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -4320,7 +4321,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -4381,10 +4382,10 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -4421,7 +4422,7 @@
         <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -4430,7 +4431,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4442,10 +4443,10 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -4453,7 +4454,7 @@
         <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4462,7 +4463,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4474,10 +4475,10 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -4541,7 +4542,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -4573,7 +4574,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -4637,7 +4638,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -4669,7 +4670,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -4701,7 +4702,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -4733,7 +4734,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -4797,7 +4798,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -4829,7 +4830,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -4861,7 +4862,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -4925,7 +4926,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -4957,7 +4958,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -4989,7 +4990,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -5021,7 +5022,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -5085,7 +5086,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -5181,7 +5182,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -5213,7 +5214,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -5245,7 +5246,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -5274,7 +5275,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -5303,7 +5304,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -5332,7 +5333,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -5361,7 +5362,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -5390,7 +5391,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -5419,7 +5420,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -5448,7 +5449,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -5477,7 +5478,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -5506,7 +5507,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -5535,7 +5536,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -5564,7 +5565,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -5596,7 +5597,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -5628,7 +5629,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -5657,7 +5658,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -5689,7 +5690,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -5721,7 +5722,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -5817,7 +5818,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -5904,7 +5905,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -5936,7 +5937,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -5968,7 +5969,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>192</v>
       </c>
@@ -5988,7 +5989,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>192</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>192</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>192</v>
       </c>
@@ -6048,7 +6049,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>192</v>
       </c>
@@ -6068,7 +6069,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -6088,7 +6089,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>192</v>
       </c>
@@ -6108,7 +6109,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>192</v>
       </c>
@@ -6134,7 +6135,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -6163,7 +6164,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>192</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>192</v>
       </c>
@@ -6218,7 +6219,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>192</v>
       </c>
@@ -6244,7 +6245,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>192</v>
       </c>
@@ -6270,7 +6271,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>192</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>192</v>
       </c>
@@ -6328,7 +6329,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>192</v>
       </c>
@@ -6357,7 +6358,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -6386,7 +6387,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -6415,7 +6416,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>192</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>192</v>
       </c>
@@ -6470,7 +6471,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>192</v>
       </c>
@@ -6502,7 +6503,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>192</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>192</v>
       </c>
@@ -6551,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="N103" t="s">
         <v>214</v>
@@ -6566,7 +6567,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>192</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>192</v>
       </c>
@@ -6630,7 +6631,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>192</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>192</v>
       </c>
@@ -6694,7 +6695,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>192</v>
       </c>
@@ -6726,7 +6727,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>192</v>
       </c>
@@ -6758,7 +6759,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>192</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>192</v>
       </c>
@@ -6822,7 +6823,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>192</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>192</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>192</v>
       </c>
@@ -6918,7 +6919,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>192</v>
       </c>
@@ -6950,7 +6951,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>192</v>
       </c>
@@ -6982,7 +6983,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>192</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>192</v>
       </c>
@@ -7046,7 +7047,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>192</v>
       </c>
@@ -7078,7 +7079,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>192</v>
       </c>
@@ -7110,7 +7111,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>192</v>
       </c>
@@ -7142,7 +7143,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>192</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>192</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>192</v>
       </c>
@@ -7238,7 +7239,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>192</v>
       </c>
@@ -7270,7 +7271,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -7302,7 +7303,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>192</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>192</v>
       </c>
@@ -7366,7 +7367,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>192</v>
       </c>
@@ -7398,7 +7399,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>192</v>
       </c>
@@ -7430,7 +7431,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>192</v>
       </c>
@@ -7462,7 +7463,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>192</v>
       </c>
@@ -7494,7 +7495,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>192</v>
       </c>
@@ -7526,7 +7527,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>192</v>
       </c>
@@ -7558,7 +7559,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>192</v>
       </c>
@@ -7590,7 +7591,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>192</v>
       </c>
@@ -7622,7 +7623,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>192</v>
       </c>
@@ -7654,7 +7655,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>192</v>
       </c>
@@ -7686,7 +7687,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>192</v>
       </c>
@@ -7718,7 +7719,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>192</v>
       </c>
@@ -7750,7 +7751,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>192</v>
       </c>
@@ -7782,7 +7783,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>192</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>192</v>
       </c>
@@ -7846,7 +7847,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>192</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>192</v>
       </c>
@@ -7910,7 +7911,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>192</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>192</v>
       </c>
@@ -7974,7 +7975,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>192</v>
       </c>
@@ -8006,7 +8007,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>192</v>
       </c>
@@ -8038,7 +8039,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>192</v>
       </c>
@@ -8070,7 +8071,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>192</v>
       </c>
@@ -8102,7 +8103,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>192</v>
       </c>
@@ -8134,7 +8135,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>192</v>
       </c>
@@ -8151,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N153" t="s">
         <v>258</v>
@@ -8163,10 +8164,10 @@
         <v>248</v>
       </c>
       <c r="Q153" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>192</v>
       </c>
@@ -8198,7 +8199,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>192</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>192</v>
       </c>
@@ -8262,7 +8263,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>192</v>
       </c>
@@ -8294,7 +8295,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>192</v>
       </c>
@@ -8326,7 +8327,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>192</v>
       </c>
@@ -8358,7 +8359,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>192</v>
       </c>
@@ -8390,7 +8391,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>192</v>
       </c>
@@ -8422,7 +8423,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>192</v>
       </c>
@@ -8454,7 +8455,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -8486,7 +8487,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>192</v>
       </c>
@@ -8550,7 +8551,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>192</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>192</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>192</v>
       </c>
@@ -8646,7 +8647,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>192</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>192</v>
       </c>
@@ -8695,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="M170" t="s">
-        <v>576</v>
+        <v>819</v>
       </c>
       <c r="N170" t="s">
         <v>517</v>
@@ -8707,1458 +8708,1458 @@
         <v>242</v>
       </c>
       <c r="Q170" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>192</v>
+      </c>
+      <c r="B171" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>192</v>
-      </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>578</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="M171" t="s">
         <v>579</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="K171">
-        <v>0</v>
-      </c>
-      <c r="M171" t="s">
-        <v>580</v>
       </c>
       <c r="N171" t="s">
         <v>249</v>
       </c>
       <c r="O171" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P171" t="s">
         <v>215</v>
       </c>
       <c r="Q171" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>192</v>
+      </c>
+      <c r="B172" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>192</v>
-      </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>583</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="M172" t="s">
         <v>584</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="K172">
-        <v>0</v>
-      </c>
-      <c r="M172" t="s">
-        <v>585</v>
       </c>
       <c r="N172" t="s">
         <v>249</v>
       </c>
       <c r="O172" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P172" t="s">
         <v>215</v>
       </c>
       <c r="Q172" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>192</v>
+      </c>
+      <c r="B173" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>192</v>
-      </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>587</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="M173" t="s">
         <v>588</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="K173">
-        <v>0</v>
-      </c>
-      <c r="M173" t="s">
-        <v>589</v>
       </c>
       <c r="N173" t="s">
         <v>249</v>
       </c>
       <c r="O173" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P173" t="s">
         <v>215</v>
       </c>
       <c r="Q173" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>192</v>
+      </c>
+      <c r="B174" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>192</v>
-      </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>591</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="M174" t="s">
         <v>592</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="M174" t="s">
-        <v>593</v>
       </c>
       <c r="N174" t="s">
         <v>249</v>
       </c>
       <c r="O174" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P174" t="s">
         <v>215</v>
       </c>
       <c r="Q174" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>192</v>
+      </c>
+      <c r="B175" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>192</v>
-      </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>595</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="M175" t="s">
         <v>596</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="K175">
-        <v>0</v>
-      </c>
-      <c r="M175" t="s">
-        <v>597</v>
       </c>
       <c r="N175" t="s">
         <v>249</v>
       </c>
       <c r="O175" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P175" t="s">
         <v>215</v>
       </c>
       <c r="Q175" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>192</v>
+      </c>
+      <c r="B176" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>192</v>
-      </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>599</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="M176" t="s">
         <v>600</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="K176">
-        <v>0</v>
-      </c>
-      <c r="M176" t="s">
-        <v>601</v>
       </c>
       <c r="N176" t="s">
         <v>249</v>
       </c>
       <c r="O176" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P176" t="s">
         <v>250</v>
       </c>
       <c r="Q176" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>192</v>
+      </c>
+      <c r="B177" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>192</v>
-      </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>604</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="M177" t="s">
         <v>605</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="K177">
-        <v>0</v>
-      </c>
-      <c r="M177" t="s">
-        <v>606</v>
       </c>
       <c r="N177" t="s">
         <v>249</v>
       </c>
       <c r="O177" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P177" t="s">
         <v>250</v>
       </c>
       <c r="Q177" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>192</v>
+      </c>
+      <c r="B178" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>192</v>
-      </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>608</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="M178" t="s">
         <v>609</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="K178">
-        <v>0</v>
-      </c>
-      <c r="M178" t="s">
-        <v>610</v>
       </c>
       <c r="N178" t="s">
         <v>249</v>
       </c>
       <c r="O178" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P178" t="s">
         <v>250</v>
       </c>
       <c r="Q178" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>192</v>
+      </c>
+      <c r="B179" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>192</v>
-      </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>612</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="M179" t="s">
         <v>613</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="K179">
-        <v>0</v>
-      </c>
-      <c r="M179" t="s">
-        <v>614</v>
       </c>
       <c r="N179" t="s">
         <v>249</v>
       </c>
       <c r="O179" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P179" t="s">
         <v>250</v>
       </c>
       <c r="Q179" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>192</v>
+      </c>
+      <c r="B180" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>192</v>
-      </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>616</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="M180" t="s">
         <v>617</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="M180" t="s">
-        <v>618</v>
       </c>
       <c r="N180" t="s">
         <v>249</v>
       </c>
       <c r="O180" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P180" t="s">
         <v>250</v>
       </c>
       <c r="Q180" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>192</v>
+      </c>
+      <c r="B181" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>192</v>
-      </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>620</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="M181" t="s">
         <v>621</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="K181">
-        <v>0</v>
-      </c>
-      <c r="M181" t="s">
-        <v>622</v>
       </c>
       <c r="N181" t="s">
         <v>249</v>
       </c>
       <c r="O181" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P181" t="s">
         <v>248</v>
       </c>
       <c r="Q181" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>192</v>
+      </c>
+      <c r="B182" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>192</v>
-      </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>625</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="M182" t="s">
         <v>626</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="K182">
-        <v>0</v>
-      </c>
-      <c r="M182" t="s">
-        <v>627</v>
       </c>
       <c r="N182" t="s">
         <v>249</v>
       </c>
       <c r="O182" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P182" t="s">
         <v>248</v>
       </c>
       <c r="Q182" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>192</v>
+      </c>
+      <c r="B183" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>192</v>
-      </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>629</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="M183" t="s">
         <v>630</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="K183">
-        <v>0</v>
-      </c>
-      <c r="M183" t="s">
-        <v>631</v>
       </c>
       <c r="N183" t="s">
         <v>249</v>
       </c>
       <c r="O183" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P183" t="s">
         <v>248</v>
       </c>
       <c r="Q183" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>192</v>
+      </c>
+      <c r="B184" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>192</v>
-      </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>633</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="M184" t="s">
         <v>634</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="K184">
-        <v>0</v>
-      </c>
-      <c r="M184" t="s">
-        <v>635</v>
       </c>
       <c r="N184" t="s">
         <v>249</v>
       </c>
       <c r="O184" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P184" t="s">
         <v>248</v>
       </c>
       <c r="Q184" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>192</v>
-      </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>637</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="s">
         <v>638</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="M185" t="s">
-        <v>639</v>
       </c>
       <c r="N185" t="s">
         <v>249</v>
       </c>
       <c r="O185" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P185" t="s">
         <v>248</v>
       </c>
       <c r="Q185" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>192</v>
+      </c>
+      <c r="B186" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>192</v>
-      </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>641</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="M186" t="s">
         <v>642</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="K186">
-        <v>0</v>
-      </c>
-      <c r="M186" t="s">
-        <v>643</v>
       </c>
       <c r="N186" t="s">
         <v>245</v>
       </c>
       <c r="O186" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P186" t="s">
         <v>263</v>
       </c>
       <c r="Q186" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>192</v>
-      </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>646</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="M187" t="s">
         <v>647</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="K187">
-        <v>0</v>
-      </c>
-      <c r="M187" t="s">
-        <v>648</v>
       </c>
       <c r="N187" t="s">
         <v>245</v>
       </c>
       <c r="O187" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P187" t="s">
         <v>263</v>
       </c>
       <c r="Q187" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>192</v>
+      </c>
+      <c r="B188" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>192</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>650</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="M188" t="s">
         <v>651</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="K188">
-        <v>0</v>
-      </c>
-      <c r="M188" t="s">
-        <v>652</v>
       </c>
       <c r="N188" t="s">
         <v>245</v>
       </c>
       <c r="O188" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P188" t="s">
         <v>263</v>
       </c>
       <c r="Q188" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>192</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>654</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="M189" t="s">
         <v>655</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="K189">
-        <v>0</v>
-      </c>
-      <c r="M189" t="s">
-        <v>656</v>
       </c>
       <c r="N189" t="s">
         <v>245</v>
       </c>
       <c r="O189" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P189" t="s">
         <v>263</v>
       </c>
       <c r="Q189" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>192</v>
+      </c>
+      <c r="B190" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>192</v>
-      </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>658</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="M190" t="s">
         <v>659</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="K190">
-        <v>0</v>
-      </c>
-      <c r="M190" t="s">
-        <v>660</v>
       </c>
       <c r="N190" t="s">
         <v>245</v>
       </c>
       <c r="O190" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P190" t="s">
         <v>263</v>
       </c>
       <c r="Q190" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>192</v>
+      </c>
+      <c r="B191" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>192</v>
-      </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>662</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="M191" t="s">
         <v>663</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="K191">
-        <v>0</v>
-      </c>
-      <c r="M191" t="s">
-        <v>664</v>
       </c>
       <c r="N191" t="s">
         <v>245</v>
       </c>
       <c r="O191" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P191" t="s">
         <v>246</v>
       </c>
       <c r="Q191" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>192</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>667</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="M192" t="s">
         <v>668</v>
-      </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="K192">
-        <v>0</v>
-      </c>
-      <c r="M192" t="s">
-        <v>669</v>
       </c>
       <c r="N192" t="s">
         <v>245</v>
       </c>
       <c r="O192" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P192" t="s">
         <v>246</v>
       </c>
       <c r="Q192" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>192</v>
-      </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>671</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="M193" t="s">
         <v>672</v>
-      </c>
-      <c r="D193">
-        <v>0</v>
-      </c>
-      <c r="K193">
-        <v>0</v>
-      </c>
-      <c r="M193" t="s">
-        <v>673</v>
       </c>
       <c r="N193" t="s">
         <v>245</v>
       </c>
       <c r="O193" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P193" t="s">
         <v>246</v>
       </c>
       <c r="Q193" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>192</v>
+      </c>
+      <c r="B194" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>192</v>
-      </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>675</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="M194" t="s">
         <v>676</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="K194">
-        <v>0</v>
-      </c>
-      <c r="M194" t="s">
-        <v>677</v>
       </c>
       <c r="N194" t="s">
         <v>245</v>
       </c>
       <c r="O194" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P194" t="s">
         <v>246</v>
       </c>
       <c r="Q194" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>192</v>
+      </c>
+      <c r="B195" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>192</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>679</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="M195" t="s">
         <v>680</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="K195">
-        <v>0</v>
-      </c>
-      <c r="M195" t="s">
-        <v>681</v>
       </c>
       <c r="N195" t="s">
         <v>245</v>
       </c>
       <c r="O195" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P195" t="s">
         <v>246</v>
       </c>
       <c r="Q195" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>192</v>
+      </c>
+      <c r="B196" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>192</v>
-      </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>683</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="M196" t="s">
         <v>684</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-      <c r="M196" t="s">
-        <v>685</v>
       </c>
       <c r="N196" t="s">
         <v>245</v>
       </c>
       <c r="O196" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P196" t="s">
         <v>247</v>
       </c>
       <c r="Q196" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>192</v>
+      </c>
+      <c r="B197" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>192</v>
-      </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>688</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="M197" t="s">
         <v>689</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="K197">
-        <v>0</v>
-      </c>
-      <c r="M197" t="s">
-        <v>690</v>
       </c>
       <c r="N197" t="s">
         <v>245</v>
       </c>
       <c r="O197" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P197" t="s">
         <v>247</v>
       </c>
       <c r="Q197" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>192</v>
+      </c>
+      <c r="B198" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>192</v>
-      </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>692</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="M198" t="s">
         <v>693</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="K198">
-        <v>0</v>
-      </c>
-      <c r="M198" t="s">
-        <v>694</v>
       </c>
       <c r="N198" t="s">
         <v>245</v>
       </c>
       <c r="O198" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P198" t="s">
         <v>247</v>
       </c>
       <c r="Q198" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>192</v>
+      </c>
+      <c r="B199" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>192</v>
-      </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>696</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="M199" t="s">
         <v>697</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="M199" t="s">
-        <v>698</v>
       </c>
       <c r="N199" t="s">
         <v>245</v>
       </c>
       <c r="O199" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P199" t="s">
         <v>247</v>
       </c>
       <c r="Q199" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>192</v>
+      </c>
+      <c r="B200" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>192</v>
-      </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>700</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="M200" t="s">
         <v>701</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="M200" t="s">
-        <v>702</v>
       </c>
       <c r="N200" t="s">
         <v>245</v>
       </c>
       <c r="O200" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P200" t="s">
         <v>247</v>
       </c>
       <c r="Q200" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>192</v>
+      </c>
+      <c r="B201" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>192</v>
-      </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>704</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="M201" t="s">
         <v>705</v>
-      </c>
-      <c r="D201">
-        <v>0</v>
-      </c>
-      <c r="K201">
-        <v>0</v>
-      </c>
-      <c r="M201" t="s">
-        <v>706</v>
       </c>
       <c r="N201" t="s">
         <v>349</v>
       </c>
       <c r="O201" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P201" t="s">
         <v>250</v>
       </c>
       <c r="Q201" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>192</v>
+      </c>
+      <c r="B202" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>192</v>
-      </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>709</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="M202" t="s">
         <v>710</v>
-      </c>
-      <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="K202">
-        <v>0</v>
-      </c>
-      <c r="M202" t="s">
-        <v>711</v>
       </c>
       <c r="N202" t="s">
         <v>349</v>
       </c>
       <c r="O202" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P202" t="s">
         <v>250</v>
       </c>
       <c r="Q202" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>192</v>
+      </c>
+      <c r="B203" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>192</v>
-      </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>713</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="M203" t="s">
         <v>714</v>
-      </c>
-      <c r="D203">
-        <v>0</v>
-      </c>
-      <c r="K203">
-        <v>0</v>
-      </c>
-      <c r="M203" t="s">
-        <v>715</v>
       </c>
       <c r="N203" t="s">
         <v>349</v>
       </c>
       <c r="O203" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P203" t="s">
         <v>250</v>
       </c>
       <c r="Q203" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>192</v>
+      </c>
+      <c r="B204" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>192</v>
-      </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>717</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="s">
         <v>718</v>
-      </c>
-      <c r="D204">
-        <v>0</v>
-      </c>
-      <c r="K204">
-        <v>0</v>
-      </c>
-      <c r="M204" t="s">
-        <v>719</v>
       </c>
       <c r="N204" t="s">
         <v>349</v>
       </c>
       <c r="O204" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P204" t="s">
         <v>250</v>
       </c>
       <c r="Q204" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>192</v>
+      </c>
+      <c r="B205" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>192</v>
-      </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>721</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="s">
         <v>722</v>
-      </c>
-      <c r="D205">
-        <v>0</v>
-      </c>
-      <c r="K205">
-        <v>0</v>
-      </c>
-      <c r="M205" t="s">
-        <v>723</v>
       </c>
       <c r="N205" t="s">
         <v>349</v>
       </c>
       <c r="O205" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P205" t="s">
         <v>250</v>
       </c>
       <c r="Q205" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>192</v>
+      </c>
+      <c r="B206" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>192</v>
-      </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>725</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="s">
         <v>726</v>
-      </c>
-      <c r="D206">
-        <v>0</v>
-      </c>
-      <c r="K206">
-        <v>0</v>
-      </c>
-      <c r="M206" t="s">
-        <v>727</v>
       </c>
       <c r="N206" t="s">
         <v>349</v>
       </c>
       <c r="O206" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P206" t="s">
         <v>219</v>
       </c>
       <c r="Q206" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>192</v>
+      </c>
+      <c r="B207" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>192</v>
-      </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
         <v>730</v>
       </c>
-      <c r="C207" t="s">
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="M207" t="s">
         <v>731</v>
-      </c>
-      <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="K207">
-        <v>0</v>
-      </c>
-      <c r="M207" t="s">
-        <v>732</v>
       </c>
       <c r="N207" t="s">
         <v>349</v>
       </c>
       <c r="O207" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P207" t="s">
         <v>219</v>
       </c>
       <c r="Q207" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>192</v>
+      </c>
+      <c r="B208" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>192</v>
-      </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>734</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="M208" t="s">
         <v>735</v>
-      </c>
-      <c r="D208">
-        <v>0</v>
-      </c>
-      <c r="K208">
-        <v>0</v>
-      </c>
-      <c r="M208" t="s">
-        <v>736</v>
       </c>
       <c r="N208" t="s">
         <v>349</v>
       </c>
       <c r="O208" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P208" t="s">
         <v>219</v>
       </c>
       <c r="Q208" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>192</v>
+      </c>
+      <c r="B209" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>192</v>
-      </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>738</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="M209" t="s">
         <v>739</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="K209">
-        <v>0</v>
-      </c>
-      <c r="M209" t="s">
-        <v>740</v>
       </c>
       <c r="N209" t="s">
         <v>349</v>
       </c>
       <c r="O209" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P209" t="s">
         <v>219</v>
       </c>
       <c r="Q209" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>192</v>
+      </c>
+      <c r="B210" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>192</v>
-      </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>742</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="M210" t="s">
         <v>743</v>
-      </c>
-      <c r="D210">
-        <v>0</v>
-      </c>
-      <c r="K210">
-        <v>0</v>
-      </c>
-      <c r="M210" t="s">
-        <v>744</v>
       </c>
       <c r="N210" t="s">
         <v>349</v>
       </c>
       <c r="O210" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P210" t="s">
         <v>219</v>
       </c>
       <c r="Q210" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>192</v>
+      </c>
+      <c r="B211" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>192</v>
-      </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>746</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="M211" t="s">
         <v>747</v>
-      </c>
-      <c r="D211">
-        <v>0</v>
-      </c>
-      <c r="K211">
-        <v>0</v>
-      </c>
-      <c r="M211" t="s">
-        <v>748</v>
       </c>
       <c r="N211" t="s">
         <v>349</v>
       </c>
       <c r="O211" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P211" t="s">
         <v>242</v>
       </c>
       <c r="Q211" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>192</v>
+      </c>
+      <c r="B212" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>192</v>
-      </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>751</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="M212" t="s">
         <v>752</v>
-      </c>
-      <c r="D212">
-        <v>0</v>
-      </c>
-      <c r="K212">
-        <v>0</v>
-      </c>
-      <c r="M212" t="s">
-        <v>753</v>
       </c>
       <c r="N212" t="s">
         <v>349</v>
       </c>
       <c r="O212" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P212" t="s">
         <v>242</v>
       </c>
       <c r="Q212" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>192</v>
+      </c>
+      <c r="B213" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>192</v>
-      </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>755</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="s">
         <v>756</v>
-      </c>
-      <c r="D213">
-        <v>0</v>
-      </c>
-      <c r="K213">
-        <v>0</v>
-      </c>
-      <c r="M213" t="s">
-        <v>757</v>
       </c>
       <c r="N213" t="s">
         <v>349</v>
       </c>
       <c r="O213" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P213" t="s">
         <v>242</v>
       </c>
       <c r="Q213" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>192</v>
+      </c>
+      <c r="B214" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>192</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>759</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
         <v>760</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="K214">
-        <v>0</v>
-      </c>
-      <c r="M214" t="s">
-        <v>761</v>
       </c>
       <c r="N214" t="s">
         <v>349</v>
       </c>
       <c r="O214" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P214" t="s">
         <v>242</v>
       </c>
       <c r="Q214" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>192</v>
+      </c>
+      <c r="B215" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>192</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>763</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="M215" t="s">
         <v>764</v>
-      </c>
-      <c r="D215">
-        <v>0</v>
-      </c>
-      <c r="K215">
-        <v>0</v>
-      </c>
-      <c r="M215" t="s">
-        <v>765</v>
       </c>
       <c r="N215" t="s">
         <v>349</v>
       </c>
       <c r="O215" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P215" t="s">
         <v>242</v>
       </c>
       <c r="Q215" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="B216" t="s">
         <v>767</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>768</v>
-      </c>
-      <c r="C216" t="s">
-        <v>769</v>
       </c>
       <c r="D216">
         <v>25</v>
@@ -10167,209 +10168,209 @@
         <v>31</v>
       </c>
       <c r="M216" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>766</v>
+      </c>
+      <c r="B217" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>767</v>
-      </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>771</v>
-      </c>
-      <c r="C217" t="s">
-        <v>772</v>
       </c>
       <c r="D217">
         <v>18</v>
       </c>
       <c r="L217" t="s">
+        <v>772</v>
+      </c>
+      <c r="M217" t="s">
         <v>773</v>
       </c>
-      <c r="M217" t="s">
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>766</v>
+      </c>
+      <c r="B218" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>767</v>
-      </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>775</v>
-      </c>
-      <c r="C218" t="s">
-        <v>776</v>
       </c>
       <c r="D218">
         <v>15</v>
       </c>
       <c r="L218" t="s">
+        <v>776</v>
+      </c>
+      <c r="M218" t="s">
         <v>777</v>
       </c>
-      <c r="M218" t="s">
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>766</v>
+      </c>
+      <c r="B219" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>767</v>
-      </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>779</v>
-      </c>
-      <c r="C219" t="s">
-        <v>780</v>
       </c>
       <c r="D219">
         <v>30</v>
       </c>
       <c r="L219" t="s">
+        <v>780</v>
+      </c>
+      <c r="M219" t="s">
         <v>781</v>
       </c>
-      <c r="M219" t="s">
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>766</v>
+      </c>
+      <c r="B220" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>767</v>
-      </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>783</v>
-      </c>
-      <c r="C220" t="s">
-        <v>784</v>
       </c>
       <c r="D220">
         <v>25</v>
       </c>
       <c r="L220" t="s">
+        <v>784</v>
+      </c>
+      <c r="M220" t="s">
         <v>785</v>
       </c>
-      <c r="M220" t="s">
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>766</v>
+      </c>
+      <c r="B221" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>767</v>
-      </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>787</v>
-      </c>
-      <c r="C221" t="s">
-        <v>788</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="L221" t="s">
+        <v>788</v>
+      </c>
+      <c r="M221" t="s">
         <v>789</v>
       </c>
-      <c r="M221" t="s">
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>766</v>
+      </c>
+      <c r="B222" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>767</v>
-      </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>791</v>
-      </c>
-      <c r="C222" t="s">
-        <v>792</v>
       </c>
       <c r="D222">
         <v>12</v>
       </c>
       <c r="M222" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>766</v>
+      </c>
+      <c r="B223" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>767</v>
-      </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>794</v>
-      </c>
-      <c r="C223" t="s">
-        <v>795</v>
       </c>
       <c r="D223">
         <v>15</v>
       </c>
       <c r="M223" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>766</v>
+      </c>
+      <c r="B224" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>767</v>
-      </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>797</v>
-      </c>
-      <c r="C224" t="s">
-        <v>798</v>
       </c>
       <c r="D224">
         <v>8</v>
       </c>
       <c r="M224" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>766</v>
+      </c>
+      <c r="B225" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>767</v>
-      </c>
-      <c r="B225" t="s">
+      <c r="C225" t="s">
         <v>800</v>
-      </c>
-      <c r="C225" t="s">
-        <v>801</v>
       </c>
       <c r="D225">
         <v>30</v>
       </c>
       <c r="M225" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>766</v>
+      </c>
+      <c r="B226" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>767</v>
-      </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
         <v>803</v>
-      </c>
-      <c r="C226" t="s">
-        <v>804</v>
       </c>
       <c r="D226">
         <v>5</v>
       </c>
       <c r="M226" s="2" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B227" t="s">
+        <v>804</v>
+      </c>
+      <c r="C227" t="s">
         <v>805</v>
-      </c>
-      <c r="C227" t="s">
-        <v>806</v>
       </c>
       <c r="D227">
         <v>35</v>
       </c>
       <c r="M227" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD99C3C-28F3-442F-A22B-5F4C34AF7B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA42D3-5FD4-4EA8-A86D-B312A160FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="825">
   <si>
     <t>池</t>
   </si>
@@ -887,222 +887,24 @@
     <t>{"thornsManaCost":10,"thornsDamagePct":100}</t>
   </si>
   <si>
-    <t>piercingFocus</t>
-  </si>
-  <si>
-    <t>凝鋒穿刺</t>
-  </si>
-  <si>
-    <t>突刺的長度 +30%、寬度 -15%，且造成的傷害 +30%。</t>
-  </si>
-  <si>
-    <t>thrust</t>
-  </si>
-  <si>
-    <t>{"thrustLenPct":30,"thrustWidthPct":-15,"skillDamagePct":30}</t>
-  </si>
-  <si>
-    <t>thousandWounds</t>
-  </si>
-  <si>
-    <t>千瘡百孔</t>
-  </si>
-  <si>
-    <t>每次突刺命中使敵人受到的傷害 +4%，持續 5 秒，最多疊加 10 層。</t>
-  </si>
-  <si>
-    <t>{"thrustVuln":{"pct":4,"dur":5,"maxStacks":10}}</t>
-  </si>
-  <si>
-    <t>sunpiercerLance</t>
-  </si>
-  <si>
-    <t>貫日之刺</t>
-  </si>
-  <si>
-    <t>{"octaToSingle":true,"thrustRangePct":100,"skillDamagePct":100}</t>
-  </si>
-  <si>
-    <t>thunderStab</t>
-  </si>
-  <si>
-    <t>迅雷穿刺</t>
-  </si>
-  <si>
-    <t>每次突刺擊中敵人時有 15% 機率附加 1 道連鎖閃電。</t>
-  </si>
-  <si>
-    <t>{"thrustChain":{"chance":15,"powerPct":50,"elem":"lightning","bounces":5,"tickSec":0.3,"label":"迅雷穿刺"}}</t>
-  </si>
-  <si>
-    <t>heartrendBleed</t>
-  </si>
-  <si>
-    <t>穿心裂血</t>
-  </si>
-  <si>
-    <t>突刺會附加流血，每 0.5 秒造成 50% 物理傷害，持續 5 秒。</t>
-  </si>
-  <si>
-    <t>{"thrustDot":{"tickPowerPct":50,"tickSec":0.5,"dur":5}}</t>
-  </si>
-  <si>
-    <t>chainSpin</t>
-  </si>
-  <si>
-    <t>連環迴旋</t>
-  </si>
-  <si>
-    <t>迴旋斬的斬擊次數 +2 次。</t>
-  </si>
-  <si>
-    <t>cleave</t>
-  </si>
-  <si>
-    <t>{"cleaveSlashAdd":2}</t>
-  </si>
-  <si>
-    <t>galeBladeDance</t>
-  </si>
-  <si>
-    <t>旋風劍舞</t>
-  </si>
-  <si>
-    <t>迴旋斬的每次斬擊會同時產生旋風，對周圍 8 米範圍內的所有敵人造成 100% 風系傷害。</t>
-  </si>
-  <si>
-    <t>{"cleaveWhirl":{"m":8,"powerPct":100,"elem":"wind"}}</t>
-  </si>
-  <si>
-    <t>skyrendSlash</t>
-  </si>
-  <si>
-    <t>裂空飛斬</t>
-  </si>
-  <si>
-    <t>迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
-  </si>
-  <si>
-    <t>{"cleaveFlyM":60}</t>
-  </si>
-  <si>
-    <t>exploitWeakness</t>
-  </si>
-  <si>
-    <t>乘虛之斬</t>
-  </si>
-  <si>
-    <t>迴旋斬對暈眩中的敵人造成額外的 50% 傷害。</t>
-  </si>
-  <si>
-    <t>{"cleaveStunnedDmgPct":50}</t>
-  </si>
-  <si>
-    <t>gatheringVortex</t>
-  </si>
-  <si>
-    <t>聚敵旋渦</t>
-  </si>
-  <si>
-    <t>迴旋斬會將 60 米內的所有敵人拉近至身邊 10 米範圍內。</t>
-  </si>
-  <si>
-    <t>{"cleavePull":{"m":60,"toM":10}}</t>
-  </si>
-  <si>
-    <t>knifeChain</t>
-  </si>
-  <si>
-    <t>連鎖</t>
-  </si>
-  <si>
-    <t>飛刀的彈射數 +2 次。</t>
-  </si>
-  <si>
-    <t>knife</t>
-  </si>
-  <si>
-    <t>{"knifeBounceAdd":2}</t>
-  </si>
-  <si>
-    <t>knifeSplitter</t>
-  </si>
-  <si>
-    <t>分裂者</t>
-  </si>
-  <si>
-    <t>飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
-  </si>
-  <si>
-    <t>{"knifeSplit":{"count":2,"pct":50,"bounces":2}}</t>
-  </si>
-  <si>
-    <t>knifeExecutioner</t>
-  </si>
-  <si>
-    <t>處刑者</t>
-  </si>
-  <si>
-    <t>飛刀會優先在生命值最高的目標間彈射，且對其造成的傷害 +30%。</t>
-  </si>
-  <si>
-    <t>{"knifeExecutor":{"pct":30}}</t>
-  </si>
-  <si>
-    <t>knifeShadowblade</t>
-  </si>
-  <si>
-    <t>影刃</t>
-  </si>
-  <si>
-    <t>射出的飛刀數量 +2 把。</t>
-  </si>
-  <si>
-    <t>{"knifeCountAdd":2}</t>
-  </si>
-  <si>
-    <t>knifeWaltzblade</t>
-  </si>
-  <si>
-    <t>輪舞刃</t>
-  </si>
-  <si>
-    <t>射出的第 1 把飛刀不再彈射，改為圍繞在你周圍 10 米處旋轉，對路徑上的所有敵人造成傷害，持續 5 秒。</t>
-  </si>
-  <si>
-    <t>{"knifeOrbit":{"m":10,"sec":5}}</t>
-  </si>
-  <si>
     <t>galeWhirlwind</t>
   </si>
   <si>
     <t>風捲殘雲</t>
   </si>
   <si>
-    <t>疾風斬命中時有 35% 機率在目標處形成一道龍捲風，造成 4 段、每段 100% 風系傷害。</t>
-  </si>
-  <si>
     <t>wind</t>
   </si>
   <si>
     <t>gale</t>
   </si>
   <si>
-    <t>{"galeTornado":{"chance":35,"hits":4,"pct":100,"m":4,"gap":0.4}}</t>
-  </si>
-  <si>
     <t>galeExecute</t>
   </si>
   <si>
     <t>斬殺</t>
   </si>
   <si>
-    <t>疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
-  </si>
-  <si>
-    <t>{"galeExecute":{"chance":35,"hpPct":20}}</t>
-  </si>
-  <si>
     <t>galeTwinShadow</t>
   </si>
   <si>
@@ -1133,12 +935,6 @@
     <t>神速斬</t>
   </si>
   <si>
-    <t>疾風斬每次命中時，疾風斬的冷卻時間 -0.1 秒。</t>
-  </si>
-  <si>
-    <t>{"galeCdrSec":0.1}</t>
-  </si>
-  <si>
     <t>bloodPoisonBurst</t>
   </si>
   <si>
@@ -1163,24 +959,12 @@
     <t>毒血祭</t>
   </si>
   <si>
-    <t>血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
-  </si>
-  <si>
-    <t>{"bloodVenomRite":{"hpPct":1,"pct":50}}</t>
-  </si>
-  <si>
     <t>bloodMist</t>
   </si>
   <si>
     <t>血霧</t>
   </si>
   <si>
-    <t>血刃斬造成流血的敵人死亡後留下一灘血霧，血霧內的敵人每次受傷都回復你 0.2% 生命值，持續 4 秒。</t>
-  </si>
-  <si>
-    <t>{"bloodMistField":{"m":6,"healPct":0.2,"sec":4}}</t>
-  </si>
-  <si>
     <t>bloodShadow</t>
   </si>
   <si>
@@ -1226,24 +1010,12 @@
     <t>狂戰士</t>
   </si>
   <si>
-    <t>鐵血之舞造成的生命損失與傷害同時提高 50%。</t>
-  </si>
-  <si>
-    <t>{"danceIronAmp":{"pct":50}}</t>
-  </si>
-  <si>
     <t>danceUnyielding</t>
   </si>
   <si>
     <t>不屈之誓</t>
   </si>
   <si>
-    <t>暴風之舞持續期間你的死亡延後 10 秒才生效，且這 10 秒內你的傷害提高 100%。</t>
-  </si>
-  <si>
-    <t>{"danceDeathDefer":{"sec":10,"pct":100}}</t>
-  </si>
-  <si>
     <t>danceThousandCuts</t>
   </si>
   <si>
@@ -1274,63 +1046,33 @@
     <t>堅韌誓言</t>
   </si>
   <si>
-    <t>反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
-  </si>
-  <si>
     <t>counter</t>
   </si>
   <si>
-    <t>{"counterOath":{"count":100,"sec":3}}</t>
-  </si>
-  <si>
     <t>counterWrath</t>
   </si>
   <si>
     <t>怒火</t>
   </si>
   <si>
-    <t>反擊 100 次後獲得怒火狀態，造成的傷害提高 30%，持續 6 秒。</t>
-  </si>
-  <si>
-    <t>{"counterWrath":{"count":100,"pct":30,"sec":6}}</t>
-  </si>
-  <si>
     <t>counterPerfect</t>
   </si>
   <si>
     <t>完美姿態</t>
   </si>
   <si>
-    <t>每次反擊有 10% 機率造成完美反擊，該次反擊傷害提高 300%。</t>
-  </si>
-  <si>
-    <t>{"counterPerfect":{"chance":10,"pct":300}}</t>
-  </si>
-  <si>
     <t>counterBloodPay</t>
   </si>
   <si>
     <t>以血還血</t>
   </si>
   <si>
-    <t>每次反擊損失自身 1% 生命值，但反擊傷害提高 50%。</t>
-  </si>
-  <si>
-    <t>{"counterBloodPay":{"hpPct":1,"pct":50}}</t>
-  </si>
-  <si>
     <t>counterWindBody</t>
   </si>
   <si>
     <t>風之體</t>
   </si>
   <si>
-    <t>反擊有 10% 機率朝目標射出一道風刃，造成 100% 普攻傷害的風系傷害。</t>
-  </si>
-  <si>
-    <t>{"counterWindBlade":{"chance":10,"powerPct":100}}</t>
-  </si>
-  <si>
     <t>rageValor</t>
   </si>
   <si>
@@ -1364,24 +1106,12 @@
     <t>血債償還</t>
   </si>
   <si>
-    <t>【血飲術】造成的自身生命損失降低 50%。</t>
-  </si>
-  <si>
-    <t>{"rageSelfCut":{"reducePct":50}}</t>
-  </si>
-  <si>
     <t>rageZealot</t>
   </si>
   <si>
     <t>狂熱者</t>
   </si>
   <si>
-    <t>每 0.1 連擊數使【狂血盛宴】的傷害加成再提高 5%（＝每 1 連擊數 +50%）。</t>
-  </si>
-  <si>
-    <t>{"rageZealotPct":50}</t>
-  </si>
-  <si>
     <t>rageSlaughterer</t>
   </si>
   <si>
@@ -1400,15 +1130,9 @@
     <t>連珠火</t>
   </si>
   <si>
-    <t>火球及殞石的數量 +1 個。</t>
-  </si>
-  <si>
     <t>fireball</t>
   </si>
   <si>
-    <t>{"fireballCountAdd":{"count":1}}</t>
-  </si>
-  <si>
     <t>fireballEmber</t>
   </si>
   <si>
@@ -1463,15 +1187,9 @@
     <t>追蹤烈焰</t>
   </si>
   <si>
-    <t>火龍捲會追蹤敵人，移動速度 12 米／秒。</t>
-  </si>
-  <si>
     <t>firepillar</t>
   </si>
   <si>
-    <t>{"firepillarChase":{"mps":12,"m":30}}</t>
-  </si>
-  <si>
     <t>firepillarSpread</t>
   </si>
   <si>
@@ -1514,12 +1232,6 @@
     <t>火龍共鳴</t>
   </si>
   <si>
-    <t>場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
-  </si>
-  <si>
-    <t>{"firepillarResonancePct":4}</t>
-  </si>
-  <si>
     <t>firehuntAmplify</t>
   </si>
   <si>
@@ -1541,12 +1253,6 @@
     <t>伴生併發</t>
   </si>
   <si>
-    <t>每 1 秒，你的 1 團火狩會飛出攻擊半徑 20 米內的敵人，對目標 10 米內的所有敵人造成 300% 火焰傷害。</t>
-  </si>
-  <si>
-    <t>{"firehuntLaunch":{"gap":1,"m":20,"aoeM":10,"pct":300}}</t>
-  </si>
-  <si>
     <t>firehuntBlaze</t>
   </si>
   <si>
@@ -1583,9 +1289,6 @@
     <t>重岩甲</t>
   </si>
   <si>
-    <t>岩甲術獲得的生命護盾 +30%。</t>
-  </si>
-  <si>
     <t>earth</t>
   </si>
   <si>
@@ -1625,24 +1328,12 @@
     <t>尖刺甲</t>
   </si>
   <si>
-    <t>【岩甲尖刺】的效果提高 100%。</t>
-  </si>
-  <si>
-    <t>{"rockSpikePct":100}</t>
-  </si>
-  <si>
     <t>rockEarthHeart</t>
   </si>
   <si>
     <t>大地之心</t>
   </si>
   <si>
-    <t>當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
-  </si>
-  <si>
-    <t>{"rockHeartInvuln":{"sec":2,"cd":30}}</t>
-  </si>
-  <si>
     <t>mireSpread</t>
   </si>
   <si>
@@ -1664,36 +1355,18 @@
     <t>削弱</t>
   </si>
   <si>
-    <t>在泥沼術範圍中的敵人造成的傷害 -30%。</t>
-  </si>
-  <si>
-    <t>{"mireWeaken":{"reducePct":30}}</t>
-  </si>
-  <si>
     <t>mireCorrupt</t>
   </si>
   <si>
     <t>腐化</t>
   </si>
   <si>
-    <t>在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
-  </si>
-  <si>
-    <t>{"mireCorruptPct":30}</t>
-  </si>
-  <si>
     <t>mireLavaBurn</t>
   </si>
   <si>
     <t>熔火</t>
   </si>
   <si>
-    <t>熔岩沼的火焰傷害 +70%。</t>
-  </si>
-  <si>
-    <t>{"mireLavaPct":70}</t>
-  </si>
-  <si>
     <t>mireErode</t>
   </si>
   <si>
@@ -1712,9 +1385,6 @@
     <t>魔力滋養</t>
   </si>
   <si>
-    <t>大地守護會使溢出的 50% 法力轉為你的生命護盾。</t>
-  </si>
-  <si>
     <t>earthguard</t>
   </si>
   <si>
@@ -1727,12 +1397,6 @@
     <t>生命滋養</t>
   </si>
   <si>
-    <t>大地守護會使溢出的 10% 生命轉為你的法力值。</t>
-  </si>
-  <si>
-    <t>{"egHpOverflowMana":{"pct":10}}</t>
-  </si>
-  <si>
     <t>earthguardSoulLink</t>
   </si>
   <si>
@@ -1751,12 +1415,6 @@
     <t>地之心</t>
   </si>
   <si>
-    <t>每殺死 1 個敵人，【天地共生】的復活冷卻時間 -1 秒。</t>
-  </si>
-  <si>
-    <t>{"egKillCdr":{"sec":1}}</t>
-  </si>
-  <si>
     <t>earthguardUndyingWill</t>
   </si>
   <si>
@@ -1772,27 +1430,15 @@
     <t>電荷連鎖</t>
   </si>
   <si>
-    <t>連鎖閃電的彈射數 +2 次。</t>
-  </si>
-  <si>
     <t>chainlightning</t>
   </si>
   <si>
-    <t>{"chainLinkAdd":{"count":2}}</t>
-  </si>
-  <si>
     <t>chainlightningVolley</t>
   </si>
   <si>
     <t>電擊</t>
   </si>
   <si>
-    <t>連鎖閃電的發射數量 +2 道。</t>
-  </si>
-  <si>
-    <t>{"chainBoltAdd":{"count":2}}</t>
-  </si>
-  <si>
     <t>chainlightningScatter</t>
   </si>
   <si>
@@ -1823,12 +1469,6 @@
     <t>過載</t>
   </si>
   <si>
-    <t>同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
-  </si>
-  <si>
-    <t>{"chainOverload":{"hits":5,"m":6,"pct":200}}</t>
-  </si>
-  <si>
     <t>thunderstrikeTriple</t>
   </si>
   <si>
@@ -1850,12 +1490,6 @@
     <t>雷鎖</t>
   </si>
   <si>
-    <t>落雷術額外攻擊 1 個目標。</t>
-  </si>
-  <si>
-    <t>{"thunderTargetAdd":{"count":1}}</t>
-  </si>
-  <si>
     <t>thunderstrikeQuake</t>
   </si>
   <si>
@@ -1898,39 +1532,21 @@
     <t>雷核</t>
   </si>
   <si>
-    <t>雷球的體積增大 30%。</t>
-  </si>
-  <si>
     <t>thunderorb</t>
   </si>
   <si>
-    <t>{"thunderorbScalePct":30}</t>
-  </si>
-  <si>
     <t>thunderorbOverload</t>
   </si>
   <si>
     <t>超載</t>
   </si>
   <si>
-    <t>場上每擁有 1 個雷球，你的雷電傷害 +3%。</t>
-  </si>
-  <si>
-    <t>{"thunderorbFieldAmpPct":3}</t>
-  </si>
-  <si>
     <t>thunderorbShockCore</t>
   </si>
   <si>
     <t>感電核心</t>
   </si>
   <si>
-    <t>【伴生雷球】的持續時間增加 100%。</t>
-  </si>
-  <si>
-    <t>{"thunderorbCompanionSecPct":100}</t>
-  </si>
-  <si>
     <t>thunderorbFallCount</t>
   </si>
   <si>
@@ -1976,24 +1592,12 @@
     <t>冰封</t>
   </si>
   <si>
-    <t>寒冰箭傷害 +50%。</t>
-  </si>
-  <si>
-    <t>{"icearrowDamagePct":50}</t>
-  </si>
-  <si>
     <t>icearrowWinter</t>
   </si>
   <si>
     <t>凜冬侵蝕</t>
   </si>
   <si>
-    <t>寒冰箭造成的寒霜狀態傷害與持續時間 +50%。</t>
-  </si>
-  <si>
-    <t>{"icearrowFrostPct":50}</t>
-  </si>
-  <si>
     <t>icearrowSplit</t>
   </si>
   <si>
@@ -2012,12 +1616,6 @@
     <t>深度凍結</t>
   </si>
   <si>
-    <t>寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
-  </si>
-  <si>
-    <t>{"icearrowControlPct":50}</t>
-  </si>
-  <si>
     <t>waterballVolley</t>
   </si>
   <si>
@@ -2087,15 +1685,9 @@
     <t>碎冰</t>
   </si>
   <si>
-    <t>冰霜新星的攻擊範圍 +30%。</t>
-  </si>
-  <si>
     <t>frostnova</t>
   </si>
   <si>
-    <t>{"frostnovaScalePct":30}</t>
-  </si>
-  <si>
     <t>frostnovaTwinBurst</t>
   </si>
   <si>
@@ -2138,27 +1730,15 @@
     <t>凜冬寒霜</t>
   </si>
   <si>
-    <t>暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
-  </si>
-  <si>
-    <t>{"frostnovaBlizzardFrost":{"stacks":1},"frostnovaFrostDmgPct":30}</t>
-  </si>
-  <si>
     <t>windbladeRend</t>
   </si>
   <si>
     <t>裂風</t>
   </si>
   <si>
-    <t>風刃每擊中敵人 1 次則傷害額外 +5%，最高為 +100%。</t>
-  </si>
-  <si>
     <t>windblade</t>
   </si>
   <si>
-    <t>{"windbladeRamp":{"pct":5,"max":100}}</t>
-  </si>
-  <si>
     <t>windbladePressure</t>
   </si>
   <si>
@@ -2325,12 +1905,6 @@
   </si>
   <si>
     <t>風暴核心</t>
-  </si>
-  <si>
-    <t>【暴風神體】的持續時間 +50%。</t>
-  </si>
-  <si>
-    <t>{"stormGodSecPct":50}</t>
   </si>
   <si>
     <t>神鑄特效</t>
@@ -2483,10 +2057,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>helmet;belt;ring;amulet</t>
   </si>
   <si>
@@ -2501,15 +2071,607 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{"firehuntFireAmp":{"gap":0.5,"pct":2,"maxStacks":50}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在火狩的持續時間內，每 0.5 秒你的火焰傷害提高 2%，最多 50 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeChain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每把飛刀有 25% 機率再彈射 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knife</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeBounceProc":{"chance":25,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeSplitter</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>分裂者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeSplit":{"count":2,"pct":50,"bounces":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeExecutioner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>處刑者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛刀會優先在生命值最高的目標間彈射，且對其造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeExecutor":{"pct":30}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeShadowblade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>影刃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>射出的飛刀數量 +2 把。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>phys</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeCountAdd":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeWaltzblade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>輪舞刃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>射出的第 1 把飛刀不再彈射，改為圍繞在你周圍 10 米處旋轉，對路徑上的所有敵人造成傷害，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeOrbit":{"m":10,"sec":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>piercingFocus</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>凝鋒穿刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺的長度 +30%、寬度 -15%，且造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrust</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dagger1h</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustLenPct":30,"thrustWidthPct":-15,"skillDamagePct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thousandWounds</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>千瘡百孔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次突刺命中使敵人受到的突刺傷害 +4%，持續 5 秒，最多疊加 10 層。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustVuln":{"pct":4,"dur":5,"maxStacks":10}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunpiercerLance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>貫日之刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺有 25% 機率使敵人重傷，使其受到的傷害 +20%，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustWound":{"chance":25,"pct":20,"dur":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thunderStab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迅雷穿刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次突刺擊中敵人時有 15% 機率附加 1 道落雷。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightning</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustThunder":{"chance":15,"powerPct":200,"label":"迅雷穿刺"}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>heartrendBleed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿心裂血</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺會附加流血，每 0.5 秒造成 50% 物理傷害，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustDot":{"tickPowerPct":50,"tickSec":0.5,"dur":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>chainSpin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連環迴旋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬的斬擊次數 +2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleave</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sword1h</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveSlashAdd":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>galeBladeDance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋風劍舞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬命中時有 25% 機率產生 1 道風刃，造成 100% 風系傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveWindBlade":{"chance":25,"powerPct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyrendSlash</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂空飛斬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveFlyM":60}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploitWeakness</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘虛之斬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬對暈眩中的敵人造成額外的 50% 傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveStunnedDmgPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gatheringVortex</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚敵旋渦</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬會將 36 米內的 2 個敵人拉近至身邊 10 米範圍內。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleavePull":{"m":36,"toM":10,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬命中時有 25% 機率在目標處形成 1 道真空斬，對周圍 6 米內的敵人造成 100% 風系傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeVacuum":{"chance":25,"pct":100,"m":6}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬有 20% 機率可立即殺死生命值 10% 以下的非 BOSS 敵人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeExecute":{"chance":20,"hpPct":10}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬每次命中時，疾風斬的冷卻時間 -0.05 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeCdrSec":0.05}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>血刃斬的中毒每感染 1 個敵人就使自身生命值 -0.5%，但造成的中毒與流血傷害提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"bloodVenomRite":{"hpPct":0.5,"pct":50}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>血刃斬造成流血的敵人死亡後留下一灘血霧，血霧內的敵人每次受傷都回復你 0.1% 生命值，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"bloodMistField":{"m":6,"healPct":0.1,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐵血之舞造成的自身生命損失 -25%，且造成的傷害 +25%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"danceIronAmp":{"pct":25,"reducePct":25}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴風之舞持續期間你的死亡延後 8 秒才生效，且這 8 秒內你的傷害提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"danceDeathDefer":{"sec":8,"pct":50}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊 200 次後獲得無敵狀態，持續 3 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterOath":{"count":200,"sec":3}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊 100 次後獲得怒火狀態，造成的傷害提高 30%，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterWrath":{"count":100,"pct":30,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次反擊有 5% 機率造成完美反擊，該次反擊傷害提高 500%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterPerfect":{"chance":5,"pct":500}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次反擊損失自身 0.25% 生命值，但反擊傷害提高 100%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterBloodPay":{"hpPct":0.25,"pct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊有 20% 機率附加 1 顆火球射向目標，造成 100% 普攻傷害的火焰傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterFireball":{"chance":20,"powerPct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【血飲術】造成的自身生命損失降低 25%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rageSelfCut":{"reducePct":25}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 0.5 連擊數使【狂血盛宴】的傷害加成再提高 10%（＝每 1 連擊數 +20%）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rageZealotPct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次發射火球數量 +1 個，且累計每發射 5 個火球會再額外發射 1 個火球。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"fireballCountAdd":{"count":1,"every":5,"extra":1}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>火龍捲移動速度 +50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firepillarSpeedPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +10%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firepillarResonancePct":10}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 1 秒，你的 1 團火狩會飛出攻擊半徑 36 米內的任意敵人，對目標 10 米內的所有敵人造成 300% 火焰傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firehuntLaunch":{"gap":1,"m":36,"aoeM":10,"pct":300}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在火狩的持續時間內，每 1 秒你的火焰傷害提高 2%，最多 20 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firehuntFireAmp":{"gap":1,"pct":2,"maxStacks":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩甲護盾效果 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【岩甲尖刺】的效果提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rockSpikePct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>當你的生命護盾降至 0 時獲得無敵 3 秒；此效果每 60 秒只能觸發 1 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rockHeartInvuln":{"sec":3,"cd":60}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在泥沼術範圍中的敵人造成的傷害 -20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireWeaken":{"reducePct":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在泥沼術範圍內所有受到控場的敵人，受到的傷害 +20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireCorruptPct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>熔岩沼的火焰傷害 +50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireLavaPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地守護會使溢出法力的 50% 轉為你的生命護盾。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地守護會使你額外獲得【魔力再生】法力回復加成的 20% 作為吸魔效果加成。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"egManaDrainFromRegen":{"pct":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每殺死 1 個敵人，【天地共生】的復活冷卻時間 -0.2 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"egKillCdr":{"sec":0.2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖閃電有 35% 機率再連鎖 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainLinkProc":{"chance":35,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖閃電有 50% 機率額外發射 2 道連鎖閃電。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainBoltProc":{"chance":50,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一個敵人受到 10 次連鎖閃電的彈射後產生爆炸，對周圍 10 米內的敵人造成 400% 雷電傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainOverload":{"hits":10,"m":10,"pct":400}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>落雷術擊中時有 25% 機率在地上留下一個雷池，每 0.5 秒造成該道落雷 20% 的雷電傷害，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderPool":{"chance":25,"pct":20,"m":6,"gap":0.5,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷球的體積增大 20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbScalePct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>場上每擁有 1 個雷球，你的雷電傷害 +2%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbFieldAmpPct":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【伴生雷球】的持續時間增加 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbCompanionSecPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowDamagePct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭造成的寒霜狀態傷害與持續時間 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowFrostPct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭擊中暈眩或凍結的敵人造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowControlPct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星的攻擊範圍 +20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"frostnovaScalePct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴風雪對帶有寒霜狀態的敵人，每層寒霜傷害 +5%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"frostnovaBlizzardLayer":{"pct":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>風刃每擊中敵人 1 次則傷害額外 +2%，最多疊加 20 層（最高 +40%）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"windbladeRamp":{"pct":2,"max":40}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【暴風神體】的持續時間 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stormGodSecPct":30}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3489,14 +3651,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q227"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3522,10 +3684,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>815</v>
+        <v>672</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>807</v>
+        <v>665</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -3549,7 +3711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3578,7 +3740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3607,7 +3769,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3636,7 +3798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3665,7 +3827,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3694,7 +3856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3723,7 +3885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3752,7 +3914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3781,7 +3943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3810,7 +3972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3839,7 +4001,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -3868,7 +4030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -3897,7 +4059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3905,7 +4067,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>816</v>
+        <v>673</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -3926,7 +4088,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -3955,7 +4117,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3984,7 +4146,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -4013,7 +4175,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4042,7 +4204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4074,7 +4236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -4106,7 +4268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4138,7 +4300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -4170,7 +4332,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -4199,7 +4361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -4228,7 +4390,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -4257,7 +4419,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -4289,7 +4451,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -4321,7 +4483,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -4353,7 +4515,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -4382,10 +4544,10 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -4414,7 +4576,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -4422,7 +4584,7 @@
         <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>808</v>
+        <v>666</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -4431,7 +4593,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>809</v>
+        <v>667</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4443,10 +4605,10 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -4454,7 +4616,7 @@
         <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>810</v>
+        <v>668</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4463,7 +4625,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>809</v>
+        <v>667</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4475,10 +4637,10 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -4510,7 +4672,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -4542,7 +4704,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -4574,7 +4736,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -4606,7 +4768,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -4638,7 +4800,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -4670,7 +4832,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -4702,7 +4864,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -4734,7 +4896,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -4766,7 +4928,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -4798,7 +4960,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -4830,7 +4992,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -4862,7 +5024,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -4894,7 +5056,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -4926,7 +5088,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -4958,7 +5120,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -4990,7 +5152,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -5022,7 +5184,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -5054,7 +5216,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -5086,7 +5248,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -5118,7 +5280,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -5150,7 +5312,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -5182,7 +5344,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -5214,7 +5376,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -5246,7 +5408,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -5275,7 +5437,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -5304,7 +5466,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -5333,7 +5495,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -5362,7 +5524,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -5391,7 +5553,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -5420,7 +5582,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -5449,7 +5611,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -5478,7 +5640,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -5507,7 +5669,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -5536,7 +5698,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -5565,7 +5727,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -5597,7 +5759,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -5629,7 +5791,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -5658,7 +5820,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -5690,7 +5852,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -5722,7 +5884,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -5754,7 +5916,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -5786,7 +5948,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -5818,7 +5980,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -5847,7 +6009,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -5876,7 +6038,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -5905,7 +6067,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -5937,7 +6099,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -5969,7 +6131,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>192</v>
       </c>
@@ -5989,7 +6151,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>192</v>
       </c>
@@ -6009,7 +6171,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>192</v>
       </c>
@@ -6029,7 +6191,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>192</v>
       </c>
@@ -6049,7 +6211,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>192</v>
       </c>
@@ -6069,7 +6231,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -6089,7 +6251,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>192</v>
       </c>
@@ -6109,7 +6271,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>192</v>
       </c>
@@ -6135,7 +6297,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -6164,7 +6326,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>192</v>
       </c>
@@ -6193,7 +6355,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>192</v>
       </c>
@@ -6219,7 +6381,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>192</v>
       </c>
@@ -6245,7 +6407,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>192</v>
       </c>
@@ -6271,7 +6433,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>192</v>
       </c>
@@ -6300,7 +6462,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>192</v>
       </c>
@@ -6329,7 +6491,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>192</v>
       </c>
@@ -6358,7 +6520,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -6387,7 +6549,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -6416,7 +6578,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>192</v>
       </c>
@@ -6445,7 +6607,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>192</v>
       </c>
@@ -6471,15 +6633,15 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>192</v>
       </c>
-      <c r="B101" t="s">
-        <v>284</v>
-      </c>
-      <c r="C101" t="s">
-        <v>285</v>
+      <c r="B101" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>676</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6487,31 +6649,31 @@
       <c r="K101">
         <v>0</v>
       </c>
-      <c r="M101" t="s">
-        <v>286</v>
+      <c r="M101" s="2" t="s">
+        <v>677</v>
       </c>
       <c r="N101" t="s">
         <v>214</v>
       </c>
-      <c r="O101" t="s">
-        <v>287</v>
+      <c r="O101" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="P101" t="s">
         <v>224</v>
       </c>
-      <c r="Q101" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q101" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>192</v>
       </c>
-      <c r="B102" t="s">
-        <v>289</v>
-      </c>
-      <c r="C102" t="s">
-        <v>290</v>
+      <c r="B102" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>681</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6519,31 +6681,31 @@
       <c r="K102">
         <v>0</v>
       </c>
-      <c r="M102" t="s">
-        <v>291</v>
+      <c r="M102" s="2" t="s">
+        <v>682</v>
       </c>
       <c r="N102" t="s">
         <v>214</v>
       </c>
-      <c r="O102" t="s">
-        <v>287</v>
+      <c r="O102" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="P102" t="s">
         <v>224</v>
       </c>
-      <c r="Q102" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q102" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>192</v>
       </c>
-      <c r="B103" t="s">
-        <v>293</v>
-      </c>
-      <c r="C103" t="s">
-        <v>294</v>
+      <c r="B103" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>685</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6551,31 +6713,31 @@
       <c r="K103">
         <v>0</v>
       </c>
-      <c r="M103" t="s">
-        <v>812</v>
+      <c r="M103" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="N103" t="s">
         <v>214</v>
       </c>
-      <c r="O103" t="s">
-        <v>287</v>
+      <c r="O103" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="P103" t="s">
         <v>224</v>
       </c>
-      <c r="Q103" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q103" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>192</v>
       </c>
-      <c r="B104" t="s">
-        <v>296</v>
-      </c>
-      <c r="C104" t="s">
-        <v>297</v>
+      <c r="B104" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6583,31 +6745,31 @@
       <c r="K104">
         <v>0</v>
       </c>
-      <c r="M104" t="s">
-        <v>298</v>
-      </c>
-      <c r="N104" t="s">
-        <v>249</v>
-      </c>
-      <c r="O104" t="s">
-        <v>287</v>
+      <c r="M104" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="P104" t="s">
         <v>224</v>
       </c>
-      <c r="Q104" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q104" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>192</v>
       </c>
-      <c r="B105" t="s">
-        <v>300</v>
-      </c>
-      <c r="C105" t="s">
-        <v>301</v>
+      <c r="B105" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>694</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6615,31 +6777,31 @@
       <c r="K105">
         <v>0</v>
       </c>
-      <c r="M105" t="s">
-        <v>302</v>
+      <c r="M105" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="N105" t="s">
         <v>214</v>
       </c>
-      <c r="O105" t="s">
-        <v>287</v>
+      <c r="O105" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="P105" t="s">
         <v>224</v>
       </c>
-      <c r="Q105" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q105" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>192</v>
       </c>
-      <c r="B106" t="s">
-        <v>304</v>
-      </c>
-      <c r="C106" t="s">
-        <v>305</v>
+      <c r="B106" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>698</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6647,31 +6809,31 @@
       <c r="K106">
         <v>0</v>
       </c>
-      <c r="M106" t="s">
-        <v>306</v>
+      <c r="M106" s="2" t="s">
+        <v>699</v>
       </c>
       <c r="N106" t="s">
         <v>214</v>
       </c>
-      <c r="O106" t="s">
-        <v>307</v>
-      </c>
-      <c r="P106" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O106" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>192</v>
       </c>
-      <c r="B107" t="s">
-        <v>309</v>
-      </c>
-      <c r="C107" t="s">
-        <v>310</v>
+      <c r="B107" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6679,31 +6841,31 @@
       <c r="K107">
         <v>0</v>
       </c>
-      <c r="M107" t="s">
-        <v>311</v>
+      <c r="M107" s="2" t="s">
+        <v>705</v>
       </c>
       <c r="N107" t="s">
         <v>214</v>
       </c>
-      <c r="O107" t="s">
-        <v>307</v>
-      </c>
-      <c r="P107" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O107" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q107" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>192</v>
       </c>
-      <c r="B108" t="s">
-        <v>313</v>
-      </c>
-      <c r="C108" t="s">
-        <v>314</v>
+      <c r="B108" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>708</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6711,31 +6873,31 @@
       <c r="K108">
         <v>0</v>
       </c>
-      <c r="M108" t="s">
-        <v>315</v>
+      <c r="M108" s="2" t="s">
+        <v>709</v>
       </c>
       <c r="N108" t="s">
         <v>214</v>
       </c>
-      <c r="O108" t="s">
-        <v>307</v>
-      </c>
-      <c r="P108" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O108" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>192</v>
       </c>
-      <c r="B109" t="s">
-        <v>317</v>
-      </c>
-      <c r="C109" t="s">
-        <v>318</v>
+      <c r="B109" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>712</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6743,31 +6905,31 @@
       <c r="K109">
         <v>0</v>
       </c>
-      <c r="M109" t="s">
-        <v>319</v>
-      </c>
-      <c r="N109" t="s">
-        <v>214</v>
-      </c>
-      <c r="O109" t="s">
-        <v>307</v>
-      </c>
-      <c r="P109" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M109" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>192</v>
       </c>
-      <c r="B110" t="s">
-        <v>321</v>
-      </c>
-      <c r="C110" t="s">
-        <v>322</v>
+      <c r="B110" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6775,31 +6937,31 @@
       <c r="K110">
         <v>0</v>
       </c>
-      <c r="M110" t="s">
-        <v>323</v>
+      <c r="M110" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="N110" t="s">
         <v>214</v>
       </c>
-      <c r="O110" t="s">
-        <v>307</v>
-      </c>
-      <c r="P110" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O110" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>192</v>
       </c>
-      <c r="B111" t="s">
-        <v>325</v>
-      </c>
-      <c r="C111" t="s">
-        <v>326</v>
+      <c r="B111" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>721</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6807,31 +6969,31 @@
       <c r="K111">
         <v>0</v>
       </c>
-      <c r="M111" t="s">
-        <v>327</v>
+      <c r="M111" s="2" t="s">
+        <v>722</v>
       </c>
       <c r="N111" t="s">
         <v>214</v>
       </c>
-      <c r="O111" t="s">
-        <v>328</v>
-      </c>
-      <c r="P111" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O111" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q111" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>192</v>
       </c>
-      <c r="B112" t="s">
-        <v>330</v>
-      </c>
-      <c r="C112" t="s">
-        <v>331</v>
+      <c r="B112" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>727</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6839,31 +7001,31 @@
       <c r="K112">
         <v>0</v>
       </c>
-      <c r="M112" t="s">
-        <v>332</v>
+      <c r="M112" s="2" t="s">
+        <v>728</v>
       </c>
       <c r="N112" t="s">
         <v>214</v>
       </c>
-      <c r="O112" t="s">
-        <v>328</v>
-      </c>
-      <c r="P112" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O112" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q112" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>192</v>
       </c>
-      <c r="B113" t="s">
-        <v>334</v>
-      </c>
-      <c r="C113" t="s">
-        <v>335</v>
+      <c r="B113" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>731</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6871,31 +7033,31 @@
       <c r="K113">
         <v>0</v>
       </c>
-      <c r="M113" t="s">
-        <v>336</v>
+      <c r="M113" s="2" t="s">
+        <v>732</v>
       </c>
       <c r="N113" t="s">
         <v>214</v>
       </c>
-      <c r="O113" t="s">
-        <v>328</v>
-      </c>
-      <c r="P113" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O113" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>192</v>
       </c>
-      <c r="B114" t="s">
-        <v>338</v>
-      </c>
-      <c r="C114" t="s">
-        <v>339</v>
+      <c r="B114" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>735</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6903,31 +7065,31 @@
       <c r="K114">
         <v>0</v>
       </c>
-      <c r="M114" t="s">
-        <v>340</v>
+      <c r="M114" s="2" t="s">
+        <v>736</v>
       </c>
       <c r="N114" t="s">
         <v>214</v>
       </c>
-      <c r="O114" t="s">
-        <v>328</v>
-      </c>
-      <c r="P114" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O114" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q114" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>192</v>
       </c>
-      <c r="B115" t="s">
-        <v>342</v>
-      </c>
-      <c r="C115" t="s">
-        <v>343</v>
+      <c r="B115" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>739</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6935,31 +7097,31 @@
       <c r="K115">
         <v>0</v>
       </c>
-      <c r="M115" t="s">
-        <v>344</v>
+      <c r="M115" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="N115" t="s">
         <v>214</v>
       </c>
-      <c r="O115" t="s">
-        <v>328</v>
-      </c>
-      <c r="P115" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O115" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q115" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>192</v>
       </c>
       <c r="B116" t="s">
-        <v>346</v>
+        <v>284</v>
       </c>
       <c r="C116" t="s">
-        <v>347</v>
+        <v>285</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -6967,31 +7129,31 @@
       <c r="K116">
         <v>0</v>
       </c>
-      <c r="M116" t="s">
-        <v>348</v>
+      <c r="M116" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="N116" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O116" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P116" t="s">
         <v>238</v>
       </c>
-      <c r="Q116" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q116" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>192</v>
       </c>
       <c r="B117" t="s">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="C117" t="s">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -6999,31 +7161,31 @@
       <c r="K117">
         <v>0</v>
       </c>
-      <c r="M117" t="s">
-        <v>354</v>
+      <c r="M117" s="2" t="s">
+        <v>744</v>
       </c>
       <c r="N117" t="s">
         <v>214</v>
       </c>
       <c r="O117" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P117" t="s">
         <v>238</v>
       </c>
-      <c r="Q117" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q117" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>192</v>
       </c>
       <c r="B118" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="C118" t="s">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -7032,30 +7194,30 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="N118" t="s">
         <v>214</v>
       </c>
       <c r="O118" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P118" t="s">
         <v>238</v>
       </c>
       <c r="Q118" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>192</v>
       </c>
       <c r="B119" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>361</v>
+        <v>295</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -7064,30 +7226,30 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>362</v>
+        <v>296</v>
       </c>
       <c r="N119" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O119" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P119" t="s">
         <v>238</v>
       </c>
       <c r="Q119" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="C120" t="s">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -7095,31 +7257,31 @@
       <c r="K120">
         <v>0</v>
       </c>
-      <c r="M120" t="s">
-        <v>366</v>
+      <c r="M120" s="2" t="s">
+        <v>746</v>
       </c>
       <c r="N120" t="s">
         <v>214</v>
       </c>
       <c r="O120" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P120" t="s">
         <v>238</v>
       </c>
-      <c r="Q120" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q120" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>192</v>
       </c>
       <c r="B121" t="s">
-        <v>368</v>
+        <v>300</v>
       </c>
       <c r="C121" t="s">
-        <v>369</v>
+        <v>301</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -7128,30 +7290,30 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>370</v>
+        <v>302</v>
       </c>
       <c r="N121" t="s">
         <v>274</v>
       </c>
       <c r="O121" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="P121" t="s">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="Q121" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>192</v>
       </c>
       <c r="B122" t="s">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="C122" t="s">
-        <v>375</v>
+        <v>307</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -7159,31 +7321,31 @@
       <c r="K122">
         <v>0</v>
       </c>
-      <c r="M122" t="s">
-        <v>376</v>
+      <c r="M122" s="2" t="s">
+        <v>748</v>
       </c>
       <c r="N122" t="s">
         <v>274</v>
       </c>
       <c r="O122" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="P122" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+      <c r="Q122" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>192</v>
       </c>
       <c r="B123" t="s">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="C123" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -7191,31 +7353,31 @@
       <c r="K123">
         <v>0</v>
       </c>
-      <c r="M123" t="s">
-        <v>380</v>
+      <c r="M123" s="2" t="s">
+        <v>750</v>
       </c>
       <c r="N123" t="s">
         <v>214</v>
       </c>
       <c r="O123" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="P123" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="C124" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -7224,30 +7386,30 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>384</v>
+        <v>312</v>
       </c>
       <c r="N124" t="s">
         <v>214</v>
       </c>
       <c r="O124" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="P124" t="s">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="Q124" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>192</v>
       </c>
       <c r="B125" t="s">
-        <v>386</v>
+        <v>314</v>
       </c>
       <c r="C125" t="s">
-        <v>387</v>
+        <v>315</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -7256,30 +7418,30 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="N125" t="s">
         <v>214</v>
       </c>
       <c r="O125" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="P125" t="s">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="Q125" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
       <c r="C126" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -7288,30 +7450,30 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="N126" t="s">
         <v>214</v>
       </c>
       <c r="O126" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="P126" t="s">
         <v>244</v>
       </c>
       <c r="Q126" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>192</v>
       </c>
       <c r="B127" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="C127" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -7319,31 +7481,31 @@
       <c r="K127">
         <v>0</v>
       </c>
-      <c r="M127" t="s">
-        <v>397</v>
+      <c r="M127" s="2" t="s">
+        <v>752</v>
       </c>
       <c r="N127" t="s">
         <v>214</v>
       </c>
       <c r="O127" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="P127" t="s">
         <v>244</v>
       </c>
-      <c r="Q127" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q127" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>192</v>
       </c>
       <c r="B128" t="s">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="C128" t="s">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -7351,31 +7513,31 @@
       <c r="K128">
         <v>0</v>
       </c>
-      <c r="M128" t="s">
-        <v>401</v>
+      <c r="M128" s="2" t="s">
+        <v>754</v>
       </c>
       <c r="N128" t="s">
         <v>214</v>
       </c>
       <c r="O128" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="P128" t="s">
         <v>244</v>
       </c>
-      <c r="Q128" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q128" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>192</v>
       </c>
       <c r="B129" t="s">
-        <v>403</v>
+        <v>327</v>
       </c>
       <c r="C129" t="s">
-        <v>404</v>
+        <v>328</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -7384,30 +7546,30 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>405</v>
+        <v>329</v>
       </c>
       <c r="N129" t="s">
         <v>214</v>
       </c>
       <c r="O129" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="P129" t="s">
         <v>244</v>
       </c>
       <c r="Q129" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>192</v>
       </c>
       <c r="B130" t="s">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="C130" t="s">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -7416,30 +7578,30 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="N130" t="s">
         <v>214</v>
       </c>
       <c r="O130" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="P130" t="s">
         <v>244</v>
       </c>
       <c r="Q130" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>192</v>
       </c>
       <c r="B131" t="s">
-        <v>411</v>
+        <v>335</v>
       </c>
       <c r="C131" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -7447,31 +7609,31 @@
       <c r="K131">
         <v>0</v>
       </c>
-      <c r="M131" t="s">
-        <v>413</v>
+      <c r="M131" s="2" t="s">
+        <v>756</v>
       </c>
       <c r="N131" t="s">
         <v>214</v>
       </c>
       <c r="O131" t="s">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="P131" t="s">
         <v>242</v>
       </c>
-      <c r="Q131" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q131" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>192</v>
       </c>
       <c r="B132" t="s">
-        <v>416</v>
+        <v>338</v>
       </c>
       <c r="C132" t="s">
-        <v>417</v>
+        <v>339</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -7479,31 +7641,31 @@
       <c r="K132">
         <v>0</v>
       </c>
-      <c r="M132" t="s">
-        <v>418</v>
+      <c r="M132" s="2" t="s">
+        <v>758</v>
       </c>
       <c r="N132" t="s">
         <v>214</v>
       </c>
       <c r="O132" t="s">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="P132" t="s">
         <v>242</v>
       </c>
-      <c r="Q132" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q132" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>192</v>
       </c>
       <c r="B133" t="s">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="C133" t="s">
-        <v>421</v>
+        <v>341</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -7511,31 +7673,31 @@
       <c r="K133">
         <v>0</v>
       </c>
-      <c r="M133" t="s">
-        <v>422</v>
+      <c r="M133" s="2" t="s">
+        <v>760</v>
       </c>
       <c r="N133" t="s">
         <v>214</v>
       </c>
       <c r="O133" t="s">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="P133" t="s">
         <v>242</v>
       </c>
-      <c r="Q133" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q133" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>192</v>
       </c>
       <c r="B134" t="s">
-        <v>424</v>
+        <v>342</v>
       </c>
       <c r="C134" t="s">
-        <v>425</v>
+        <v>343</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -7543,31 +7705,31 @@
       <c r="K134">
         <v>0</v>
       </c>
-      <c r="M134" t="s">
-        <v>426</v>
+      <c r="M134" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="N134" t="s">
         <v>214</v>
       </c>
       <c r="O134" t="s">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="P134" t="s">
         <v>242</v>
       </c>
-      <c r="Q134" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q134" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>192</v>
       </c>
       <c r="B135" t="s">
-        <v>428</v>
+        <v>344</v>
       </c>
       <c r="C135" t="s">
-        <v>429</v>
+        <v>345</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -7575,31 +7737,31 @@
       <c r="K135">
         <v>0</v>
       </c>
-      <c r="M135" t="s">
-        <v>430</v>
-      </c>
-      <c r="N135" t="s">
-        <v>349</v>
+      <c r="M135" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>765</v>
       </c>
       <c r="O135" t="s">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="P135" t="s">
         <v>242</v>
       </c>
-      <c r="Q135" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q135" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>192</v>
       </c>
       <c r="B136" t="s">
-        <v>432</v>
+        <v>346</v>
       </c>
       <c r="C136" t="s">
-        <v>433</v>
+        <v>347</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -7608,30 +7770,30 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>434</v>
+        <v>348</v>
       </c>
       <c r="N136" t="s">
         <v>214</v>
       </c>
       <c r="O136" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="P136" t="s">
         <v>244</v>
       </c>
       <c r="Q136" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>192</v>
       </c>
       <c r="B137" t="s">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="C137" t="s">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -7640,30 +7802,30 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>439</v>
+        <v>353</v>
       </c>
       <c r="N137" t="s">
         <v>214</v>
       </c>
       <c r="O137" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="P137" t="s">
         <v>244</v>
       </c>
       <c r="Q137" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>192</v>
       </c>
       <c r="B138" t="s">
-        <v>441</v>
+        <v>355</v>
       </c>
       <c r="C138" t="s">
-        <v>442</v>
+        <v>356</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -7671,31 +7833,31 @@
       <c r="K138">
         <v>0</v>
       </c>
-      <c r="M138" t="s">
-        <v>443</v>
+      <c r="M138" s="2" t="s">
+        <v>767</v>
       </c>
       <c r="N138" t="s">
         <v>214</v>
       </c>
       <c r="O138" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="P138" t="s">
         <v>244</v>
       </c>
-      <c r="Q138" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q138" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>445</v>
+        <v>357</v>
       </c>
       <c r="C139" t="s">
-        <v>446</v>
+        <v>358</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -7703,31 +7865,31 @@
       <c r="K139">
         <v>0</v>
       </c>
-      <c r="M139" t="s">
-        <v>447</v>
+      <c r="M139" s="2" t="s">
+        <v>769</v>
       </c>
       <c r="N139" t="s">
         <v>214</v>
       </c>
       <c r="O139" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="P139" t="s">
         <v>244</v>
       </c>
-      <c r="Q139" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q139" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>192</v>
       </c>
       <c r="B140" t="s">
-        <v>449</v>
+        <v>359</v>
       </c>
       <c r="C140" t="s">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -7736,30 +7898,30 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>451</v>
+        <v>361</v>
       </c>
       <c r="N140" t="s">
         <v>214</v>
       </c>
       <c r="O140" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="P140" t="s">
         <v>244</v>
       </c>
       <c r="Q140" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>453</v>
+        <v>363</v>
       </c>
       <c r="C141" t="s">
-        <v>454</v>
+        <v>364</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -7767,31 +7929,31 @@
       <c r="K141">
         <v>0</v>
       </c>
-      <c r="M141" t="s">
-        <v>455</v>
+      <c r="M141" s="2" t="s">
+        <v>771</v>
       </c>
       <c r="N141" t="s">
         <v>258</v>
       </c>
       <c r="O141" t="s">
-        <v>456</v>
+        <v>365</v>
       </c>
       <c r="P141" t="s">
         <v>250</v>
       </c>
-      <c r="Q141" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q141" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>192</v>
       </c>
       <c r="B142" t="s">
-        <v>458</v>
+        <v>366</v>
       </c>
       <c r="C142" t="s">
-        <v>459</v>
+        <v>367</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -7800,30 +7962,30 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>460</v>
+        <v>368</v>
       </c>
       <c r="N142" t="s">
         <v>258</v>
       </c>
       <c r="O142" t="s">
-        <v>456</v>
+        <v>365</v>
       </c>
       <c r="P142" t="s">
         <v>250</v>
       </c>
       <c r="Q142" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>462</v>
+        <v>370</v>
       </c>
       <c r="C143" t="s">
-        <v>463</v>
+        <v>371</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -7832,30 +7994,30 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>464</v>
+        <v>372</v>
       </c>
       <c r="N143" t="s">
         <v>258</v>
       </c>
       <c r="O143" t="s">
-        <v>456</v>
+        <v>365</v>
       </c>
       <c r="P143" t="s">
         <v>250</v>
       </c>
       <c r="Q143" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>192</v>
       </c>
       <c r="B144" t="s">
-        <v>466</v>
+        <v>374</v>
       </c>
       <c r="C144" t="s">
-        <v>467</v>
+        <v>375</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -7864,30 +8026,30 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>468</v>
+        <v>376</v>
       </c>
       <c r="N144" t="s">
         <v>258</v>
       </c>
       <c r="O144" t="s">
-        <v>456</v>
+        <v>365</v>
       </c>
       <c r="P144" t="s">
         <v>250</v>
       </c>
       <c r="Q144" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>470</v>
+        <v>378</v>
       </c>
       <c r="C145" t="s">
-        <v>471</v>
+        <v>379</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -7896,30 +8058,30 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>472</v>
+        <v>380</v>
       </c>
       <c r="N145" t="s">
         <v>258</v>
       </c>
       <c r="O145" t="s">
-        <v>456</v>
+        <v>365</v>
       </c>
       <c r="P145" t="s">
         <v>250</v>
       </c>
       <c r="Q145" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>192</v>
       </c>
       <c r="B146" t="s">
-        <v>474</v>
+        <v>382</v>
       </c>
       <c r="C146" t="s">
-        <v>475</v>
+        <v>383</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -7927,31 +8089,31 @@
       <c r="K146">
         <v>0</v>
       </c>
-      <c r="M146" t="s">
-        <v>476</v>
+      <c r="M146" s="2" t="s">
+        <v>773</v>
       </c>
       <c r="N146" t="s">
         <v>258</v>
       </c>
       <c r="O146" t="s">
-        <v>477</v>
+        <v>384</v>
       </c>
       <c r="P146" t="s">
         <v>247</v>
       </c>
-      <c r="Q146" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q146" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>479</v>
+        <v>385</v>
       </c>
       <c r="C147" t="s">
-        <v>480</v>
+        <v>386</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -7960,30 +8122,30 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>481</v>
+        <v>387</v>
       </c>
       <c r="N147" t="s">
         <v>258</v>
       </c>
       <c r="O147" t="s">
-        <v>477</v>
+        <v>384</v>
       </c>
       <c r="P147" t="s">
         <v>247</v>
       </c>
       <c r="Q147" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>192</v>
       </c>
       <c r="B148" t="s">
-        <v>483</v>
+        <v>389</v>
       </c>
       <c r="C148" t="s">
-        <v>484</v>
+        <v>390</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -7992,30 +8154,30 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>485</v>
+        <v>391</v>
       </c>
       <c r="N148" t="s">
         <v>258</v>
       </c>
       <c r="O148" t="s">
-        <v>477</v>
+        <v>384</v>
       </c>
       <c r="P148" t="s">
         <v>247</v>
       </c>
       <c r="Q148" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>192</v>
       </c>
       <c r="B149" t="s">
-        <v>487</v>
+        <v>393</v>
       </c>
       <c r="C149" t="s">
-        <v>488</v>
+        <v>394</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -8024,30 +8186,30 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>489</v>
+        <v>395</v>
       </c>
       <c r="N149" t="s">
         <v>258</v>
       </c>
       <c r="O149" t="s">
-        <v>477</v>
+        <v>384</v>
       </c>
       <c r="P149" t="s">
         <v>247</v>
       </c>
       <c r="Q149" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>491</v>
+        <v>397</v>
       </c>
       <c r="C150" t="s">
-        <v>492</v>
+        <v>398</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -8055,31 +8217,31 @@
       <c r="K150">
         <v>0</v>
       </c>
-      <c r="M150" t="s">
-        <v>493</v>
+      <c r="M150" s="2" t="s">
+        <v>775</v>
       </c>
       <c r="N150" t="s">
         <v>258</v>
       </c>
       <c r="O150" t="s">
-        <v>477</v>
+        <v>384</v>
       </c>
       <c r="P150" t="s">
         <v>247</v>
       </c>
-      <c r="Q150" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q150" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>192</v>
       </c>
       <c r="B151" t="s">
-        <v>495</v>
+        <v>399</v>
       </c>
       <c r="C151" t="s">
-        <v>496</v>
+        <v>400</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -8088,30 +8250,30 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>497</v>
+        <v>401</v>
       </c>
       <c r="N151" t="s">
         <v>258</v>
       </c>
       <c r="O151" t="s">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="P151" t="s">
         <v>248</v>
       </c>
       <c r="Q151" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>192</v>
       </c>
       <c r="B152" t="s">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="C152" t="s">
-        <v>501</v>
+        <v>405</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -8119,31 +8281,31 @@
       <c r="K152">
         <v>0</v>
       </c>
-      <c r="M152" t="s">
-        <v>502</v>
+      <c r="M152" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="N152" t="s">
         <v>258</v>
       </c>
       <c r="O152" t="s">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="P152" t="s">
         <v>248</v>
       </c>
-      <c r="Q152" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q152" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>192</v>
       </c>
       <c r="B153" t="s">
-        <v>504</v>
+        <v>406</v>
       </c>
       <c r="C153" t="s">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -8151,31 +8313,31 @@
       <c r="K153">
         <v>0</v>
       </c>
-      <c r="M153" t="s">
-        <v>818</v>
+      <c r="M153" s="2" t="s">
+        <v>779</v>
       </c>
       <c r="N153" t="s">
         <v>258</v>
       </c>
       <c r="O153" t="s">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="P153" t="s">
         <v>248</v>
       </c>
-      <c r="Q153" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q153" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>192</v>
       </c>
       <c r="B154" t="s">
-        <v>506</v>
+        <v>408</v>
       </c>
       <c r="C154" t="s">
-        <v>507</v>
+        <v>409</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -8184,30 +8346,30 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>508</v>
+        <v>410</v>
       </c>
       <c r="N154" t="s">
         <v>258</v>
       </c>
       <c r="O154" t="s">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="P154" t="s">
         <v>248</v>
       </c>
       <c r="Q154" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>192</v>
       </c>
       <c r="B155" t="s">
-        <v>510</v>
+        <v>412</v>
       </c>
       <c r="C155" t="s">
-        <v>511</v>
+        <v>413</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -8216,30 +8378,30 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>512</v>
+        <v>414</v>
       </c>
       <c r="N155" t="s">
         <v>258</v>
       </c>
       <c r="O155" t="s">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="P155" t="s">
         <v>248</v>
       </c>
       <c r="Q155" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>192</v>
       </c>
       <c r="B156" t="s">
-        <v>514</v>
+        <v>416</v>
       </c>
       <c r="C156" t="s">
-        <v>515</v>
+        <v>417</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -8247,31 +8409,31 @@
       <c r="K156">
         <v>0</v>
       </c>
-      <c r="M156" t="s">
-        <v>516</v>
+      <c r="M156" s="2" t="s">
+        <v>781</v>
       </c>
       <c r="N156" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O156" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="P156" t="s">
         <v>246</v>
       </c>
       <c r="Q156" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>192</v>
       </c>
       <c r="B157" t="s">
-        <v>520</v>
+        <v>421</v>
       </c>
       <c r="C157" t="s">
-        <v>521</v>
+        <v>422</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -8280,30 +8442,30 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>522</v>
+        <v>423</v>
       </c>
       <c r="N157" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O157" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="P157" t="s">
         <v>246</v>
       </c>
       <c r="Q157" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>192</v>
       </c>
       <c r="B158" t="s">
-        <v>524</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>525</v>
+        <v>426</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -8312,30 +8474,30 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>526</v>
+        <v>427</v>
       </c>
       <c r="N158" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O158" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="P158" t="s">
         <v>246</v>
       </c>
       <c r="Q158" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>192</v>
       </c>
       <c r="B159" t="s">
-        <v>528</v>
+        <v>429</v>
       </c>
       <c r="C159" t="s">
-        <v>529</v>
+        <v>430</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -8343,31 +8505,31 @@
       <c r="K159">
         <v>0</v>
       </c>
-      <c r="M159" t="s">
-        <v>530</v>
+      <c r="M159" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="N159" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O159" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="P159" t="s">
         <v>246</v>
       </c>
-      <c r="Q159" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q159" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>192</v>
       </c>
       <c r="B160" t="s">
-        <v>532</v>
+        <v>431</v>
       </c>
       <c r="C160" t="s">
-        <v>533</v>
+        <v>432</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -8375,31 +8537,31 @@
       <c r="K160">
         <v>0</v>
       </c>
-      <c r="M160" t="s">
-        <v>534</v>
+      <c r="M160" s="2" t="s">
+        <v>784</v>
       </c>
       <c r="N160" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O160" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="P160" t="s">
         <v>246</v>
       </c>
-      <c r="Q160" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q160" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>192</v>
       </c>
       <c r="B161" t="s">
-        <v>536</v>
+        <v>433</v>
       </c>
       <c r="C161" t="s">
-        <v>537</v>
+        <v>434</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -8408,30 +8570,30 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>538</v>
+        <v>435</v>
       </c>
       <c r="N161" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O161" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="P161" t="s">
         <v>238</v>
       </c>
       <c r="Q161" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>541</v>
+        <v>438</v>
       </c>
       <c r="C162" t="s">
-        <v>542</v>
+        <v>439</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -8439,31 +8601,31 @@
       <c r="K162">
         <v>0</v>
       </c>
-      <c r="M162" t="s">
-        <v>543</v>
+      <c r="M162" s="2" t="s">
+        <v>786</v>
       </c>
       <c r="N162" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O162" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="P162" t="s">
         <v>238</v>
       </c>
-      <c r="Q162" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q162" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>545</v>
+        <v>440</v>
       </c>
       <c r="C163" t="s">
-        <v>546</v>
+        <v>441</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -8471,31 +8633,31 @@
       <c r="K163">
         <v>0</v>
       </c>
-      <c r="M163" t="s">
-        <v>547</v>
+      <c r="M163" s="2" t="s">
+        <v>788</v>
       </c>
       <c r="N163" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O163" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="P163" t="s">
         <v>238</v>
       </c>
-      <c r="Q163" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q163" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>549</v>
+        <v>442</v>
       </c>
       <c r="C164" t="s">
-        <v>550</v>
+        <v>443</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -8503,31 +8665,31 @@
       <c r="K164">
         <v>0</v>
       </c>
-      <c r="M164" t="s">
-        <v>551</v>
+      <c r="M164" s="2" t="s">
+        <v>790</v>
       </c>
       <c r="N164" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O164" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="P164" t="s">
         <v>238</v>
       </c>
-      <c r="Q164" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q164" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>553</v>
+        <v>444</v>
       </c>
       <c r="C165" t="s">
-        <v>554</v>
+        <v>445</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -8536,30 +8698,30 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>555</v>
+        <v>446</v>
       </c>
       <c r="N165" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O165" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="P165" t="s">
         <v>238</v>
       </c>
       <c r="Q165" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>192</v>
       </c>
       <c r="B166" t="s">
-        <v>557</v>
+        <v>448</v>
       </c>
       <c r="C166" t="s">
-        <v>558</v>
+        <v>449</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -8567,31 +8729,31 @@
       <c r="K166">
         <v>0</v>
       </c>
-      <c r="M166" t="s">
-        <v>559</v>
+      <c r="M166" s="2" t="s">
+        <v>792</v>
       </c>
       <c r="N166" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O166" t="s">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="P166" t="s">
         <v>242</v>
       </c>
       <c r="Q166" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>562</v>
+        <v>452</v>
       </c>
       <c r="C167" t="s">
-        <v>563</v>
+        <v>453</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -8599,31 +8761,31 @@
       <c r="K167">
         <v>0</v>
       </c>
-      <c r="M167" t="s">
-        <v>564</v>
+      <c r="M167" s="2" t="s">
+        <v>793</v>
       </c>
       <c r="N167" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O167" t="s">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="P167" t="s">
         <v>242</v>
       </c>
-      <c r="Q167" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q167" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>192</v>
       </c>
       <c r="B168" t="s">
-        <v>566</v>
+        <v>454</v>
       </c>
       <c r="C168" t="s">
-        <v>567</v>
+        <v>455</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -8632,30 +8794,30 @@
         <v>0</v>
       </c>
       <c r="M168" t="s">
-        <v>568</v>
+        <v>456</v>
       </c>
       <c r="N168" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O168" t="s">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="P168" t="s">
         <v>242</v>
       </c>
       <c r="Q168" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>192</v>
       </c>
       <c r="B169" t="s">
-        <v>570</v>
+        <v>458</v>
       </c>
       <c r="C169" t="s">
-        <v>571</v>
+        <v>459</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -8663,31 +8825,31 @@
       <c r="K169">
         <v>0</v>
       </c>
-      <c r="M169" t="s">
-        <v>572</v>
+      <c r="M169" s="2" t="s">
+        <v>795</v>
       </c>
       <c r="N169" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O169" t="s">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="P169" t="s">
         <v>242</v>
       </c>
-      <c r="Q169" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q169" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>192</v>
       </c>
       <c r="B170" t="s">
-        <v>574</v>
+        <v>460</v>
       </c>
       <c r="C170" t="s">
-        <v>575</v>
+        <v>461</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -8696,30 +8858,30 @@
         <v>0</v>
       </c>
       <c r="M170" t="s">
-        <v>819</v>
+        <v>674</v>
       </c>
       <c r="N170" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="O170" t="s">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="P170" t="s">
         <v>242</v>
       </c>
       <c r="Q170" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>192</v>
       </c>
       <c r="B171" t="s">
-        <v>577</v>
+        <v>463</v>
       </c>
       <c r="C171" t="s">
-        <v>578</v>
+        <v>464</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -8727,31 +8889,31 @@
       <c r="K171">
         <v>0</v>
       </c>
-      <c r="M171" t="s">
-        <v>579</v>
+      <c r="M171" s="2" t="s">
+        <v>797</v>
       </c>
       <c r="N171" t="s">
         <v>249</v>
       </c>
       <c r="O171" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
       <c r="P171" t="s">
         <v>215</v>
       </c>
-      <c r="Q171" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q171" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>582</v>
+        <v>466</v>
       </c>
       <c r="C172" t="s">
-        <v>583</v>
+        <v>467</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -8759,31 +8921,31 @@
       <c r="K172">
         <v>0</v>
       </c>
-      <c r="M172" t="s">
-        <v>584</v>
+      <c r="M172" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="N172" t="s">
         <v>249</v>
       </c>
       <c r="O172" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
       <c r="P172" t="s">
         <v>215</v>
       </c>
-      <c r="Q172" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q172" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>586</v>
+        <v>468</v>
       </c>
       <c r="C173" t="s">
-        <v>587</v>
+        <v>469</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -8792,30 +8954,30 @@
         <v>0</v>
       </c>
       <c r="M173" t="s">
-        <v>588</v>
+        <v>470</v>
       </c>
       <c r="N173" t="s">
         <v>249</v>
       </c>
       <c r="O173" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
       <c r="P173" t="s">
         <v>215</v>
       </c>
       <c r="Q173" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>590</v>
+        <v>472</v>
       </c>
       <c r="C174" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -8824,30 +8986,30 @@
         <v>0</v>
       </c>
       <c r="M174" t="s">
-        <v>592</v>
+        <v>474</v>
       </c>
       <c r="N174" t="s">
         <v>249</v>
       </c>
       <c r="O174" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
       <c r="P174" t="s">
         <v>215</v>
       </c>
       <c r="Q174" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>594</v>
+        <v>476</v>
       </c>
       <c r="C175" t="s">
-        <v>595</v>
+        <v>477</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -8855,31 +9017,31 @@
       <c r="K175">
         <v>0</v>
       </c>
-      <c r="M175" t="s">
-        <v>596</v>
+      <c r="M175" s="2" t="s">
+        <v>801</v>
       </c>
       <c r="N175" t="s">
         <v>249</v>
       </c>
       <c r="O175" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
       <c r="P175" t="s">
         <v>215</v>
       </c>
-      <c r="Q175" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q175" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>598</v>
+        <v>478</v>
       </c>
       <c r="C176" t="s">
-        <v>599</v>
+        <v>479</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -8888,30 +9050,30 @@
         <v>0</v>
       </c>
       <c r="M176" t="s">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="N176" t="s">
         <v>249</v>
       </c>
       <c r="O176" t="s">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="P176" t="s">
         <v>250</v>
       </c>
       <c r="Q176" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>192</v>
       </c>
       <c r="B177" t="s">
-        <v>603</v>
+        <v>483</v>
       </c>
       <c r="C177" t="s">
-        <v>604</v>
+        <v>484</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -8919,31 +9081,31 @@
       <c r="K177">
         <v>0</v>
       </c>
-      <c r="M177" t="s">
-        <v>605</v>
+      <c r="M177" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="N177" t="s">
         <v>249</v>
       </c>
       <c r="O177" t="s">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="P177" t="s">
         <v>250</v>
       </c>
-      <c r="Q177" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q177" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>192</v>
       </c>
       <c r="B178" t="s">
-        <v>607</v>
+        <v>485</v>
       </c>
       <c r="C178" t="s">
-        <v>608</v>
+        <v>486</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -8952,30 +9114,30 @@
         <v>0</v>
       </c>
       <c r="M178" t="s">
-        <v>609</v>
+        <v>487</v>
       </c>
       <c r="N178" t="s">
         <v>249</v>
       </c>
       <c r="O178" t="s">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="P178" t="s">
         <v>250</v>
       </c>
       <c r="Q178" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>192</v>
       </c>
       <c r="B179" t="s">
-        <v>611</v>
+        <v>489</v>
       </c>
       <c r="C179" t="s">
-        <v>612</v>
+        <v>490</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -8984,30 +9146,30 @@
         <v>0</v>
       </c>
       <c r="M179" t="s">
-        <v>613</v>
+        <v>491</v>
       </c>
       <c r="N179" t="s">
         <v>249</v>
       </c>
       <c r="O179" t="s">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="P179" t="s">
         <v>250</v>
       </c>
       <c r="Q179" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>192</v>
       </c>
       <c r="B180" t="s">
-        <v>615</v>
+        <v>493</v>
       </c>
       <c r="C180" t="s">
-        <v>616</v>
+        <v>494</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -9016,30 +9178,30 @@
         <v>0</v>
       </c>
       <c r="M180" t="s">
-        <v>617</v>
+        <v>495</v>
       </c>
       <c r="N180" t="s">
         <v>249</v>
       </c>
       <c r="O180" t="s">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="P180" t="s">
         <v>250</v>
       </c>
       <c r="Q180" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>192</v>
       </c>
       <c r="B181" t="s">
-        <v>619</v>
+        <v>497</v>
       </c>
       <c r="C181" t="s">
-        <v>620</v>
+        <v>498</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -9047,31 +9209,31 @@
       <c r="K181">
         <v>0</v>
       </c>
-      <c r="M181" t="s">
-        <v>621</v>
+      <c r="M181" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="N181" t="s">
         <v>249</v>
       </c>
       <c r="O181" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="P181" t="s">
         <v>248</v>
       </c>
-      <c r="Q181" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q181" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>624</v>
+        <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>625</v>
+        <v>501</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -9079,31 +9241,31 @@
       <c r="K182">
         <v>0</v>
       </c>
-      <c r="M182" t="s">
-        <v>626</v>
+      <c r="M182" s="2" t="s">
+        <v>807</v>
       </c>
       <c r="N182" t="s">
         <v>249</v>
       </c>
       <c r="O182" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="P182" t="s">
         <v>248</v>
       </c>
-      <c r="Q182" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q182" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>192</v>
       </c>
       <c r="B183" t="s">
-        <v>628</v>
+        <v>502</v>
       </c>
       <c r="C183" t="s">
-        <v>629</v>
+        <v>503</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -9111,31 +9273,31 @@
       <c r="K183">
         <v>0</v>
       </c>
-      <c r="M183" t="s">
-        <v>630</v>
+      <c r="M183" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="N183" t="s">
         <v>249</v>
       </c>
       <c r="O183" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="P183" t="s">
         <v>248</v>
       </c>
-      <c r="Q183" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q183" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>192</v>
       </c>
       <c r="B184" t="s">
-        <v>632</v>
+        <v>504</v>
       </c>
       <c r="C184" t="s">
-        <v>633</v>
+        <v>505</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -9144,30 +9306,30 @@
         <v>0</v>
       </c>
       <c r="M184" t="s">
-        <v>634</v>
+        <v>506</v>
       </c>
       <c r="N184" t="s">
         <v>249</v>
       </c>
       <c r="O184" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="P184" t="s">
         <v>248</v>
       </c>
       <c r="Q184" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>192</v>
       </c>
       <c r="B185" t="s">
-        <v>636</v>
+        <v>508</v>
       </c>
       <c r="C185" t="s">
-        <v>637</v>
+        <v>509</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -9176,30 +9338,30 @@
         <v>0</v>
       </c>
       <c r="M185" t="s">
-        <v>638</v>
+        <v>510</v>
       </c>
       <c r="N185" t="s">
         <v>249</v>
       </c>
       <c r="O185" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="P185" t="s">
         <v>248</v>
       </c>
       <c r="Q185" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>192</v>
       </c>
       <c r="B186" t="s">
-        <v>640</v>
+        <v>512</v>
       </c>
       <c r="C186" t="s">
-        <v>641</v>
+        <v>513</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -9208,30 +9370,30 @@
         <v>0</v>
       </c>
       <c r="M186" t="s">
-        <v>642</v>
+        <v>514</v>
       </c>
       <c r="N186" t="s">
         <v>245</v>
       </c>
       <c r="O186" t="s">
-        <v>643</v>
+        <v>515</v>
       </c>
       <c r="P186" t="s">
         <v>263</v>
       </c>
       <c r="Q186" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>645</v>
+        <v>517</v>
       </c>
       <c r="C187" t="s">
-        <v>646</v>
+        <v>518</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -9239,31 +9401,31 @@
       <c r="K187">
         <v>0</v>
       </c>
-      <c r="M187" t="s">
-        <v>647</v>
+      <c r="M187" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="N187" t="s">
         <v>245</v>
       </c>
       <c r="O187" t="s">
-        <v>643</v>
+        <v>515</v>
       </c>
       <c r="P187" t="s">
         <v>263</v>
       </c>
-      <c r="Q187" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q187" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>192</v>
       </c>
       <c r="B188" t="s">
-        <v>649</v>
+        <v>519</v>
       </c>
       <c r="C188" t="s">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -9271,31 +9433,31 @@
       <c r="K188">
         <v>0</v>
       </c>
-      <c r="M188" t="s">
-        <v>651</v>
+      <c r="M188" s="2" t="s">
+        <v>813</v>
       </c>
       <c r="N188" t="s">
         <v>245</v>
       </c>
       <c r="O188" t="s">
-        <v>643</v>
+        <v>515</v>
       </c>
       <c r="P188" t="s">
         <v>263</v>
       </c>
-      <c r="Q188" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q188" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>653</v>
+        <v>521</v>
       </c>
       <c r="C189" t="s">
-        <v>654</v>
+        <v>522</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -9304,30 +9466,30 @@
         <v>0</v>
       </c>
       <c r="M189" t="s">
-        <v>655</v>
+        <v>523</v>
       </c>
       <c r="N189" t="s">
         <v>245</v>
       </c>
       <c r="O189" t="s">
-        <v>643</v>
+        <v>515</v>
       </c>
       <c r="P189" t="s">
         <v>263</v>
       </c>
       <c r="Q189" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>192</v>
       </c>
       <c r="B190" t="s">
-        <v>657</v>
+        <v>525</v>
       </c>
       <c r="C190" t="s">
-        <v>658</v>
+        <v>526</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -9335,31 +9497,31 @@
       <c r="K190">
         <v>0</v>
       </c>
-      <c r="M190" t="s">
-        <v>659</v>
+      <c r="M190" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="N190" t="s">
         <v>245</v>
       </c>
       <c r="O190" t="s">
-        <v>643</v>
+        <v>515</v>
       </c>
       <c r="P190" t="s">
         <v>263</v>
       </c>
-      <c r="Q190" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q190" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>192</v>
       </c>
       <c r="B191" t="s">
-        <v>661</v>
+        <v>527</v>
       </c>
       <c r="C191" t="s">
-        <v>662</v>
+        <v>528</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -9368,30 +9530,30 @@
         <v>0</v>
       </c>
       <c r="M191" t="s">
-        <v>663</v>
+        <v>529</v>
       </c>
       <c r="N191" t="s">
         <v>245</v>
       </c>
       <c r="O191" t="s">
-        <v>664</v>
+        <v>530</v>
       </c>
       <c r="P191" t="s">
         <v>246</v>
       </c>
       <c r="Q191" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>666</v>
+        <v>532</v>
       </c>
       <c r="C192" t="s">
-        <v>667</v>
+        <v>533</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -9400,30 +9562,30 @@
         <v>0</v>
       </c>
       <c r="M192" t="s">
-        <v>668</v>
+        <v>534</v>
       </c>
       <c r="N192" t="s">
         <v>245</v>
       </c>
       <c r="O192" t="s">
-        <v>664</v>
+        <v>530</v>
       </c>
       <c r="P192" t="s">
         <v>246</v>
       </c>
       <c r="Q192" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>670</v>
+        <v>536</v>
       </c>
       <c r="C193" t="s">
-        <v>671</v>
+        <v>537</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -9432,30 +9594,30 @@
         <v>0</v>
       </c>
       <c r="M193" t="s">
-        <v>672</v>
+        <v>538</v>
       </c>
       <c r="N193" t="s">
         <v>245</v>
       </c>
       <c r="O193" t="s">
-        <v>664</v>
+        <v>530</v>
       </c>
       <c r="P193" t="s">
         <v>246</v>
       </c>
       <c r="Q193" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>674</v>
+        <v>540</v>
       </c>
       <c r="C194" t="s">
-        <v>675</v>
+        <v>541</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -9464,30 +9626,30 @@
         <v>0</v>
       </c>
       <c r="M194" t="s">
-        <v>676</v>
+        <v>542</v>
       </c>
       <c r="N194" t="s">
         <v>245</v>
       </c>
       <c r="O194" t="s">
-        <v>664</v>
+        <v>530</v>
       </c>
       <c r="P194" t="s">
         <v>246</v>
       </c>
       <c r="Q194" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>192</v>
       </c>
       <c r="B195" t="s">
-        <v>678</v>
+        <v>544</v>
       </c>
       <c r="C195" t="s">
-        <v>679</v>
+        <v>545</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -9496,30 +9658,30 @@
         <v>0</v>
       </c>
       <c r="M195" t="s">
-        <v>680</v>
+        <v>546</v>
       </c>
       <c r="N195" t="s">
         <v>245</v>
       </c>
       <c r="O195" t="s">
-        <v>664</v>
+        <v>530</v>
       </c>
       <c r="P195" t="s">
         <v>246</v>
       </c>
       <c r="Q195" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>192</v>
       </c>
       <c r="B196" t="s">
-        <v>682</v>
+        <v>548</v>
       </c>
       <c r="C196" t="s">
-        <v>683</v>
+        <v>549</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -9527,31 +9689,31 @@
       <c r="K196">
         <v>0</v>
       </c>
-      <c r="M196" t="s">
-        <v>684</v>
+      <c r="M196" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="N196" t="s">
         <v>245</v>
       </c>
       <c r="O196" t="s">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="P196" t="s">
         <v>247</v>
       </c>
-      <c r="Q196" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q196" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>192</v>
       </c>
       <c r="B197" t="s">
-        <v>687</v>
+        <v>551</v>
       </c>
       <c r="C197" t="s">
-        <v>688</v>
+        <v>552</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -9560,30 +9722,30 @@
         <v>0</v>
       </c>
       <c r="M197" t="s">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="N197" t="s">
         <v>245</v>
       </c>
       <c r="O197" t="s">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="P197" t="s">
         <v>247</v>
       </c>
       <c r="Q197" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>192</v>
       </c>
       <c r="B198" t="s">
-        <v>691</v>
+        <v>555</v>
       </c>
       <c r="C198" t="s">
-        <v>692</v>
+        <v>556</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -9592,30 +9754,30 @@
         <v>0</v>
       </c>
       <c r="M198" t="s">
-        <v>693</v>
+        <v>557</v>
       </c>
       <c r="N198" t="s">
         <v>245</v>
       </c>
       <c r="O198" t="s">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="P198" t="s">
         <v>247</v>
       </c>
       <c r="Q198" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>192</v>
       </c>
       <c r="B199" t="s">
-        <v>695</v>
+        <v>559</v>
       </c>
       <c r="C199" t="s">
-        <v>696</v>
+        <v>560</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -9624,30 +9786,30 @@
         <v>0</v>
       </c>
       <c r="M199" t="s">
-        <v>697</v>
+        <v>561</v>
       </c>
       <c r="N199" t="s">
         <v>245</v>
       </c>
       <c r="O199" t="s">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="P199" t="s">
         <v>247</v>
       </c>
       <c r="Q199" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>192</v>
       </c>
       <c r="B200" t="s">
-        <v>699</v>
+        <v>563</v>
       </c>
       <c r="C200" t="s">
-        <v>700</v>
+        <v>564</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -9655,31 +9817,31 @@
       <c r="K200">
         <v>0</v>
       </c>
-      <c r="M200" t="s">
-        <v>701</v>
+      <c r="M200" s="2" t="s">
+        <v>819</v>
       </c>
       <c r="N200" t="s">
         <v>245</v>
       </c>
       <c r="O200" t="s">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="P200" t="s">
         <v>247</v>
       </c>
-      <c r="Q200" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q200" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>192</v>
       </c>
       <c r="B201" t="s">
-        <v>703</v>
+        <v>565</v>
       </c>
       <c r="C201" t="s">
-        <v>704</v>
+        <v>566</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -9687,31 +9849,31 @@
       <c r="K201">
         <v>0</v>
       </c>
-      <c r="M201" t="s">
-        <v>705</v>
+      <c r="M201" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="N201" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O201" t="s">
-        <v>706</v>
+        <v>567</v>
       </c>
       <c r="P201" t="s">
         <v>250</v>
       </c>
-      <c r="Q201" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q201" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>192</v>
       </c>
       <c r="B202" t="s">
-        <v>708</v>
+        <v>568</v>
       </c>
       <c r="C202" t="s">
-        <v>709</v>
+        <v>569</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -9720,30 +9882,30 @@
         <v>0</v>
       </c>
       <c r="M202" t="s">
-        <v>710</v>
+        <v>570</v>
       </c>
       <c r="N202" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O202" t="s">
-        <v>706</v>
+        <v>567</v>
       </c>
       <c r="P202" t="s">
         <v>250</v>
       </c>
       <c r="Q202" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>192</v>
       </c>
       <c r="B203" t="s">
-        <v>712</v>
+        <v>572</v>
       </c>
       <c r="C203" t="s">
-        <v>713</v>
+        <v>573</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -9752,30 +9914,30 @@
         <v>0</v>
       </c>
       <c r="M203" t="s">
-        <v>714</v>
+        <v>574</v>
       </c>
       <c r="N203" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O203" t="s">
-        <v>706</v>
+        <v>567</v>
       </c>
       <c r="P203" t="s">
         <v>250</v>
       </c>
       <c r="Q203" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>192</v>
       </c>
       <c r="B204" t="s">
-        <v>716</v>
+        <v>576</v>
       </c>
       <c r="C204" t="s">
-        <v>717</v>
+        <v>577</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -9784,30 +9946,30 @@
         <v>0</v>
       </c>
       <c r="M204" t="s">
-        <v>718</v>
+        <v>578</v>
       </c>
       <c r="N204" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O204" t="s">
-        <v>706</v>
+        <v>567</v>
       </c>
       <c r="P204" t="s">
         <v>250</v>
       </c>
       <c r="Q204" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>192</v>
       </c>
       <c r="B205" t="s">
-        <v>720</v>
+        <v>580</v>
       </c>
       <c r="C205" t="s">
-        <v>721</v>
+        <v>581</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -9816,30 +9978,30 @@
         <v>0</v>
       </c>
       <c r="M205" t="s">
-        <v>722</v>
+        <v>582</v>
       </c>
       <c r="N205" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O205" t="s">
-        <v>706</v>
+        <v>567</v>
       </c>
       <c r="P205" t="s">
         <v>250</v>
       </c>
       <c r="Q205" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>192</v>
       </c>
       <c r="B206" t="s">
-        <v>724</v>
+        <v>584</v>
       </c>
       <c r="C206" t="s">
-        <v>725</v>
+        <v>585</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -9848,30 +10010,30 @@
         <v>0</v>
       </c>
       <c r="M206" t="s">
-        <v>726</v>
+        <v>586</v>
       </c>
       <c r="N206" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O206" t="s">
-        <v>727</v>
+        <v>587</v>
       </c>
       <c r="P206" t="s">
         <v>219</v>
       </c>
       <c r="Q206" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>192</v>
       </c>
       <c r="B207" t="s">
-        <v>729</v>
+        <v>589</v>
       </c>
       <c r="C207" t="s">
-        <v>730</v>
+        <v>590</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -9880,30 +10042,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="s">
-        <v>731</v>
+        <v>591</v>
       </c>
       <c r="N207" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O207" t="s">
-        <v>727</v>
+        <v>587</v>
       </c>
       <c r="P207" t="s">
         <v>219</v>
       </c>
       <c r="Q207" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>192</v>
       </c>
       <c r="B208" t="s">
-        <v>733</v>
+        <v>593</v>
       </c>
       <c r="C208" t="s">
-        <v>734</v>
+        <v>594</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -9912,30 +10074,30 @@
         <v>0</v>
       </c>
       <c r="M208" t="s">
-        <v>735</v>
+        <v>595</v>
       </c>
       <c r="N208" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O208" t="s">
-        <v>727</v>
+        <v>587</v>
       </c>
       <c r="P208" t="s">
         <v>219</v>
       </c>
       <c r="Q208" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>192</v>
       </c>
       <c r="B209" t="s">
-        <v>737</v>
+        <v>597</v>
       </c>
       <c r="C209" t="s">
-        <v>738</v>
+        <v>598</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -9944,30 +10106,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="s">
-        <v>739</v>
+        <v>599</v>
       </c>
       <c r="N209" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O209" t="s">
-        <v>727</v>
+        <v>587</v>
       </c>
       <c r="P209" t="s">
         <v>219</v>
       </c>
       <c r="Q209" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>192</v>
       </c>
       <c r="B210" t="s">
-        <v>741</v>
+        <v>601</v>
       </c>
       <c r="C210" t="s">
-        <v>742</v>
+        <v>602</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -9976,30 +10138,30 @@
         <v>0</v>
       </c>
       <c r="M210" t="s">
-        <v>743</v>
+        <v>603</v>
       </c>
       <c r="N210" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O210" t="s">
-        <v>727</v>
+        <v>587</v>
       </c>
       <c r="P210" t="s">
         <v>219</v>
       </c>
       <c r="Q210" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>192</v>
       </c>
       <c r="B211" t="s">
-        <v>745</v>
+        <v>605</v>
       </c>
       <c r="C211" t="s">
-        <v>746</v>
+        <v>606</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -10008,30 +10170,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="s">
-        <v>747</v>
+        <v>607</v>
       </c>
       <c r="N211" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O211" t="s">
-        <v>748</v>
+        <v>608</v>
       </c>
       <c r="P211" t="s">
         <v>242</v>
       </c>
       <c r="Q211" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>192</v>
       </c>
       <c r="B212" t="s">
-        <v>750</v>
+        <v>610</v>
       </c>
       <c r="C212" t="s">
-        <v>751</v>
+        <v>611</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -10040,30 +10202,30 @@
         <v>0</v>
       </c>
       <c r="M212" t="s">
-        <v>752</v>
+        <v>612</v>
       </c>
       <c r="N212" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O212" t="s">
-        <v>748</v>
+        <v>608</v>
       </c>
       <c r="P212" t="s">
         <v>242</v>
       </c>
       <c r="Q212" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>192</v>
       </c>
       <c r="B213" t="s">
-        <v>754</v>
+        <v>614</v>
       </c>
       <c r="C213" t="s">
-        <v>755</v>
+        <v>615</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -10072,30 +10234,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="s">
-        <v>756</v>
+        <v>616</v>
       </c>
       <c r="N213" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O213" t="s">
-        <v>748</v>
+        <v>608</v>
       </c>
       <c r="P213" t="s">
         <v>242</v>
       </c>
       <c r="Q213" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>192</v>
       </c>
       <c r="B214" t="s">
-        <v>758</v>
+        <v>618</v>
       </c>
       <c r="C214" t="s">
-        <v>759</v>
+        <v>619</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -10104,30 +10266,30 @@
         <v>0</v>
       </c>
       <c r="M214" t="s">
-        <v>760</v>
+        <v>620</v>
       </c>
       <c r="N214" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O214" t="s">
-        <v>748</v>
+        <v>608</v>
       </c>
       <c r="P214" t="s">
         <v>242</v>
       </c>
       <c r="Q214" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>192</v>
       </c>
       <c r="B215" t="s">
-        <v>762</v>
+        <v>622</v>
       </c>
       <c r="C215" t="s">
-        <v>763</v>
+        <v>623</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -10135,31 +10297,31 @@
       <c r="K215">
         <v>0</v>
       </c>
-      <c r="M215" t="s">
-        <v>764</v>
+      <c r="M215" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="N215" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="O215" t="s">
-        <v>748</v>
+        <v>608</v>
       </c>
       <c r="P215" t="s">
         <v>242</v>
       </c>
-      <c r="Q215" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q215" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B216" t="s">
-        <v>767</v>
+        <v>625</v>
       </c>
       <c r="C216" t="s">
-        <v>768</v>
+        <v>626</v>
       </c>
       <c r="D216">
         <v>25</v>
@@ -10168,209 +10330,209 @@
         <v>31</v>
       </c>
       <c r="M216" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B217" t="s">
-        <v>770</v>
+        <v>628</v>
       </c>
       <c r="C217" t="s">
-        <v>771</v>
+        <v>629</v>
       </c>
       <c r="D217">
         <v>18</v>
       </c>
       <c r="L217" t="s">
-        <v>772</v>
+        <v>630</v>
       </c>
       <c r="M217" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B218" t="s">
-        <v>774</v>
+        <v>632</v>
       </c>
       <c r="C218" t="s">
-        <v>775</v>
+        <v>633</v>
       </c>
       <c r="D218">
         <v>15</v>
       </c>
       <c r="L218" t="s">
-        <v>776</v>
+        <v>634</v>
       </c>
       <c r="M218" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B219" t="s">
-        <v>778</v>
+        <v>636</v>
       </c>
       <c r="C219" t="s">
-        <v>779</v>
+        <v>637</v>
       </c>
       <c r="D219">
         <v>30</v>
       </c>
       <c r="L219" t="s">
-        <v>780</v>
+        <v>638</v>
       </c>
       <c r="M219" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B220" t="s">
-        <v>782</v>
+        <v>640</v>
       </c>
       <c r="C220" t="s">
-        <v>783</v>
+        <v>641</v>
       </c>
       <c r="D220">
         <v>25</v>
       </c>
       <c r="L220" t="s">
-        <v>784</v>
+        <v>642</v>
       </c>
       <c r="M220" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B221" t="s">
-        <v>786</v>
+        <v>644</v>
       </c>
       <c r="C221" t="s">
-        <v>787</v>
+        <v>645</v>
       </c>
       <c r="D221">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>788</v>
+        <v>646</v>
       </c>
       <c r="M221" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B222" t="s">
-        <v>790</v>
+        <v>648</v>
       </c>
       <c r="C222" t="s">
-        <v>791</v>
+        <v>649</v>
       </c>
       <c r="D222">
         <v>12</v>
       </c>
       <c r="M222" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B223" t="s">
-        <v>793</v>
+        <v>651</v>
       </c>
       <c r="C223" t="s">
-        <v>794</v>
+        <v>652</v>
       </c>
       <c r="D223">
         <v>15</v>
       </c>
       <c r="M223" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B224" t="s">
-        <v>796</v>
+        <v>654</v>
       </c>
       <c r="C224" t="s">
-        <v>797</v>
+        <v>655</v>
       </c>
       <c r="D224">
         <v>8</v>
       </c>
       <c r="M224" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B225" t="s">
-        <v>799</v>
+        <v>657</v>
       </c>
       <c r="C225" t="s">
-        <v>800</v>
+        <v>658</v>
       </c>
       <c r="D225">
         <v>30</v>
       </c>
       <c r="M225" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B226" t="s">
-        <v>802</v>
+        <v>660</v>
       </c>
       <c r="C226" t="s">
-        <v>803</v>
+        <v>661</v>
       </c>
       <c r="D226">
         <v>5</v>
       </c>
       <c r="M226" s="2" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>766</v>
+        <v>624</v>
       </c>
       <c r="B227" t="s">
-        <v>804</v>
+        <v>662</v>
       </c>
       <c r="C227" t="s">
-        <v>805</v>
+        <v>663</v>
       </c>
       <c r="D227">
         <v>35</v>
       </c>
       <c r="M227" t="s">
-        <v>806</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA42D3-5FD4-4EA8-A86D-B312A160FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABA358E-2578-416D-8065-FC02E9CDC868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="854">
   <si>
     <t>池</t>
   </si>
@@ -680,9 +680,6 @@
     <t>phys</t>
   </si>
   <si>
-    <t>sword1h</t>
-  </si>
-  <si>
     <t>mountainSunderer</t>
   </si>
   <si>
@@ -692,9 +689,6 @@
     <t>當你對敵人造成暈眩或緩速效果時，該效果持續時間 +100%，且對處於該狀態的敵人造成的傷害提高 300%。</t>
   </si>
   <si>
-    <t>axe2h</t>
-  </si>
-  <si>
     <t>{"controlDurationMult":2,"controlledTargetDamagePct":300}</t>
   </si>
   <si>
@@ -707,9 +701,6 @@
     <t>射出三把飛刀追蹤攻擊敵人，每 1 秒各攻擊 1 次並造成 60% 物理傷害；飛刀存在 4 秒，期間擊殺敵人會使所有飛刀持續時間 +0.5 秒。</t>
   </si>
   <si>
-    <t>dagger1h</t>
-  </si>
-  <si>
     <t>{"shadowKnives":{"count":3,"tickSec":1,"powerPct":60,"dur":4,"killExtend":0.5}}</t>
   </si>
   <si>
@@ -749,9 +740,6 @@
     <t>{"onKillBuff":{"atkPct":3,"aspdPct":3,"dur":6,"maxStacks":20}}</t>
   </si>
   <si>
-    <t>magicSword1h</t>
-  </si>
-  <si>
     <t>unyieldingGuard</t>
   </si>
   <si>
@@ -761,33 +749,15 @@
     <t>格擋成功時有 35% 機率，以自身原始普攻最終傷害 × 實際格擋減傷 × 500% 反擊，並使受到的傷害降低 20%，持續 3 秒。</t>
   </si>
   <si>
-    <t>shield</t>
-  </si>
-  <si>
     <t>{"onBlock":{"chance":35,"reflectBlockPct":500,"dmgRedPct":20,"dur":3}}</t>
   </si>
   <si>
-    <t>greatsword2h</t>
-  </si>
-  <si>
     <t>ice</t>
   </si>
   <si>
-    <t>focus</t>
-  </si>
-  <si>
-    <t>staff2h</t>
-  </si>
-  <si>
-    <t>orb</t>
-  </si>
-  <si>
     <t>lightning</t>
   </si>
   <si>
-    <t>wand1h</t>
-  </si>
-  <si>
     <t>thunderShock</t>
   </si>
   <si>
@@ -824,9 +794,6 @@
     <t>身體永久被火焰包覆，每秒損失 1% 最大生命；攻擊你的敵人持續受到 20% 火焰灼燒傷害，最多疊加 10 層。</t>
   </si>
   <si>
-    <t>spellbook</t>
-  </si>
-  <si>
     <t>{"selfHpDrainPctPerSec":1,"retaliateBurnPct":20,"maxStacks":10}</t>
   </si>
   <si>
@@ -947,9 +914,6 @@
     <t>bloodblade</t>
   </si>
   <si>
-    <t>magicSword2h</t>
-  </si>
-  <si>
     <t>{"bloodPoisonMist":{"m":6,"pct":50,"sec":3,"gap":0.5}}</t>
   </si>
   <si>
@@ -2030,649 +1994,770 @@
     <t>生命低於 30% 時，造成的傷害提高 {v}%</t>
   </si>
   <si>
-    <t>出現部位
-空白＝不限（全部部位）
-weapon＝主／副武器；helmet＝頭盔
-shoulder＝肩甲；chest＝胸甲；belt＝腰帶
-gloves＝護手；wrist＝手腕；legs＝護腿
-boots＝靴子；ring＝戒指 I／II；amulet＝項鍊
-all_lock＝全鎖定（不會出現在任何裝備部位上，也不會出現在屬性面板）
+    <t>吸血</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FALSE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸魔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次對敵人造成傷害時，額外回復 {v} 點生命與法力</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>helmet;belt;ring;amulet</t>
+  </si>
+  <si>
+    <t>chest;wrist;legs;ring;amulet</t>
+  </si>
+  <si>
+    <t>最低稀有度</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>體質</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeChain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每把飛刀有 25% 機率再彈射 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knife</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeBounceProc":{"chance":25,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeSplitter</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>分裂者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeSplit":{"count":2,"pct":50,"bounces":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeExecutioner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>處刑者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛刀會優先在生命值最高的目標間彈射，且對其造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeExecutor":{"pct":30}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeShadowblade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>影刃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>射出的飛刀數量 +2 把。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>phys</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeCountAdd":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeWaltzblade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>輪舞刃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>射出的第 1 把飛刀不再彈射，改為圍繞在你周圍 10 米處旋轉，對路徑上的所有敵人造成傷害，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"knifeOrbit":{"m":10,"sec":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>piercingFocus</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>凝鋒穿刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺的長度 +30%、寬度 -15%，且造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrust</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustLenPct":30,"thrustWidthPct":-15,"skillDamagePct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thousandWounds</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>千瘡百孔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次突刺命中使敵人受到的突刺傷害 +4%，持續 5 秒，最多疊加 10 層。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustVuln":{"pct":4,"dur":5,"maxStacks":10}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunpiercerLance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>貫日之刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺有 25% 機率使敵人重傷，使其受到的傷害 +20%，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustWound":{"chance":25,"pct":20,"dur":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thunderStab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迅雷穿刺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次突刺擊中敵人時有 15% 機率附加 1 道落雷。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightning</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustThunder":{"chance":15,"powerPct":200,"label":"迅雷穿刺"}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>heartrendBleed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿心裂血</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺會附加流血，每 0.5 秒造成 50% 物理傷害，持續 5 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thrustDot":{"tickPowerPct":50,"tickSec":0.5,"dur":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>chainSpin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連環迴旋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬的斬擊次數 +2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cleave</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveSlashAdd":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>galeBladeDance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋風劍舞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬命中時有 25% 機率產生 1 道風刃，造成 100% 風系傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveWindBlade":{"chance":25,"powerPct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyrendSlash</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂空飛斬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveFlyM":60}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploitWeakness</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘虛之斬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬對暈眩中的敵人造成額外的 50% 傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleaveStunnedDmgPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gatheringVortex</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚敵旋渦</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬會將 36 米內的 2 個敵人拉近至身邊 10 米範圍內。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"cleavePull":{"m":36,"toM":10,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬命中時有 25% 機率在目標處形成 1 道真空斬，對周圍 6 米內的敵人造成 100% 風系傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeVacuum":{"chance":25,"pct":100,"m":6}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬有 20% 機率可立即殺死生命值 10% 以下的非 BOSS 敵人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeExecute":{"chance":20,"hpPct":10}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾風斬每次命中時，疾風斬的冷卻時間 -0.05 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"galeCdrSec":0.05}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>血刃斬的中毒每感染 1 個敵人就使自身生命值 -0.5%，但造成的中毒與流血傷害提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"bloodVenomRite":{"hpPct":0.5,"pct":50}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>血刃斬造成流血的敵人死亡後留下一灘血霧，血霧內的敵人每次受傷都回復你 0.1% 生命值，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"bloodMistField":{"m":6,"healPct":0.1,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐵血之舞造成的自身生命損失 -25%，且造成的傷害 +25%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"danceIronAmp":{"pct":25,"reducePct":25}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴風之舞持續期間你的死亡延後 8 秒才生效，且這 8 秒內你的傷害提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"danceDeathDefer":{"sec":8,"pct":50}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊 200 次後獲得無敵狀態，持續 3 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterOath":{"count":200,"sec":3}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊 100 次後獲得怒火狀態，造成的傷害提高 30%，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterWrath":{"count":100,"pct":30,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次反擊有 5% 機率造成完美反擊，該次反擊傷害提高 500%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterPerfect":{"chance":5,"pct":500}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次反擊損失自身 0.25% 生命值，但反擊傷害提高 100%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterBloodPay":{"hpPct":0.25,"pct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>反擊有 20% 機率附加 1 顆火球射向目標，造成 100% 普攻傷害的火焰傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"counterFireball":{"chance":20,"powerPct":100}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【血飲術】造成的自身生命損失降低 25%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rageSelfCut":{"reducePct":25}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 0.5 連擊數使【狂血盛宴】的傷害加成再提高 10%（＝每 1 連擊數 +20%）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rageZealotPct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次發射火球數量 +1 個，且累計每發射 5 個火球會再額外發射 1 個火球。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"fireballCountAdd":{"count":1,"every":5,"extra":1}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>火龍捲移動速度 +50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firepillarSpeedPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +10%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firepillarResonancePct":10}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 1 秒，你的 1 團火狩會飛出攻擊半徑 36 米內的任意敵人，對目標 10 米內的所有敵人造成 300% 火焰傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firehuntLaunch":{"gap":1,"m":36,"aoeM":10,"pct":300}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在火狩的持續時間內，每 1 秒你的火焰傷害提高 2%，最多 20 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"firehuntFireAmp":{"gap":1,"pct":2,"maxStacks":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩甲護盾效果 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【岩甲尖刺】的效果提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rockSpikePct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>當你的生命護盾降至 0 時獲得無敵 3 秒；此效果每 60 秒只能觸發 1 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rockHeartInvuln":{"sec":3,"cd":60}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在泥沼術範圍中的敵人造成的傷害 -20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireWeaken":{"reducePct":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在泥沼術範圍內所有受到控場的敵人，受到的傷害 +20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireCorruptPct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>熔岩沼的火焰傷害 +50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"mireLavaPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地守護會使溢出法力的 50% 轉為你的生命護盾。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地守護會使你額外獲得【魔力再生】法力回復加成的 20% 作為吸魔效果加成。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"egManaDrainFromRegen":{"pct":20}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每殺死 1 個敵人，【天地共生】的復活冷卻時間 -0.2 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"egKillCdr":{"sec":0.2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖閃電有 35% 機率再連鎖 2 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainLinkProc":{"chance":35,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>連鎖閃電有 50% 機率額外發射 2 道連鎖閃電。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainBoltProc":{"chance":50,"count":2}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一個敵人受到 10 次連鎖閃電的彈射後產生爆炸，對周圍 10 米內的敵人造成 400% 雷電傷害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chainOverload":{"hits":10,"m":10,"pct":400}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>落雷術擊中時有 25% 機率在地上留下一個雷池，每 0.5 秒造成該道落雷 20% 的雷電傷害，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderPool":{"chance":25,"pct":20,"m":6,"gap":0.5,"sec":4}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷球的體積增大 20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbScalePct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>場上每擁有 1 個雷球，你的雷電傷害 +2%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbFieldAmpPct":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【伴生雷球】的持續時間增加 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"thunderorbCompanionSecPct":50}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowDamagePct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭造成的寒霜狀態傷害與持續時間 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowFrostPct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭擊中暈眩或凍結的敵人造成的傷害 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"icearrowControlPct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星的攻擊範圍 +20%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"frostnovaScalePct":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴風雪對帶有寒霜狀態的敵人，每層寒霜傷害 +5%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"frostnovaBlizzardLayer":{"pct":5}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>風刃每擊中敵人 1 次則傷害額外 +2%，最多疊加 20 層（最高 +40%）。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"windbladeRamp":{"pct":2,"max":40}}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>【暴風神體】的持續時間 +30%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stormGodSecPct":30}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>出現部位_x000D_
+空白＝不限（全部部位）_x000D_
+weapon＝主／副武器；helmet＝頭盔_x000D_
+shoulder＝肩甲；chest＝胸甲；belt＝腰帶_x000D_
+gloves＝護手；wrist＝手腕；legs＝護腿_x000D_
+boots＝靴子；ring＝戒指 I／II；amulet＝項鍊_x000D_
+all_lock＝全鎖定（不會出現在任何裝備部位上，也不會出現在屬性面板）_x000D_
 多部位用 ; 分隔，例如 ring;amulet＝戒指與項鍊</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>吸血</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FALSE</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸魔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次對敵人造成傷害時，額外回復 {v} 點生命與法力</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>helmet;belt;ring;amulet</t>
-  </si>
-  <si>
-    <t>chest;wrist;legs;ring;amulet</t>
-  </si>
-  <si>
-    <t>最低稀有度</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>體質</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knifeChain</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>連鎖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每把飛刀有 25% 機率再彈射 2 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knife</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"knifeBounceProc":{"chance":25,"count":2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knifeSplitter</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>分裂者</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"knifeSplit":{"count":2,"pct":50,"bounces":2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knifeExecutioner</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>處刑者</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>飛刀會優先在生命值最高的目標間彈射，且對其造成的傷害 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"knifeExecutor":{"pct":30}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knifeShadowblade</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>影刃</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>射出的飛刀數量 +2 把。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>phys</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"knifeCountAdd":2}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>knifeWaltzblade</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>輪舞刃</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>射出的第 1 把飛刀不再彈射，改為圍繞在你周圍 10 米處旋轉，對路徑上的所有敵人造成傷害，持續 5 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"knifeOrbit":{"m":10,"sec":5}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>piercingFocus</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>凝鋒穿刺</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>突刺的長度 +30%、寬度 -15%，且造成的傷害 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>thrust</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>dagger1h</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thrustLenPct":30,"thrustWidthPct":-15,"skillDamagePct":30}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>thousandWounds</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>千瘡百孔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次突刺命中使敵人受到的突刺傷害 +4%，持續 5 秒，最多疊加 10 層。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thrustVuln":{"pct":4,"dur":5,"maxStacks":10}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>sunpiercerLance</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>貫日之刺</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>突刺有 25% 機率使敵人重傷，使其受到的傷害 +20%，持續 5 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thrustWound":{"chance":25,"pct":20,"dur":5}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>thunderStab</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迅雷穿刺</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次突刺擊中敵人時有 15% 機率附加 1 道落雷。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>lightning</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thrustThunder":{"chance":15,"powerPct":200,"label":"迅雷穿刺"}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>heartrendBleed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>穿心裂血</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>突刺會附加流血，每 0.5 秒造成 50% 物理傷害，持續 5 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thrustDot":{"tickPowerPct":50,"tickSec":0.5,"dur":5}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>chainSpin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>連環迴旋</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迴旋斬的斬擊次數 +2 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>cleave</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>sword1h</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"cleaveSlashAdd":2}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>galeBladeDance</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋風劍舞</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迴旋斬命中時有 25% 機率產生 1 道風刃，造成 100% 風系傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"cleaveWindBlade":{"chance":25,"powerPct":100}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>skyrendSlash</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂空飛斬</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"cleaveFlyM":60}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>exploitWeakness</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>乘虛之斬</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迴旋斬對暈眩中的敵人造成額外的 50% 傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"cleaveStunnedDmgPct":50}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>gatheringVortex</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚敵旋渦</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>迴旋斬會將 36 米內的 2 個敵人拉近至身邊 10 米範圍內。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"cleavePull":{"m":36,"toM":10,"count":2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾風斬命中時有 25% 機率在目標處形成 1 道真空斬，對周圍 6 米內的敵人造成 100% 風系傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"galeVacuum":{"chance":25,"pct":100,"m":6}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾風斬有 20% 機率可立即殺死生命值 10% 以下的非 BOSS 敵人。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"galeExecute":{"chance":20,"hpPct":10}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾風斬每次命中時，疾風斬的冷卻時間 -0.05 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"galeCdrSec":0.05}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>血刃斬的中毒每感染 1 個敵人就使自身生命值 -0.5%，但造成的中毒與流血傷害提高 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"bloodVenomRite":{"hpPct":0.5,"pct":50}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>血刃斬造成流血的敵人死亡後留下一灘血霧，血霧內的敵人每次受傷都回復你 0.1% 生命值，持續 4 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"bloodMistField":{"m":6,"healPct":0.1,"sec":4}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>鐵血之舞造成的自身生命損失 -25%，且造成的傷害 +25%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"danceIronAmp":{"pct":25,"reducePct":25}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴風之舞持續期間你的死亡延後 8 秒才生效，且這 8 秒內你的傷害提高 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"danceDeathDefer":{"sec":8,"pct":50}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>反擊 200 次後獲得無敵狀態，持續 3 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"counterOath":{"count":200,"sec":3}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>反擊 100 次後獲得怒火狀態，造成的傷害提高 30%，持續 4 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"counterWrath":{"count":100,"pct":30,"sec":4}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次反擊有 5% 機率造成完美反擊，該次反擊傷害提高 500%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"counterPerfect":{"chance":5,"pct":500}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次反擊損失自身 0.25% 生命值，但反擊傷害提高 100%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"counterBloodPay":{"hpPct":0.25,"pct":100}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>反擊有 20% 機率附加 1 顆火球射向目標，造成 100% 普攻傷害的火焰傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>fire</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"counterFireball":{"chance":20,"powerPct":100}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【血飲術】造成的自身生命損失降低 25%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rageSelfCut":{"reducePct":25}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每 0.5 連擊數使【狂血盛宴】的傷害加成再提高 10%（＝每 1 連擊數 +20%）。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rageZealotPct":20}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次發射火球數量 +1 個，且累計每發射 5 個火球會再額外發射 1 個火球。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"fireballCountAdd":{"count":1,"every":5,"extra":1}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>火龍捲移動速度 +50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"firepillarSpeedPct":50}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +10%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"firepillarResonancePct":10}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每 1 秒，你的 1 團火狩會飛出攻擊半徑 36 米內的任意敵人，對目標 10 米內的所有敵人造成 300% 火焰傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"firehuntLaunch":{"gap":1,"m":36,"aoeM":10,"pct":300}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在火狩的持續時間內，每 1 秒你的火焰傷害提高 2%，最多 20 層（與火焰增幅各自計算層數，火狩全部消失後結束）。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"firehuntFireAmp":{"gap":1,"pct":2,"maxStacks":20}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>岩甲護盾效果 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【岩甲尖刺】的效果提高 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rockSpikePct":50}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>當你的生命護盾降至 0 時獲得無敵 3 秒；此效果每 60 秒只能觸發 1 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rockHeartInvuln":{"sec":3,"cd":60}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在泥沼術範圍中的敵人造成的傷害 -20%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"mireWeaken":{"reducePct":20}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在泥沼術範圍內所有受到控場的敵人，受到的傷害 +20%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"mireCorruptPct":20}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>熔岩沼的火焰傷害 +50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"mireLavaPct":50}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地守護會使溢出法力的 50% 轉為你的生命護盾。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地守護會使你額外獲得【魔力再生】法力回復加成的 20% 作為吸魔效果加成。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"egManaDrainFromRegen":{"pct":20}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每殺死 1 個敵人，【天地共生】的復活冷卻時間 -0.2 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"egKillCdr":{"sec":0.2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>連鎖閃電有 35% 機率再連鎖 2 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"chainLinkProc":{"chance":35,"count":2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>連鎖閃電有 50% 機率額外發射 2 道連鎖閃電。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"chainBoltProc":{"chance":50,"count":2}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>同一個敵人受到 10 次連鎖閃電的彈射後產生爆炸，對周圍 10 米內的敵人造成 400% 雷電傷害。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"chainOverload":{"hits":10,"m":10,"pct":400}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>落雷術擊中時有 25% 機率在地上留下一個雷池，每 0.5 秒造成該道落雷 20% 的雷電傷害，持續 4 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thunderPool":{"chance":25,"pct":20,"m":6,"gap":0.5,"sec":4}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷球的體積增大 20%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thunderorbScalePct":20}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>場上每擁有 1 個雷球，你的雷電傷害 +2%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thunderorbFieldAmpPct":2}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【伴生雷球】的持續時間增加 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"thunderorbCompanionSecPct":50}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰箭傷害 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"icearrowDamagePct":30}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰箭造成的寒霜狀態傷害與持續時間 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"icearrowFrostPct":30}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰箭擊中暈眩或凍結的敵人造成的傷害 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"icearrowControlPct":30}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星的攻擊範圍 +20%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"frostnovaScalePct":20}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴風雪對帶有寒霜狀態的敵人，每層寒霜傷害 +5%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"frostnovaBlizzardLayer":{"pct":5}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>風刃每擊中敵人 1 次則傷害額外 +2%，最多疊加 20 層（最高 +40%）。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"windbladeRamp":{"pct":2,"max":40}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【暴風神體】的持續時間 +30%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"stormGodSecPct":30}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>bloodthirst</t>
+  </si>
+  <si>
+    <t>嗜血</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>對流血的敵人造成傷害額外+{v}%</t>
+  </si>
+  <si>
+    <t>{"bleedingDamage":true}</t>
+  </si>
+  <si>
+    <t>chainReaction</t>
+  </si>
+  <si>
+    <t>連鎖反應</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>敵人每擁有1種異常狀態則受到傷害+{v}%，最多5種</t>
+  </si>
+  <si>
+    <t>{"debuffDamage":{"maxStacks":5}}</t>
+  </si>
+  <si>
+    <t>elation</t>
+  </si>
+  <si>
+    <t>激昂</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>在敵人疊加異常狀態效果時，最高疊加層數+{v}層</t>
+  </si>
+  <si>
+    <t>{"debuffStacks":true}</t>
+  </si>
+  <si>
+    <t>experienceTome</t>
+  </si>
+  <si>
+    <t>經驗寶典</t>
+  </si>
+  <si>
+    <t>獲得升級經驗值+{v}%</t>
+  </si>
+  <si>
+    <t>{"xpBonus":true}</t>
+  </si>
+  <si>
+    <t>goldenTouch</t>
+  </si>
+  <si>
+    <t>點金手</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>獲得金幣+{v}%</t>
+  </si>
+  <si>
+    <t>{"goldBonus":true}</t>
+  </si>
+  <si>
+    <t>fortify</t>
+  </si>
+  <si>
+    <t>強固</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>當你沒有護盾時，獲得{v}%額外傷害減免</t>
+  </si>
+  <si>
+    <t>{"noShieldReduction":true}</t>
+  </si>
+  <si>
+    <t>softenBlow</t>
+  </si>
+  <si>
+    <t>以柔剋剛</t>
+  </si>
+  <si>
+    <t>當你一次性受到超過生命上限的{v}%的傷害時，該次傷害會轉為接下來5秒內每秒-{tick}%生命傷害</t>
+  </si>
+  <si>
+    <t>{"stagger":{"sec":5,"tickSec":1}}</t>
+  </si>
+  <si>
+    <t>shieldWall</t>
+  </si>
+  <si>
+    <t>盾牆</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>格擋減傷率上限提升至{v}%</t>
+  </si>
+  <si>
+    <t>{"blockCap":true}</t>
+  </si>
+  <si>
+    <t>manaReflux</t>
+  </si>
+  <si>
+    <t>返哺</t>
+  </si>
+  <si>
+    <t>每次施放技能有25%機率回復該技能消耗的{v}%法力值，返還的法力將在5秒內緩慢回復</t>
+  </si>
+  <si>
+    <t>{"manaRefund":{"chance":25,"sec":5}}</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q227"/>
+  <dimension ref="A1:Q236"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.5" customWidth="1"/>
@@ -3684,10 +3769,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>665</v>
+        <v>810</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -4067,7 +4152,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -4544,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4584,7 +4669,7 @@
         <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -4593,7 +4678,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4605,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4616,7 +4701,7 @@
         <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4625,7 +4710,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4637,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6276,25 +6361,22 @@
         <v>192</v>
       </c>
       <c r="B88" t="s">
+        <v>215</v>
+      </c>
+      <c r="C88" t="s">
         <v>216</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="M88" t="s">
         <v>217</v>
       </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="M88" t="s">
+      <c r="Q88" t="s">
         <v>218</v>
-      </c>
-      <c r="P88" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -6302,28 +6384,25 @@
         <v>192</v>
       </c>
       <c r="B89" t="s">
+        <v>219</v>
+      </c>
+      <c r="C89" t="s">
+        <v>220</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
         <v>221</v>
-      </c>
-      <c r="C89" t="s">
-        <v>222</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="M89" t="s">
-        <v>223</v>
       </c>
       <c r="N89" t="s">
         <v>214</v>
       </c>
-      <c r="P89" t="s">
-        <v>224</v>
-      </c>
       <c r="Q89" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -6331,10 +6410,10 @@
         <v>192</v>
       </c>
       <c r="B90" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C90" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -6343,16 +6422,13 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N90" t="s">
         <v>214</v>
       </c>
-      <c r="P90" t="s">
-        <v>224</v>
-      </c>
       <c r="Q90" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -6360,25 +6436,22 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
+        <v>227</v>
+      </c>
+      <c r="C91" t="s">
+        <v>228</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="M91" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q91" t="s">
         <v>230</v>
-      </c>
-      <c r="C91" t="s">
-        <v>231</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>0</v>
-      </c>
-      <c r="M91" t="s">
-        <v>232</v>
-      </c>
-      <c r="P91" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -6386,25 +6459,22 @@
         <v>192</v>
       </c>
       <c r="B92" t="s">
+        <v>231</v>
+      </c>
+      <c r="C92" t="s">
+        <v>232</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="M92" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q92" t="s">
         <v>234</v>
-      </c>
-      <c r="C92" t="s">
-        <v>235</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="K92">
-        <v>0</v>
-      </c>
-      <c r="M92" t="s">
-        <v>236</v>
-      </c>
-      <c r="P92" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -6412,10 +6482,10 @@
         <v>192</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C93" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -6424,13 +6494,10 @@
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>241</v>
-      </c>
-      <c r="P93" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q93" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -6438,10 +6505,10 @@
         <v>192</v>
       </c>
       <c r="B94" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C94" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -6450,16 +6517,13 @@
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="N94" t="s">
-        <v>249</v>
-      </c>
-      <c r="P94" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Q94" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -6467,10 +6531,10 @@
         <v>192</v>
       </c>
       <c r="B95" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -6479,16 +6543,13 @@
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="N95" t="s">
-        <v>258</v>
-      </c>
-      <c r="P95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q95" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -6496,10 +6557,10 @@
         <v>192</v>
       </c>
       <c r="B96" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -6508,16 +6569,13 @@
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="N96" t="s">
-        <v>258</v>
-      </c>
-      <c r="P96" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="Q96" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -6525,10 +6583,10 @@
         <v>192</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -6537,16 +6595,13 @@
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="N97" t="s">
-        <v>268</v>
-      </c>
-      <c r="P97" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="Q97" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -6554,10 +6609,10 @@
         <v>192</v>
       </c>
       <c r="B98" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -6566,16 +6621,13 @@
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="N98" t="s">
-        <v>268</v>
-      </c>
-      <c r="P98" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="Q98" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -6583,10 +6635,10 @@
         <v>192</v>
       </c>
       <c r="B99" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C99" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -6595,16 +6647,13 @@
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="N99" t="s">
-        <v>278</v>
-      </c>
-      <c r="P99" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="Q99" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -6612,10 +6661,10 @@
         <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C100" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6624,13 +6673,10 @@
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>282</v>
-      </c>
-      <c r="P100" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="Q100" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -6638,10 +6684,10 @@
         <v>192</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6650,19 +6696,16 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="N101" t="s">
         <v>214</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="P101" t="s">
-        <v>224</v>
+        <v>665</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -6670,10 +6713,10 @@
         <v>192</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6682,19 +6725,16 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="N102" t="s">
         <v>214</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="P102" t="s">
-        <v>224</v>
+        <v>665</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -6702,10 +6742,10 @@
         <v>192</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6714,19 +6754,16 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="N103" t="s">
         <v>214</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="P103" t="s">
-        <v>224</v>
+        <v>665</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -6734,10 +6771,10 @@
         <v>192</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6746,19 +6783,16 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="P104" t="s">
-        <v>224</v>
+        <v>665</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -6766,10 +6800,10 @@
         <v>192</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6778,19 +6812,16 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="N105" t="s">
         <v>214</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="P105" t="s">
-        <v>224</v>
+        <v>665</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -6798,10 +6829,10 @@
         <v>192</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6810,19 +6841,17 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="N106" t="s">
         <v>214</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="P106" s="2" t="s">
-        <v>701</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="P106" s="2"/>
       <c r="Q106" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -6830,10 +6859,10 @@
         <v>192</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6842,19 +6871,17 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="N107" t="s">
         <v>214</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="P107" s="2" t="s">
-        <v>701</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="P107" s="2"/>
       <c r="Q107" s="2" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -6862,10 +6889,10 @@
         <v>192</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6874,19 +6901,17 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="N108" t="s">
         <v>214</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>701</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="P108" s="2"/>
       <c r="Q108" s="2" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -6894,10 +6919,10 @@
         <v>192</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6906,19 +6931,17 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="P109" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="P109" s="2"/>
+      <c r="Q109" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="Q109" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -6926,10 +6949,10 @@
         <v>192</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6938,19 +6961,17 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="N110" t="s">
         <v>214</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>701</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="P110" s="2"/>
       <c r="Q110" s="2" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -6958,10 +6979,10 @@
         <v>192</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6970,19 +6991,17 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="N111" t="s">
         <v>214</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="P111" s="2" t="s">
-        <v>724</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="P111" s="2"/>
       <c r="Q111" s="2" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -6990,10 +7009,10 @@
         <v>192</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -7002,19 +7021,17 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="N112" t="s">
         <v>214</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="P112" s="2" t="s">
-        <v>724</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="P112" s="2"/>
       <c r="Q112" s="2" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -7022,10 +7039,10 @@
         <v>192</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -7034,19 +7051,17 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="N113" t="s">
         <v>214</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="P113" s="2" t="s">
-        <v>724</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="P113" s="2"/>
       <c r="Q113" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -7054,10 +7069,10 @@
         <v>192</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -7066,19 +7081,17 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="N114" t="s">
         <v>214</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="P114" s="2" t="s">
-        <v>724</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="P114" s="2"/>
       <c r="Q114" s="2" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -7086,10 +7099,10 @@
         <v>192</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -7098,19 +7111,17 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="N115" t="s">
         <v>214</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="P115" s="2" t="s">
-        <v>724</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="P115" s="2"/>
       <c r="Q115" s="2" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -7118,10 +7129,10 @@
         <v>192</v>
       </c>
       <c r="B116" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C116" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -7130,19 +7141,16 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="N116" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O116" t="s">
-        <v>287</v>
-      </c>
-      <c r="P116" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -7150,10 +7158,10 @@
         <v>192</v>
       </c>
       <c r="B117" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C117" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -7162,19 +7170,16 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="N117" t="s">
         <v>214</v>
       </c>
       <c r="O117" t="s">
-        <v>287</v>
-      </c>
-      <c r="P117" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -7182,10 +7187,10 @@
         <v>192</v>
       </c>
       <c r="B118" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C118" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -7194,19 +7199,16 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="N118" t="s">
         <v>214</v>
       </c>
       <c r="O118" t="s">
-        <v>287</v>
-      </c>
-      <c r="P118" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="Q118" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -7214,10 +7216,10 @@
         <v>192</v>
       </c>
       <c r="B119" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C119" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -7226,19 +7228,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N119" t="s">
+        <v>275</v>
+      </c>
+      <c r="O119" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q119" t="s">
         <v>286</v>
-      </c>
-      <c r="O119" t="s">
-        <v>287</v>
-      </c>
-      <c r="P119" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -7246,10 +7245,10 @@
         <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C120" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -7258,19 +7257,16 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="N120" t="s">
         <v>214</v>
       </c>
       <c r="O120" t="s">
-        <v>287</v>
-      </c>
-      <c r="P120" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>747</v>
+        <v>732</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -7278,10 +7274,10 @@
         <v>192</v>
       </c>
       <c r="B121" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C121" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -7290,19 +7286,16 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="N121" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="O121" t="s">
-        <v>303</v>
-      </c>
-      <c r="P121" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q121" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -7310,10 +7303,10 @@
         <v>192</v>
       </c>
       <c r="B122" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C122" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -7322,19 +7315,16 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
       <c r="N122" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="O122" t="s">
-        <v>303</v>
-      </c>
-      <c r="P122" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -7342,10 +7332,10 @@
         <v>192</v>
       </c>
       <c r="B123" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C123" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -7354,19 +7344,16 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="N123" t="s">
         <v>214</v>
       </c>
       <c r="O123" t="s">
-        <v>303</v>
-      </c>
-      <c r="P123" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -7374,10 +7361,10 @@
         <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C124" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -7386,19 +7373,16 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="N124" t="s">
         <v>214</v>
       </c>
       <c r="O124" t="s">
-        <v>303</v>
-      </c>
-      <c r="P124" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q124" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -7406,10 +7390,10 @@
         <v>192</v>
       </c>
       <c r="B125" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -7418,19 +7402,16 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="N125" t="s">
         <v>214</v>
       </c>
       <c r="O125" t="s">
-        <v>303</v>
-      </c>
-      <c r="P125" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Q125" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -7438,10 +7419,10 @@
         <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C126" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -7450,19 +7431,16 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="N126" t="s">
         <v>214</v>
       </c>
       <c r="O126" t="s">
-        <v>321</v>
-      </c>
-      <c r="P126" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="Q126" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -7470,10 +7448,10 @@
         <v>192</v>
       </c>
       <c r="B127" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C127" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -7482,19 +7460,16 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="N127" t="s">
         <v>214</v>
       </c>
       <c r="O127" t="s">
-        <v>321</v>
-      </c>
-      <c r="P127" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -7502,10 +7477,10 @@
         <v>192</v>
       </c>
       <c r="B128" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C128" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -7514,19 +7489,16 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="N128" t="s">
         <v>214</v>
       </c>
       <c r="O128" t="s">
-        <v>321</v>
-      </c>
-      <c r="P128" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -7534,10 +7506,10 @@
         <v>192</v>
       </c>
       <c r="B129" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C129" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -7546,19 +7518,16 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="N129" t="s">
         <v>214</v>
       </c>
       <c r="O129" t="s">
-        <v>321</v>
-      </c>
-      <c r="P129" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="Q129" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -7566,10 +7535,10 @@
         <v>192</v>
       </c>
       <c r="B130" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C130" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -7578,19 +7547,16 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="N130" t="s">
         <v>214</v>
       </c>
       <c r="O130" t="s">
-        <v>321</v>
-      </c>
-      <c r="P130" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="Q130" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -7598,10 +7564,10 @@
         <v>192</v>
       </c>
       <c r="B131" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C131" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -7610,19 +7576,16 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="N131" t="s">
         <v>214</v>
       </c>
       <c r="O131" t="s">
-        <v>337</v>
-      </c>
-      <c r="P131" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="Q131" s="2" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -7630,10 +7593,10 @@
         <v>192</v>
       </c>
       <c r="B132" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C132" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -7642,19 +7605,16 @@
         <v>0</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="N132" t="s">
         <v>214</v>
       </c>
       <c r="O132" t="s">
-        <v>337</v>
-      </c>
-      <c r="P132" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="Q132" s="2" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -7662,10 +7622,10 @@
         <v>192</v>
       </c>
       <c r="B133" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C133" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -7674,19 +7634,16 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>760</v>
+        <v>745</v>
       </c>
       <c r="N133" t="s">
         <v>214</v>
       </c>
       <c r="O133" t="s">
-        <v>337</v>
-      </c>
-      <c r="P133" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="Q133" s="2" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -7694,10 +7651,10 @@
         <v>192</v>
       </c>
       <c r="B134" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C134" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -7706,19 +7663,16 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="N134" t="s">
         <v>214</v>
       </c>
       <c r="O134" t="s">
-        <v>337</v>
-      </c>
-      <c r="P134" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -7726,10 +7680,10 @@
         <v>192</v>
       </c>
       <c r="B135" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C135" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -7738,19 +7692,16 @@
         <v>0</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>764</v>
+        <v>749</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="O135" t="s">
-        <v>337</v>
-      </c>
-      <c r="P135" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -7758,10 +7709,10 @@
         <v>192</v>
       </c>
       <c r="B136" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C136" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -7770,19 +7721,16 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="N136" t="s">
         <v>214</v>
       </c>
       <c r="O136" t="s">
-        <v>349</v>
-      </c>
-      <c r="P136" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="Q136" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -7790,10 +7738,10 @@
         <v>192</v>
       </c>
       <c r="B137" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C137" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -7802,19 +7750,16 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="N137" t="s">
         <v>214</v>
       </c>
       <c r="O137" t="s">
-        <v>349</v>
-      </c>
-      <c r="P137" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="Q137" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -7822,10 +7767,10 @@
         <v>192</v>
       </c>
       <c r="B138" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C138" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -7834,19 +7779,16 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="N138" t="s">
         <v>214</v>
       </c>
       <c r="O138" t="s">
-        <v>349</v>
-      </c>
-      <c r="P138" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="Q138" s="2" t="s">
-        <v>768</v>
+        <v>753</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -7854,10 +7796,10 @@
         <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C139" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -7866,19 +7808,16 @@
         <v>0</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="N139" t="s">
         <v>214</v>
       </c>
       <c r="O139" t="s">
-        <v>349</v>
-      </c>
-      <c r="P139" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="Q139" s="2" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -7886,10 +7825,10 @@
         <v>192</v>
       </c>
       <c r="B140" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C140" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -7898,19 +7837,16 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="N140" t="s">
         <v>214</v>
       </c>
       <c r="O140" t="s">
-        <v>349</v>
-      </c>
-      <c r="P140" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="Q140" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -7918,10 +7854,10 @@
         <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C141" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -7930,19 +7866,16 @@
         <v>0</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="N141" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O141" t="s">
-        <v>365</v>
-      </c>
-      <c r="P141" t="s">
-        <v>250</v>
+        <v>353</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -7950,10 +7883,10 @@
         <v>192</v>
       </c>
       <c r="B142" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C142" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -7962,19 +7895,16 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="N142" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O142" t="s">
-        <v>365</v>
-      </c>
-      <c r="P142" t="s">
-        <v>250</v>
+        <v>353</v>
       </c>
       <c r="Q142" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -7982,10 +7912,10 @@
         <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C143" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -7994,19 +7924,16 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="N143" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O143" t="s">
-        <v>365</v>
-      </c>
-      <c r="P143" t="s">
-        <v>250</v>
+        <v>353</v>
       </c>
       <c r="Q143" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -8014,10 +7941,10 @@
         <v>192</v>
       </c>
       <c r="B144" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C144" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -8026,19 +7953,16 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="N144" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O144" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q144" t="s">
         <v>365</v>
-      </c>
-      <c r="P144" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q144" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -8046,10 +7970,10 @@
         <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C145" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -8058,19 +7982,16 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="N145" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O145" t="s">
-        <v>365</v>
-      </c>
-      <c r="P145" t="s">
-        <v>250</v>
+        <v>353</v>
       </c>
       <c r="Q145" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -8078,10 +7999,10 @@
         <v>192</v>
       </c>
       <c r="B146" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C146" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -8090,19 +8011,16 @@
         <v>0</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="N146" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O146" t="s">
-        <v>384</v>
-      </c>
-      <c r="P146" t="s">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -8110,10 +8028,10 @@
         <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C147" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -8122,19 +8040,16 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="N147" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O147" t="s">
-        <v>384</v>
-      </c>
-      <c r="P147" t="s">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="Q147" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -8142,10 +8057,10 @@
         <v>192</v>
       </c>
       <c r="B148" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C148" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -8154,19 +8069,16 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="N148" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O148" t="s">
-        <v>384</v>
-      </c>
-      <c r="P148" t="s">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="Q148" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -8174,10 +8086,10 @@
         <v>192</v>
       </c>
       <c r="B149" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C149" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -8186,19 +8098,16 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="N149" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O149" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q149" t="s">
         <v>384</v>
-      </c>
-      <c r="P149" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -8206,10 +8115,10 @@
         <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C150" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -8218,19 +8127,16 @@
         <v>0</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="N150" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O150" t="s">
-        <v>384</v>
-      </c>
-      <c r="P150" t="s">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="Q150" s="2" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -8238,10 +8144,10 @@
         <v>192</v>
       </c>
       <c r="B151" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C151" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -8250,19 +8156,16 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="N151" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O151" t="s">
-        <v>402</v>
-      </c>
-      <c r="P151" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="Q151" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -8270,10 +8173,10 @@
         <v>192</v>
       </c>
       <c r="B152" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C152" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -8282,19 +8185,16 @@
         <v>0</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="N152" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O152" t="s">
-        <v>402</v>
-      </c>
-      <c r="P152" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -8302,10 +8202,10 @@
         <v>192</v>
       </c>
       <c r="B153" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C153" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -8314,19 +8214,16 @@
         <v>0</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="N153" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O153" t="s">
-        <v>402</v>
-      </c>
-      <c r="P153" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -8334,10 +8231,10 @@
         <v>192</v>
       </c>
       <c r="B154" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C154" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -8346,19 +8243,16 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="N154" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O154" t="s">
-        <v>402</v>
-      </c>
-      <c r="P154" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="Q154" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -8366,10 +8260,10 @@
         <v>192</v>
       </c>
       <c r="B155" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C155" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -8378,19 +8272,16 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="N155" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O155" t="s">
-        <v>402</v>
-      </c>
-      <c r="P155" t="s">
-        <v>248</v>
+        <v>390</v>
       </c>
       <c r="Q155" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -8398,10 +8289,10 @@
         <v>192</v>
       </c>
       <c r="B156" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C156" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -8410,19 +8301,16 @@
         <v>0</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="N156" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O156" t="s">
-        <v>419</v>
-      </c>
-      <c r="P156" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="Q156" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -8430,10 +8318,10 @@
         <v>192</v>
       </c>
       <c r="B157" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C157" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -8442,19 +8330,16 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="N157" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O157" t="s">
-        <v>419</v>
-      </c>
-      <c r="P157" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="Q157" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -8462,10 +8347,10 @@
         <v>192</v>
       </c>
       <c r="B158" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C158" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -8474,19 +8359,16 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="N158" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O158" t="s">
-        <v>419</v>
-      </c>
-      <c r="P158" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="Q158" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -8494,10 +8376,10 @@
         <v>192</v>
       </c>
       <c r="B159" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C159" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -8506,19 +8388,16 @@
         <v>0</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="N159" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O159" t="s">
-        <v>419</v>
-      </c>
-      <c r="P159" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="Q159" s="2" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -8526,10 +8405,10 @@
         <v>192</v>
       </c>
       <c r="B160" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C160" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -8538,19 +8417,16 @@
         <v>0</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="N160" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O160" t="s">
-        <v>419</v>
-      </c>
-      <c r="P160" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="Q160" s="2" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -8558,10 +8434,10 @@
         <v>192</v>
       </c>
       <c r="B161" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C161" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -8570,19 +8446,16 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="N161" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O161" t="s">
-        <v>436</v>
-      </c>
-      <c r="P161" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="Q161" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -8590,10 +8463,10 @@
         <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C162" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -8602,19 +8475,16 @@
         <v>0</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="N162" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O162" t="s">
-        <v>436</v>
-      </c>
-      <c r="P162" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="Q162" s="2" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -8622,10 +8492,10 @@
         <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C163" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -8634,19 +8504,16 @@
         <v>0</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="N163" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O163" t="s">
-        <v>436</v>
-      </c>
-      <c r="P163" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="Q163" s="2" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -8654,10 +8521,10 @@
         <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -8666,19 +8533,16 @@
         <v>0</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="N164" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O164" t="s">
-        <v>436</v>
-      </c>
-      <c r="P164" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -8686,10 +8550,10 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C165" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -8698,19 +8562,16 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="N165" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O165" t="s">
-        <v>436</v>
-      </c>
-      <c r="P165" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="Q165" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -8718,10 +8579,10 @@
         <v>192</v>
       </c>
       <c r="B166" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C166" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -8730,19 +8591,16 @@
         <v>0</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="N166" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O166" t="s">
-        <v>450</v>
-      </c>
-      <c r="P166" t="s">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="Q166" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -8750,10 +8608,10 @@
         <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C167" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -8762,19 +8620,16 @@
         <v>0</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="N167" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O167" t="s">
-        <v>450</v>
-      </c>
-      <c r="P167" t="s">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -8782,10 +8637,10 @@
         <v>192</v>
       </c>
       <c r="B168" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C168" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -8794,19 +8649,16 @@
         <v>0</v>
       </c>
       <c r="M168" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="N168" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O168" t="s">
-        <v>450</v>
-      </c>
-      <c r="P168" t="s">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="Q168" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -8814,10 +8666,10 @@
         <v>192</v>
       </c>
       <c r="B169" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C169" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -8826,19 +8678,16 @@
         <v>0</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="N169" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O169" t="s">
-        <v>450</v>
-      </c>
-      <c r="P169" t="s">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -8846,10 +8695,10 @@
         <v>192</v>
       </c>
       <c r="B170" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C170" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -8858,19 +8707,16 @@
         <v>0</v>
       </c>
       <c r="M170" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="N170" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O170" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q170" t="s">
         <v>450</v>
-      </c>
-      <c r="P170" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -8878,10 +8724,10 @@
         <v>192</v>
       </c>
       <c r="B171" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C171" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -8890,19 +8736,16 @@
         <v>0</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="N171" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O171" t="s">
-        <v>465</v>
-      </c>
-      <c r="P171" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="Q171" s="2" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -8910,10 +8753,10 @@
         <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C172" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -8922,19 +8765,16 @@
         <v>0</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="N172" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O172" t="s">
-        <v>465</v>
-      </c>
-      <c r="P172" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="Q172" s="2" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -8942,10 +8782,10 @@
         <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C173" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -8954,19 +8794,16 @@
         <v>0</v>
       </c>
       <c r="M173" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N173" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O173" t="s">
-        <v>465</v>
-      </c>
-      <c r="P173" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="Q173" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -8974,10 +8811,10 @@
         <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C174" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -8986,19 +8823,16 @@
         <v>0</v>
       </c>
       <c r="M174" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="N174" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O174" t="s">
-        <v>465</v>
-      </c>
-      <c r="P174" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="Q174" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -9006,10 +8840,10 @@
         <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C175" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -9018,19 +8852,16 @@
         <v>0</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="N175" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O175" t="s">
-        <v>465</v>
-      </c>
-      <c r="P175" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="Q175" s="2" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -9038,10 +8869,10 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C176" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -9050,19 +8881,16 @@
         <v>0</v>
       </c>
       <c r="M176" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="N176" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O176" t="s">
-        <v>481</v>
-      </c>
-      <c r="P176" t="s">
-        <v>250</v>
+        <v>469</v>
       </c>
       <c r="Q176" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -9070,10 +8898,10 @@
         <v>192</v>
       </c>
       <c r="B177" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C177" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -9082,19 +8910,16 @@
         <v>0</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="N177" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O177" t="s">
-        <v>481</v>
-      </c>
-      <c r="P177" t="s">
-        <v>250</v>
+        <v>469</v>
       </c>
       <c r="Q177" s="2" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -9102,10 +8927,10 @@
         <v>192</v>
       </c>
       <c r="B178" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C178" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -9114,19 +8939,16 @@
         <v>0</v>
       </c>
       <c r="M178" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="N178" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O178" t="s">
-        <v>481</v>
-      </c>
-      <c r="P178" t="s">
-        <v>250</v>
+        <v>469</v>
       </c>
       <c r="Q178" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -9134,10 +8956,10 @@
         <v>192</v>
       </c>
       <c r="B179" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C179" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -9146,19 +8968,16 @@
         <v>0</v>
       </c>
       <c r="M179" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="N179" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O179" t="s">
-        <v>481</v>
-      </c>
-      <c r="P179" t="s">
-        <v>250</v>
+        <v>469</v>
       </c>
       <c r="Q179" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -9166,10 +8985,10 @@
         <v>192</v>
       </c>
       <c r="B180" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C180" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -9178,19 +8997,16 @@
         <v>0</v>
       </c>
       <c r="M180" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="N180" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O180" t="s">
-        <v>481</v>
-      </c>
-      <c r="P180" t="s">
-        <v>250</v>
+        <v>469</v>
       </c>
       <c r="Q180" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -9198,10 +9014,10 @@
         <v>192</v>
       </c>
       <c r="B181" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C181" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -9210,19 +9026,16 @@
         <v>0</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="N181" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O181" t="s">
-        <v>499</v>
-      </c>
-      <c r="P181" t="s">
-        <v>248</v>
+        <v>487</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -9230,10 +9043,10 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C182" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -9242,19 +9055,16 @@
         <v>0</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="N182" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O182" t="s">
-        <v>499</v>
-      </c>
-      <c r="P182" t="s">
-        <v>248</v>
+        <v>487</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -9262,10 +9072,10 @@
         <v>192</v>
       </c>
       <c r="B183" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C183" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -9274,19 +9084,16 @@
         <v>0</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="N183" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O183" t="s">
-        <v>499</v>
-      </c>
-      <c r="P183" t="s">
-        <v>248</v>
+        <v>487</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -9294,10 +9101,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C184" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -9306,19 +9113,16 @@
         <v>0</v>
       </c>
       <c r="M184" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N184" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O184" t="s">
-        <v>499</v>
-      </c>
-      <c r="P184" t="s">
-        <v>248</v>
+        <v>487</v>
       </c>
       <c r="Q184" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -9326,10 +9130,10 @@
         <v>192</v>
       </c>
       <c r="B185" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C185" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -9338,19 +9142,16 @@
         <v>0</v>
       </c>
       <c r="M185" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="N185" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="O185" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q185" t="s">
         <v>499</v>
-      </c>
-      <c r="P185" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -9358,10 +9159,10 @@
         <v>192</v>
       </c>
       <c r="B186" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C186" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -9370,19 +9171,16 @@
         <v>0</v>
       </c>
       <c r="M186" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="N186" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O186" t="s">
-        <v>515</v>
-      </c>
-      <c r="P186" t="s">
-        <v>263</v>
+        <v>503</v>
       </c>
       <c r="Q186" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -9390,10 +9188,10 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C187" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -9402,19 +9200,16 @@
         <v>0</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="N187" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O187" t="s">
-        <v>515</v>
-      </c>
-      <c r="P187" t="s">
-        <v>263</v>
+        <v>503</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -9422,10 +9217,10 @@
         <v>192</v>
       </c>
       <c r="B188" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C188" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -9434,19 +9229,16 @@
         <v>0</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="N188" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O188" t="s">
-        <v>515</v>
-      </c>
-      <c r="P188" t="s">
-        <v>263</v>
+        <v>503</v>
       </c>
       <c r="Q188" s="2" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -9454,10 +9246,10 @@
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C189" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -9466,19 +9258,16 @@
         <v>0</v>
       </c>
       <c r="M189" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="N189" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O189" t="s">
-        <v>515</v>
-      </c>
-      <c r="P189" t="s">
-        <v>263</v>
+        <v>503</v>
       </c>
       <c r="Q189" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -9486,10 +9275,10 @@
         <v>192</v>
       </c>
       <c r="B190" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C190" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -9498,19 +9287,16 @@
         <v>0</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="N190" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O190" t="s">
-        <v>515</v>
-      </c>
-      <c r="P190" t="s">
-        <v>263</v>
+        <v>503</v>
       </c>
       <c r="Q190" s="2" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -9518,10 +9304,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C191" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -9530,19 +9316,16 @@
         <v>0</v>
       </c>
       <c r="M191" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="N191" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O191" t="s">
-        <v>530</v>
-      </c>
-      <c r="P191" t="s">
-        <v>246</v>
+        <v>518</v>
       </c>
       <c r="Q191" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -9550,10 +9333,10 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="C192" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -9562,19 +9345,16 @@
         <v>0</v>
       </c>
       <c r="M192" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="N192" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O192" t="s">
-        <v>530</v>
-      </c>
-      <c r="P192" t="s">
-        <v>246</v>
+        <v>518</v>
       </c>
       <c r="Q192" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -9582,10 +9362,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C193" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -9594,19 +9374,16 @@
         <v>0</v>
       </c>
       <c r="M193" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="N193" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O193" t="s">
-        <v>530</v>
-      </c>
-      <c r="P193" t="s">
-        <v>246</v>
+        <v>518</v>
       </c>
       <c r="Q193" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -9614,10 +9391,10 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C194" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -9626,19 +9403,16 @@
         <v>0</v>
       </c>
       <c r="M194" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="N194" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O194" t="s">
-        <v>530</v>
-      </c>
-      <c r="P194" t="s">
-        <v>246</v>
+        <v>518</v>
       </c>
       <c r="Q194" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -9646,10 +9420,10 @@
         <v>192</v>
       </c>
       <c r="B195" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C195" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -9658,19 +9432,16 @@
         <v>0</v>
       </c>
       <c r="M195" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="N195" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O195" t="s">
-        <v>530</v>
-      </c>
-      <c r="P195" t="s">
-        <v>246</v>
+        <v>518</v>
       </c>
       <c r="Q195" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -9678,10 +9449,10 @@
         <v>192</v>
       </c>
       <c r="B196" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C196" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -9690,19 +9461,16 @@
         <v>0</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="N196" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O196" t="s">
-        <v>550</v>
-      </c>
-      <c r="P196" t="s">
-        <v>247</v>
+        <v>538</v>
       </c>
       <c r="Q196" s="2" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -9710,10 +9478,10 @@
         <v>192</v>
       </c>
       <c r="B197" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C197" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -9722,19 +9490,16 @@
         <v>0</v>
       </c>
       <c r="M197" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="N197" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O197" t="s">
-        <v>550</v>
-      </c>
-      <c r="P197" t="s">
-        <v>247</v>
+        <v>538</v>
       </c>
       <c r="Q197" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -9742,10 +9507,10 @@
         <v>192</v>
       </c>
       <c r="B198" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C198" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -9754,19 +9519,16 @@
         <v>0</v>
       </c>
       <c r="M198" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="N198" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O198" t="s">
-        <v>550</v>
-      </c>
-      <c r="P198" t="s">
-        <v>247</v>
+        <v>538</v>
       </c>
       <c r="Q198" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -9774,10 +9536,10 @@
         <v>192</v>
       </c>
       <c r="B199" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C199" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -9786,19 +9548,16 @@
         <v>0</v>
       </c>
       <c r="M199" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="N199" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O199" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q199" t="s">
         <v>550</v>
-      </c>
-      <c r="P199" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q199" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -9806,10 +9565,10 @@
         <v>192</v>
       </c>
       <c r="B200" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C200" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -9818,19 +9577,16 @@
         <v>0</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="N200" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O200" t="s">
-        <v>550</v>
-      </c>
-      <c r="P200" t="s">
-        <v>247</v>
+        <v>538</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -9838,10 +9594,10 @@
         <v>192</v>
       </c>
       <c r="B201" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C201" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -9850,19 +9606,16 @@
         <v>0</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="N201" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O201" t="s">
-        <v>567</v>
-      </c>
-      <c r="P201" t="s">
-        <v>250</v>
+        <v>555</v>
       </c>
       <c r="Q201" s="2" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -9870,10 +9623,10 @@
         <v>192</v>
       </c>
       <c r="B202" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C202" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -9882,19 +9635,16 @@
         <v>0</v>
       </c>
       <c r="M202" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="N202" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O202" t="s">
-        <v>567</v>
-      </c>
-      <c r="P202" t="s">
-        <v>250</v>
+        <v>555</v>
       </c>
       <c r="Q202" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -9902,10 +9652,10 @@
         <v>192</v>
       </c>
       <c r="B203" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C203" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -9914,19 +9664,16 @@
         <v>0</v>
       </c>
       <c r="M203" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="N203" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O203" t="s">
-        <v>567</v>
-      </c>
-      <c r="P203" t="s">
-        <v>250</v>
+        <v>555</v>
       </c>
       <c r="Q203" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -9934,10 +9681,10 @@
         <v>192</v>
       </c>
       <c r="B204" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C204" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -9946,19 +9693,16 @@
         <v>0</v>
       </c>
       <c r="M204" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="N204" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O204" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q204" t="s">
         <v>567</v>
-      </c>
-      <c r="P204" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -9966,10 +9710,10 @@
         <v>192</v>
       </c>
       <c r="B205" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C205" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -9978,19 +9722,16 @@
         <v>0</v>
       </c>
       <c r="M205" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="N205" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O205" t="s">
-        <v>567</v>
-      </c>
-      <c r="P205" t="s">
-        <v>250</v>
+        <v>555</v>
       </c>
       <c r="Q205" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -9998,10 +9739,10 @@
         <v>192</v>
       </c>
       <c r="B206" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C206" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -10010,19 +9751,16 @@
         <v>0</v>
       </c>
       <c r="M206" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="N206" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O206" t="s">
-        <v>587</v>
-      </c>
-      <c r="P206" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="Q206" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -10030,10 +9768,10 @@
         <v>192</v>
       </c>
       <c r="B207" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C207" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -10042,19 +9780,16 @@
         <v>0</v>
       </c>
       <c r="M207" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="N207" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O207" t="s">
-        <v>587</v>
-      </c>
-      <c r="P207" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="Q207" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -10062,10 +9797,10 @@
         <v>192</v>
       </c>
       <c r="B208" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="C208" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -10074,19 +9809,16 @@
         <v>0</v>
       </c>
       <c r="M208" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="N208" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O208" t="s">
-        <v>587</v>
-      </c>
-      <c r="P208" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="Q208" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -10094,10 +9826,10 @@
         <v>192</v>
       </c>
       <c r="B209" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="C209" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -10106,19 +9838,16 @@
         <v>0</v>
       </c>
       <c r="M209" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="N209" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O209" t="s">
-        <v>587</v>
-      </c>
-      <c r="P209" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="Q209" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -10126,10 +9855,10 @@
         <v>192</v>
       </c>
       <c r="B210" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C210" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -10138,19 +9867,16 @@
         <v>0</v>
       </c>
       <c r="M210" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="N210" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O210" t="s">
-        <v>587</v>
-      </c>
-      <c r="P210" t="s">
-        <v>219</v>
+        <v>575</v>
       </c>
       <c r="Q210" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -10158,10 +9884,10 @@
         <v>192</v>
       </c>
       <c r="B211" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C211" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -10170,19 +9896,16 @@
         <v>0</v>
       </c>
       <c r="M211" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="N211" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O211" t="s">
-        <v>608</v>
-      </c>
-      <c r="P211" t="s">
-        <v>242</v>
+        <v>596</v>
       </c>
       <c r="Q211" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -10190,10 +9913,10 @@
         <v>192</v>
       </c>
       <c r="B212" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C212" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -10202,19 +9925,16 @@
         <v>0</v>
       </c>
       <c r="M212" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="N212" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O212" t="s">
-        <v>608</v>
-      </c>
-      <c r="P212" t="s">
-        <v>242</v>
+        <v>596</v>
       </c>
       <c r="Q212" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -10222,10 +9942,10 @@
         <v>192</v>
       </c>
       <c r="B213" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="C213" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -10234,19 +9954,16 @@
         <v>0</v>
       </c>
       <c r="M213" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="N213" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O213" t="s">
-        <v>608</v>
-      </c>
-      <c r="P213" t="s">
-        <v>242</v>
+        <v>596</v>
       </c>
       <c r="Q213" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -10254,10 +9971,10 @@
         <v>192</v>
       </c>
       <c r="B214" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C214" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -10266,19 +9983,16 @@
         <v>0</v>
       </c>
       <c r="M214" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="N214" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="O214" t="s">
-        <v>608</v>
-      </c>
-      <c r="P214" t="s">
-        <v>242</v>
+        <v>596</v>
       </c>
       <c r="Q214" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -10286,10 +10000,10 @@
         <v>192</v>
       </c>
       <c r="B215" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C215" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -10298,241 +10012,445 @@
         <v>0</v>
       </c>
       <c r="M215" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="N215" t="s">
+        <v>275</v>
+      </c>
+      <c r="O215" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q215" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M216" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q216" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M217" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q217" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="N215" t="s">
-        <v>286</v>
-      </c>
-      <c r="O215" t="s">
-        <v>608</v>
-      </c>
-      <c r="P215" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q215" s="2" t="s">
+      <c r="D218" s="2" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>624</v>
-      </c>
-      <c r="B216" t="s">
-        <v>625</v>
-      </c>
-      <c r="C216" t="s">
-        <v>626</v>
-      </c>
-      <c r="D216">
-        <v>25</v>
-      </c>
-      <c r="L216" t="s">
-        <v>31</v>
-      </c>
-      <c r="M216" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>624</v>
-      </c>
-      <c r="B217" t="s">
-        <v>628</v>
-      </c>
-      <c r="C217" t="s">
-        <v>629</v>
-      </c>
-      <c r="D217">
-        <v>18</v>
-      </c>
-      <c r="L217" t="s">
-        <v>630</v>
-      </c>
-      <c r="M217" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>624</v>
-      </c>
-      <c r="B218" t="s">
-        <v>632</v>
-      </c>
-      <c r="C218" t="s">
-        <v>633</v>
-      </c>
-      <c r="D218">
-        <v>15</v>
-      </c>
-      <c r="L218" t="s">
-        <v>634</v>
-      </c>
-      <c r="M218" t="s">
-        <v>635</v>
+      <c r="K218" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M218" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="Q218" s="2" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>624</v>
-      </c>
-      <c r="B219" t="s">
-        <v>636</v>
-      </c>
-      <c r="C219" t="s">
-        <v>637</v>
-      </c>
-      <c r="D219">
-        <v>30</v>
-      </c>
-      <c r="L219" t="s">
-        <v>638</v>
-      </c>
-      <c r="M219" t="s">
-        <v>639</v>
+      <c r="A219" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M219" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q219" s="2" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>624</v>
-      </c>
-      <c r="B220" t="s">
-        <v>640</v>
-      </c>
-      <c r="C220" t="s">
-        <v>641</v>
-      </c>
-      <c r="D220">
-        <v>25</v>
-      </c>
-      <c r="L220" t="s">
-        <v>642</v>
-      </c>
-      <c r="M220" t="s">
-        <v>643</v>
+      <c r="A220" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q220" s="2" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>624</v>
-      </c>
-      <c r="B221" t="s">
-        <v>644</v>
-      </c>
-      <c r="C221" t="s">
-        <v>645</v>
-      </c>
-      <c r="D221">
-        <v>25</v>
-      </c>
-      <c r="L221" t="s">
-        <v>646</v>
-      </c>
-      <c r="M221" t="s">
-        <v>647</v>
+      <c r="A221" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q221" s="2" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>624</v>
-      </c>
-      <c r="B222" t="s">
-        <v>648</v>
-      </c>
-      <c r="C222" t="s">
-        <v>649</v>
-      </c>
-      <c r="D222">
-        <v>12</v>
-      </c>
-      <c r="M222" t="s">
-        <v>650</v>
+      <c r="A222" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M222" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="Q222" s="2" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>624</v>
-      </c>
-      <c r="B223" t="s">
-        <v>651</v>
-      </c>
-      <c r="C223" t="s">
-        <v>652</v>
-      </c>
-      <c r="D223">
-        <v>15</v>
-      </c>
-      <c r="M223" t="s">
-        <v>653</v>
+      <c r="A223" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M223" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="Q223" s="2" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>624</v>
-      </c>
-      <c r="B224" t="s">
-        <v>654</v>
-      </c>
-      <c r="C224" t="s">
-        <v>655</v>
-      </c>
-      <c r="D224">
-        <v>8</v>
-      </c>
-      <c r="M224" t="s">
-        <v>656</v>
+      <c r="A224" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="M224" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="Q224" s="2" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B225" t="s">
-        <v>657</v>
+        <v>613</v>
       </c>
       <c r="C225" t="s">
-        <v>658</v>
+        <v>614</v>
       </c>
       <c r="D225">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="L225" t="s">
+        <v>31</v>
       </c>
       <c r="M225" t="s">
-        <v>659</v>
+        <v>615</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B226" t="s">
-        <v>660</v>
+        <v>616</v>
       </c>
       <c r="C226" t="s">
-        <v>661</v>
+        <v>617</v>
       </c>
       <c r="D226">
-        <v>5</v>
-      </c>
-      <c r="M226" s="2" t="s">
-        <v>669</v>
+        <v>18</v>
+      </c>
+      <c r="L226" t="s">
+        <v>618</v>
+      </c>
+      <c r="M226" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>612</v>
+      </c>
+      <c r="B227" t="s">
+        <v>620</v>
+      </c>
+      <c r="C227" t="s">
+        <v>621</v>
+      </c>
+      <c r="D227">
+        <v>15</v>
+      </c>
+      <c r="L227" t="s">
+        <v>622</v>
+      </c>
+      <c r="M227" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>612</v>
+      </c>
+      <c r="B228" t="s">
         <v>624</v>
       </c>
-      <c r="B227" t="s">
-        <v>662</v>
-      </c>
-      <c r="C227" t="s">
-        <v>663</v>
-      </c>
-      <c r="D227">
+      <c r="C228" t="s">
+        <v>625</v>
+      </c>
+      <c r="D228">
+        <v>30</v>
+      </c>
+      <c r="L228" t="s">
+        <v>626</v>
+      </c>
+      <c r="M228" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>612</v>
+      </c>
+      <c r="B229" t="s">
+        <v>628</v>
+      </c>
+      <c r="C229" t="s">
+        <v>629</v>
+      </c>
+      <c r="D229">
+        <v>25</v>
+      </c>
+      <c r="L229" t="s">
+        <v>630</v>
+      </c>
+      <c r="M229" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>612</v>
+      </c>
+      <c r="B230" t="s">
+        <v>632</v>
+      </c>
+      <c r="C230" t="s">
+        <v>633</v>
+      </c>
+      <c r="D230">
+        <v>25</v>
+      </c>
+      <c r="L230" t="s">
+        <v>634</v>
+      </c>
+      <c r="M230" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>612</v>
+      </c>
+      <c r="B231" t="s">
+        <v>636</v>
+      </c>
+      <c r="C231" t="s">
+        <v>637</v>
+      </c>
+      <c r="D231">
+        <v>12</v>
+      </c>
+      <c r="M231" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>612</v>
+      </c>
+      <c r="B232" t="s">
+        <v>639</v>
+      </c>
+      <c r="C232" t="s">
+        <v>640</v>
+      </c>
+      <c r="D232">
+        <v>15</v>
+      </c>
+      <c r="M232" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>612</v>
+      </c>
+      <c r="B233" t="s">
+        <v>642</v>
+      </c>
+      <c r="C233" t="s">
+        <v>643</v>
+      </c>
+      <c r="D233">
+        <v>8</v>
+      </c>
+      <c r="M233" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>612</v>
+      </c>
+      <c r="B234" t="s">
+        <v>645</v>
+      </c>
+      <c r="C234" t="s">
+        <v>646</v>
+      </c>
+      <c r="D234">
+        <v>30</v>
+      </c>
+      <c r="M234" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>612</v>
+      </c>
+      <c r="B235" t="s">
+        <v>648</v>
+      </c>
+      <c r="C235" t="s">
+        <v>649</v>
+      </c>
+      <c r="D235">
+        <v>5</v>
+      </c>
+      <c r="M235" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>612</v>
+      </c>
+      <c r="B236" t="s">
+        <v>650</v>
+      </c>
+      <c r="C236" t="s">
+        <v>651</v>
+      </c>
+      <c r="D236">
         <v>35</v>
       </c>
-      <c r="M227" t="s">
-        <v>664</v>
+      <c r="M236" t="s">
+        <v>652</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABA358E-2578-416D-8065-FC02E9CDC868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE3AD24-6C46-4BA5-83B9-FD0E7CEFF196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,9 +1058,6 @@
     <t>燃血</t>
   </si>
   <si>
-    <t>【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
-  </si>
-  <si>
     <t>{"rageBurnBlood":{"pct":1,"maxStacks":50,"sec":4}}</t>
   </si>
   <si>
@@ -1082,9 +1079,6 @@
     <t>屠戮者</t>
   </si>
   <si>
-    <t>狂怒期間每殺死 1 個敵人使【嗜血反震】的效果提高 5%，最多疊 10 層，持續 4 秒。</t>
-  </si>
-  <si>
     <t>{"rageThornsStack":{"pct":5,"maxStacks":10,"sec":4}}</t>
   </si>
   <si>
@@ -1139,9 +1133,6 @@
     <t>爆裂</t>
   </si>
   <si>
-    <t>【火球爆裂】會額外產生 3 個小火球。</t>
-  </si>
-  <si>
     <t>{"fireballSplitAdd":{"count":3}}</t>
   </si>
   <si>
@@ -1280,9 +1271,6 @@
     <t>巨岩增幅</t>
   </si>
   <si>
-    <t>【岩甲增幅】可疊加的層數 +10 層。</t>
-  </si>
-  <si>
     <t>{"rockAmpStacksAdd":{"maxStacks":10}}</t>
   </si>
   <si>
@@ -1367,9 +1355,6 @@
     <t>靈魂連結</t>
   </si>
   <si>
-    <t>【生命反射之盾】可以額外對 1 個敵人產生作用。</t>
-  </si>
-  <si>
     <t>{"egReflectAdd":{"count":1}}</t>
   </si>
   <si>
@@ -1409,9 +1394,6 @@
     <t>雷散落</t>
   </si>
   <si>
-    <t>【電殛擴散】額外對 1 個敵人造成傷害，且其傷害提高 50%。</t>
-  </si>
-  <si>
     <t>{"chainSplashAdd":{"count":1},"chainSplashPct":50}</t>
   </si>
   <si>
@@ -1439,9 +1421,6 @@
     <t>三重雷</t>
   </si>
   <si>
-    <t>【雙重落雷】的攻擊次數 +1 次。</t>
-  </si>
-  <si>
     <t>thunderstrike</t>
   </si>
   <si>
@@ -1472,9 +1451,6 @@
     <t>雷之再生</t>
   </si>
   <si>
-    <t>【迅雷重生】的機率提高至 100%。</t>
-  </si>
-  <si>
     <t>{"thunderRegenTo":{"chance":100}}</t>
   </si>
   <si>
@@ -1517,9 +1493,6 @@
     <t>雷殞落</t>
   </si>
   <si>
-    <t>【雷殞天落】降下的雷球數量 +1 顆。</t>
-  </si>
-  <si>
     <t>{"thunderorbFallAdd":{"count":1}}</t>
   </si>
   <si>
@@ -1529,9 +1502,6 @@
     <t>雷殞震</t>
   </si>
   <si>
-    <t>被【雷殞天落】降下的雷球擊中的敵人會暈眩 4 秒。</t>
-  </si>
-  <si>
     <t>{"thunderorbFallStunTo":{"sec":4}}</t>
   </si>
   <si>
@@ -1601,9 +1571,6 @@
     <t>冰霜擴散</t>
   </si>
   <si>
-    <t>【寒流爆散】的擴散爆炸變成冰霜新星，且範圍增大 30%。</t>
-  </si>
-  <si>
     <t>{"waterballBurstNova":{"scalePct":30}}</t>
   </si>
   <si>
@@ -1721,9 +1688,6 @@
     <t>風之痕</t>
   </si>
   <si>
-    <t>【亂披風】會在風刃另一側額外射出 1 道小型風刃，且小型風刃傷害 +30%。</t>
-  </si>
-  <si>
     <t>{"windbladeSmallMirror":{"count":1},"windbladeSmallDmgPct":30}</t>
   </si>
   <si>
@@ -1745,9 +1709,6 @@
     <t>斷空刃</t>
   </si>
   <si>
-    <t>【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
-  </si>
-  <si>
     <t>{"windbladeVolleyTo":{"count":3},"windbladeDmgPct":30}</t>
   </si>
   <si>
@@ -1757,9 +1718,6 @@
     <t>共振</t>
   </si>
   <si>
-    <t>【真空爆震】會額外多造成 1 次傷害。</t>
-  </si>
-  <si>
     <t>vacuumslash</t>
   </si>
   <si>
@@ -1808,9 +1766,6 @@
     <t>虛空漲落</t>
   </si>
   <si>
-    <t>【虛空斬】的持續時間 +3 秒。</t>
-  </si>
-  <si>
     <t>{"vacuumVoidSec":{"sec":3}}</t>
   </si>
   <si>
@@ -1835,9 +1790,6 @@
     <t>暴風反射</t>
   </si>
   <si>
-    <t>【暴風之刃】射出風刃的機率 +10%。</t>
-  </si>
-  <si>
     <t>{"stormbladeChanceAdd":{"chance":10}}</t>
   </si>
   <si>
@@ -1847,9 +1799,6 @@
     <t>逆風切</t>
   </si>
   <si>
-    <t>【亂風切】所附加的風切狀態，每層傷害 +35%。</t>
-  </si>
-  <si>
     <t>{"stormRendDmgPct":35}</t>
   </si>
   <si>
@@ -2024,10 +1973,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>knifeChain</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2388,18 +2333,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>【血飲術】造成的自身生命損失降低 25%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"rageSelfCut":{"reducePct":25}}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>每 0.5 連擊數使【狂血盛宴】的傷害加成再提高 10%（＝每 1 連擊數 +20%）。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"rageZealotPct":20}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2448,10 +2385,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>【岩甲尖刺】的效果提高 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"rockSpikePct":50}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2492,18 +2425,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>大地守護會使你額外獲得【魔力再生】法力回復加成的 20% 作為吸魔效果加成。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"egManaDrainFromRegen":{"pct":20}}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>每殺死 1 個敵人，【天地共生】的復活冷卻時間 -0.2 秒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"egKillCdr":{"sec":0.2}}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2556,10 +2481,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>【伴生雷球】的持續時間增加 50%。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{"thunderorbCompanionSecPct":50}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2609,10 +2530,6 @@
   </si>
   <si>
     <t>{"windbladeRamp":{"pct":2,"max":40}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【暴風神體】的持續時間 +30%。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -2758,6 +2675,88 @@
   </si>
   <si>
     <t>{"manaRefund":{"chance":25,"sec":5}}</t>
+  </si>
+  <si>
+    <t>血飲術每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>血飲術造成的自身生命損失降低 25%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 0.5 連擊數使狂血盛宴的傷害加成再提高 10%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂怒期間每殺死 1 個敵人使嗜血反震的效果提高 5%，最多疊 10 層，持續 4 秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球爆裂會額外產生 3 個小火球。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩甲增幅可疊加的層數 +10 層。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩甲尖刺的效果提高 50%。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地守護會使你額外獲得魔力再生法力回復加成的 20% 作為吸魔效果加成。</t>
+  </si>
+  <si>
+    <t>生命反射之盾可以額外對 1 個敵人產生作用。</t>
+  </si>
+  <si>
+    <t>每殺死 1 個敵人，天地共生的復活冷卻時間 -0.2 秒。</t>
+  </si>
+  <si>
+    <t>天地共生復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
+  </si>
+  <si>
+    <t>電殛擴散額外對 1 個敵人造成傷害，且其傷害提高 50%。</t>
+  </si>
+  <si>
+    <t>雙重落雷的攻擊次數 +1 次。</t>
+  </si>
+  <si>
+    <t>迅雷重生的機率提高至 100%。</t>
+  </si>
+  <si>
+    <t>伴生雷球的持續時間增加 50%。</t>
+  </si>
+  <si>
+    <t>雷殞天落降下的雷球數量 +1 顆。</t>
+  </si>
+  <si>
+    <t>被雷殞天落降下的雷球擊中的敵人會暈眩 4 秒。</t>
+  </si>
+  <si>
+    <t>寒流爆散的擴散爆炸變成冰霜新星，且範圍增大 30%。</t>
+  </si>
+  <si>
+    <t>亂披風會在風刃另一側額外射出 1 道小型風刃，且小型風刃傷害 +30%。</t>
+  </si>
+  <si>
+    <t>暴風真空刃每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
+  </si>
+  <si>
+    <t>真空爆震會額外多造成 1 次傷害。</t>
+  </si>
+  <si>
+    <t>虛空斬的持續時間 +3 秒。</t>
+  </si>
+  <si>
+    <t>暴風之刃射出風刃的機率 +10%。</t>
+  </si>
+  <si>
+    <t>亂風切所附加的風切狀態，每層傷害 +35%。</t>
+  </si>
+  <si>
+    <t>暴風神體的持續時間 +30%。</t>
   </si>
 </sst>
 </file>
@@ -3741,6 +3740,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
+    <col min="13" max="13" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3769,10 +3769,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -4152,7 +4152,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -4629,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -4678,7 +4678,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4690,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4710,7 +4710,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4722,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6230,7 +6230,7 @@
         <v>10</v>
       </c>
       <c r="K81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="s">
         <v>195</v>
@@ -6250,7 +6250,7 @@
         <v>5</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="s">
         <v>198</v>
@@ -6270,7 +6270,7 @@
         <v>10</v>
       </c>
       <c r="K83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="s">
         <v>201</v>
@@ -6290,7 +6290,7 @@
         <v>6</v>
       </c>
       <c r="K84">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M84" t="s">
         <v>204</v>
@@ -6310,7 +6310,7 @@
         <v>12</v>
       </c>
       <c r="K85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M85" t="s">
         <v>207</v>
@@ -6330,7 +6330,7 @@
         <v>6</v>
       </c>
       <c r="K86">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M86" t="s">
         <v>210</v>
@@ -6350,7 +6350,7 @@
         <v>5</v>
       </c>
       <c r="K87">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M87" t="s">
         <v>213</v>
@@ -6684,10 +6684,10 @@
         <v>192</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6696,16 +6696,16 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="N101" t="s">
         <v>214</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -6713,10 +6713,10 @@
         <v>192</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6725,16 +6725,16 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="N102" t="s">
         <v>214</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -6742,10 +6742,10 @@
         <v>192</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6754,16 +6754,16 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="N103" t="s">
         <v>214</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -6771,10 +6771,10 @@
         <v>192</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6783,16 +6783,16 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -6800,10 +6800,10 @@
         <v>192</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6812,16 +6812,16 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="N105" t="s">
         <v>214</v>
       </c>
       <c r="O105" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q105" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="Q105" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -6829,10 +6829,10 @@
         <v>192</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6841,17 +6841,17 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="N106" t="s">
         <v>214</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" s="2" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -6859,10 +6859,10 @@
         <v>192</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6871,17 +6871,17 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="N107" t="s">
         <v>214</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" s="2" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -6889,10 +6889,10 @@
         <v>192</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6901,17 +6901,17 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="N108" t="s">
         <v>214</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" s="2" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -6919,10 +6919,10 @@
         <v>192</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6931,17 +6931,17 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" s="2" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -6949,10 +6949,10 @@
         <v>192</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6961,17 +6961,17 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="N110" t="s">
         <v>214</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110" s="2" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -6979,10 +6979,10 @@
         <v>192</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6991,17 +6991,17 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="N111" t="s">
         <v>214</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -7009,10 +7009,10 @@
         <v>192</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -7021,17 +7021,17 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="N112" t="s">
         <v>214</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" s="2" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -7039,10 +7039,10 @@
         <v>192</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -7051,17 +7051,17 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="N113" t="s">
         <v>214</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="P113" s="2"/>
       <c r="Q113" s="2" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -7069,10 +7069,10 @@
         <v>192</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -7081,17 +7081,17 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="N114" t="s">
         <v>214</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="P114" s="2"/>
       <c r="Q114" s="2" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -7099,10 +7099,10 @@
         <v>192</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -7111,17 +7111,17 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="N115" t="s">
         <v>214</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="P115" s="2"/>
       <c r="Q115" s="2" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="N116" t="s">
         <v>275</v>
@@ -7150,7 +7150,7 @@
         <v>276</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="N117" t="s">
         <v>214</v>
@@ -7179,7 +7179,7 @@
         <v>276</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="N120" t="s">
         <v>214</v>
@@ -7266,7 +7266,7 @@
         <v>276</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -7315,7 +7315,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="N122" t="s">
         <v>263</v>
@@ -7324,7 +7324,7 @@
         <v>292</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="N123" t="s">
         <v>214</v>
@@ -7353,7 +7353,7 @@
         <v>292</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -7460,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="N127" t="s">
         <v>214</v>
@@ -7469,7 +7469,7 @@
         <v>309</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="N128" t="s">
         <v>214</v>
@@ -7498,7 +7498,7 @@
         <v>309</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="N131" t="s">
         <v>214</v>
@@ -7585,7 +7585,7 @@
         <v>325</v>
       </c>
       <c r="Q131" s="2" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="N132" t="s">
         <v>214</v>
@@ -7614,7 +7614,7 @@
         <v>325</v>
       </c>
       <c r="Q132" s="2" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="N133" t="s">
         <v>214</v>
@@ -7643,7 +7643,7 @@
         <v>325</v>
       </c>
       <c r="Q133" s="2" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="N134" t="s">
         <v>214</v>
@@ -7672,7 +7672,7 @@
         <v>325</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -7692,16 +7692,16 @@
         <v>0</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="O135" t="s">
         <v>325</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>341</v>
+        <v>829</v>
       </c>
       <c r="N137" t="s">
         <v>214</v>
@@ -7759,7 +7759,7 @@
         <v>337</v>
       </c>
       <c r="Q137" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -7767,11 +7767,11 @@
         <v>192</v>
       </c>
       <c r="B138" t="s">
+        <v>342</v>
+      </c>
+      <c r="C138" t="s">
         <v>343</v>
       </c>
-      <c r="C138" t="s">
-        <v>344</v>
-      </c>
       <c r="D138">
         <v>0</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>752</v>
+        <v>830</v>
       </c>
       <c r="N138" t="s">
         <v>214</v>
@@ -7788,7 +7788,7 @@
         <v>337</v>
       </c>
       <c r="Q138" s="2" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -7796,11 +7796,11 @@
         <v>192</v>
       </c>
       <c r="B139" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139" t="s">
         <v>345</v>
       </c>
-      <c r="C139" t="s">
-        <v>346</v>
-      </c>
       <c r="D139">
         <v>0</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="N139" t="s">
         <v>214</v>
@@ -7817,7 +7817,7 @@
         <v>337</v>
       </c>
       <c r="Q139" s="2" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -7825,11 +7825,11 @@
         <v>192</v>
       </c>
       <c r="B140" t="s">
+        <v>346</v>
+      </c>
+      <c r="C140" t="s">
         <v>347</v>
       </c>
-      <c r="C140" t="s">
-        <v>348</v>
-      </c>
       <c r="D140">
         <v>0</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>349</v>
+        <v>832</v>
       </c>
       <c r="N140" t="s">
         <v>214</v>
@@ -7846,7 +7846,7 @@
         <v>337</v>
       </c>
       <c r="Q140" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -7854,10 +7854,10 @@
         <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C141" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="N141" t="s">
         <v>248</v>
       </c>
       <c r="O141" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -7883,28 +7883,28 @@
         <v>192</v>
       </c>
       <c r="B142" t="s">
+        <v>352</v>
+      </c>
+      <c r="C142" t="s">
+        <v>353</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="M142" t="s">
         <v>354</v>
-      </c>
-      <c r="C142" t="s">
-        <v>355</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="M142" t="s">
-        <v>356</v>
       </c>
       <c r="N142" t="s">
         <v>248</v>
       </c>
       <c r="O142" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -7912,28 +7912,28 @@
         <v>192</v>
       </c>
       <c r="B143" t="s">
+        <v>356</v>
+      </c>
+      <c r="C143" t="s">
+        <v>357</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="M143" t="s">
         <v>358</v>
-      </c>
-      <c r="C143" t="s">
-        <v>359</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="M143" t="s">
-        <v>360</v>
       </c>
       <c r="N143" t="s">
         <v>248</v>
       </c>
       <c r="O143" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q143" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -7941,28 +7941,28 @@
         <v>192</v>
       </c>
       <c r="B144" t="s">
+        <v>360</v>
+      </c>
+      <c r="C144" t="s">
+        <v>361</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="M144" t="s">
         <v>362</v>
-      </c>
-      <c r="C144" t="s">
-        <v>363</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="M144" t="s">
-        <v>364</v>
       </c>
       <c r="N144" t="s">
         <v>248</v>
       </c>
       <c r="O144" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q144" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -7970,10 +7970,10 @@
         <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C145" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -7982,16 +7982,16 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>368</v>
+        <v>833</v>
       </c>
       <c r="N145" t="s">
         <v>248</v>
       </c>
       <c r="O145" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q145" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -7999,10 +7999,10 @@
         <v>192</v>
       </c>
       <c r="B146" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C146" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -8011,16 +8011,16 @@
         <v>0</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="N146" t="s">
         <v>248</v>
       </c>
       <c r="O146" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -8028,10 +8028,10 @@
         <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C147" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -8040,16 +8040,16 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="N147" t="s">
         <v>248</v>
       </c>
       <c r="O147" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q147" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -8057,10 +8057,10 @@
         <v>192</v>
       </c>
       <c r="B148" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C148" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -8069,16 +8069,16 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="N148" t="s">
         <v>248</v>
       </c>
       <c r="O148" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q148" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -8086,10 +8086,10 @@
         <v>192</v>
       </c>
       <c r="B149" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C149" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -8098,16 +8098,16 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="N149" t="s">
         <v>248</v>
       </c>
       <c r="O149" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q149" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -8115,10 +8115,10 @@
         <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C150" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -8127,16 +8127,16 @@
         <v>0</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="N150" t="s">
         <v>248</v>
       </c>
       <c r="O150" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q150" s="2" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -8144,10 +8144,10 @@
         <v>192</v>
       </c>
       <c r="B151" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C151" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -8156,16 +8156,16 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="N151" t="s">
         <v>248</v>
       </c>
       <c r="O151" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q151" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -8173,10 +8173,10 @@
         <v>192</v>
       </c>
       <c r="B152" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C152" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -8185,16 +8185,16 @@
         <v>0</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="N152" t="s">
         <v>248</v>
       </c>
       <c r="O152" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -8202,10 +8202,10 @@
         <v>192</v>
       </c>
       <c r="B153" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C153" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -8214,16 +8214,16 @@
         <v>0</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="N153" t="s">
         <v>248</v>
       </c>
       <c r="O153" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -8231,10 +8231,10 @@
         <v>192</v>
       </c>
       <c r="B154" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C154" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -8243,16 +8243,16 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N154" t="s">
         <v>248</v>
       </c>
       <c r="O154" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q154" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -8260,10 +8260,10 @@
         <v>192</v>
       </c>
       <c r="B155" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C155" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -8272,16 +8272,16 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="N155" t="s">
         <v>248</v>
       </c>
       <c r="O155" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q155" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -8289,28 +8289,28 @@
         <v>192</v>
       </c>
       <c r="B156" t="s">
+        <v>401</v>
+      </c>
+      <c r="C156" t="s">
+        <v>402</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="N156" t="s">
+        <v>403</v>
+      </c>
+      <c r="O156" t="s">
         <v>404</v>
       </c>
-      <c r="C156" t="s">
+      <c r="Q156" t="s">
         <v>405</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="M156" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="N156" t="s">
-        <v>406</v>
-      </c>
-      <c r="O156" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -8318,28 +8318,28 @@
         <v>192</v>
       </c>
       <c r="B157" t="s">
+        <v>406</v>
+      </c>
+      <c r="C157" t="s">
+        <v>407</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="M157" t="s">
+        <v>408</v>
+      </c>
+      <c r="N157" t="s">
+        <v>403</v>
+      </c>
+      <c r="O157" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q157" t="s">
         <v>409</v>
-      </c>
-      <c r="C157" t="s">
-        <v>410</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <v>0</v>
-      </c>
-      <c r="M157" t="s">
-        <v>411</v>
-      </c>
-      <c r="N157" t="s">
-        <v>406</v>
-      </c>
-      <c r="O157" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -8347,10 +8347,10 @@
         <v>192</v>
       </c>
       <c r="B158" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C158" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -8359,16 +8359,16 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>415</v>
+        <v>834</v>
       </c>
       <c r="N158" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O158" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q158" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -8376,10 +8376,10 @@
         <v>192</v>
       </c>
       <c r="B159" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C159" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -8388,16 +8388,16 @@
         <v>0</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>767</v>
+        <v>835</v>
       </c>
       <c r="N159" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O159" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q159" s="2" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -8405,10 +8405,10 @@
         <v>192</v>
       </c>
       <c r="B160" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C160" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -8417,16 +8417,16 @@
         <v>0</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="N160" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O160" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q160" s="2" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -8434,28 +8434,28 @@
         <v>192</v>
       </c>
       <c r="B161" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" t="s">
+        <v>418</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="M161" t="s">
+        <v>419</v>
+      </c>
+      <c r="N161" t="s">
+        <v>403</v>
+      </c>
+      <c r="O161" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q161" t="s">
         <v>421</v>
-      </c>
-      <c r="C161" t="s">
-        <v>422</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <v>0</v>
-      </c>
-      <c r="M161" t="s">
-        <v>423</v>
-      </c>
-      <c r="N161" t="s">
-        <v>406</v>
-      </c>
-      <c r="O161" t="s">
-        <v>424</v>
-      </c>
-      <c r="Q161" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -8463,10 +8463,10 @@
         <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C162" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -8475,16 +8475,16 @@
         <v>0</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="N162" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O162" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="Q162" s="2" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -8492,10 +8492,10 @@
         <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C163" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -8504,16 +8504,16 @@
         <v>0</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="N163" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O163" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="Q163" s="2" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -8521,10 +8521,10 @@
         <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C164" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -8533,16 +8533,16 @@
         <v>0</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="N164" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O164" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -8550,10 +8550,10 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C165" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -8562,16 +8562,16 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="N165" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O165" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="Q165" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -8579,10 +8579,10 @@
         <v>192</v>
       </c>
       <c r="B166" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C166" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -8591,16 +8591,16 @@
         <v>0</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="N166" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O166" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q166" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -8608,10 +8608,10 @@
         <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C167" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -8620,16 +8620,16 @@
         <v>0</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>778</v>
+        <v>836</v>
       </c>
       <c r="N167" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O167" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>779</v>
+        <v>757</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -8637,10 +8637,10 @@
         <v>192</v>
       </c>
       <c r="B168" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C168" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>0</v>
       </c>
       <c r="M168" t="s">
-        <v>444</v>
+        <v>837</v>
       </c>
       <c r="N168" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O168" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q168" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -8666,10 +8666,10 @@
         <v>192</v>
       </c>
       <c r="B169" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C169" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>780</v>
+        <v>838</v>
       </c>
       <c r="N169" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O169" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>781</v>
+        <v>758</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -8695,10 +8695,10 @@
         <v>192</v>
       </c>
       <c r="B170" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C170" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -8707,16 +8707,16 @@
         <v>0</v>
       </c>
       <c r="M170" t="s">
-        <v>661</v>
+        <v>839</v>
       </c>
       <c r="N170" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O170" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q170" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -8724,10 +8724,10 @@
         <v>192</v>
       </c>
       <c r="B171" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C171" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -8736,16 +8736,16 @@
         <v>0</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="N171" t="s">
         <v>240</v>
       </c>
       <c r="O171" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q171" s="2" t="s">
-        <v>783</v>
+        <v>760</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -8753,10 +8753,10 @@
         <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C172" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -8765,16 +8765,16 @@
         <v>0</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>784</v>
+        <v>761</v>
       </c>
       <c r="N172" t="s">
         <v>240</v>
       </c>
       <c r="O172" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q172" s="2" t="s">
-        <v>785</v>
+        <v>762</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -8782,10 +8782,10 @@
         <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C173" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -8794,16 +8794,16 @@
         <v>0</v>
       </c>
       <c r="M173" t="s">
-        <v>458</v>
+        <v>840</v>
       </c>
       <c r="N173" t="s">
         <v>240</v>
       </c>
       <c r="O173" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q173" t="s">
         <v>453</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -8811,10 +8811,10 @@
         <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C174" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -8823,16 +8823,16 @@
         <v>0</v>
       </c>
       <c r="M174" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="N174" t="s">
         <v>240</v>
       </c>
       <c r="O174" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q174" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -8840,10 +8840,10 @@
         <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C175" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -8852,16 +8852,16 @@
         <v>0</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="N175" t="s">
         <v>240</v>
       </c>
       <c r="O175" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q175" s="2" t="s">
-        <v>787</v>
+        <v>764</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -8869,10 +8869,10 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C176" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -8881,16 +8881,16 @@
         <v>0</v>
       </c>
       <c r="M176" t="s">
-        <v>468</v>
+        <v>841</v>
       </c>
       <c r="N176" t="s">
         <v>240</v>
       </c>
       <c r="O176" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q176" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -8898,10 +8898,10 @@
         <v>192</v>
       </c>
       <c r="B177" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C177" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -8910,16 +8910,16 @@
         <v>0</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
       <c r="N177" t="s">
         <v>240</v>
       </c>
       <c r="O177" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q177" s="2" t="s">
-        <v>789</v>
+        <v>766</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -8927,10 +8927,10 @@
         <v>192</v>
       </c>
       <c r="B178" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C178" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -8939,16 +8939,16 @@
         <v>0</v>
       </c>
       <c r="M178" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="N178" t="s">
         <v>240</v>
       </c>
       <c r="O178" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q178" t="s">
         <v>469</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -8956,10 +8956,10 @@
         <v>192</v>
       </c>
       <c r="B179" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C179" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -8968,16 +8968,16 @@
         <v>0</v>
       </c>
       <c r="M179" t="s">
-        <v>479</v>
+        <v>842</v>
       </c>
       <c r="N179" t="s">
         <v>240</v>
       </c>
       <c r="O179" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q179" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -8985,10 +8985,10 @@
         <v>192</v>
       </c>
       <c r="B180" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -8997,16 +8997,16 @@
         <v>0</v>
       </c>
       <c r="M180" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="N180" t="s">
         <v>240</v>
       </c>
       <c r="O180" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q180" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -9014,10 +9014,10 @@
         <v>192</v>
       </c>
       <c r="B181" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C181" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -9026,16 +9026,16 @@
         <v>0</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="N181" t="s">
         <v>240</v>
       </c>
       <c r="O181" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>791</v>
+        <v>768</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -9043,10 +9043,10 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C182" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -9055,16 +9055,16 @@
         <v>0</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="N182" t="s">
         <v>240</v>
       </c>
       <c r="O182" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>793</v>
+        <v>770</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -9072,10 +9072,10 @@
         <v>192</v>
       </c>
       <c r="B183" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C183" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -9084,16 +9084,16 @@
         <v>0</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>794</v>
+        <v>843</v>
       </c>
       <c r="N183" t="s">
         <v>240</v>
       </c>
       <c r="O183" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -9101,10 +9101,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C184" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -9113,16 +9113,16 @@
         <v>0</v>
       </c>
       <c r="M184" t="s">
-        <v>494</v>
+        <v>844</v>
       </c>
       <c r="N184" t="s">
         <v>240</v>
       </c>
       <c r="O184" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="Q184" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -9130,10 +9130,10 @@
         <v>192</v>
       </c>
       <c r="B185" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C185" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -9142,16 +9142,16 @@
         <v>0</v>
       </c>
       <c r="M185" t="s">
-        <v>498</v>
+        <v>845</v>
       </c>
       <c r="N185" t="s">
         <v>240</v>
       </c>
       <c r="O185" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="Q185" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -9159,10 +9159,10 @@
         <v>192</v>
       </c>
       <c r="B186" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C186" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -9171,16 +9171,16 @@
         <v>0</v>
       </c>
       <c r="M186" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="N186" t="s">
         <v>239</v>
       </c>
       <c r="O186" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Q186" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -9188,10 +9188,10 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C187" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -9200,16 +9200,16 @@
         <v>0</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>796</v>
+        <v>772</v>
       </c>
       <c r="N187" t="s">
         <v>239</v>
       </c>
       <c r="O187" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>797</v>
+        <v>773</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -9217,10 +9217,10 @@
         <v>192</v>
       </c>
       <c r="B188" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C188" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -9229,16 +9229,16 @@
         <v>0</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>798</v>
+        <v>774</v>
       </c>
       <c r="N188" t="s">
         <v>239</v>
       </c>
       <c r="O188" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Q188" s="2" t="s">
-        <v>799</v>
+        <v>775</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -9246,10 +9246,10 @@
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C189" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -9258,16 +9258,16 @@
         <v>0</v>
       </c>
       <c r="M189" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="N189" t="s">
         <v>239</v>
       </c>
       <c r="O189" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Q189" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -9275,10 +9275,10 @@
         <v>192</v>
       </c>
       <c r="B190" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C190" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -9287,16 +9287,16 @@
         <v>0</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>800</v>
+        <v>776</v>
       </c>
       <c r="N190" t="s">
         <v>239</v>
       </c>
       <c r="O190" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Q190" s="2" t="s">
-        <v>801</v>
+        <v>777</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -9304,10 +9304,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C191" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -9316,16 +9316,16 @@
         <v>0</v>
       </c>
       <c r="M191" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="N191" t="s">
         <v>239</v>
       </c>
       <c r="O191" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q191" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -9333,10 +9333,10 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="M192" t="s">
-        <v>522</v>
+        <v>846</v>
       </c>
       <c r="N192" t="s">
         <v>239</v>
       </c>
       <c r="O192" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q192" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -9362,10 +9362,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C193" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -9374,16 +9374,16 @@
         <v>0</v>
       </c>
       <c r="M193" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="N193" t="s">
         <v>239</v>
       </c>
       <c r="O193" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q193" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -9391,10 +9391,10 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C194" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -9403,16 +9403,16 @@
         <v>0</v>
       </c>
       <c r="M194" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="N194" t="s">
         <v>239</v>
       </c>
       <c r="O194" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q194" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -9420,10 +9420,10 @@
         <v>192</v>
       </c>
       <c r="B195" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="C195" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -9432,16 +9432,16 @@
         <v>0</v>
       </c>
       <c r="M195" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="N195" t="s">
         <v>239</v>
       </c>
       <c r="O195" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q195" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -9449,10 +9449,10 @@
         <v>192</v>
       </c>
       <c r="B196" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="C196" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -9461,16 +9461,16 @@
         <v>0</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="N196" t="s">
         <v>239</v>
       </c>
       <c r="O196" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="Q196" s="2" t="s">
-        <v>803</v>
+        <v>779</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -9478,10 +9478,10 @@
         <v>192</v>
       </c>
       <c r="B197" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="C197" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -9490,16 +9490,16 @@
         <v>0</v>
       </c>
       <c r="M197" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N197" t="s">
         <v>239</v>
       </c>
       <c r="O197" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="Q197" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -9507,10 +9507,10 @@
         <v>192</v>
       </c>
       <c r="B198" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="C198" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -9519,16 +9519,16 @@
         <v>0</v>
       </c>
       <c r="M198" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="N198" t="s">
         <v>239</v>
       </c>
       <c r="O198" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="Q198" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -9536,10 +9536,10 @@
         <v>192</v>
       </c>
       <c r="B199" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="C199" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -9548,16 +9548,16 @@
         <v>0</v>
       </c>
       <c r="M199" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="N199" t="s">
         <v>239</v>
       </c>
       <c r="O199" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="Q199" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -9565,10 +9565,10 @@
         <v>192</v>
       </c>
       <c r="B200" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="C200" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -9577,16 +9577,16 @@
         <v>0</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="N200" t="s">
         <v>239</v>
       </c>
       <c r="O200" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>805</v>
+        <v>781</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -9594,10 +9594,10 @@
         <v>192</v>
       </c>
       <c r="B201" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="C201" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -9606,16 +9606,16 @@
         <v>0</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>806</v>
+        <v>782</v>
       </c>
       <c r="N201" t="s">
         <v>275</v>
       </c>
       <c r="O201" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="Q201" s="2" t="s">
-        <v>807</v>
+        <v>783</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -9623,10 +9623,10 @@
         <v>192</v>
       </c>
       <c r="B202" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C202" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>0</v>
       </c>
       <c r="M202" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="N202" t="s">
         <v>275</v>
       </c>
       <c r="O202" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="Q202" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -9652,10 +9652,10 @@
         <v>192</v>
       </c>
       <c r="B203" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C203" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -9664,16 +9664,16 @@
         <v>0</v>
       </c>
       <c r="M203" t="s">
-        <v>562</v>
+        <v>847</v>
       </c>
       <c r="N203" t="s">
         <v>275</v>
       </c>
       <c r="O203" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="Q203" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -9681,10 +9681,10 @@
         <v>192</v>
       </c>
       <c r="B204" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C204" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -9693,16 +9693,16 @@
         <v>0</v>
       </c>
       <c r="M204" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="N204" t="s">
         <v>275</v>
       </c>
       <c r="O204" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q204" t="s">
         <v>555</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -9710,10 +9710,10 @@
         <v>192</v>
       </c>
       <c r="B205" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C205" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -9722,16 +9722,16 @@
         <v>0</v>
       </c>
       <c r="M205" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
       <c r="N205" t="s">
         <v>275</v>
       </c>
       <c r="O205" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="Q205" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -9739,10 +9739,10 @@
         <v>192</v>
       </c>
       <c r="B206" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C206" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>0</v>
       </c>
       <c r="M206" t="s">
-        <v>574</v>
+        <v>849</v>
       </c>
       <c r="N206" t="s">
         <v>275</v>
       </c>
       <c r="O206" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="Q206" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -9768,10 +9768,10 @@
         <v>192</v>
       </c>
       <c r="B207" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="C207" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="M207" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="N207" t="s">
         <v>275</v>
       </c>
       <c r="O207" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="Q207" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -9797,10 +9797,10 @@
         <v>192</v>
       </c>
       <c r="B208" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C208" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -9809,16 +9809,16 @@
         <v>0</v>
       </c>
       <c r="M208" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="N208" t="s">
         <v>275</v>
       </c>
       <c r="O208" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="Q208" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -9826,10 +9826,10 @@
         <v>192</v>
       </c>
       <c r="B209" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="C209" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -9838,16 +9838,16 @@
         <v>0</v>
       </c>
       <c r="M209" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="N209" t="s">
         <v>275</v>
       </c>
       <c r="O209" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="Q209" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -9855,10 +9855,10 @@
         <v>192</v>
       </c>
       <c r="B210" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="C210" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="M210" t="s">
-        <v>591</v>
+        <v>850</v>
       </c>
       <c r="N210" t="s">
         <v>275</v>
       </c>
       <c r="O210" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="Q210" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -9884,10 +9884,10 @@
         <v>192</v>
       </c>
       <c r="B211" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="C211" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -9896,16 +9896,16 @@
         <v>0</v>
       </c>
       <c r="M211" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="N211" t="s">
         <v>275</v>
       </c>
       <c r="O211" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="Q211" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -9913,10 +9913,10 @@
         <v>192</v>
       </c>
       <c r="B212" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="C212" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -9925,16 +9925,16 @@
         <v>0</v>
       </c>
       <c r="M212" t="s">
-        <v>600</v>
+        <v>851</v>
       </c>
       <c r="N212" t="s">
         <v>275</v>
       </c>
       <c r="O212" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="Q212" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -9942,10 +9942,10 @@
         <v>192</v>
       </c>
       <c r="B213" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="C213" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -9954,16 +9954,16 @@
         <v>0</v>
       </c>
       <c r="M213" t="s">
-        <v>604</v>
+        <v>852</v>
       </c>
       <c r="N213" t="s">
         <v>275</v>
       </c>
       <c r="O213" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="Q213" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -9971,10 +9971,10 @@
         <v>192</v>
       </c>
       <c r="B214" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="C214" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -9983,16 +9983,16 @@
         <v>0</v>
       </c>
       <c r="M214" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="N214" t="s">
         <v>275</v>
       </c>
       <c r="O214" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="Q214" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -10000,10 +10000,10 @@
         <v>192</v>
       </c>
       <c r="B215" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C215" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -10012,16 +10012,16 @@
         <v>0</v>
       </c>
       <c r="M215" s="2" t="s">
-        <v>808</v>
+        <v>853</v>
       </c>
       <c r="N215" t="s">
         <v>275</v>
       </c>
       <c r="O215" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="Q215" s="2" t="s">
-        <v>809</v>
+        <v>784</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
@@ -10029,22 +10029,22 @@
         <v>192</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>811</v>
+        <v>786</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>812</v>
+        <v>787</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>813</v>
+        <v>788</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M216" s="2" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="Q216" s="2" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
@@ -10052,22 +10052,22 @@
         <v>192</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>818</v>
+        <v>793</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>819</v>
+        <v>794</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="Q217" s="2" t="s">
-        <v>821</v>
+        <v>796</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
@@ -10075,22 +10075,22 @@
         <v>192</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>822</v>
+        <v>797</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>823</v>
+        <v>798</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M218" s="2" t="s">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="Q218" s="2" t="s">
-        <v>826</v>
+        <v>801</v>
       </c>
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
@@ -10098,22 +10098,22 @@
         <v>192</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>813</v>
+        <v>788</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M219" s="2" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="Q219" s="2" t="s">
-        <v>830</v>
+        <v>805</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
@@ -10121,22 +10121,22 @@
         <v>192</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>831</v>
+        <v>806</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>833</v>
+        <v>808</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="Q220" s="2" t="s">
-        <v>835</v>
+        <v>810</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
@@ -10144,22 +10144,22 @@
         <v>192</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>836</v>
+        <v>811</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>837</v>
+        <v>812</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>838</v>
+        <v>813</v>
       </c>
       <c r="K221" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="M221" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="M221" s="2" t="s">
-        <v>839</v>
-      </c>
       <c r="Q221" s="2" t="s">
-        <v>840</v>
+        <v>815</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
@@ -10167,22 +10167,22 @@
         <v>192</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>841</v>
+        <v>816</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>842</v>
+        <v>817</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>833</v>
+        <v>808</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M222" s="2" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="Q222" s="2" t="s">
-        <v>844</v>
+        <v>819</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
@@ -10190,22 +10190,22 @@
         <v>192</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>845</v>
+        <v>820</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>846</v>
+        <v>821</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>847</v>
+        <v>822</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M223" s="2" t="s">
-        <v>848</v>
+        <v>823</v>
       </c>
       <c r="Q223" s="2" t="s">
-        <v>849</v>
+        <v>824</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
@@ -10213,33 +10213,33 @@
         <v>192</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>851</v>
+        <v>826</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>847</v>
+        <v>822</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="M224" s="2" t="s">
-        <v>852</v>
+        <v>827</v>
       </c>
       <c r="Q224" s="2" t="s">
-        <v>853</v>
+        <v>828</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B225" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="C225" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="D225">
         <v>25</v>
@@ -10248,209 +10248,209 @@
         <v>31</v>
       </c>
       <c r="M225" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B226" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C226" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="D226">
         <v>18</v>
       </c>
       <c r="L226" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="M226" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B227" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C227" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="D227">
         <v>15</v>
       </c>
       <c r="L227" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="M227" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B228" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C228" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="D228">
         <v>30</v>
       </c>
       <c r="L228" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="M228" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>595</v>
+      </c>
+      <c r="B229" t="s">
+        <v>611</v>
+      </c>
+      <c r="C229" t="s">
         <v>612</v>
-      </c>
-      <c r="B229" t="s">
-        <v>628</v>
-      </c>
-      <c r="C229" t="s">
-        <v>629</v>
       </c>
       <c r="D229">
         <v>25</v>
       </c>
       <c r="L229" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="M229" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B230" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="C230" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="D230">
         <v>25</v>
       </c>
       <c r="L230" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="M230" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B231" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="C231" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="D231">
         <v>12</v>
       </c>
       <c r="M231" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B232" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="C232" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D232">
         <v>15</v>
       </c>
       <c r="M232" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B233" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="C233" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="D233">
         <v>8</v>
       </c>
       <c r="M233" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B234" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="C234" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D234">
         <v>30</v>
       </c>
       <c r="M234" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B235" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="C235" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="D235">
         <v>5</v>
       </c>
       <c r="M235" s="2" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B236" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="C236" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="D236">
         <v>35</v>
       </c>
       <c r="M236" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
